--- a/salida/Analisis_alternativas_corte_chapa.xlsx
+++ b/salida/Analisis_alternativas_corte_chapa.xlsx
@@ -2517,19 +2517,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1140654.11959019</c:v>
+                  <c:v>1139515.48976354</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1141330.0215304</c:v>
+                  <c:v>1140050.0842414</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1203055.32553162</c:v>
+                  <c:v>1201797.48321688</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1108751.45007791</c:v>
+                  <c:v>1107544.2636078</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1029277.71500999</c:v>
+                  <c:v>1028038.84321599</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2537,11 +2537,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="80172079"/>
-        <c:axId val="78665016"/>
+        <c:axId val="96473633"/>
+        <c:axId val="92612424"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="80172079"/>
+        <c:axId val="96473633"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2573,7 +2573,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78665016"/>
+        <c:crossAx val="92612424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2581,7 +2581,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78665016"/>
+        <c:axId val="92612424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2658,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80172079"/>
+        <c:crossAx val="96473633"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3968,44 +3968,44 @@
         <v>39</v>
       </c>
       <c r="C34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3)</f>
-        <v>3</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
+        <v>2</v>
       </c>
       <c r="D34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.24)</f>
-        <v>6.24</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.16)</f>
+        <v>4.16</v>
       </c>
       <c r="E34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.72)</f>
-        <v>10.72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.48)</f>
+        <v>8.48</v>
       </c>
       <c r="F34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52)</f>
-        <v>17.52</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.12)</f>
+        <v>12.12</v>
       </c>
       <c r="G34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.8)</f>
-        <v>18.8</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13)</f>
+        <v>13</v>
       </c>
       <c r="H34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.08)</f>
-        <v>21.08</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.88)</f>
+        <v>13.88</v>
       </c>
       <c r="I34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.44)</f>
-        <v>18.44</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.76)</f>
+        <v>12.76</v>
       </c>
       <c r="J34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.48)</f>
-        <v>15.48</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.48)</f>
+        <v>11.48</v>
       </c>
       <c r="K34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.2)</f>
-        <v>14.2</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.04)</f>
+        <v>10.04</v>
       </c>
       <c r="L34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.76)</f>
-        <v>14.76</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.44)</f>
+        <v>10.44</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4016,44 +4016,44 @@
         <v>39</v>
       </c>
       <c r="C35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11)</f>
-        <v>11</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9)</f>
+        <v>9</v>
       </c>
       <c r="D35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.88)</f>
-        <v>33.88</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.72)</f>
+        <v>25.72</v>
       </c>
       <c r="E35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.52)</f>
-        <v>57.52</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.72)</f>
+        <v>44.72</v>
       </c>
       <c r="F35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.84)</f>
-        <v>95.84</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.08)</f>
+        <v>73.08</v>
       </c>
       <c r="G35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.88)</f>
-        <v>95.88</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.44)</f>
+        <v>74.44</v>
       </c>
       <c r="H35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),109.36)</f>
-        <v>109.36</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.48)</f>
+        <v>83.48</v>
       </c>
       <c r="I35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.4)</f>
-        <v>93.4</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.84)</f>
+        <v>71.84</v>
       </c>
       <c r="J35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),79.6)</f>
-        <v>79.6</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.84)</f>
+        <v>60.84</v>
       </c>
       <c r="K35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.28)</f>
-        <v>73.28</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.64)</f>
+        <v>57.64</v>
       </c>
       <c r="L35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.16)</f>
-        <v>78.16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.96)</f>
+        <v>58.96</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4068,40 +4068,40 @@
         <v>1</v>
       </c>
       <c r="D36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.08)</f>
-        <v>3.08</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.08)</f>
+        <v>2.08</v>
       </c>
       <c r="E36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.32)</f>
-        <v>4.32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.24)</f>
+        <v>3.24</v>
       </c>
       <c r="F36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.64)</f>
-        <v>7.64</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.48)</f>
+        <v>4.48</v>
       </c>
       <c r="G36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.2)</f>
-        <v>7.2</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.68)</f>
-        <v>8.68</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.12)</f>
+        <v>6.12</v>
       </c>
       <c r="I36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.24)</f>
-        <v>6.24</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.52)</f>
+        <v>4.52</v>
       </c>
       <c r="J36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.56)</f>
-        <v>6.56</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.76)</f>
+        <v>3.76</v>
       </c>
       <c r="K36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.88)</f>
-        <v>4.88</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.92)</f>
+        <v>3.92</v>
       </c>
       <c r="L36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.04)</f>
-        <v>6.04</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.08)</f>
+        <v>4.08</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4132,24 +4132,24 @@
         <v>1.16</v>
       </c>
       <c r="H37" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
+        <v>0.24</v>
+      </c>
+      <c r="I37" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
         <v>1.24</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="J37" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
         <v>0.32</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="K37" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
+        <v>0.32</v>
+      </c>
+      <c r="L37" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
         <v>1.32</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
-        <v>0.4</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
-        <v>0.4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4168,36 +4168,36 @@
         <v>0.08</v>
       </c>
       <c r="E38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.08)</f>
-        <v>2.08</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
+        <v>1.08</v>
       </c>
       <c r="F38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
-        <v>1.24</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.16)</f>
+        <v>2.16</v>
       </c>
       <c r="G38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.32)</f>
-        <v>2.32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
+        <v>1.32</v>
       </c>
       <c r="H38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.48)</f>
-        <v>2.48</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="I38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.64)</f>
-        <v>0.64</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.56)</f>
+        <v>0.56</v>
       </c>
       <c r="J38" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.56)</f>
+        <v>1.56</v>
+      </c>
+      <c r="K38" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.64)</f>
         <v>1.64</v>
       </c>
-      <c r="K38" s="9" t="n">
+      <c r="L38" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.72)</f>
         <v>1.72</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4240,12 +4240,12 @@
         <v>0.16</v>
       </c>
       <c r="K39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
-        <v>1.16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
+        <v>0.16</v>
       </c>
       <c r="L39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
-        <v>0.24</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
+        <v>0.16</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4276,12 +4276,12 @@
         <v>0.08</v>
       </c>
       <c r="H40" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
+        <v>0.08</v>
+      </c>
+      <c r="I40" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
         <v>1.08</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
       </c>
       <c r="J40" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
@@ -4395,44 +4395,44 @@
         <v>39</v>
       </c>
       <c r="C45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4)</f>
-        <v>4</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3)</f>
+        <v>3</v>
       </c>
       <c r="D45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.32)</f>
-        <v>11.32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.24)</f>
+        <v>8.24</v>
       </c>
       <c r="E45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.2)</f>
-        <v>20.2</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.88)</f>
+        <v>14.88</v>
       </c>
       <c r="F45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.72)</f>
-        <v>30.72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23)</f>
+        <v>23</v>
       </c>
       <c r="G45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.96)</f>
-        <v>32.96</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.68)</f>
+        <v>23.68</v>
       </c>
       <c r="H45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.2)</f>
-        <v>36.2</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.28)</f>
+        <v>27.28</v>
       </c>
       <c r="I45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.52)</f>
-        <v>33.52</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.04)</f>
+        <v>24.04</v>
       </c>
       <c r="J45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.44)</f>
-        <v>27.44</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.4)</f>
+        <v>20.4</v>
       </c>
       <c r="K45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.72)</f>
-        <v>25.72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.36)</f>
+        <v>18.36</v>
       </c>
       <c r="L45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.76)</f>
-        <v>26.76</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.08)</f>
+        <v>20.08</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4443,44 +4443,44 @@
         <v>39</v>
       </c>
       <c r="C46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20)</f>
-        <v>20</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16)</f>
+        <v>16</v>
       </c>
       <c r="D46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.6)</f>
-        <v>59.6</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.28)</f>
+        <v>48.28</v>
       </c>
       <c r="E46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.24)</f>
-        <v>103.24</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.04)</f>
+        <v>83.04</v>
       </c>
       <c r="F46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170)</f>
-        <v>170</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.28)</f>
+        <v>137.28</v>
       </c>
       <c r="G46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.48)</f>
-        <v>172.48</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.36)</f>
+        <v>138.36</v>
       </c>
       <c r="H46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),195.16)</f>
-        <v>195.16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),156.72)</f>
+        <v>156.72</v>
       </c>
       <c r="I46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.72)</f>
-        <v>169.72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),136.8)</f>
+        <v>136.8</v>
       </c>
       <c r="J46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.24)</f>
-        <v>141.24</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.48)</f>
+        <v>114.48</v>
       </c>
       <c r="K46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132.72)</f>
-        <v>132.72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.76)</f>
+        <v>106.76</v>
       </c>
       <c r="L46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139)</f>
-        <v>139</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111)</f>
+        <v>111</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4495,40 +4495,40 @@
         <v>2</v>
       </c>
       <c r="D47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.16)</f>
-        <v>4.16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.16)</f>
+        <v>2.16</v>
       </c>
       <c r="E47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.48)</f>
-        <v>8.48</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.32)</f>
+        <v>6.32</v>
       </c>
       <c r="F47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.12)</f>
-        <v>13.12</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.8)</f>
+        <v>8.8</v>
       </c>
       <c r="G47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.08)</f>
-        <v>13.08</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.44)</f>
+        <v>9.44</v>
       </c>
       <c r="H47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.96)</f>
-        <v>15.96</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.08)</f>
+        <v>11.08</v>
       </c>
       <c r="I47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11)</f>
-        <v>11</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.8)</f>
+        <v>7.8</v>
       </c>
       <c r="J47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.56)</f>
-        <v>10.56</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.2)</f>
+        <v>7.2</v>
       </c>
       <c r="K47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.04)</f>
-        <v>10.04</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.52)</f>
+        <v>7.52</v>
       </c>
       <c r="L47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.44)</f>
-        <v>10.44</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.84)</f>
+        <v>6.84</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4551,32 +4551,32 @@
         <v>1.08</v>
       </c>
       <c r="F48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.16)</f>
-        <v>2.16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
+        <v>1.16</v>
       </c>
       <c r="G48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
-        <v>1.32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
+        <v>1.24</v>
       </c>
       <c r="H48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.32)</f>
+        <v>2.32</v>
       </c>
       <c r="I48" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.48)</f>
+        <v>0.48</v>
+      </c>
+      <c r="J48" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.48)</f>
         <v>1.48</v>
       </c>
-      <c r="J48" s="9" t="n">
+      <c r="K48" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.56)</f>
         <v>1.56</v>
       </c>
-      <c r="K48" s="9" t="n">
+      <c r="L48" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.64)</f>
         <v>0.64</v>
-      </c>
-      <c r="L48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.64)</f>
-        <v>1.64</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4603,28 +4603,28 @@
         <v>3.32</v>
       </c>
       <c r="G49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.56)</f>
-        <v>3.56</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.56)</f>
+        <v>2.56</v>
       </c>
       <c r="H49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.72)</f>
+        <v>3.72</v>
       </c>
       <c r="I49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.04)</f>
-        <v>3.04</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.96)</f>
+        <v>2.96</v>
       </c>
       <c r="J49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.12)</f>
+        <v>2.12</v>
       </c>
       <c r="K49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.36)</f>
-        <v>2.36</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="L49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.44)</f>
-        <v>2.44</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.28)</f>
+        <v>3.28</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4651,28 +4651,28 @@
         <v>1.08</v>
       </c>
       <c r="G50" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
+        <v>0.16</v>
+      </c>
+      <c r="H50" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
         <v>1.16</v>
       </c>
-      <c r="H50" s="9" t="n">
+      <c r="I50" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
         <v>0.24</v>
       </c>
-      <c r="I50" s="9" t="n">
+      <c r="J50" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
         <v>1.24</v>
-      </c>
-      <c r="J50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
-        <v>0.32</v>
       </c>
       <c r="K50" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
         <v>0.32</v>
       </c>
       <c r="L50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
-        <v>1.32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
+        <v>0.32</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4707,12 +4707,12 @@
         <v>0.16</v>
       </c>
       <c r="I51" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
+        <v>0.16</v>
+      </c>
+      <c r="J51" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
         <v>1.16</v>
-      </c>
-      <c r="J51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
-        <v>0.24</v>
       </c>
       <c r="K51" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
@@ -4859,23 +4859,23 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$32:$L$32)</f>
-        <v>1818.77492799882</v>
+        <v>1816.95312368953</v>
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$61:$L$61)</f>
-        <v>1926.06386162666</v>
+        <v>1924.11199317846</v>
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$85:$L$85)</f>
-        <v>1835.29684556646</v>
+        <v>1833.28277104146</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$99:$L$99)</f>
-        <v>1878.86081842415</v>
+        <v>1876.9739821074</v>
       </c>
       <c r="F8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$113:$L$113)</f>
-        <v>1761.41907398161</v>
+        <v>1759.63837965896</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4884,23 +4884,23 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/B8</f>
-        <v>0.905245478360841</v>
+        <v>0.905243149641851</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/C8</f>
-        <v>0.854819932261489</v>
+        <v>0.854827772121138</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/D8</f>
-        <v>0.897096174771025</v>
+        <v>0.897179853769059</v>
       </c>
       <c r="E9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/E8</f>
-        <v>0.876295765807663</v>
+        <v>0.876295774006202</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/F8</f>
-        <v>0.934722352021144</v>
+        <v>0.934728628025886</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4909,23 +4909,23 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$41:$L$41,Datos!$B$6-2025)</f>
-        <v>318.33495142202</v>
+        <v>318.251396835488</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$67:$L$67,Datos!$B$6-2025)</f>
-        <v>399.48603539978</v>
+        <v>399.343543865388</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$93:$L$93,Datos!$B$6-2025)</f>
-        <v>406.129287447283</v>
+        <v>405.986474853472</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$105:$L$105,Datos!$B$6-2025)</f>
-        <v>113.636671133687</v>
+        <v>113.59536747308</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$119:$L$119,Datos!$B$6-2025)</f>
-        <v>20.155450074562</v>
+        <v>20.1444510435848</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4934,23 +4934,23 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$44:$L$44,Datos!$B$6-2025)</f>
-        <v>511025.237281572</v>
+        <v>510774.458819745</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$70:$L$70,Datos!$B$6-2025)</f>
-        <v>565726.313719922</v>
+        <v>565439.483307224</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$96:$L$96,Datos!$B$6-2025)</f>
-        <v>523613.790553217</v>
+        <v>523350.679103644</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$108:$L$108,Datos!$B$6-2025)</f>
-        <v>539924.557597455</v>
+        <v>539654.056908405</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$122:$L$122,Datos!$B$6-2025)</f>
-        <v>539391.983464073</v>
+        <v>539115.723516464</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4959,23 +4959,23 @@
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B7+SUMPRODUCT(Cálculo!$C$44:$L$44,Cálculo!$C$6:$L$6)</f>
-        <v>1140654.11959019</v>
+        <v>1139515.48976354</v>
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">C7+SUMPRODUCT(Cálculo!$C$70:$L$70,Cálculo!$C$6:$L$6)</f>
-        <v>1141330.0215304</v>
+        <v>1140050.0842414</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">D7+SUMPRODUCT(Cálculo!$C$96:$L$96,Cálculo!$C$6:$L$6)</f>
-        <v>1203055.32553162</v>
+        <v>1201797.48321688</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">E7+SUMPRODUCT(Cálculo!$C$108:$L$108,Cálculo!$C$6:$L$6)</f>
-        <v>1108751.45007791</v>
+        <v>1107544.2636078</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">F7+SUMPRODUCT(Cálculo!$C$122:$L$122,Cálculo!$C$6:$L$6)</f>
-        <v>1029277.71500999</v>
+        <v>1028038.84321599</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5008,15 +5008,15 @@
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">B12-MIN($B$12:$E$12)</f>
-        <v>31902.6695122805</v>
+        <v>31971.2261557409</v>
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">C12-MIN($B$12:$E$12)</f>
-        <v>32578.5714524875</v>
+        <v>32505.8206336012</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">D12-MIN($B$12:$E$12)</f>
-        <v>94303.875453711</v>
+        <v>94253.2196090804</v>
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">E12-MIN($B$12:$E$12)</f>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">F12-MIN($B$12:$E$12)</f>
-        <v>-79473.7350679198</v>
+        <v>-79505.4203918114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">($B$12-$E$12)/SUMPRODUCT(Cálculo!$C$55:$L$55,Cálculo!$C$6:$L$6)</f>
-        <v>0.040102702644706</v>
+        <v>0.0402355014547532</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="B18" s="10" t="n">
         <f aca="false">($C$12-$E$12)/SUMPRODUCT(Cálculo!$C$31:$L$31,Cálculo!$C$6:$L$6)</f>
-        <v>0.144366445856081</v>
+        <v>0.144236820127873</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7718,43 +7718,43 @@
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">IFERROR(Links!C12,0)+IFERROR(Links!C23,0)+IFERROR(Links!C34,0)+IFERROR(Links!C45,0)</f>
-        <v>302.0303572</v>
+        <v>300.0303572</v>
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false">IFERROR(Links!D12,0)+IFERROR(Links!D23,0)+IFERROR(Links!D34,0)+IFERROR(Links!D45,0)</f>
-        <v>727.2874503</v>
+        <v>722.1274503</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">IFERROR(Links!E12,0)+IFERROR(Links!E23,0)+IFERROR(Links!E34,0)+IFERROR(Links!E45,0)</f>
-        <v>1317.3880576</v>
+        <v>1309.8280576</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">IFERROR(Links!F12,0)+IFERROR(Links!F23,0)+IFERROR(Links!F34,0)+IFERROR(Links!F45,0)</f>
-        <v>2592.678174</v>
+        <v>2579.558174</v>
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">IFERROR(Links!G12,0)+IFERROR(Links!G23,0)+IFERROR(Links!G34,0)+IFERROR(Links!G45,0)</f>
-        <v>4297.387726</v>
+        <v>4282.307726</v>
       </c>
       <c r="H7" s="11" t="n">
         <f aca="false">IFERROR(Links!H12,0)+IFERROR(Links!H23,0)+IFERROR(Links!H34,0)+IFERROR(Links!H45,0)</f>
-        <v>6113.149887</v>
+        <v>6097.029887</v>
       </c>
       <c r="I7" s="11" t="n">
         <f aca="false">IFERROR(Links!I12,0)+IFERROR(Links!I23,0)+IFERROR(Links!I34,0)+IFERROR(Links!I45,0)</f>
-        <v>8117.275524</v>
+        <v>8102.115524</v>
       </c>
       <c r="J7" s="11" t="n">
         <f aca="false">IFERROR(Links!J12,0)+IFERROR(Links!J23,0)+IFERROR(Links!J34,0)+IFERROR(Links!J45,0)</f>
-        <v>10270.226587</v>
+        <v>10259.186587</v>
       </c>
       <c r="K7" s="11" t="n">
         <f aca="false">IFERROR(Links!K12,0)+IFERROR(Links!K23,0)+IFERROR(Links!K34,0)+IFERROR(Links!K45,0)</f>
-        <v>11976.506243</v>
+        <v>11964.986243</v>
       </c>
       <c r="L7" s="11" t="n">
         <f aca="false">IFERROR(Links!L12,0)+IFERROR(Links!L23,0)+IFERROR(Links!L34,0)+IFERROR(Links!L45,0)</f>
-        <v>14135.378444</v>
+        <v>14124.378444</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7766,43 +7766,43 @@
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">IFERROR(Links!C13,0)+IFERROR(Links!C24,0)+IFERROR(Links!C35,0)+IFERROR(Links!C46,0)</f>
-        <v>2286.773025</v>
+        <v>2280.773025</v>
       </c>
       <c r="D8" s="11" t="n">
         <f aca="false">IFERROR(Links!D13,0)+IFERROR(Links!D24,0)+IFERROR(Links!D35,0)+IFERROR(Links!D46,0)</f>
-        <v>3940.458881</v>
+        <v>3920.978881</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">IFERROR(Links!E13,0)+IFERROR(Links!E24,0)+IFERROR(Links!E35,0)+IFERROR(Links!E46,0)</f>
-        <v>6733.097591</v>
+        <v>6700.097591</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">IFERROR(Links!F13,0)+IFERROR(Links!F24,0)+IFERROR(Links!F35,0)+IFERROR(Links!F46,0)</f>
-        <v>12240.955313</v>
+        <v>12185.475313</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">IFERROR(Links!G13,0)+IFERROR(Links!G24,0)+IFERROR(Links!G35,0)+IFERROR(Links!G46,0)</f>
-        <v>20628.46694</v>
+        <v>20572.90694</v>
       </c>
       <c r="H8" s="11" t="n">
         <f aca="false">IFERROR(Links!H13,0)+IFERROR(Links!H24,0)+IFERROR(Links!H35,0)+IFERROR(Links!H46,0)</f>
-        <v>28744.68411</v>
+        <v>28680.36411</v>
       </c>
       <c r="I8" s="11" t="n">
         <f aca="false">IFERROR(Links!I13,0)+IFERROR(Links!I24,0)+IFERROR(Links!I35,0)+IFERROR(Links!I46,0)</f>
-        <v>38699.47984</v>
+        <v>38644.99984</v>
       </c>
       <c r="J8" s="11" t="n">
         <f aca="false">IFERROR(Links!J13,0)+IFERROR(Links!J24,0)+IFERROR(Links!J35,0)+IFERROR(Links!J46,0)</f>
-        <v>48872.02637</v>
+        <v>48826.50637</v>
       </c>
       <c r="K8" s="11" t="n">
         <f aca="false">IFERROR(Links!K13,0)+IFERROR(Links!K24,0)+IFERROR(Links!K35,0)+IFERROR(Links!K46,0)</f>
-        <v>55509.52455</v>
+        <v>55467.92455</v>
       </c>
       <c r="L8" s="11" t="n">
         <f aca="false">IFERROR(Links!L13,0)+IFERROR(Links!L24,0)+IFERROR(Links!L35,0)+IFERROR(Links!L46,0)</f>
-        <v>63882.93872</v>
+        <v>63835.73872</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7818,39 +7818,39 @@
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">IFERROR(Links!D14,0)+IFERROR(Links!D25,0)+IFERROR(Links!D36,0)+IFERROR(Links!D47,0)</f>
-        <v>184.4872967</v>
+        <v>181.4872967</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">IFERROR(Links!E14,0)+IFERROR(Links!E25,0)+IFERROR(Links!E36,0)+IFERROR(Links!E47,0)</f>
-        <v>356.1787798</v>
+        <v>352.9387798</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">IFERROR(Links!F14,0)+IFERROR(Links!F25,0)+IFERROR(Links!F36,0)+IFERROR(Links!F47,0)</f>
-        <v>693.7804941</v>
+        <v>686.3004941</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">IFERROR(Links!G14,0)+IFERROR(Links!G25,0)+IFERROR(Links!G36,0)+IFERROR(Links!G47,0)</f>
-        <v>1206.3981519</v>
+        <v>1200.3581519</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">IFERROR(Links!H14,0)+IFERROR(Links!H25,0)+IFERROR(Links!H36,0)+IFERROR(Links!H47,0)</f>
-        <v>1743.045032</v>
+        <v>1735.605032</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">IFERROR(Links!I14,0)+IFERROR(Links!I25,0)+IFERROR(Links!I36,0)+IFERROR(Links!I47,0)</f>
-        <v>2339.800545</v>
+        <v>2334.880545</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">IFERROR(Links!J14,0)+IFERROR(Links!J25,0)+IFERROR(Links!J36,0)+IFERROR(Links!J47,0)</f>
-        <v>2957.564812</v>
+        <v>2951.404812</v>
       </c>
       <c r="K9" s="11" t="n">
         <f aca="false">IFERROR(Links!K14,0)+IFERROR(Links!K25,0)+IFERROR(Links!K36,0)+IFERROR(Links!K47,0)</f>
-        <v>3358.670054</v>
+        <v>3355.190054</v>
       </c>
       <c r="L9" s="11" t="n">
         <f aca="false">IFERROR(Links!L14,0)+IFERROR(Links!L25,0)+IFERROR(Links!L36,0)+IFERROR(Links!L47,0)</f>
-        <v>3868.328079</v>
+        <v>3862.768079</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7874,31 +7874,31 @@
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">IFERROR(Links!F15,0)+IFERROR(Links!F26,0)+IFERROR(Links!F37,0)+IFERROR(Links!F48,0)</f>
-        <v>153.9698529</v>
+        <v>152.9698529</v>
       </c>
       <c r="G10" s="11" t="n">
         <f aca="false">IFERROR(Links!G15,0)+IFERROR(Links!G26,0)+IFERROR(Links!G37,0)+IFERROR(Links!G48,0)</f>
-        <v>251.3560035</v>
+        <v>251.2760035</v>
       </c>
       <c r="H10" s="11" t="n">
         <f aca="false">IFERROR(Links!H15,0)+IFERROR(Links!H26,0)+IFERROR(Links!H37,0)+IFERROR(Links!H48,0)</f>
-        <v>349.5744827</v>
+        <v>349.4944827</v>
       </c>
       <c r="I10" s="11" t="n">
         <f aca="false">IFERROR(Links!I15,0)+IFERROR(Links!I26,0)+IFERROR(Links!I37,0)+IFERROR(Links!I48,0)</f>
-        <v>465.4682332</v>
+        <v>465.3882332</v>
       </c>
       <c r="J10" s="11" t="n">
         <f aca="false">IFERROR(Links!J15,0)+IFERROR(Links!J26,0)+IFERROR(Links!J37,0)+IFERROR(Links!J48,0)</f>
-        <v>587.7286707</v>
+        <v>586.6486707</v>
       </c>
       <c r="K10" s="11" t="n">
         <f aca="false">IFERROR(Links!K15,0)+IFERROR(Links!K26,0)+IFERROR(Links!K37,0)+IFERROR(Links!K48,0)</f>
-        <v>671.6674156</v>
+        <v>672.5074156</v>
       </c>
       <c r="L10" s="11" t="n">
         <f aca="false">IFERROR(Links!L15,0)+IFERROR(Links!L26,0)+IFERROR(Links!L37,0)+IFERROR(Links!L48,0)</f>
-        <v>777.3105332</v>
+        <v>777.2305332</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7918,35 +7918,35 @@
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">IFERROR(Links!E16,0)+IFERROR(Links!E27,0)+IFERROR(Links!E38,0)+IFERROR(Links!E49,0)</f>
-        <v>201.498788</v>
+        <v>200.498788</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">IFERROR(Links!F16,0)+IFERROR(Links!F27,0)+IFERROR(Links!F38,0)+IFERROR(Links!F49,0)</f>
-        <v>336.5256765</v>
+        <v>337.4456765</v>
       </c>
       <c r="G11" s="11" t="n">
         <f aca="false">IFERROR(Links!G16,0)+IFERROR(Links!G27,0)+IFERROR(Links!G38,0)+IFERROR(Links!G49,0)</f>
-        <v>554.0072077</v>
+        <v>552.0072077</v>
       </c>
       <c r="H11" s="11" t="n">
         <f aca="false">IFERROR(Links!H16,0)+IFERROR(Links!H27,0)+IFERROR(Links!H38,0)+IFERROR(Links!H49,0)</f>
-        <v>770.135862</v>
+        <v>769.975862</v>
       </c>
       <c r="I11" s="11" t="n">
         <f aca="false">IFERROR(Links!I16,0)+IFERROR(Links!I27,0)+IFERROR(Links!I38,0)+IFERROR(Links!I49,0)</f>
-        <v>1024.3501129</v>
+        <v>1024.1901129</v>
       </c>
       <c r="J11" s="11" t="n">
         <f aca="false">IFERROR(Links!J16,0)+IFERROR(Links!J27,0)+IFERROR(Links!J38,0)+IFERROR(Links!J49,0)</f>
-        <v>1292.1070756</v>
+        <v>1290.9470756</v>
       </c>
       <c r="K11" s="11" t="n">
         <f aca="false">IFERROR(Links!K16,0)+IFERROR(Links!K27,0)+IFERROR(Links!K38,0)+IFERROR(Links!K49,0)</f>
-        <v>1479.6603143</v>
+        <v>1479.4203143</v>
       </c>
       <c r="L11" s="11" t="n">
         <f aca="false">IFERROR(Links!L16,0)+IFERROR(Links!L27,0)+IFERROR(Links!L38,0)+IFERROR(Links!L49,0)</f>
-        <v>1709.4351731</v>
+        <v>1710.1951731</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7974,27 +7974,27 @@
       </c>
       <c r="G12" s="11" t="n">
         <f aca="false">IFERROR(Links!G17,0)+IFERROR(Links!G28,0)+IFERROR(Links!G39,0)+IFERROR(Links!G50,0)</f>
-        <v>122.26048167</v>
+        <v>121.26048167</v>
       </c>
       <c r="H12" s="11" t="n">
         <f aca="false">IFERROR(Links!H17,0)+IFERROR(Links!H28,0)+IFERROR(Links!H39,0)+IFERROR(Links!H50,0)</f>
-        <v>167.5285517</v>
+        <v>168.4485517</v>
       </c>
       <c r="I12" s="11" t="n">
         <f aca="false">IFERROR(Links!I17,0)+IFERROR(Links!I28,0)+IFERROR(Links!I39,0)+IFERROR(Links!I50,0)</f>
-        <v>224.4807519</v>
+        <v>223.4807519</v>
       </c>
       <c r="J12" s="11" t="n">
         <f aca="false">IFERROR(Links!J17,0)+IFERROR(Links!J28,0)+IFERROR(Links!J39,0)+IFERROR(Links!J50,0)</f>
-        <v>281.6473619</v>
+        <v>282.5673619</v>
       </c>
       <c r="K12" s="11" t="n">
         <f aca="false">IFERROR(Links!K17,0)+IFERROR(Links!K28,0)+IFERROR(Links!K39,0)+IFERROR(Links!K50,0)</f>
-        <v>323.8211595</v>
+        <v>322.8211595</v>
       </c>
       <c r="L12" s="11" t="n">
         <f aca="false">IFERROR(Links!L17,0)+IFERROR(Links!L28,0)+IFERROR(Links!L39,0)+IFERROR(Links!L50,0)</f>
-        <v>374.129856</v>
+        <v>373.049856</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8026,15 +8026,15 @@
       </c>
       <c r="H13" s="11" t="n">
         <f aca="false">IFERROR(Links!H18,0)+IFERROR(Links!H29,0)+IFERROR(Links!H40,0)+IFERROR(Links!H51,0)</f>
-        <v>111.85903447</v>
+        <v>110.85903447</v>
       </c>
       <c r="I13" s="11" t="n">
         <f aca="false">IFERROR(Links!I18,0)+IFERROR(Links!I29,0)+IFERROR(Links!I40,0)+IFERROR(Links!I51,0)</f>
-        <v>148.97383461</v>
+        <v>148.89383461</v>
       </c>
       <c r="J13" s="11" t="n">
         <f aca="false">IFERROR(Links!J18,0)+IFERROR(Links!J29,0)+IFERROR(Links!J40,0)+IFERROR(Links!J51,0)</f>
-        <v>186.5115746</v>
+        <v>187.4315746</v>
       </c>
       <c r="K13" s="11" t="n">
         <f aca="false">IFERROR(Links!K18,0)+IFERROR(Links!K29,0)+IFERROR(Links!K40,0)+IFERROR(Links!K51,0)</f>
@@ -8051,43 +8051,43 @@
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">SUM(C6:C13)</f>
-        <v>7006.58027218</v>
+        <v>6998.58027218</v>
       </c>
       <c r="D14" s="11" t="n">
         <f aca="false">SUM(D6:D13)</f>
-        <v>11085.02619482</v>
+        <v>11057.38619482</v>
       </c>
       <c r="E14" s="11" t="n">
         <f aca="false">SUM(E6:E13)</f>
-        <v>23285.16634636</v>
+        <v>23240.36634636</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">SUM(F6:F13)</f>
-        <v>51301.98894185</v>
+        <v>51225.82894185</v>
       </c>
       <c r="G14" s="11" t="n">
         <f aca="false">SUM(G6:G13)</f>
-        <v>89255.94954189</v>
+        <v>89176.18954189</v>
       </c>
       <c r="H14" s="11" t="n">
         <f aca="false">SUM(H6:H13)</f>
-        <v>125300.43002987</v>
+        <v>125212.23002987</v>
       </c>
       <c r="I14" s="11" t="n">
         <f aca="false">SUM(I6:I13)</f>
-        <v>172692.98210161</v>
+        <v>172617.10210161</v>
       </c>
       <c r="J14" s="11" t="n">
         <f aca="false">SUM(J6:J13)</f>
-        <v>220580.8909318</v>
+        <v>220517.7709318</v>
       </c>
       <c r="K14" s="11" t="n">
         <f aca="false">SUM(K6:K13)</f>
-        <v>248926.9466494</v>
+        <v>248869.9466494</v>
       </c>
       <c r="L14" s="11" t="n">
         <f aca="false">SUM(L6:L13)</f>
-        <v>287615.6065059</v>
+        <v>287551.4465059</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="B23" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$52,I10)</f>
-        <v>7.11145428027089</v>
+        <v>7.11095864376074</v>
       </c>
       <c r="C23" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$53,P10)</f>
@@ -10595,11 +10595,11 @@
       </c>
       <c r="D23" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$54,R10)</f>
-        <v>4.11145428027089</v>
+        <v>4.11095864376074</v>
       </c>
       <c r="E23" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$55,O10/N10)</f>
-        <v>2.05572714013545</v>
+        <v>2.05547932188037</v>
       </c>
       <c r="F23" s="9" t="n">
         <f aca="false">Datos!$B$32</f>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B24" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$52,I11)</f>
-        <v>7.11145428027089</v>
+        <v>7.11095864376074</v>
       </c>
       <c r="C24" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$53,P11)</f>
@@ -10625,11 +10625,11 @@
       </c>
       <c r="D24" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$54,R11)</f>
-        <v>4.11145428027089</v>
+        <v>4.11095864376074</v>
       </c>
       <c r="E24" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$55,O11/N11)</f>
-        <v>2.05572714013545</v>
+        <v>2.05547932188037</v>
       </c>
       <c r="F24" s="9" t="n">
         <f aca="false">Datos!$B$32</f>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="F64" s="20" t="n">
         <f aca="false">H82+H83+H84</f>
-        <v>5.7688</v>
+        <v>5.7717</v>
       </c>
       <c r="G64" s="28" t="n">
         <f aca="false">MIN(ROUNDDOWN(MIN(B64*Datos!$B$57,Datos!$B$60)*2,0)/2,MAX(Datos!$B$54,ROUNDUP(INDEX(Cálculo!$C$80:$L$80,Datos!$B$6-2025)/12*Datos!$B$52*2,0)/2))</f>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="H81" s="22" t="n">
         <f aca="false">E81*$E$85+F81*$F$85+G81*$G$85</f>
-        <v>0.9064</v>
+        <v>0.9061</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="H82" s="22" t="n">
         <f aca="false">E82*$E$85+F82*$F$85+G82*$G$85</f>
-        <v>0.5368</v>
+        <v>0.5367</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="H83" s="22" t="n">
         <f aca="false">E83*$E$85+F83*$F$85+G83*$G$85</f>
-        <v>0.4872</v>
+        <v>0.4833</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H84" s="22" t="n">
         <f aca="false">E84*$E$85+F84*$F$85+G84*$G$85</f>
-        <v>4.7448</v>
+        <v>4.7517</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12578,13 +12578,13 @@
         <v>486</v>
       </c>
       <c r="E85" s="17" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="F85" s="17" t="n">
-        <v>0.1624</v>
+        <v>0.1611</v>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.0936</v>
+        <v>0.0939</v>
       </c>
       <c r="H85" s="7" t="str">
         <f aca="false">IF(ABS(SUM(E85:G85)-1)&lt;0.001,"Suma 100 %","Revisar: no suma 100 %")</f>
@@ -14438,11 +14438,11 @@
       </c>
       <c r="B43" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)</f>
-        <v>777.3105332</v>
+        <v>777.2305332</v>
       </c>
       <c r="C43" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)</f>
-        <v>777.3105332</v>
+        <v>777.2305332</v>
       </c>
       <c r="D43" s="9" t="n">
         <f aca="false">C43-B43</f>
@@ -14455,11 +14455,11 @@
       </c>
       <c r="B44" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)</f>
-        <v>1709.4351731</v>
+        <v>1710.1951731</v>
       </c>
       <c r="C44" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)</f>
-        <v>1709.4351731</v>
+        <v>1710.1951731</v>
       </c>
       <c r="D44" s="9" t="n">
         <f aca="false">C44-B44</f>
@@ -14472,15 +14472,15 @@
       </c>
       <c r="B45" s="30" t="n">
         <f aca="false">INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)/Corte!$I$10+INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)/Corte!$I$11</f>
-        <v>371.273699205556</v>
+        <v>371.391476983333</v>
       </c>
       <c r="C45" s="30" t="n">
         <f aca="false">INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)</f>
-        <v>349.68173995</v>
+        <v>349.80173995</v>
       </c>
       <c r="D45" s="30" t="n">
         <f aca="false">C45-B45</f>
-        <v>-21.5919592555556</v>
+        <v>-21.5897370333334</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14489,15 +14489,15 @@
       </c>
       <c r="B46" s="30" t="n">
         <f aca="false">B45*Corte!$W$10/1000</f>
-        <v>42.0757057835672</v>
+        <v>42.0890533035672</v>
       </c>
       <c r="C46" s="30" t="n">
         <f aca="false">C45*Corte!$W$10/1000</f>
-        <v>39.6287322250536</v>
+        <v>39.6423315850536</v>
       </c>
       <c r="D46" s="30" t="n">
         <f aca="false">C46-B46</f>
-        <v>-2.44697355851361</v>
+        <v>-2.44672171851361</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14506,15 +14506,15 @@
       </c>
       <c r="B47" s="10" t="n">
         <f aca="false">(INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)*Piezas!$F$10*Piezas!$G$10+INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)*Piezas!$F$11*Piezas!$G$11)/(B45*Corte!$B$10*Corte!$C$10)</f>
-        <v>0.848792586916481</v>
+        <v>0.848792881238399</v>
       </c>
       <c r="C47" s="10" t="n">
         <f aca="false">(INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)*Piezas!$F$10*Piezas!$G$10+INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)*Piezas!$F$11*Piezas!$G$11)/(C45*Corte!$B$10*Corte!$C$10)</f>
-        <v>0.901203373238177</v>
+        <v>0.901180313914754</v>
       </c>
       <c r="D47" s="10" t="n">
         <f aca="false">C47-B47</f>
-        <v>0.0524107863216959</v>
+        <v>0.0523874326763549</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14523,15 +14523,15 @@
       </c>
       <c r="B48" s="9" t="n">
         <f aca="false">B46*1000*INDEX(Datos!$C$95:$C$100,MATCH(Piezas!$E$10,Datos!$A$95:$A$100,0))</f>
-        <v>46364.7044268384</v>
+        <v>46379.4125299613</v>
       </c>
       <c r="C48" s="9" t="n">
         <f aca="false">C46*1000*INDEX(Datos!$C$95:$C$100,MATCH(Piezas!$E$10,Datos!$A$95:$A$100,0))</f>
-        <v>43668.297945522</v>
+        <v>43683.2835600245</v>
       </c>
       <c r="D48" s="9" t="n">
         <f aca="false">C48-B48</f>
-        <v>-2696.40648131639</v>
+        <v>-2696.12896993672</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="B52" s="20" t="n">
         <f aca="false">IF((INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025))=0,0,(INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)+INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025))/(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)))</f>
-        <v>7.11145428027089</v>
+        <v>7.11095864376074</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B54" s="20" t="n">
         <f aca="false">IF((INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025))=0,0,(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)*H26+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)*H28+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)*H29)/(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)))</f>
-        <v>4.11145428027089</v>
+        <v>4.11095864376074</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="B55" s="20" t="n">
         <f aca="false">IF((INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025))=0,0,(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)*I26+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)*I28+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)*I29)/(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)))</f>
-        <v>2.05572714013545</v>
+        <v>2.05547932188037</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14799,15 +14799,15 @@
       </c>
       <c r="F69" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$18:$L$18,Datos!$B$6-2025)*Corte!$X$46</f>
-        <v>3588.44027106548</v>
+        <v>3585.64778530799</v>
       </c>
       <c r="G69" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$18:$L$18,Datos!$B$6-2025)*Corte!$Y$46</f>
-        <v>3312.11956142799</v>
+        <v>3309.54210548509</v>
       </c>
       <c r="H69" s="9" t="n">
         <f aca="false">F69-G69</f>
-        <v>276.320709637491</v>
+        <v>276.105679822898</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14833,15 +14833,15 @@
       </c>
       <c r="F70" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$19:$L$19,Datos!$B$6-2025)*Corte!$X$47</f>
-        <v>2907.55116686693</v>
+        <v>2905.28854171244</v>
       </c>
       <c r="G70" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$19:$L$19,Datos!$B$6-2025)*Corte!$Y$47</f>
-        <v>2680.4723346738</v>
+        <v>2678.38641983267</v>
       </c>
       <c r="H70" s="9" t="n">
         <f aca="false">F70-G70</f>
-        <v>227.078832193124</v>
+        <v>226.902121879776</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14867,15 +14867,15 @@
       </c>
       <c r="F71" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$20:$L$20,Datos!$B$6-2025)*Corte!$X$48</f>
-        <v>32918.3010106937</v>
+        <v>32893.9792772413</v>
       </c>
       <c r="G71" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$20:$L$20,Datos!$B$6-2025)*Corte!$Y$48</f>
-        <v>30378.1322242056</v>
+        <v>30355.6872980687</v>
       </c>
       <c r="H71" s="9" t="n">
         <f aca="false">F71-G71</f>
-        <v>2540.16878648806</v>
+        <v>2538.29197917261</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14901,15 +14901,15 @@
       </c>
       <c r="F72" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$21:$L$21,Datos!$B$6-2025)*Corte!$X$49</f>
-        <v>24697.7562142835</v>
+        <v>24679.5082420288</v>
       </c>
       <c r="G72" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$21:$L$21,Datos!$B$6-2025)*Corte!$Y$49</f>
-        <v>22753.628820976</v>
+        <v>22736.8172700069</v>
       </c>
       <c r="H72" s="9" t="n">
         <f aca="false">F72-G72</f>
-        <v>1944.12739330746</v>
+        <v>1942.69097202186</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14935,15 +14935,15 @@
       </c>
       <c r="F73" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$22:$L$22,Datos!$B$6-2025)*Corte!$X$50</f>
-        <v>2733.23878795901</v>
+        <v>2729.31026707074</v>
       </c>
       <c r="G73" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$22:$L$22,Datos!$B$6-2025)*Corte!$Y$50</f>
-        <v>2526.3470505006</v>
+        <v>2522.7158978905</v>
       </c>
       <c r="H73" s="9" t="n">
         <f aca="false">F73-G73</f>
-        <v>206.89173745841</v>
+        <v>206.594369180234</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14969,15 +14969,15 @@
       </c>
       <c r="F74" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$23:$L$23,Datos!$B$6-2025)*Corte!$X$51</f>
-        <v>2496.38684250186</v>
+        <v>2492.79875210186</v>
       </c>
       <c r="G74" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$23:$L$23,Datos!$B$6-2025)*Corte!$Y$51</f>
-        <v>2297.52256815992</v>
+        <v>2294.22030805734</v>
       </c>
       <c r="H74" s="9" t="n">
         <f aca="false">F74-G74</f>
-        <v>198.864274341937</v>
+        <v>198.578444044516</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14986,15 +14986,15 @@
       </c>
       <c r="F75" s="11" t="n">
         <f aca="false">SUM(F67:F74)</f>
-        <v>100996.041943413</v>
+        <v>100940.900515505</v>
       </c>
       <c r="G75" s="11" t="n">
         <f aca="false">SUM(G67:G74)</f>
-        <v>93014.6604153314</v>
+        <v>92963.8071547285</v>
       </c>
       <c r="H75" s="11" t="n">
         <f aca="false">SUM(H67:H74)</f>
-        <v>7981.38152808131</v>
+        <v>7977.09336077672</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15224,43 +15224,43 @@
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">Demanda!C7</f>
-        <v>302.0303572</v>
+        <v>300.0303572</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">Demanda!D7</f>
-        <v>727.2874503</v>
+        <v>722.1274503</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">Demanda!E7</f>
-        <v>1317.3880576</v>
+        <v>1309.8280576</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">Demanda!F7</f>
-        <v>2592.678174</v>
+        <v>2579.558174</v>
       </c>
       <c r="G9" s="9" t="n">
         <f aca="false">Demanda!G7</f>
-        <v>4297.387726</v>
+        <v>4282.307726</v>
       </c>
       <c r="H9" s="9" t="n">
         <f aca="false">Demanda!H7</f>
-        <v>6113.149887</v>
+        <v>6097.029887</v>
       </c>
       <c r="I9" s="9" t="n">
         <f aca="false">Demanda!I7</f>
-        <v>8117.275524</v>
+        <v>8102.115524</v>
       </c>
       <c r="J9" s="9" t="n">
         <f aca="false">Demanda!J7</f>
-        <v>10270.226587</v>
+        <v>10259.186587</v>
       </c>
       <c r="K9" s="9" t="n">
         <f aca="false">Demanda!K7</f>
-        <v>11976.506243</v>
+        <v>11964.986243</v>
       </c>
       <c r="L9" s="9" t="n">
         <f aca="false">Demanda!L7</f>
-        <v>14135.378444</v>
+        <v>14124.378444</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15272,43 +15272,43 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">Demanda!C8</f>
-        <v>2286.773025</v>
+        <v>2280.773025</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">Demanda!D8</f>
-        <v>3940.458881</v>
+        <v>3920.978881</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">Demanda!E8</f>
-        <v>6733.097591</v>
+        <v>6700.097591</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">Demanda!F8</f>
-        <v>12240.955313</v>
+        <v>12185.475313</v>
       </c>
       <c r="G10" s="9" t="n">
         <f aca="false">Demanda!G8</f>
-        <v>20628.46694</v>
+        <v>20572.90694</v>
       </c>
       <c r="H10" s="9" t="n">
         <f aca="false">Demanda!H8</f>
-        <v>28744.68411</v>
+        <v>28680.36411</v>
       </c>
       <c r="I10" s="9" t="n">
         <f aca="false">Demanda!I8</f>
-        <v>38699.47984</v>
+        <v>38644.99984</v>
       </c>
       <c r="J10" s="9" t="n">
         <f aca="false">Demanda!J8</f>
-        <v>48872.02637</v>
+        <v>48826.50637</v>
       </c>
       <c r="K10" s="9" t="n">
         <f aca="false">Demanda!K8</f>
-        <v>55509.52455</v>
+        <v>55467.92455</v>
       </c>
       <c r="L10" s="9" t="n">
         <f aca="false">Demanda!L8</f>
-        <v>63882.93872</v>
+        <v>63835.73872</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15324,39 +15324,39 @@
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">Demanda!D9</f>
-        <v>184.4872967</v>
+        <v>181.4872967</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">Demanda!E9</f>
-        <v>356.1787798</v>
+        <v>352.9387798</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">Demanda!F9</f>
-        <v>693.7804941</v>
+        <v>686.3004941</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">Demanda!G9</f>
-        <v>1206.3981519</v>
+        <v>1200.3581519</v>
       </c>
       <c r="H11" s="9" t="n">
         <f aca="false">Demanda!H9</f>
-        <v>1743.045032</v>
+        <v>1735.605032</v>
       </c>
       <c r="I11" s="9" t="n">
         <f aca="false">Demanda!I9</f>
-        <v>2339.800545</v>
+        <v>2334.880545</v>
       </c>
       <c r="J11" s="9" t="n">
         <f aca="false">Demanda!J9</f>
-        <v>2957.564812</v>
+        <v>2951.404812</v>
       </c>
       <c r="K11" s="9" t="n">
         <f aca="false">Demanda!K9</f>
-        <v>3358.670054</v>
+        <v>3355.190054</v>
       </c>
       <c r="L11" s="9" t="n">
         <f aca="false">Demanda!L9</f>
-        <v>3868.328079</v>
+        <v>3862.768079</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15380,31 +15380,31 @@
       </c>
       <c r="F12" s="9" t="n">
         <f aca="false">Demanda!F10</f>
-        <v>153.9698529</v>
+        <v>152.9698529</v>
       </c>
       <c r="G12" s="9" t="n">
         <f aca="false">Demanda!G10</f>
-        <v>251.3560035</v>
+        <v>251.2760035</v>
       </c>
       <c r="H12" s="9" t="n">
         <f aca="false">Demanda!H10</f>
-        <v>349.5744827</v>
+        <v>349.4944827</v>
       </c>
       <c r="I12" s="9" t="n">
         <f aca="false">Demanda!I10</f>
-        <v>465.4682332</v>
+        <v>465.3882332</v>
       </c>
       <c r="J12" s="9" t="n">
         <f aca="false">Demanda!J10</f>
-        <v>587.7286707</v>
+        <v>586.6486707</v>
       </c>
       <c r="K12" s="9" t="n">
         <f aca="false">Demanda!K10</f>
-        <v>671.6674156</v>
+        <v>672.5074156</v>
       </c>
       <c r="L12" s="9" t="n">
         <f aca="false">Demanda!L10</f>
-        <v>777.3105332</v>
+        <v>777.2305332</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15424,35 +15424,35 @@
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">Demanda!E11</f>
-        <v>201.498788</v>
+        <v>200.498788</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">Demanda!F11</f>
-        <v>336.5256765</v>
+        <v>337.4456765</v>
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">Demanda!G11</f>
-        <v>554.0072077</v>
+        <v>552.0072077</v>
       </c>
       <c r="H13" s="9" t="n">
         <f aca="false">Demanda!H11</f>
-        <v>770.135862</v>
+        <v>769.975862</v>
       </c>
       <c r="I13" s="9" t="n">
         <f aca="false">Demanda!I11</f>
-        <v>1024.3501129</v>
+        <v>1024.1901129</v>
       </c>
       <c r="J13" s="9" t="n">
         <f aca="false">Demanda!J11</f>
-        <v>1292.1070756</v>
+        <v>1290.9470756</v>
       </c>
       <c r="K13" s="9" t="n">
         <f aca="false">Demanda!K11</f>
-        <v>1479.6603143</v>
+        <v>1479.4203143</v>
       </c>
       <c r="L13" s="9" t="n">
         <f aca="false">Demanda!L11</f>
-        <v>1709.4351731</v>
+        <v>1710.1951731</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15480,27 +15480,27 @@
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">Demanda!G12</f>
-        <v>122.26048167</v>
+        <v>121.26048167</v>
       </c>
       <c r="H14" s="9" t="n">
         <f aca="false">Demanda!H12</f>
-        <v>167.5285517</v>
+        <v>168.4485517</v>
       </c>
       <c r="I14" s="9" t="n">
         <f aca="false">Demanda!I12</f>
-        <v>224.4807519</v>
+        <v>223.4807519</v>
       </c>
       <c r="J14" s="9" t="n">
         <f aca="false">Demanda!J12</f>
-        <v>281.6473619</v>
+        <v>282.5673619</v>
       </c>
       <c r="K14" s="9" t="n">
         <f aca="false">Demanda!K12</f>
-        <v>323.8211595</v>
+        <v>322.8211595</v>
       </c>
       <c r="L14" s="9" t="n">
         <f aca="false">Demanda!L12</f>
-        <v>374.129856</v>
+        <v>373.049856</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15532,15 +15532,15 @@
       </c>
       <c r="H15" s="9" t="n">
         <f aca="false">Demanda!H13</f>
-        <v>111.85903447</v>
+        <v>110.85903447</v>
       </c>
       <c r="I15" s="9" t="n">
         <f aca="false">Demanda!I13</f>
-        <v>148.97383461</v>
+        <v>148.89383461</v>
       </c>
       <c r="J15" s="9" t="n">
         <f aca="false">Demanda!J13</f>
-        <v>186.5115746</v>
+        <v>187.4315746</v>
       </c>
       <c r="K15" s="9" t="n">
         <f aca="false">Demanda!K13</f>
@@ -15656,43 +15656,43 @@
       </c>
       <c r="C18" s="9" t="n">
         <f aca="false">C9</f>
-        <v>302.0303572</v>
+        <v>300.0303572</v>
       </c>
       <c r="D18" s="9" t="n">
         <f aca="false">D9</f>
-        <v>727.2874503</v>
+        <v>722.1274503</v>
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">E9</f>
-        <v>1317.3880576</v>
+        <v>1309.8280576</v>
       </c>
       <c r="F18" s="9" t="n">
         <f aca="false">F9</f>
-        <v>2592.678174</v>
+        <v>2579.558174</v>
       </c>
       <c r="G18" s="9" t="n">
         <f aca="false">G9</f>
-        <v>4297.387726</v>
+        <v>4282.307726</v>
       </c>
       <c r="H18" s="9" t="n">
         <f aca="false">H9</f>
-        <v>6113.149887</v>
+        <v>6097.029887</v>
       </c>
       <c r="I18" s="9" t="n">
         <f aca="false">I9</f>
-        <v>8117.275524</v>
+        <v>8102.115524</v>
       </c>
       <c r="J18" s="9" t="n">
         <f aca="false">J9</f>
-        <v>10270.226587</v>
+        <v>10259.186587</v>
       </c>
       <c r="K18" s="9" t="n">
         <f aca="false">K9</f>
-        <v>11976.506243</v>
+        <v>11964.986243</v>
       </c>
       <c r="L18" s="9" t="n">
         <f aca="false">L9</f>
-        <v>14135.378444</v>
+        <v>14124.378444</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15704,43 +15704,43 @@
       </c>
       <c r="C19" s="9" t="n">
         <f aca="false">C9</f>
-        <v>302.0303572</v>
+        <v>300.0303572</v>
       </c>
       <c r="D19" s="9" t="n">
         <f aca="false">D9</f>
-        <v>727.2874503</v>
+        <v>722.1274503</v>
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">E9</f>
-        <v>1317.3880576</v>
+        <v>1309.8280576</v>
       </c>
       <c r="F19" s="9" t="n">
         <f aca="false">F9</f>
-        <v>2592.678174</v>
+        <v>2579.558174</v>
       </c>
       <c r="G19" s="9" t="n">
         <f aca="false">G9</f>
-        <v>4297.387726</v>
+        <v>4282.307726</v>
       </c>
       <c r="H19" s="9" t="n">
         <f aca="false">H9</f>
-        <v>6113.149887</v>
+        <v>6097.029887</v>
       </c>
       <c r="I19" s="9" t="n">
         <f aca="false">I9</f>
-        <v>8117.275524</v>
+        <v>8102.115524</v>
       </c>
       <c r="J19" s="9" t="n">
         <f aca="false">J9</f>
-        <v>10270.226587</v>
+        <v>10259.186587</v>
       </c>
       <c r="K19" s="9" t="n">
         <f aca="false">K9</f>
-        <v>11976.506243</v>
+        <v>11964.986243</v>
       </c>
       <c r="L19" s="9" t="n">
         <f aca="false">L9</f>
-        <v>14135.378444</v>
+        <v>14124.378444</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15752,43 +15752,43 @@
       </c>
       <c r="C20" s="9" t="n">
         <f aca="false">C10</f>
-        <v>2286.773025</v>
+        <v>2280.773025</v>
       </c>
       <c r="D20" s="9" t="n">
         <f aca="false">D10</f>
-        <v>3940.458881</v>
+        <v>3920.978881</v>
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">E10</f>
-        <v>6733.097591</v>
+        <v>6700.097591</v>
       </c>
       <c r="F20" s="9" t="n">
         <f aca="false">F10</f>
-        <v>12240.955313</v>
+        <v>12185.475313</v>
       </c>
       <c r="G20" s="9" t="n">
         <f aca="false">G10</f>
-        <v>20628.46694</v>
+        <v>20572.90694</v>
       </c>
       <c r="H20" s="9" t="n">
         <f aca="false">H10</f>
-        <v>28744.68411</v>
+        <v>28680.36411</v>
       </c>
       <c r="I20" s="9" t="n">
         <f aca="false">I10</f>
-        <v>38699.47984</v>
+        <v>38644.99984</v>
       </c>
       <c r="J20" s="9" t="n">
         <f aca="false">J10</f>
-        <v>48872.02637</v>
+        <v>48826.50637</v>
       </c>
       <c r="K20" s="9" t="n">
         <f aca="false">K10</f>
-        <v>55509.52455</v>
+        <v>55467.92455</v>
       </c>
       <c r="L20" s="9" t="n">
         <f aca="false">L10</f>
-        <v>63882.93872</v>
+        <v>63835.73872</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15800,43 +15800,43 @@
       </c>
       <c r="C21" s="9" t="n">
         <f aca="false">C10</f>
-        <v>2286.773025</v>
+        <v>2280.773025</v>
       </c>
       <c r="D21" s="9" t="n">
         <f aca="false">D10</f>
-        <v>3940.458881</v>
+        <v>3920.978881</v>
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">E10</f>
-        <v>6733.097591</v>
+        <v>6700.097591</v>
       </c>
       <c r="F21" s="9" t="n">
         <f aca="false">F10</f>
-        <v>12240.955313</v>
+        <v>12185.475313</v>
       </c>
       <c r="G21" s="9" t="n">
         <f aca="false">G10</f>
-        <v>20628.46694</v>
+        <v>20572.90694</v>
       </c>
       <c r="H21" s="9" t="n">
         <f aca="false">H10</f>
-        <v>28744.68411</v>
+        <v>28680.36411</v>
       </c>
       <c r="I21" s="9" t="n">
         <f aca="false">I10</f>
-        <v>38699.47984</v>
+        <v>38644.99984</v>
       </c>
       <c r="J21" s="9" t="n">
         <f aca="false">J10</f>
-        <v>48872.02637</v>
+        <v>48826.50637</v>
       </c>
       <c r="K21" s="9" t="n">
         <f aca="false">K10</f>
-        <v>55509.52455</v>
+        <v>55467.92455</v>
       </c>
       <c r="L21" s="9" t="n">
         <f aca="false">L10</f>
-        <v>63882.93872</v>
+        <v>63835.73872</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15852,39 +15852,39 @@
       </c>
       <c r="D22" s="9" t="n">
         <f aca="false">D11</f>
-        <v>184.4872967</v>
+        <v>181.4872967</v>
       </c>
       <c r="E22" s="9" t="n">
         <f aca="false">E11</f>
-        <v>356.1787798</v>
+        <v>352.9387798</v>
       </c>
       <c r="F22" s="9" t="n">
         <f aca="false">F11</f>
-        <v>693.7804941</v>
+        <v>686.3004941</v>
       </c>
       <c r="G22" s="9" t="n">
         <f aca="false">G11</f>
-        <v>1206.3981519</v>
+        <v>1200.3581519</v>
       </c>
       <c r="H22" s="9" t="n">
         <f aca="false">H11</f>
-        <v>1743.045032</v>
+        <v>1735.605032</v>
       </c>
       <c r="I22" s="9" t="n">
         <f aca="false">I11</f>
-        <v>2339.800545</v>
+        <v>2334.880545</v>
       </c>
       <c r="J22" s="9" t="n">
         <f aca="false">J11</f>
-        <v>2957.564812</v>
+        <v>2951.404812</v>
       </c>
       <c r="K22" s="9" t="n">
         <f aca="false">K11</f>
-        <v>3358.670054</v>
+        <v>3355.190054</v>
       </c>
       <c r="L22" s="9" t="n">
         <f aca="false">L11</f>
-        <v>3868.328079</v>
+        <v>3862.768079</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15900,39 +15900,39 @@
       </c>
       <c r="D23" s="9" t="n">
         <f aca="false">D11</f>
-        <v>184.4872967</v>
+        <v>181.4872967</v>
       </c>
       <c r="E23" s="9" t="n">
         <f aca="false">E11</f>
-        <v>356.1787798</v>
+        <v>352.9387798</v>
       </c>
       <c r="F23" s="9" t="n">
         <f aca="false">F11</f>
-        <v>693.7804941</v>
+        <v>686.3004941</v>
       </c>
       <c r="G23" s="9" t="n">
         <f aca="false">G11</f>
-        <v>1206.3981519</v>
+        <v>1200.3581519</v>
       </c>
       <c r="H23" s="9" t="n">
         <f aca="false">H11</f>
-        <v>1743.045032</v>
+        <v>1735.605032</v>
       </c>
       <c r="I23" s="9" t="n">
         <f aca="false">I11</f>
-        <v>2339.800545</v>
+        <v>2334.880545</v>
       </c>
       <c r="J23" s="9" t="n">
         <f aca="false">J11</f>
-        <v>2957.564812</v>
+        <v>2951.404812</v>
       </c>
       <c r="K23" s="9" t="n">
         <f aca="false">K11</f>
-        <v>3358.670054</v>
+        <v>3355.190054</v>
       </c>
       <c r="L23" s="9" t="n">
         <f aca="false">L11</f>
-        <v>3868.328079</v>
+        <v>3862.768079</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15944,43 +15944,43 @@
       </c>
       <c r="C25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(C$8:C$15,Piezas!$H$6:$H$13)+SUMPRODUCT(C$16:C$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>11.9634730682401</v>
+        <v>11.9449774721977</v>
       </c>
       <c r="D25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(D$8:D$15,Piezas!$H$6:$H$13)+SUMPRODUCT(D$16:D$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>20.018287462186</v>
+        <v>19.943902339016</v>
       </c>
       <c r="E25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(E$8:E$15,Piezas!$H$6:$H$13)+SUMPRODUCT(E$16:E$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>36.1789056910757</v>
+        <v>36.0483641302406</v>
       </c>
       <c r="F25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(F$8:F$15,Piezas!$H$6:$H$13)+SUMPRODUCT(F$16:F$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>70.2519659947985</v>
+        <v>70.0520801863879</v>
       </c>
       <c r="G25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(G$8:G$15,Piezas!$H$6:$H$13)+SUMPRODUCT(G$16:G$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>119.68468846272</v>
+        <v>119.421866410137</v>
       </c>
       <c r="H25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(H$8:H$15,Piezas!$H$6:$H$13)+SUMPRODUCT(H$16:H$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>167.546739287584</v>
+        <v>167.299806541106</v>
       </c>
       <c r="I25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(I$8:I$15,Piezas!$H$6:$H$13)+SUMPRODUCT(I$16:I$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>227.324226565904</v>
+        <v>227.096429333187</v>
       </c>
       <c r="J25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(J$8:J$15,Piezas!$H$6:$H$13)+SUMPRODUCT(J$16:J$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>288.346816763556</v>
+        <v>288.214606279629</v>
       </c>
       <c r="K25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(K$8:K$15,Piezas!$H$6:$H$13)+SUMPRODUCT(K$16:K$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>327.292236133152</v>
+        <v>327.122786687787</v>
       </c>
       <c r="L25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(L$8:L$15,Piezas!$H$6:$H$13)+SUMPRODUCT(L$16:L$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>377.830440297784</v>
+        <v>377.63954906062</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15997,43 +15997,43 @@
       </c>
       <c r="C28" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15,Corte!$F$32:$F$39)/1000</f>
-        <v>10.2189564320188</v>
+        <v>10.2047701967592</v>
       </c>
       <c r="D28" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15,Corte!$F$32:$F$39)/1000</f>
-        <v>17.0353980978299</v>
+        <v>16.97739121086</v>
       </c>
       <c r="E28" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15,Corte!$F$32:$F$39)/1000</f>
-        <v>30.5378330085562</v>
+        <v>30.4301574679783</v>
       </c>
       <c r="F28" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15,Corte!$F$32:$F$39)/1000</f>
-        <v>58.9448083660154</v>
+        <v>58.7925651485816</v>
       </c>
       <c r="G28" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15,Corte!$F$32:$F$39)/1000</f>
-        <v>100.294445441478</v>
+        <v>100.069365182897</v>
       </c>
       <c r="H28" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15,Corte!$F$32:$F$39)/1000</f>
-        <v>140.353555427362</v>
+        <v>140.157283249732</v>
       </c>
       <c r="I28" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15,Corte!$F$32:$F$39)/1000</f>
-        <v>190.307982153913</v>
+        <v>190.121382063911</v>
       </c>
       <c r="J28" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15,Corte!$F$32:$F$39)/1000</f>
-        <v>241.342613668821</v>
+        <v>241.246290761434</v>
       </c>
       <c r="K28" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15,Corte!$F$32:$F$39)/1000</f>
-        <v>274.04920971688</v>
+        <v>273.91063527891</v>
       </c>
       <c r="L28" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15,Corte!$F$32:$F$39)/1000</f>
-        <v>316.40197064345</v>
+        <v>316.249801347332</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16045,43 +16045,43 @@
       </c>
       <c r="C29" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15,Corte!$G$32:$G$39)</f>
-        <v>12401.5215124621</v>
+        <v>12383.7807740959</v>
       </c>
       <c r="D29" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15,Corte!$G$32:$G$39)</f>
-        <v>20693.4106068345</v>
+        <v>20620.7050377513</v>
       </c>
       <c r="E29" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15,Corte!$G$32:$G$39)</f>
-        <v>37280.27764195</v>
+        <v>37148.0310270457</v>
       </c>
       <c r="F29" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15,Corte!$G$32:$G$39)</f>
-        <v>72251.1390310842</v>
+        <v>72059.4473710889</v>
       </c>
       <c r="G29" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15,Corte!$G$32:$G$39)</f>
-        <v>123036.969262122</v>
+        <v>122764.804323169</v>
       </c>
       <c r="H29" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15,Corte!$G$32:$G$39)</f>
-        <v>172222.670651704</v>
+        <v>171979.101486817</v>
       </c>
       <c r="I29" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15,Corte!$G$32:$G$39)</f>
-        <v>233628.465299562</v>
+        <v>233400.186573223</v>
       </c>
       <c r="J29" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15,Corte!$G$32:$G$39)</f>
-        <v>296338.911247755</v>
+        <v>296213.417553126</v>
       </c>
       <c r="K29" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15,Corte!$G$32:$G$39)</f>
-        <v>336419.391102678</v>
+        <v>336249.628657763</v>
       </c>
       <c r="L29" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15,Corte!$G$32:$G$39)</f>
-        <v>388402.130208456</v>
+        <v>388214.382638995</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16093,43 +16093,43 @@
       </c>
       <c r="C30" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$16:C$23,Corte!$I$44:$I$51)/1000</f>
-        <v>2.98226960100047</v>
+        <v>2.97593908665771</v>
       </c>
       <c r="D30" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$16:D$23,Corte!$I$44:$I$51)/1000</f>
-        <v>5.07446851111212</v>
+        <v>5.05047245641396</v>
       </c>
       <c r="E30" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$16:E$23,Corte!$I$44:$I$51)/1000</f>
-        <v>9.42698822961981</v>
+        <v>9.38937108822696</v>
       </c>
       <c r="F30" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$16:F$23,Corte!$I$44:$I$51)/1000</f>
-        <v>18.6626977711183</v>
+        <v>18.5965186846321</v>
       </c>
       <c r="G30" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$16:G$23,Corte!$I$44:$I$51)/1000</f>
-        <v>31.9146245086367</v>
+        <v>31.8494192895008</v>
       </c>
       <c r="H30" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$16:H$23,Corte!$I$44:$I$51)/1000</f>
-        <v>44.7291108547456</v>
+        <v>44.6536343771726</v>
       </c>
       <c r="I30" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$16:I$23,Corte!$I$44:$I$51)/1000</f>
-        <v>60.8049804466597</v>
+        <v>60.7422266531947</v>
       </c>
       <c r="J30" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$16:J$23,Corte!$I$44:$I$51)/1000</f>
-        <v>77.1876617778975</v>
+        <v>77.1332060155806</v>
       </c>
       <c r="K30" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$16:K$23,Corte!$I$44:$I$51)/1000</f>
-        <v>87.5093113982959</v>
+        <v>87.4617936142496</v>
       </c>
       <c r="L30" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$16:L$23,Corte!$I$44:$I$51)/1000</f>
-        <v>100.996041943413</v>
+        <v>100.940900515505</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16141,43 +16141,43 @@
       </c>
       <c r="C31" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$16:C$23,Corte!$J$44:$J$51)</f>
-        <v>3556.9249996593</v>
+        <v>3549.41700964878</v>
       </c>
       <c r="D31" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$16:D$23,Corte!$J$44:$J$51)</f>
-        <v>6047.33115626532</v>
+        <v>6018.8486031533</v>
       </c>
       <c r="E31" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$16:E$23,Corte!$J$44:$J$51)</f>
-        <v>11249.9198274114</v>
+        <v>11205.2808069003</v>
       </c>
       <c r="F31" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$16:F$23,Corte!$J$44:$J$51)</f>
-        <v>22301.0491233122</v>
+        <v>22222.5028010211</v>
       </c>
       <c r="G31" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$16:G$23,Corte!$J$44:$J$51)</f>
-        <v>38145.7685878325</v>
+        <v>38068.3884236941</v>
       </c>
       <c r="H31" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$16:H$23,Corte!$J$44:$J$51)</f>
-        <v>53463.7362487711</v>
+        <v>53374.1635304143</v>
       </c>
       <c r="I31" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$16:I$23,Corte!$J$44:$J$51)</f>
-        <v>72692.4259287981</v>
+        <v>72617.961828875</v>
       </c>
       <c r="J31" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$16:J$23,Corte!$J$44:$J$51)</f>
-        <v>92285.5581907436</v>
+        <v>92220.9259531029</v>
       </c>
       <c r="K31" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$16:K$23,Corte!$J$44:$J$51)</f>
-        <v>104618.721744208</v>
+        <v>104562.338702931</v>
       </c>
       <c r="L31" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$16:L$23,Corte!$J$44:$J$51)</f>
-        <v>120743.155813304</v>
+        <v>120677.715022721</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16189,43 +16189,43 @@
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">C28+C30</f>
-        <v>13.2012260330193</v>
+        <v>13.1807092834169</v>
       </c>
       <c r="D32" s="30" t="n">
         <f aca="false">D28+D30</f>
-        <v>22.109866608942</v>
+        <v>22.027863667274</v>
       </c>
       <c r="E32" s="30" t="n">
         <f aca="false">E28+E30</f>
-        <v>39.964821238176</v>
+        <v>39.8195285562053</v>
       </c>
       <c r="F32" s="30" t="n">
         <f aca="false">F28+F30</f>
-        <v>77.6075061371337</v>
+        <v>77.3890838332137</v>
       </c>
       <c r="G32" s="30" t="n">
         <f aca="false">G28+G30</f>
-        <v>132.209069950115</v>
+        <v>131.918784472398</v>
       </c>
       <c r="H32" s="30" t="n">
         <f aca="false">H28+H30</f>
-        <v>185.082666282108</v>
+        <v>184.810917626905</v>
       </c>
       <c r="I32" s="30" t="n">
         <f aca="false">I28+I30</f>
-        <v>251.112962600573</v>
+        <v>250.863608717106</v>
       </c>
       <c r="J32" s="30" t="n">
         <f aca="false">J28+J30</f>
-        <v>318.530275446719</v>
+        <v>318.379496777015</v>
       </c>
       <c r="K32" s="30" t="n">
         <f aca="false">K28+K30</f>
-        <v>361.558521115176</v>
+        <v>361.37242889316</v>
       </c>
       <c r="L32" s="30" t="n">
         <f aca="false">L28+L30</f>
-        <v>417.398012586863</v>
+        <v>417.190701862837</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16237,43 +16237,43 @@
       </c>
       <c r="C33" s="9" t="n">
         <f aca="false">C29+C31</f>
-        <v>15958.4465121214</v>
+        <v>15933.1977837446</v>
       </c>
       <c r="D33" s="9" t="n">
         <f aca="false">D29+D31</f>
-        <v>26740.7417630998</v>
+        <v>26639.5536409046</v>
       </c>
       <c r="E33" s="9" t="n">
         <f aca="false">E29+E31</f>
-        <v>48530.1974693613</v>
+        <v>48353.3118339459</v>
       </c>
       <c r="F33" s="9" t="n">
         <f aca="false">F29+F31</f>
-        <v>94552.1881543964</v>
+        <v>94281.95017211</v>
       </c>
       <c r="G33" s="9" t="n">
         <f aca="false">G29+G31</f>
-        <v>161182.737849955</v>
+        <v>160833.192746863</v>
       </c>
       <c r="H33" s="9" t="n">
         <f aca="false">H29+H31</f>
-        <v>225686.406900475</v>
+        <v>225353.265017231</v>
       </c>
       <c r="I33" s="9" t="n">
         <f aca="false">I29+I31</f>
-        <v>306320.891228361</v>
+        <v>306018.148402098</v>
       </c>
       <c r="J33" s="9" t="n">
         <f aca="false">J29+J31</f>
-        <v>388624.469438498</v>
+        <v>388434.343506229</v>
       </c>
       <c r="K33" s="9" t="n">
         <f aca="false">K29+K31</f>
-        <v>441038.112846886</v>
+        <v>440811.967360693</v>
       </c>
       <c r="L33" s="9" t="n">
         <f aca="false">L29+L31</f>
-        <v>509145.28602176</v>
+        <v>508892.097661716</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16285,43 +16285,43 @@
       </c>
       <c r="C34" s="30" t="n">
         <f aca="false">C32-C25</f>
-        <v>1.23775296477918</v>
+        <v>1.23573181121919</v>
       </c>
       <c r="D34" s="30" t="n">
         <f aca="false">D32-D25</f>
-        <v>2.09157914675599</v>
+        <v>2.08396132825798</v>
       </c>
       <c r="E34" s="30" t="n">
         <f aca="false">E32-E25</f>
-        <v>3.78591554710032</v>
+        <v>3.77116442596473</v>
       </c>
       <c r="F34" s="30" t="n">
         <f aca="false">F32-F25</f>
-        <v>7.35554014233526</v>
+        <v>7.33700364682575</v>
       </c>
       <c r="G34" s="30" t="n">
         <f aca="false">G32-G25</f>
-        <v>12.5243814873953</v>
+        <v>12.4969180622603</v>
       </c>
       <c r="H34" s="30" t="n">
         <f aca="false">H32-H25</f>
-        <v>17.5359269945234</v>
+        <v>17.5111110857987</v>
       </c>
       <c r="I34" s="30" t="n">
         <f aca="false">I32-I25</f>
-        <v>23.7887360346685</v>
+        <v>23.7671793839187</v>
       </c>
       <c r="J34" s="30" t="n">
         <f aca="false">J32-J25</f>
-        <v>30.183458683163</v>
+        <v>30.1648904973857</v>
       </c>
       <c r="K34" s="30" t="n">
         <f aca="false">K32-K25</f>
-        <v>34.266284982024</v>
+        <v>34.2496422053726</v>
       </c>
       <c r="L34" s="30" t="n">
         <f aca="false">L32-L25</f>
-        <v>39.5675722890794</v>
+        <v>39.5511528022171</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16333,43 +16333,43 @@
       </c>
       <c r="C35" s="9" t="n">
         <f aca="false">-C34*Datos!$B$9</f>
-        <v>-309.438241194794</v>
+        <v>-308.932952804798</v>
       </c>
       <c r="D35" s="9" t="n">
         <f aca="false">-D34*Datos!$B$9</f>
-        <v>-522.894786688998</v>
+        <v>-520.990332064496</v>
       </c>
       <c r="E35" s="9" t="n">
         <f aca="false">-E34*Datos!$B$9</f>
-        <v>-946.478886775081</v>
+        <v>-942.791106491182</v>
       </c>
       <c r="F35" s="9" t="n">
         <f aca="false">-F34*Datos!$B$9</f>
-        <v>-1838.88503558381</v>
+        <v>-1834.25091170644</v>
       </c>
       <c r="G35" s="9" t="n">
         <f aca="false">-G34*Datos!$B$9</f>
-        <v>-3131.09537184883</v>
+        <v>-3124.22951556507</v>
       </c>
       <c r="H35" s="9" t="n">
         <f aca="false">-H34*Datos!$B$9</f>
-        <v>-4383.98174863086</v>
+        <v>-4377.77777144969</v>
       </c>
       <c r="I35" s="9" t="n">
         <f aca="false">-I34*Datos!$B$9</f>
-        <v>-5947.18400866714</v>
+        <v>-5941.79484597967</v>
       </c>
       <c r="J35" s="9" t="n">
         <f aca="false">-J34*Datos!$B$9</f>
-        <v>-7545.86467079075</v>
+        <v>-7541.22262434642</v>
       </c>
       <c r="K35" s="9" t="n">
         <f aca="false">-K34*Datos!$B$9</f>
-        <v>-8566.571245506</v>
+        <v>-8562.41055134315</v>
       </c>
       <c r="L35" s="9" t="n">
         <f aca="false">-L34*Datos!$B$9</f>
-        <v>-9891.89307226985</v>
+        <v>-9887.78820055428</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16381,43 +16381,43 @@
       </c>
       <c r="C36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+C$8:C$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-C$8:C$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+C$8:C$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>1.67040633984923</v>
+        <v>1.66808743600872</v>
       </c>
       <c r="D36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+D$8:D$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-D$8:D$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+D$8:D$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>2.78463238137603</v>
+        <v>2.77515048639058</v>
       </c>
       <c r="E36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+E$8:E$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-E$8:E$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+E$8:E$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>4.99176116486015</v>
+        <v>4.97416035534262</v>
       </c>
       <c r="F36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+F$8:F$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-F$8:F$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+F$8:F$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>9.63520905982944</v>
+        <v>9.61032314928737</v>
       </c>
       <c r="G36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+G$8:G$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-G$8:G$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+G$8:G$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>16.2220538950066</v>
+        <v>16.1991926364354</v>
       </c>
       <c r="H36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+H$8:H$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-H$8:H$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+H$8:H$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>18.8729600596383</v>
+        <v>18.8653024841817</v>
       </c>
       <c r="I36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+I$8:I$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-I$8:I$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+I$8:I$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>20.8195377751505</v>
+        <v>20.812360848612</v>
       </c>
       <c r="J36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+J$8:J$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-J$8:J$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+J$8:J$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>22.7824082180316</v>
+        <v>22.7787034908244</v>
       </c>
       <c r="K36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+K$8:K$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-K$8:K$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+K$8:K$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>24.04035421988</v>
+        <v>24.0350244338042</v>
       </c>
       <c r="L36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+L$8:L$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-L$8:L$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+L$8:L$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>25.6693065632096</v>
+        <v>25.6634538979743</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16429,43 +16429,43 @@
       </c>
       <c r="C37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+C$16:C$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-C$16:C$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+C$16:C$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>0.487486377086616</v>
+        <v>0.486451581472894</v>
       </c>
       <c r="D37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+D$16:D$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-D$16:D$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+D$16:D$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>0.82948042970102</v>
+        <v>0.825557997683051</v>
       </c>
       <c r="E37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+E$16:E$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-E$16:E$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+E$16:E$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>1.54094999907247</v>
+        <v>1.53480104326787</v>
       </c>
       <c r="F37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+F$16:F$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-F$16:F$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+F$16:F$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>3.05063328950973</v>
+        <v>3.03981555421871</v>
       </c>
       <c r="G37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+G$16:G$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-G$16:G$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+G$16:G$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>4.88978330073879</v>
+        <v>4.88270345104098</v>
       </c>
       <c r="H37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+H$16:H$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-H$16:H$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+H$16:H$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>5.61607157815997</v>
+        <v>5.61098535739716</v>
       </c>
       <c r="I37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+I$16:I$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-I$16:I$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+I$16:I$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>6.44276116925404</v>
+        <v>6.43912634947629</v>
       </c>
       <c r="J37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+J$16:J$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-J$16:J$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+J$16:J$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>7.20733558169884</v>
+        <v>7.20474421750203</v>
       </c>
       <c r="K37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+K$16:K$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-K$16:K$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+K$16:K$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>7.6157427460883</v>
+        <v>7.6139151390096</v>
       </c>
       <c r="L37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+L$16:L$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-L$16:L$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+L$16:L$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>8.13446315166972</v>
+        <v>8.13234232751943</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16477,43 +16477,43 @@
       </c>
       <c r="C38" s="30" t="n">
         <f aca="false">C36+C37</f>
-        <v>2.15789271693585</v>
+        <v>2.15453901748161</v>
       </c>
       <c r="D38" s="30" t="n">
         <f aca="false">D36+D37</f>
-        <v>3.61411281107705</v>
+        <v>3.60070848407363</v>
       </c>
       <c r="E38" s="30" t="n">
         <f aca="false">E36+E37</f>
-        <v>6.53271116393262</v>
+        <v>6.50896139861048</v>
       </c>
       <c r="F38" s="30" t="n">
         <f aca="false">F36+F37</f>
-        <v>12.6858423493392</v>
+        <v>12.6501387035061</v>
       </c>
       <c r="G38" s="30" t="n">
         <f aca="false">G36+G37</f>
-        <v>21.1118371957454</v>
+        <v>21.0818960874764</v>
       </c>
       <c r="H38" s="30" t="n">
         <f aca="false">H36+H37</f>
-        <v>24.4890316377983</v>
+        <v>24.4762878415789</v>
       </c>
       <c r="I38" s="30" t="n">
         <f aca="false">I36+I37</f>
-        <v>27.2622989444045</v>
+        <v>27.2514871980883</v>
       </c>
       <c r="J38" s="30" t="n">
         <f aca="false">J36+J37</f>
-        <v>29.9897437997304</v>
+        <v>29.9834477083264</v>
       </c>
       <c r="K38" s="30" t="n">
         <f aca="false">K36+K37</f>
-        <v>31.6560969659683</v>
+        <v>31.6489395728138</v>
       </c>
       <c r="L38" s="30" t="n">
         <f aca="false">L36+L37</f>
-        <v>33.8037697148794</v>
+        <v>33.7957962254937</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16525,43 +16525,43 @@
       </c>
       <c r="C39" s="9" t="n">
         <f aca="false">IF(C32=0,0,C38*C33/C32*Datos!$B$7)</f>
-        <v>313.031066199305</v>
+        <v>312.535802681145</v>
       </c>
       <c r="D39" s="9" t="n">
         <f aca="false">IF(D32=0,0,D38*D33/D32*Datos!$B$7)</f>
-        <v>524.529934583881</v>
+        <v>522.545090648514</v>
       </c>
       <c r="E39" s="9" t="n">
         <f aca="false">IF(E32=0,0,E38*E33/E32*Datos!$B$7)</f>
-        <v>951.938488822088</v>
+        <v>948.468809050478</v>
       </c>
       <c r="F39" s="9" t="n">
         <f aca="false">IF(F32=0,0,F38*F33/F32*Datos!$B$7)</f>
-        <v>1854.6775368747</v>
+        <v>1849.37671491447</v>
       </c>
       <c r="G39" s="9" t="n">
         <f aca="false">IF(G32=0,0,G38*G33/G32*Datos!$B$7)</f>
-        <v>3088.6205203955</v>
+        <v>3084.32374097494</v>
       </c>
       <c r="H39" s="9" t="n">
         <f aca="false">IF(H32=0,0,H38*H33/H32*Datos!$B$7)</f>
-        <v>3583.37709510793</v>
+        <v>3581.48411452832</v>
       </c>
       <c r="I39" s="9" t="n">
         <f aca="false">IF(I32=0,0,I38*I33/I32*Datos!$B$7)</f>
-        <v>3990.7195342364</v>
+        <v>3989.15555566292</v>
       </c>
       <c r="J39" s="9" t="n">
         <f aca="false">IF(J32=0,0,J38*J33/J32*Datos!$B$7)</f>
-        <v>4390.69658534217</v>
+        <v>4389.70509515974</v>
       </c>
       <c r="K39" s="9" t="n">
         <f aca="false">IF(K32=0,0,K38*K33/K32*Datos!$B$7)</f>
-        <v>4633.78771090432</v>
+        <v>4632.74899882187</v>
       </c>
       <c r="L39" s="9" t="n">
         <f aca="false">IF(L32=0,0,L38*L33/L32*Datos!$B$7)</f>
-        <v>4948.09160017672</v>
+        <v>4946.92146010306</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16573,43 +16573,43 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$16:C$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>2.10021884302814</v>
+        <v>2.09598409382219</v>
       </c>
       <c r="D40" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$16:D$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>3.67810814111204</v>
+        <v>3.65747335242606</v>
       </c>
       <c r="E40" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$16:E$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>7.13067970183033</v>
+        <v>7.10178995618229</v>
       </c>
       <c r="F40" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$16:F$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>14.6412776364786</v>
+        <v>14.586834461094</v>
       </c>
       <c r="G40" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$16:G$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>25.1550737131839</v>
+        <v>25.102690622893</v>
       </c>
       <c r="H40" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$16:H$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>35.4512694173555</v>
+        <v>35.3906461782305</v>
       </c>
       <c r="I40" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$16:I$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>48.2528254238431</v>
+        <v>48.2038284545877</v>
       </c>
       <c r="J40" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$16:J$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>61.3485733470001</v>
+        <v>61.3035891960178</v>
       </c>
       <c r="K40" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$16:K$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>69.6614049251538</v>
+        <v>69.6247915614529</v>
       </c>
       <c r="L40" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$16:L$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>80.621800298248</v>
+        <v>80.5778041743391</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16621,43 +16621,43 @@
       </c>
       <c r="C41" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(C$8:C$15)/(Datos!$B$32*60)+C40*Datos!$B$46/60</f>
-        <v>7.88704996046954</v>
+        <v>7.87710238427916</v>
       </c>
       <c r="D41" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(D$8:D$15)/(Datos!$B$32*60)+D40*Datos!$B$46/60</f>
-        <v>12.6396644338808</v>
+        <v>12.6033779589315</v>
       </c>
       <c r="E41" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(E$8:E$15)/(Datos!$B$32*60)+E40*Datos!$B$46/60</f>
-        <v>26.1598973504854</v>
+        <v>26.1023082474067</v>
       </c>
       <c r="F41" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(F$8:F$15)/(Datos!$B$32*60)+F40*Datos!$B$46/60</f>
-        <v>56.9666034085086</v>
+        <v>56.8674592813291</v>
       </c>
       <c r="G41" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(G$8:G$15)/(Datos!$B$32*60)+G40*Datos!$B$46/60</f>
-        <v>98.9175543641127</v>
+        <v>98.8141641470955</v>
       </c>
       <c r="H41" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(H$8:H$15)/(Datos!$B$32*60)+H40*Datos!$B$46/60</f>
-        <v>138.889735274011</v>
+        <v>138.77547946423</v>
       </c>
       <c r="I41" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(I$8:I$15)/(Datos!$B$32*60)+I40*Datos!$B$46/60</f>
-        <v>191.099776246075</v>
+        <v>191.001910337094</v>
       </c>
       <c r="J41" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(J$8:J$15)/(Datos!$B$32*60)+J40*Datos!$B$46/60</f>
-        <v>243.929222823417</v>
+        <v>243.847849007893</v>
       </c>
       <c r="K41" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(K$8:K$15)/(Datos!$B$32*60)+K40*Datos!$B$46/60</f>
-        <v>275.48347933983</v>
+        <v>275.409920443349</v>
       </c>
       <c r="L41" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(L$8:L$15)/(Datos!$B$32*60)+L40*Datos!$B$46/60</f>
-        <v>318.33495142202</v>
+        <v>318.251396835488</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16669,43 +16669,43 @@
       </c>
       <c r="C42" s="9" t="n">
         <f aca="false">C41*Datos!$B$15</f>
-        <v>49.5411157615555</v>
+        <v>49.4786318130495</v>
       </c>
       <c r="D42" s="9" t="n">
         <f aca="false">D41*Datos!$B$15</f>
-        <v>79.393826848388</v>
+        <v>79.1658997444581</v>
       </c>
       <c r="E42" s="9" t="n">
         <f aca="false">E41*Datos!$B$15</f>
-        <v>164.318789591343</v>
+        <v>163.957053779281</v>
       </c>
       <c r="F42" s="9" t="n">
         <f aca="false">F41*Datos!$B$15</f>
-        <v>357.82568997896</v>
+        <v>357.202933599034</v>
       </c>
       <c r="G42" s="9" t="n">
         <f aca="false">G41*Datos!$B$15</f>
-        <v>621.333202675786</v>
+        <v>620.683775230095</v>
       </c>
       <c r="H42" s="9" t="n">
         <f aca="false">H41*Datos!$B$15</f>
-        <v>872.411419705519</v>
+        <v>871.693741951837</v>
       </c>
       <c r="I42" s="9" t="n">
         <f aca="false">I41*Datos!$B$15</f>
-        <v>1200.35960016291</v>
+        <v>1199.74487268557</v>
       </c>
       <c r="J42" s="9" t="n">
         <f aca="false">J41*Datos!$B$15</f>
-        <v>1532.19846787958</v>
+        <v>1531.68733258375</v>
       </c>
       <c r="K42" s="9" t="n">
         <f aca="false">K41*Datos!$B$15</f>
-        <v>1730.40097486058</v>
+        <v>1729.93892760285</v>
       </c>
       <c r="L42" s="9" t="n">
         <f aca="false">L41*Datos!$B$15</f>
-        <v>1999.56495247161</v>
+        <v>1999.04011904662</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16765,43 +16765,43 @@
       </c>
       <c r="C44" s="11" t="n">
         <f aca="false">C33+C35+C39+C42+C43</f>
-        <v>20835.7682323212</v>
+        <v>20810.4670448677</v>
       </c>
       <c r="D44" s="11" t="n">
         <f aca="false">D33+D35+D39+D42+D43</f>
-        <v>31645.9585172768</v>
+        <v>31544.4620786668</v>
       </c>
       <c r="E44" s="11" t="n">
         <f aca="false">E33+E35+E39+E42+E43</f>
-        <v>53524.1636404334</v>
+        <v>53347.1343697182</v>
       </c>
       <c r="F44" s="11" t="n">
         <f aca="false">F33+F35+F39+F42+F43</f>
-        <v>99749.9941250999</v>
+        <v>99478.4666883508</v>
       </c>
       <c r="G44" s="11" t="n">
         <f aca="false">G33+G35+G39+G42+G43</f>
-        <v>166585.783980611</v>
+        <v>166238.158526937</v>
       </c>
       <c r="H44" s="11" t="n">
         <f aca="false">H33+H35+H39+H42+H43</f>
-        <v>230582.401446091</v>
+        <v>230252.852881695</v>
       </c>
       <c r="I44" s="11" t="n">
         <f aca="false">I33+I35+I39+I42+I43</f>
-        <v>310388.974133526</v>
+        <v>310089.4417639</v>
       </c>
       <c r="J44" s="11" t="n">
         <f aca="false">J33+J35+J39+J42+J43</f>
-        <v>391825.687600363</v>
+        <v>391638.70108906</v>
       </c>
       <c r="K44" s="11" t="n">
         <f aca="false">K33+K35+K39+K42+K43</f>
-        <v>443659.918066578</v>
+        <v>443436.432515209</v>
       </c>
       <c r="L44" s="11" t="n">
         <f aca="false">L33+L35+L39+L42+L43</f>
-        <v>511025.237281572</v>
+        <v>510774.458819745</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16834,27 +16834,27 @@
       </c>
       <c r="G47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(G15/Datos!$B$25,G14/Datos!$B$26),0)</f>
-        <v>40.75349389</v>
+        <v>40.4201605566667</v>
       </c>
       <c r="H47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(H15/Datos!$B$25,H14/Datos!$B$26),0)</f>
-        <v>55.8428505666667</v>
+        <v>56.1495172333333</v>
       </c>
       <c r="I47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(I15/Datos!$B$25,I14/Datos!$B$26),0)</f>
-        <v>74.8269173</v>
+        <v>74.4935839666667</v>
       </c>
       <c r="J47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(J15/Datos!$B$25,J14/Datos!$B$26),0)</f>
-        <v>93.8824539666667</v>
+        <v>94.1891206333334</v>
       </c>
       <c r="K47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(K15/Datos!$B$25,K14/Datos!$B$26),0)</f>
-        <v>107.9403865</v>
+        <v>107.607053166667</v>
       </c>
       <c r="L47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(L15/Datos!$B$25,L14/Datos!$B$26),0)</f>
-        <v>124.709952</v>
+        <v>124.349952</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16930,27 +16930,27 @@
       </c>
       <c r="G49" s="30" t="n">
         <f aca="false">(G15-Datos!$B$25*G47)/Corte!$I$13</f>
-        <v>13.2956090766667</v>
+        <v>13.4067201877778</v>
       </c>
       <c r="H49" s="30" t="n">
         <f aca="false">(H15-Datos!$B$25*H47)/Corte!$I$13</f>
-        <v>18.6720613011111</v>
+        <v>18.2365057455556</v>
       </c>
       <c r="I49" s="30" t="n">
         <f aca="false">(I15-Datos!$B$25*I47)/Corte!$I$13</f>
-        <v>24.7156391033333</v>
+        <v>24.8000835477778</v>
       </c>
       <c r="J49" s="30" t="n">
         <f aca="false">(J15-Datos!$B$25*J47)/Corte!$I$13</f>
-        <v>30.8763735444444</v>
+        <v>31.0808179888889</v>
       </c>
       <c r="K49" s="30" t="n">
         <f aca="false">(K15-Datos!$B$25*K47)/Corte!$I$13</f>
-        <v>35.3401288333333</v>
+        <v>35.4512399444444</v>
       </c>
       <c r="L49" s="30" t="n">
         <f aca="false">(L15-Datos!$B$25*L47)/Corte!$I$13</f>
-        <v>40.9122062</v>
+        <v>41.0322062</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16974,31 +16974,31 @@
       </c>
       <c r="F50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(F12/Nesting!$E$26,F13/Nesting!$F$26),0)</f>
-        <v>25.66164215</v>
+        <v>25.4949754833333</v>
       </c>
       <c r="G50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(G12/Nesting!$E$26,G13/Nesting!$F$26),0)</f>
-        <v>41.89266725</v>
+        <v>41.8793339166667</v>
       </c>
       <c r="H50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(H12/Nesting!$E$26,H13/Nesting!$F$26),0)</f>
-        <v>58.2624137833333</v>
+        <v>58.24908045</v>
       </c>
       <c r="I50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(I12/Nesting!$E$26,I13/Nesting!$F$26),0)</f>
-        <v>77.5780388666667</v>
+        <v>77.5647055333333</v>
       </c>
       <c r="J50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(J12/Nesting!$E$26,J13/Nesting!$F$26),0)</f>
-        <v>97.95477845</v>
+        <v>97.77477845</v>
       </c>
       <c r="K50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(K12/Nesting!$E$26,K13/Nesting!$F$26),0)</f>
-        <v>111.944569266667</v>
+        <v>112.084569266667</v>
       </c>
       <c r="L50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(L12/Nesting!$E$26,L13/Nesting!$F$26),0)</f>
-        <v>129.551755533333</v>
+        <v>129.5384222</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17018,35 +17018,35 @@
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(E13-E50*Nesting!$F$26)/Nesting!$F$28,E13/Corte!$I$11)</f>
-        <v>26.019086335</v>
+        <v>25.8524196683333</v>
       </c>
       <c r="F51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(F13-F50*Nesting!$F$26)/Nesting!$F$28,F13/Corte!$I$11)</f>
-        <v>43.256791675</v>
+        <v>43.4934583416667</v>
       </c>
       <c r="G51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(G13-G50*Nesting!$F$26)/Nesting!$F$28,G13/Corte!$I$11)</f>
-        <v>71.3882009916667</v>
+        <v>71.061534325</v>
       </c>
       <c r="H51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(H13-H50*Nesting!$F$26)/Nesting!$F$28,H13/Corte!$I$11)</f>
-        <v>99.2247701083333</v>
+        <v>99.2047701083333</v>
       </c>
       <c r="I51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(I13-I50*Nesting!$F$26)/Nesting!$F$28,I13/Corte!$I$11)</f>
-        <v>131.935999383333</v>
+        <v>131.915999383333</v>
       </c>
       <c r="J51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(J13-J50*Nesting!$F$26)/Nesting!$F$28,J13/Corte!$I$11)</f>
-        <v>166.373790041667</v>
+        <v>166.270456708333</v>
       </c>
       <c r="K51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(K13-K50*Nesting!$F$26)/Nesting!$F$28,K13/Corte!$I$11)</f>
-        <v>190.63776775</v>
+        <v>190.52776775</v>
       </c>
       <c r="L51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(L13-L50*Nesting!$F$26)/Nesting!$F$28,L13/Corte!$I$11)</f>
-        <v>220.129984416667</v>
+        <v>220.26331775</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17106,43 +17106,43 @@
       </c>
       <c r="C53" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9)+C50+C51+C52+C48+C49+C47</f>
-        <v>325.132551826815</v>
+        <v>324.558477752741</v>
       </c>
       <c r="D53" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9)+D50+D51+D52+D48+D49+D47</f>
-        <v>539.956167176389</v>
+        <v>537.941722731944</v>
       </c>
       <c r="E53" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9)+E50+E51+E52+E48+E49+E47</f>
-        <v>1016.53492766648</v>
+        <v>1013.12226099981</v>
       </c>
       <c r="F53" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9)+F50+F51+F52+F48+F49+F47</f>
-        <v>2045.16457456389</v>
+        <v>2039.62664863796</v>
       </c>
       <c r="G53" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9)+G50+G51+G52+G48+G49+G47</f>
-        <v>3506.30088381648</v>
+        <v>3500.14747640907</v>
       </c>
       <c r="H53" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9)+H50+H51+H52+H48+H49+H47</f>
-        <v>4910.01846739278</v>
+        <v>4903.40320813352</v>
       </c>
       <c r="I53" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9)+I50+I51+I52+I48+I49+I47</f>
-        <v>6694.48763543111</v>
+        <v>6688.77593172741</v>
       </c>
       <c r="J53" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9)+J50+J51+J52+J48+J49+J47</f>
-        <v>8508.92997633982</v>
+        <v>8504.5448652287</v>
       </c>
       <c r="K53" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9)+K50+K51+K52+K48+K49+K47</f>
-        <v>9636.76745463519</v>
+        <v>9632.44989907963</v>
       </c>
       <c r="L53" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9)+L50+L51+L52+L48+L49+L47</f>
-        <v>11122.9840679352</v>
+        <v>11118.1526605278</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17154,43 +17154,43 @@
       </c>
       <c r="C54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(C50+C51+C52)*Corte!$W$10+C48*Corte!$W$12+C49*Corte!$W$13+C47*Corte!$W$14)/1000</f>
-        <v>10.7346590826616</v>
+        <v>10.7198978774764</v>
       </c>
       <c r="D54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(D50+D51+D52)*Corte!$W$10+D48*Corte!$W$12+D49*Corte!$W$13+D47*Corte!$W$14)/1000</f>
-        <v>17.8575493864895</v>
+        <v>17.796904810445</v>
       </c>
       <c r="E54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(E50+E51+E52)*Corte!$W$10+E48*Corte!$W$12+E49*Corte!$W$13+E47*Corte!$W$14)/1000</f>
-        <v>31.9385465918956</v>
+        <v>31.8269037162956</v>
       </c>
       <c r="F54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(F50+F51+F52)*Corte!$W$10+F48*Corte!$W$12+F49*Corte!$W$13+F47*Corte!$W$14)/1000</f>
-        <v>61.5325793822586</v>
+        <v>61.3745277695772</v>
       </c>
       <c r="G54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(G50+G51+G52)*Corte!$W$10+G48*Corte!$W$12+G49*Corte!$W$13+G47*Corte!$W$14)/1000</f>
-        <v>104.684029434547</v>
+        <v>104.446636807451</v>
       </c>
       <c r="H54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(H50+H51+H52)*Corte!$W$10+H48*Corte!$W$12+H49*Corte!$W$13+H47*Corte!$W$14)/1000</f>
-        <v>146.473687058271</v>
+        <v>146.260625894478</v>
       </c>
       <c r="I54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(I50+I51+I52)*Corte!$W$10+I48*Corte!$W$12+I49*Corte!$W$13+I47*Corte!$W$14)/1000</f>
-        <v>198.568596351391</v>
+        <v>198.368940176088</v>
       </c>
       <c r="J54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(J50+J51+J52)*Corte!$W$10+J48*Corte!$W$12+J49*Corte!$W$13+J47*Corte!$W$14)/1000</f>
-        <v>251.76963364092</v>
+        <v>251.686910951631</v>
       </c>
       <c r="K54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(K50+K51+K52)*Corte!$W$10+K48*Corte!$W$12+K49*Corte!$W$13+K47*Corte!$W$14)/1000</f>
-        <v>285.919416329318</v>
+        <v>285.769201954118</v>
       </c>
       <c r="L54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(L50+L51+L52)*Corte!$W$10+L48*Corte!$W$12+L49*Corte!$W$13+L47*Corte!$W$14)/1000</f>
-        <v>330.093966123894</v>
+        <v>329.929950368709</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17202,43 +17202,43 @@
       </c>
       <c r="C55" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(C50+C51+C52)*Corte!$X$10+C48*Corte!$X$12+C49*Corte!$X$13+C47*Corte!$X$14</f>
-        <v>13535.3469700972</v>
+        <v>13515.8319046806</v>
       </c>
       <c r="D55" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(D50+D51+D52)*Corte!$X$10+D48*Corte!$X$12+D49*Corte!$X$13+D47*Corte!$X$14</f>
-        <v>22538.5021233628</v>
+        <v>22458.8709932631</v>
       </c>
       <c r="E55" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(E50+E51+E52)*Corte!$X$10+E48*Corte!$X$12+E49*Corte!$X$13+E47*Corte!$X$14</f>
-        <v>40644.1888913575</v>
+        <v>40501.2676034959</v>
       </c>
       <c r="F55" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(F50+F51+F52)*Corte!$X$10+F48*Corte!$X$12+F49*Corte!$X$13+F47*Corte!$X$14</f>
-        <v>78841.9346839642</v>
+        <v>78632.5222632994</v>
       </c>
       <c r="G55" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(G50+G51+G52)*Corte!$X$10+G48*Corte!$X$12+G49*Corte!$X$13+G47*Corte!$X$14</f>
-        <v>134313.346075938</v>
+        <v>134017.689840092</v>
       </c>
       <c r="H55" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(H50+H51+H52)*Corte!$X$10+H48*Corte!$X$12+H49*Corte!$X$13+H47*Corte!$X$14</f>
-        <v>187990.016997884</v>
+        <v>187715.460898824</v>
       </c>
       <c r="I55" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(I50+I51+I52)*Corte!$X$10+I48*Corte!$X$12+I49*Corte!$X$13+I47*Corte!$X$14</f>
-        <v>255067.719646977</v>
+        <v>254815.134497008</v>
       </c>
       <c r="J55" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(J50+J51+J52)*Corte!$X$10+J48*Corte!$X$12+J49*Corte!$X$13+J47*Corte!$X$14</f>
-        <v>323525.54237717</v>
+        <v>323404.44807697</v>
       </c>
       <c r="K55" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(K50+K51+K52)*Corte!$X$10+K48*Corte!$X$12+K49*Corte!$X$13+K47*Corte!$X$14</f>
-        <v>367244.895462997</v>
+        <v>367054.797748087</v>
       </c>
       <c r="L55" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(L50+L51+L52)*Corte!$X$10+L48*Corte!$X$12+L49*Corte!$X$13+L47*Corte!$X$14</f>
-        <v>423958.458946489</v>
+        <v>423748.887955503</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17250,43 +17250,43 @@
       </c>
       <c r="C56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+C50*Nesting!$G$26+C51*Nesting!$G$28+C52*Nesting!$G$29+C48*Corte!$P$12+C49*Corte!$P$13+C47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>1.50750348439444</v>
+        <v>1.50528126217222</v>
       </c>
       <c r="D56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+D50*Nesting!$G$26+D51*Nesting!$G$28+D52*Nesting!$G$29+D48*Corte!$P$12+D49*Corte!$P$13+D47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>2.45292135147153</v>
+        <v>2.44524357369375</v>
       </c>
       <c r="E56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+E50*Nesting!$G$26+E51*Nesting!$G$28+E52*Nesting!$G$29+E48*Corte!$P$12+E49*Corte!$P$13+E47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>4.91714949059028</v>
+        <v>4.90456615725694</v>
       </c>
       <c r="F56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+F50*Nesting!$G$26+F51*Nesting!$G$28+F52*Nesting!$G$29+F48*Corte!$P$12+F49*Corte!$P$13+F47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>10.4475757949931</v>
+        <v>10.4266174616597</v>
       </c>
       <c r="G56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+G50*Nesting!$G$26+G51*Nesting!$G$28+G52*Nesting!$G$29+G48*Corte!$P$12+G49*Corte!$P$13+G47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>18.0638174073458</v>
+        <v>18.0408340740125</v>
       </c>
       <c r="H56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+H50*Nesting!$G$26+H51*Nesting!$G$28+H52*Nesting!$G$29+H48*Corte!$P$12+H49*Corte!$P$13+H47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>25.3435273012597</v>
+        <v>25.3189661901486</v>
       </c>
       <c r="I56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+I50*Nesting!$G$26+I51*Nesting!$G$28+I52*Nesting!$G$29+I48*Corte!$P$12+I49*Corte!$P$13+I47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>34.7684549913278</v>
+        <v>34.7467605468833</v>
       </c>
       <c r="J56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+J50*Nesting!$G$26+J51*Nesting!$G$28+J52*Nesting!$G$29+J48*Corte!$P$12+J49*Corte!$P$13+J47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>44.323082995257</v>
+        <v>44.3064857730347</v>
       </c>
       <c r="K56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+K50*Nesting!$G$26+K51*Nesting!$G$28+K52*Nesting!$G$29+K48*Corte!$P$12+K49*Corte!$P$13+K47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>50.1158803782361</v>
+        <v>50.0993998226806</v>
       </c>
       <c r="L56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+L50*Nesting!$G$26+L51*Nesting!$G$28+L52*Nesting!$G$29+L48*Corte!$P$12+L49*Corte!$P$13+L47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>57.9085815723194</v>
+        <v>57.8902704612083</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17298,43 +17298,43 @@
       </c>
       <c r="C57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+C50*Nesting!$H$26+C51*Nesting!$H$28+C52*Nesting!$H$29+C48*Corte!$R$12+C49*Corte!$R$13+C47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>0.975253696321991</v>
+        <v>0.973818511136806</v>
       </c>
       <c r="D57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+D50*Nesting!$H$26+D51*Nesting!$H$28+D52*Nesting!$H$29+D48*Corte!$R$12+D49*Corte!$R$13+D47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>1.58711806958495</v>
+        <v>1.58195695847384</v>
       </c>
       <c r="E57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+E50*Nesting!$H$26+E51*Nesting!$H$28+E52*Nesting!$H$29+E48*Corte!$R$12+E49*Corte!$R$13+E47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>3.10552873947176</v>
+        <v>3.09686207280509</v>
       </c>
       <c r="F57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+F50*Nesting!$H$26+F51*Nesting!$H$28+F52*Nesting!$H$29+F48*Corte!$R$12+F49*Corte!$R$13+F47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>6.4642083474125</v>
+        <v>6.44963519926435</v>
       </c>
       <c r="G57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+G50*Nesting!$H$26+G51*Nesting!$H$28+G52*Nesting!$H$29+G48*Corte!$R$12+G49*Corte!$R$13+G47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>11.1481004629875</v>
+        <v>11.1327560185431</v>
       </c>
       <c r="H57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+H50*Nesting!$H$26+H51*Nesting!$H$28+H52*Nesting!$H$29+H48*Corte!$R$12+H49*Corte!$R$13+H47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>15.625779601675</v>
+        <v>15.609016638712</v>
       </c>
       <c r="I57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+I50*Nesting!$H$26+I51*Nesting!$H$28+I52*Nesting!$H$29+I48*Corte!$R$12+I49*Corte!$R$13+I47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>21.3992481359162</v>
+        <v>21.385087950731</v>
       </c>
       <c r="J57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+J50*Nesting!$H$26+J51*Nesting!$H$28+J52*Nesting!$H$29+J48*Corte!$R$12+J49*Corte!$R$13+J47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>27.2541626004051</v>
+        <v>27.2418116744792</v>
       </c>
       <c r="K57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+K50*Nesting!$H$26+K51*Nesting!$H$28+K52*Nesting!$H$29+K48*Corte!$R$12+K49*Corte!$R$13+K47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>30.8136743600833</v>
+        <v>30.8034095452685</v>
       </c>
       <c r="L57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+L50*Nesting!$H$26+L51*Nesting!$H$28+L52*Nesting!$H$29+L48*Corte!$R$12+L49*Corte!$R$13+L47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>35.5726394868056</v>
+        <v>35.5606459682871</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17346,43 +17346,43 @@
       </c>
       <c r="C58" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11,Corte!$E$55:$E$58)/1000</f>
-        <v>3.32791906718684</v>
+        <v>3.32074873524904</v>
       </c>
       <c r="D58" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11,Corte!$E$55:$E$58)/1000</f>
-        <v>5.6739256879675</v>
+        <v>5.6467936531952</v>
       </c>
       <c r="E58" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11,Corte!$E$55:$E$58)/1000</f>
-        <v>10.4947804871295</v>
+        <v>10.452198478162</v>
       </c>
       <c r="F58" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11,Corte!$E$55:$E$58)/1000</f>
-        <v>20.6895545270799</v>
+        <v>20.614687829746</v>
       </c>
       <c r="G58" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11,Corte!$E$55:$E$58)/1000</f>
-        <v>35.3551267826173</v>
+        <v>35.281357011278</v>
       </c>
       <c r="H58" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11,Corte!$E$55:$E$58)/1000</f>
-        <v>49.5449149040569</v>
+        <v>49.459517231543</v>
       </c>
       <c r="I58" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11,Corte!$E$55:$E$58)/1000</f>
-        <v>67.3144976299033</v>
+        <v>67.2434860643128</v>
       </c>
       <c r="J58" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11,Corte!$E$55:$E$58)/1000</f>
-        <v>85.4290395503951</v>
+        <v>85.3674389561632</v>
       </c>
       <c r="K58" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11,Corte!$E$55:$E$58)/1000</f>
-        <v>96.8696367118935</v>
+        <v>96.8158598211794</v>
       </c>
       <c r="L58" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11,Corte!$E$55:$E$58)/1000</f>
-        <v>111.791802896779</v>
+        <v>111.729405071367</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17394,43 +17394,43 @@
       </c>
       <c r="C59" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11,Corte!$F$55:$F$58)</f>
-        <v>4400.57884766033</v>
+        <v>4391.09787631857</v>
       </c>
       <c r="D59" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11,Corte!$F$55:$F$58)</f>
-        <v>7500.22136157293</v>
+        <v>7464.40269422972</v>
       </c>
       <c r="E59" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11,Corte!$F$55:$F$58)</f>
-        <v>13865.9569613516</v>
+        <v>13809.6816558783</v>
       </c>
       <c r="F59" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11,Corte!$F$55:$F$58)</f>
-        <v>27322.7968252111</v>
+        <v>27223.9123848681</v>
       </c>
       <c r="G59" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11,Corte!$F$55:$F$58)</f>
-        <v>46688.015088239</v>
+        <v>46590.5748387755</v>
       </c>
       <c r="H59" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11,Corte!$F$55:$F$58)</f>
-        <v>65422.2436878575</v>
+        <v>65309.4344869033</v>
       </c>
       <c r="I59" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11,Corte!$F$55:$F$58)</f>
-        <v>88884.7231854953</v>
+        <v>88790.907881232</v>
       </c>
       <c r="J59" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11,Corte!$F$55:$F$58)</f>
-        <v>112801.440719698</v>
+        <v>112720.083049376</v>
       </c>
       <c r="K59" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11,Corte!$F$55:$F$58)</f>
-        <v>127904.608088476</v>
+        <v>127833.554349814</v>
       </c>
       <c r="L59" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11,Corte!$F$55:$F$58)</f>
-        <v>147601.429814246</v>
+        <v>147518.992613239</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17442,43 +17442,43 @@
       </c>
       <c r="C60" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11,Corte!$G$55:$G$58)</f>
-        <v>1626.3096415681</v>
+        <v>1623.57392728239</v>
       </c>
       <c r="D60" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11,Corte!$G$55:$G$58)</f>
-        <v>2673.22762035206</v>
+        <v>2663.52423939968</v>
       </c>
       <c r="E60" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11,Corte!$G$55:$G$58)</f>
-        <v>5287.58684658297</v>
+        <v>5272.18898944011</v>
       </c>
       <c r="F60" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11,Corte!$G$55:$G$58)</f>
-        <v>11090.2998409012</v>
+        <v>11063.5043170917</v>
       </c>
       <c r="G60" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11,Corte!$G$55:$G$58)</f>
-        <v>19143.1956081008</v>
+        <v>19116.4114652437</v>
       </c>
       <c r="H60" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11,Corte!$G$55:$G$58)</f>
-        <v>26852.3932834886</v>
+        <v>26821.5685692028</v>
       </c>
       <c r="I60" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11,Corte!$G$55:$G$58)</f>
-        <v>36782.1896272995</v>
+        <v>36756.2200558709</v>
       </c>
       <c r="J60" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11,Corte!$G$55:$G$58)</f>
-        <v>46853.9236937669</v>
+        <v>46831.8558842431</v>
       </c>
       <c r="K60" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11,Corte!$G$55:$G$58)</f>
-        <v>52988.8369812853</v>
+        <v>52969.1307908091</v>
       </c>
       <c r="L60" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11,Corte!$G$55:$G$58)</f>
-        <v>61200.962868131</v>
+        <v>61178.5254871786</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17490,43 +17490,43 @@
       </c>
       <c r="C61" s="30" t="n">
         <f aca="false">C54+C58</f>
-        <v>14.0625781498485</v>
+        <v>14.0406466127255</v>
       </c>
       <c r="D61" s="30" t="n">
         <f aca="false">D54+D58</f>
-        <v>23.531475074457</v>
+        <v>23.4436984636402</v>
       </c>
       <c r="E61" s="30" t="n">
         <f aca="false">E54+E58</f>
-        <v>42.4333270790252</v>
+        <v>42.2791021944577</v>
       </c>
       <c r="F61" s="30" t="n">
         <f aca="false">F54+F58</f>
-        <v>82.2221339093386</v>
+        <v>81.9892155993232</v>
       </c>
       <c r="G61" s="30" t="n">
         <f aca="false">G54+G58</f>
-        <v>140.039156217164</v>
+        <v>139.727993818729</v>
       </c>
       <c r="H61" s="30" t="n">
         <f aca="false">H54+H58</f>
-        <v>196.018601962328</v>
+        <v>195.720143126021</v>
       </c>
       <c r="I61" s="30" t="n">
         <f aca="false">I54+I58</f>
-        <v>265.883093981295</v>
+        <v>265.6124262404</v>
       </c>
       <c r="J61" s="30" t="n">
         <f aca="false">J54+J58</f>
-        <v>337.198673191315</v>
+        <v>337.054349907794</v>
       </c>
       <c r="K61" s="30" t="n">
         <f aca="false">K54+K58</f>
-        <v>382.789053041211</v>
+        <v>382.585061775297</v>
       </c>
       <c r="L61" s="30" t="n">
         <f aca="false">L54+L58</f>
-        <v>441.885769020673</v>
+        <v>441.659355440076</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17538,43 +17538,43 @@
       </c>
       <c r="C62" s="9" t="n">
         <f aca="false">C55+C59</f>
-        <v>17935.9258177575</v>
+        <v>17906.9297809991</v>
       </c>
       <c r="D62" s="9" t="n">
         <f aca="false">D55+D59</f>
-        <v>30038.7234849357</v>
+        <v>29923.2736874929</v>
       </c>
       <c r="E62" s="9" t="n">
         <f aca="false">E55+E59</f>
-        <v>54510.1458527092</v>
+        <v>54310.9492593743</v>
       </c>
       <c r="F62" s="9" t="n">
         <f aca="false">F55+F59</f>
-        <v>106164.731509175</v>
+        <v>105856.434648167</v>
       </c>
       <c r="G62" s="9" t="n">
         <f aca="false">G55+G59</f>
-        <v>181001.361164177</v>
+        <v>180608.264678868</v>
       </c>
       <c r="H62" s="9" t="n">
         <f aca="false">H55+H59</f>
-        <v>253412.260685742</v>
+        <v>253024.895385727</v>
       </c>
       <c r="I62" s="9" t="n">
         <f aca="false">I55+I59</f>
-        <v>343952.442832472</v>
+        <v>343606.04237824</v>
       </c>
       <c r="J62" s="9" t="n">
         <f aca="false">J55+J59</f>
-        <v>436326.983096869</v>
+        <v>436124.531126346</v>
       </c>
       <c r="K62" s="9" t="n">
         <f aca="false">K55+K59</f>
-        <v>495149.503551473</v>
+        <v>494888.352097901</v>
       </c>
       <c r="L62" s="9" t="n">
         <f aca="false">L55+L59</f>
-        <v>571559.888760734</v>
+        <v>571267.880568742</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17586,43 +17586,43 @@
       </c>
       <c r="C63" s="30" t="n">
         <f aca="false">C61-C25</f>
-        <v>2.09910508160832</v>
+        <v>2.09566914052775</v>
       </c>
       <c r="D63" s="30" t="n">
         <f aca="false">D61-D25</f>
-        <v>3.51318761227097</v>
+        <v>3.49979612462422</v>
       </c>
       <c r="E63" s="30" t="n">
         <f aca="false">E61-E25</f>
-        <v>6.25442138794946</v>
+        <v>6.23073806421711</v>
       </c>
       <c r="F63" s="30" t="n">
         <f aca="false">F61-F25</f>
-        <v>11.9701679145401</v>
+        <v>11.9371354129353</v>
       </c>
       <c r="G63" s="30" t="n">
         <f aca="false">G61-G25</f>
-        <v>20.3544677544446</v>
+        <v>20.3061274085911</v>
       </c>
       <c r="H63" s="30" t="n">
         <f aca="false">H61-H25</f>
-        <v>28.4718626747435</v>
+        <v>28.4203365849152</v>
       </c>
       <c r="I63" s="30" t="n">
         <f aca="false">I61-I25</f>
-        <v>38.5588674153904</v>
+        <v>38.515996907213</v>
       </c>
       <c r="J63" s="30" t="n">
         <f aca="false">J61-J25</f>
-        <v>48.8518564277595</v>
+        <v>48.8397436281654</v>
       </c>
       <c r="K63" s="30" t="n">
         <f aca="false">K61-K25</f>
-        <v>55.4968169080593</v>
+        <v>55.4622750875099</v>
       </c>
       <c r="L63" s="30" t="n">
         <f aca="false">L61-L25</f>
-        <v>64.0553287228897</v>
+        <v>64.0198063794565</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17634,43 +17634,43 @@
       </c>
       <c r="C64" s="9" t="n">
         <f aca="false">-C63*Datos!$B$9</f>
-        <v>-524.77627040208</v>
+        <v>-523.917285131936</v>
       </c>
       <c r="D64" s="9" t="n">
         <f aca="false">-D63*Datos!$B$9</f>
-        <v>-878.296903067742</v>
+        <v>-874.949031156055</v>
       </c>
       <c r="E64" s="9" t="n">
         <f aca="false">-E63*Datos!$B$9</f>
-        <v>-1563.60534698736</v>
+        <v>-1557.68451605428</v>
       </c>
       <c r="F64" s="9" t="n">
         <f aca="false">-F63*Datos!$B$9</f>
-        <v>-2992.54197863502</v>
+        <v>-2984.28385323382</v>
       </c>
       <c r="G64" s="9" t="n">
         <f aca="false">-G63*Datos!$B$9</f>
-        <v>-5088.61693861115</v>
+        <v>-5076.53185214776</v>
       </c>
       <c r="H64" s="9" t="n">
         <f aca="false">-H63*Datos!$B$9</f>
-        <v>-7117.96566868587</v>
+        <v>-7105.0841462288</v>
       </c>
       <c r="I64" s="9" t="n">
         <f aca="false">-I63*Datos!$B$9</f>
-        <v>-9639.71685384761</v>
+        <v>-9628.99922680325</v>
       </c>
       <c r="J64" s="9" t="n">
         <f aca="false">-J63*Datos!$B$9</f>
-        <v>-12212.9641069399</v>
+        <v>-12209.9359070414</v>
       </c>
       <c r="K64" s="9" t="n">
         <f aca="false">-K63*Datos!$B$9</f>
-        <v>-13874.2042270148</v>
+        <v>-13865.5687718775</v>
       </c>
       <c r="L64" s="9" t="n">
         <f aca="false">-L63*Datos!$B$9</f>
-        <v>-16013.8321807224</v>
+        <v>-16004.9515948641</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17682,43 +17682,43 @@
       </c>
       <c r="C65" s="30" t="n">
         <f aca="false">C61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>1.12680914662247</v>
+        <v>1.12505181191711</v>
       </c>
       <c r="D65" s="30" t="n">
         <f aca="false">D61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>1.88553486173533</v>
+        <v>1.87850147945835</v>
       </c>
       <c r="E65" s="30" t="n">
         <f aca="false">E61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>3.40010633646035</v>
+        <v>3.38774857327385</v>
       </c>
       <c r="F65" s="30" t="n">
         <f aca="false">F61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>6.58831201196623</v>
+        <v>6.5696486858432</v>
       </c>
       <c r="G65" s="30" t="n">
         <f aca="false">G61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>11.2210862353497</v>
+        <v>11.1961533508597</v>
       </c>
       <c r="H65" s="30" t="n">
         <f aca="false">H61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>15.7066187469814</v>
+        <v>15.6827037761235</v>
       </c>
       <c r="I65" s="30" t="n">
         <f aca="false">I61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>21.304735094655</v>
+        <v>21.283046974391</v>
       </c>
       <c r="J65" s="30" t="n">
         <f aca="false">J61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>27.0191244544323</v>
+        <v>27.0075600887656</v>
       </c>
       <c r="K65" s="30" t="n">
         <f aca="false">K61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>30.6721997629176</v>
+        <v>30.655854308918</v>
       </c>
       <c r="L65" s="30" t="n">
         <f aca="false">L61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>35.4075135433232</v>
+        <v>35.3893714294933</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17730,43 +17730,43 @@
       </c>
       <c r="C66" s="9" t="n">
         <f aca="false">IF(C61=0,0,C65*C62/C61*Datos!$B$7)</f>
-        <v>172.460825170746</v>
+        <v>172.182017124992</v>
       </c>
       <c r="D66" s="9" t="n">
         <f aca="false">IF(D61=0,0,D65*D62/D61*Datos!$B$7)</f>
-        <v>288.833879662843</v>
+        <v>287.723785456662</v>
       </c>
       <c r="E66" s="9" t="n">
         <f aca="false">IF(E61=0,0,E65*E62/E61*Datos!$B$7)</f>
-        <v>524.136017814511</v>
+        <v>522.220665955522</v>
       </c>
       <c r="F66" s="9" t="n">
         <f aca="false">IF(F61=0,0,F65*F62/F61*Datos!$B$7)</f>
-        <v>1020.81472604976</v>
+        <v>1017.85033315546</v>
       </c>
       <c r="G66" s="9" t="n">
         <f aca="false">IF(G61=0,0,G65*G62/G61*Datos!$B$7)</f>
-        <v>1740.3977035017</v>
+        <v>1736.6179296045</v>
       </c>
       <c r="H66" s="9" t="n">
         <f aca="false">IF(H61=0,0,H65*H62/H61*Datos!$B$7)</f>
-        <v>2436.65635274752</v>
+        <v>2432.93168640122</v>
       </c>
       <c r="I66" s="9" t="n">
         <f aca="false">IF(I61=0,0,I65*I62/I61*Datos!$B$7)</f>
-        <v>3307.23502723531</v>
+        <v>3303.90425363693</v>
       </c>
       <c r="J66" s="9" t="n">
         <f aca="false">IF(J61=0,0,J65*J62/J61*Datos!$B$7)</f>
-        <v>4195.45176054681</v>
+        <v>4193.50510698409</v>
       </c>
       <c r="K66" s="9" t="n">
         <f aca="false">IF(K61=0,0,K65*K62/K61*Datos!$B$7)</f>
-        <v>4761.05291876417</v>
+        <v>4758.5418470952</v>
       </c>
       <c r="L66" s="9" t="n">
         <f aca="false">IF(L61=0,0,L65*L62/L61*Datos!$B$7)</f>
-        <v>5495.76816116091</v>
+        <v>5492.96039008406</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17778,43 +17778,43 @@
       </c>
       <c r="C67" s="9" t="n">
         <f aca="false">C56+C57+C60/Datos!$B$32/60+C60*Datos!$B$45/3600</f>
-        <v>10.614305388557</v>
+        <v>10.596969409721</v>
       </c>
       <c r="D67" s="9" t="n">
         <f aca="false">D56+D57+D60/Datos!$B$32/60+D60*Datos!$B$45/3600</f>
-        <v>17.4061775228168</v>
+        <v>17.344821729166</v>
       </c>
       <c r="E67" s="9" t="n">
         <f aca="false">E56+E57+E60/Datos!$B$32/60+E60*Datos!$B$45/3600</f>
-        <v>34.4606124629769</v>
+        <v>34.3623731772626</v>
       </c>
       <c r="F67" s="9" t="n">
         <f aca="false">F56+F57+F60/Datos!$B$32/60+F60*Datos!$B$45/3600</f>
-        <v>72.3632833469115</v>
+        <v>72.1937742463824</v>
       </c>
       <c r="G67" s="9" t="n">
         <f aca="false">G56+G57+G60/Datos!$B$32/60+G60*Datos!$B$45/3600</f>
-        <v>124.927895910837</v>
+        <v>124.755647418774</v>
       </c>
       <c r="H67" s="9" t="n">
         <f aca="false">H56+H57+H60/Datos!$B$32/60+H60*Datos!$B$45/3600</f>
-        <v>175.231273320377</v>
+        <v>175.035825674875</v>
       </c>
       <c r="I67" s="9" t="n">
         <f aca="false">I56+I57+I60/Datos!$B$32/60+I60*Datos!$B$45/3600</f>
-        <v>240.078651263741</v>
+        <v>239.912948776969</v>
       </c>
       <c r="J67" s="9" t="n">
         <f aca="false">J56+J57+J60/Datos!$B$32/60+J60*Datos!$B$45/3600</f>
-        <v>305.846864064497</v>
+        <v>305.70757686873</v>
       </c>
       <c r="K67" s="9" t="n">
         <f aca="false">K56+K57+K60/Datos!$B$32/60+K60*Datos!$B$45/3600</f>
-        <v>345.873739644746</v>
+        <v>345.748463321994</v>
       </c>
       <c r="L67" s="9" t="n">
         <f aca="false">L56+L57+L60/Datos!$B$32/60+L60*Datos!$B$45/3600</f>
-        <v>399.48603539978</v>
+        <v>399.343543865388</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17826,43 +17826,43 @@
       </c>
       <c r="C68" s="9" t="n">
         <f aca="false">C67*Datos!$B$15</f>
-        <v>66.6718905824831</v>
+        <v>66.5629976835339</v>
       </c>
       <c r="D68" s="9" t="n">
         <f aca="false">D67*Datos!$B$15</f>
-        <v>109.3338396417</v>
+        <v>108.948444025959</v>
       </c>
       <c r="E68" s="9" t="n">
         <f aca="false">E67*Datos!$B$15</f>
-        <v>216.458270176953</v>
+        <v>215.841197399387</v>
       </c>
       <c r="F68" s="9" t="n">
         <f aca="false">F67*Datos!$B$15</f>
-        <v>454.537224328951</v>
+        <v>453.472482757129</v>
       </c>
       <c r="G68" s="9" t="n">
         <f aca="false">G67*Datos!$B$15</f>
-        <v>784.712583816054</v>
+        <v>783.630635238596</v>
       </c>
       <c r="H68" s="9" t="n">
         <f aca="false">H67*Datos!$B$15</f>
-        <v>1100.68439278566</v>
+        <v>1099.45672281023</v>
       </c>
       <c r="I68" s="9" t="n">
         <f aca="false">I67*Datos!$B$15</f>
-        <v>1508.01178054501</v>
+        <v>1506.97094954732</v>
       </c>
       <c r="J68" s="9" t="n">
         <f aca="false">J67*Datos!$B$15</f>
-        <v>1921.12323034225</v>
+        <v>1920.24832234443</v>
       </c>
       <c r="K68" s="9" t="n">
         <f aca="false">K67*Datos!$B$15</f>
-        <v>2172.54500231445</v>
+        <v>2171.75810114878</v>
       </c>
       <c r="L68" s="9" t="n">
         <f aca="false">L67*Datos!$B$15</f>
-        <v>2509.30119931523</v>
+        <v>2508.40616382849</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17922,43 +17922,43 @@
       </c>
       <c r="C70" s="11" t="n">
         <f aca="false">C62+C64+C66+C68+C69</f>
-        <v>19825.4700425424</v>
+        <v>19796.9452901094</v>
       </c>
       <c r="D70" s="11" t="n">
         <f aca="false">D62+D64+D66+D68+D69</f>
-        <v>31733.7820806062</v>
+        <v>31620.1846652531</v>
       </c>
       <c r="E70" s="11" t="n">
         <f aca="false">E62+E64+E66+E68+E69</f>
-        <v>55862.322573147</v>
+        <v>55666.5143861086</v>
       </c>
       <c r="F70" s="11" t="n">
         <f aca="false">F62+F64+F66+F68+F69</f>
-        <v>106822.729260353</v>
+        <v>106518.66139028</v>
       </c>
       <c r="G70" s="11" t="n">
         <f aca="false">G62+G64+G66+G68+G69</f>
-        <v>180613.042292317</v>
+        <v>180227.169170997</v>
       </c>
       <c r="H70" s="11" t="n">
         <f aca="false">H62+H64+H66+H68+H69</f>
-        <v>252006.823542023</v>
+        <v>251627.387428144</v>
       </c>
       <c r="I70" s="11" t="n">
         <f aca="false">I62+I64+I66+I68+I69</f>
-        <v>341303.160565839</v>
+        <v>340963.106134055</v>
       </c>
       <c r="J70" s="11" t="n">
         <f aca="false">J62+J64+J66+J68+J69</f>
-        <v>432405.781760252</v>
+        <v>432203.536428067</v>
       </c>
       <c r="K70" s="11" t="n">
         <f aca="false">K62+K64+K66+K68+K69</f>
-        <v>490384.085024971</v>
+        <v>490128.271053701</v>
       </c>
       <c r="L70" s="11" t="n">
         <f aca="false">L62+L64+L66+L68+L69</f>
-        <v>565726.313719922</v>
+        <v>565439.483307224</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18023,43 +18023,43 @@
       </c>
       <c r="C74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(C9&gt;0,1000000000000,0),C9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(C9&gt;0,1000000000000,0),C9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(C9&gt;0,1000000000000,0),C9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(C8&gt;0,1000000000000,0),C8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>89.1362759830097</v>
+        <v>88.5753454927712</v>
       </c>
       <c r="D74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(D9&gt;0,1000000000000,0),D9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(D9&gt;0,1000000000000,0),D9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(D9&gt;0,1000000000000,0),D9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(D8&gt;0,1000000000000,0),D8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>214.639665661132</v>
+        <v>213.187388759795</v>
       </c>
       <c r="E74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(E9&gt;0,1000000000000,0),E9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(E9&gt;0,1000000000000,0),E9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(E9&gt;0,1000000000000,0),E9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(E8&gt;0,1000000000000,0),E8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>388.792261041483</v>
+        <v>386.689113131001</v>
       </c>
       <c r="F74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(F9&gt;0,1000000000000,0),F9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(F9&gt;0,1000000000000,0),F9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(F9&gt;0,1000000000000,0),F9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(F8&gt;0,1000000000000,0),F8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>765.160427565093</v>
+        <v>761.540460815583</v>
       </c>
       <c r="G74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(G9&gt;0,1000000000000,0),G9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(G9&gt;0,1000000000000,0),G9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(G9&gt;0,1000000000000,0),G9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(G8&gt;0,1000000000000,0),G8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>1268.26038912732</v>
+        <v>1266.37467512285</v>
       </c>
       <c r="H74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(H9&gt;0,1000000000000,0),H9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(H9&gt;0,1000000000000,0),H9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(H9&gt;0,1000000000000,0),H9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(H8&gt;0,1000000000000,0),H8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>1804.13459264398</v>
+        <v>1799.9729552726</v>
       </c>
       <c r="I74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(I9&gt;0,1000000000000,0),I9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(I9&gt;0,1000000000000,0),I9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(I9&gt;0,1000000000000,0),I9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(I8&gt;0,1000000000000,0),I8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>2484.21149933875</v>
+        <v>2480.60414631869</v>
       </c>
       <c r="J74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(J9&gt;0,1000000000000,0),J9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(J9&gt;0,1000000000000,0),J9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(J9&gt;0,1000000000000,0),J9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(J8&gt;0,1000000000000,0),J8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>3187.78283125738</v>
+        <v>3183.1538139508</v>
       </c>
       <c r="K74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(K9&gt;0,1000000000000,0),K9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(K9&gt;0,1000000000000,0),K9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(K9&gt;0,1000000000000,0),K9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(K8&gt;0,1000000000000,0),K8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>3581.01712686783</v>
+        <v>3575.81708937065</v>
       </c>
       <c r="L74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(L9&gt;0,1000000000000,0),L9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(L9&gt;0,1000000000000,0),L9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(L9&gt;0,1000000000000,0),L9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(L8&gt;0,1000000000000,0),L8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>4171.68328968447</v>
+        <v>4169.8170552588</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18071,43 +18071,43 @@
       </c>
       <c r="C75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(C10&gt;0,1000000000000,0),C10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(C10&gt;0,1000000000000,0),C10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(C10&gt;0,1000000000000,0),C10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(C11&gt;0,1000000000000,0),C11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>540.249701091817</v>
+        <v>538.832202209718</v>
       </c>
       <c r="D75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(D10&gt;0,1000000000000,0),D10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(D10&gt;0,1000000000000,0),D10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(D10&gt;0,1000000000000,0),D10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(D11&gt;0,1000000000000,0),D11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>930.932676462215</v>
+        <v>926.330530091668</v>
       </c>
       <c r="E75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(E10&gt;0,1000000000000,0),E10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(E10&gt;0,1000000000000,0),E10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(E10&gt;0,1000000000000,0),E10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(E11&gt;0,1000000000000,0),E11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>1590.69305138396</v>
+        <v>1582.89680753242</v>
       </c>
       <c r="F75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(F10&gt;0,1000000000000,0),F10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(F10&gt;0,1000000000000,0),F10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(F10&gt;0,1000000000000,0),F10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(F11&gt;0,1000000000000,0),F11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>2891.92341199955</v>
+        <v>2878.81627233641</v>
       </c>
       <c r="G75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(G10&gt;0,1000000000000,0),G10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(G10&gt;0,1000000000000,0),G10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(G10&gt;0,1000000000000,0),G10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(G11&gt;0,1000000000000,0),G11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>4873.47147114324</v>
+        <v>4860.34543149501</v>
       </c>
       <c r="H75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(H10&gt;0,1000000000000,0),H10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(H10&gt;0,1000000000000,0),H10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(H10&gt;0,1000000000000,0),H10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(H11&gt;0,1000000000000,0),H11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>6790.92626536742</v>
+        <v>6775.73067735132</v>
       </c>
       <c r="I75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(I10&gt;0,1000000000000,0),I10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(I10&gt;0,1000000000000,0),I10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(I10&gt;0,1000000000000,0),I10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(I11&gt;0,1000000000000,0),I11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>9142.74490183336</v>
+        <v>9129.8740119839</v>
       </c>
       <c r="J75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(J10&gt;0,1000000000000,0),J10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(J10&gt;0,1000000000000,0),J10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(J10&gt;0,1000000000000,0),J10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(J11&gt;0,1000000000000,0),J11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>11546.0071242286</v>
+        <v>11535.2530327098</v>
       </c>
       <c r="K75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(K10&gt;0,1000000000000,0),K10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(K10&gt;0,1000000000000,0),K10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(K10&gt;0,1000000000000,0),K10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(K11&gt;0,1000000000000,0),K11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>13114.1148325756</v>
+        <v>13104.2868403264</v>
       </c>
       <c r="L75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(L10&gt;0,1000000000000,0),L10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(L10&gt;0,1000000000000,0),L10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(L10&gt;0,1000000000000,0),L10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(L11&gt;0,1000000000000,0),L11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>15092.3323701297</v>
+        <v>15081.1813789238</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18123,39 +18123,39 @@
       </c>
       <c r="D76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(D11&gt;0,1000000000000,0),D11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(D11&gt;0,1000000000000,0),D11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>61.2086896353785</v>
+        <v>60.2133578581194</v>
       </c>
       <c r="E76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(E11&gt;0,1000000000000,0),E11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(E11&gt;0,1000000000000,0),E11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>118.172019306769</v>
+        <v>117.097060987329</v>
       </c>
       <c r="F76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(F11&gt;0,1000000000000,0),F11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(F11&gt;0,1000000000000,0),F11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>230.18059074008</v>
+        <v>227.698896842114</v>
       </c>
       <c r="G76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(G11&gt;0,1000000000000,0),G11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(G11&gt;0,1000000000000,0),G11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>400.255472204235</v>
+        <v>398.251537559353</v>
       </c>
       <c r="H76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(H11&gt;0,1000000000000,0),H11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(H11&gt;0,1000000000000,0),H11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>578.30270318106</v>
+        <v>575.834280373458</v>
       </c>
       <c r="I76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(I11&gt;0,1000000000000,0),I11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(I11&gt;0,1000000000000,0),I11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>776.292611628876</v>
+        <v>774.660267514172</v>
       </c>
       <c r="J76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(J11&gt;0,1000000000000,0),J11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(J11&gt;0,1000000000000,0),J11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>981.252746895632</v>
+        <v>979.20899897966</v>
       </c>
       <c r="K76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(K11&gt;0,1000000000000,0),K11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(K11&gt;0,1000000000000,0),K11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>1114.33034469156</v>
+        <v>1113.17575982994</v>
       </c>
       <c r="L76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(L11&gt;0,1000000000000,0),L11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(L11&gt;0,1000000000000,0),L11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>1283.42328729743</v>
+        <v>1281.57860573691</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18175,35 +18175,35 @@
       </c>
       <c r="E77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(E12&gt;0,1000000000000,0),E12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(E13&gt;0,1000000000000,0),E13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>126.508604600151</v>
+        <v>125.88076655777</v>
       </c>
       <c r="F77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(F12&gt;0,1000000000000,0),F12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(F13&gt;0,1000000000000,0),F13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>212.649804881998</v>
+        <v>211.861232943838</v>
       </c>
       <c r="G77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(G12&gt;0,1000000000000,0),G12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(G13&gt;0,1000000000000,0),G13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>347.826800747572</v>
+        <v>347.040619377011</v>
       </c>
       <c r="H77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(H12&gt;0,1000000000000,0),H12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(H13&gt;0,1000000000000,0),H13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>483.520591965817</v>
+        <v>483.420137879036</v>
       </c>
       <c r="I77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(I12&gt;0,1000000000000,0),I12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(I13&gt;0,1000000000000,0),I13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>643.125969596336</v>
+        <v>643.025515509555</v>
       </c>
       <c r="J77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(J12&gt;0,1000000000000,0),J12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(J13&gt;0,1000000000000,0),J13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>811.719858101593</v>
+        <v>810.50568476274</v>
       </c>
       <c r="K77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(K12&gt;0,1000000000000,0),K12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(K13&gt;0,1000000000000,0),K13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>928.987035119608</v>
+        <v>928.836353989437</v>
       </c>
       <c r="L77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(L12&gt;0,1000000000000,0),L12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(L13&gt;0,1000000000000,0),L13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>1073.55388151898</v>
+        <v>1073.72558956928</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18231,27 +18231,27 @@
       </c>
       <c r="G78" s="9" t="n">
         <f aca="false">(G14*Piezas!$F$12+G15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>155.7134165436</v>
+        <v>155.0334165436</v>
       </c>
       <c r="H78" s="9" t="n">
         <f aca="false">(H14*Piezas!$F$12+H15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>214.592546179</v>
+        <v>214.318146179</v>
       </c>
       <c r="I78" s="9" t="n">
         <f aca="false">(I14*Piezas!$F$12+I15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>286.723362441</v>
+        <v>285.971362441</v>
       </c>
       <c r="J78" s="9" t="n">
         <f aca="false">(J14*Piezas!$F$12+J15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>359.380623232</v>
+        <v>360.834223232</v>
       </c>
       <c r="K78" s="9" t="n">
         <f aca="false">(K14*Piezas!$F$12+K15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>412.76308416</v>
+        <v>412.08308416</v>
       </c>
       <c r="L78" s="9" t="n">
         <f aca="false">(L14*Piezas!$F$12+L15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>477.11021562</v>
+        <v>476.37581562</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18311,43 +18311,43 @@
       </c>
       <c r="C80" s="30" t="n">
         <f aca="false">C74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>0.881284537671214</v>
+        <v>0.875738654557927</v>
       </c>
       <c r="D80" s="30" t="n">
         <f aca="false">D74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>2.12212835270491</v>
+        <v>2.10776978585375</v>
       </c>
       <c r="E80" s="30" t="n">
         <f aca="false">E74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>3.84396368642773</v>
+        <v>3.82317000042836</v>
       </c>
       <c r="F80" s="30" t="n">
         <f aca="false">F74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>7.56509116198151</v>
+        <v>7.52930078720935</v>
       </c>
       <c r="G80" s="30" t="n">
         <f aca="false">G74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>12.5392076161206</v>
+        <v>12.5205636849458</v>
       </c>
       <c r="H80" s="30" t="n">
         <f aca="false">H74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>17.8373608594323</v>
+        <v>17.7962150226072</v>
       </c>
       <c r="I80" s="30" t="n">
         <f aca="false">I74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>24.5612368087889</v>
+        <v>24.5255711451358</v>
       </c>
       <c r="J80" s="30" t="n">
         <f aca="false">J74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>31.5174006055221</v>
+        <v>31.47163381381</v>
       </c>
       <c r="K80" s="30" t="n">
         <f aca="false">K74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>35.4052823975501</v>
+        <v>35.3538699665163</v>
       </c>
       <c r="L80" s="30" t="n">
         <f aca="false">L74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>41.2451601630864</v>
+        <v>41.2267088252346</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18359,43 +18359,43 @@
       </c>
       <c r="C81" s="30" t="n">
         <f aca="false">C75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>6.83700928256096</v>
+        <v>6.81907044243696</v>
       </c>
       <c r="D81" s="30" t="n">
         <f aca="false">D75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>11.7812103135801</v>
+        <v>11.7229688793108</v>
       </c>
       <c r="E81" s="30" t="n">
         <f aca="false">E75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>20.1306602040471</v>
+        <v>20.031996583365</v>
       </c>
       <c r="F81" s="30" t="n">
         <f aca="false">F75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>36.5980900541692</v>
+        <v>36.4322155791559</v>
       </c>
       <c r="G81" s="30" t="n">
         <f aca="false">G75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>61.675128406669</v>
+        <v>61.5090147471207</v>
       </c>
       <c r="H81" s="30" t="n">
         <f aca="false">H75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>85.9410487773935</v>
+        <v>85.7487444112641</v>
       </c>
       <c r="I81" s="30" t="n">
         <f aca="false">I75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>115.703963621996</v>
+        <v>115.54107895367</v>
       </c>
       <c r="J81" s="30" t="n">
         <f aca="false">J75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>146.11791126461</v>
+        <v>145.981815264203</v>
       </c>
       <c r="K81" s="30" t="n">
         <f aca="false">K75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>165.962747710344</v>
+        <v>165.838371752151</v>
       </c>
       <c r="L81" s="30" t="n">
         <f aca="false">L75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>190.997637391631</v>
+        <v>190.856518515989</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18411,39 +18411,39 @@
       </c>
       <c r="D82" s="30" t="n">
         <f aca="false">D76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>0.968266105387796</v>
+        <v>0.952520856971657</v>
       </c>
       <c r="E82" s="30" t="n">
         <f aca="false">E76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>1.86937445616939</v>
+        <v>1.85236958787996</v>
       </c>
       <c r="F82" s="30" t="n">
         <f aca="false">F76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>3.64124874195865</v>
+        <v>3.60199058924108</v>
       </c>
       <c r="G82" s="30" t="n">
         <f aca="false">G76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>6.33167953014538</v>
+        <v>6.29997909666756</v>
       </c>
       <c r="H82" s="30" t="n">
         <f aca="false">H76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>9.14822567645215</v>
+        <v>9.10917746038013</v>
       </c>
       <c r="I82" s="30" t="n">
         <f aca="false">I76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>12.2802469417472</v>
+        <v>12.2544247343448</v>
       </c>
       <c r="J82" s="30" t="n">
         <f aca="false">J76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>15.5225308905902</v>
+        <v>15.4902006471757</v>
       </c>
       <c r="K82" s="30" t="n">
         <f aca="false">K76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>17.6276981160253</v>
+        <v>17.6094336278626</v>
       </c>
       <c r="L82" s="30" t="n">
         <f aca="false">L76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>20.3025955196599</v>
+        <v>20.2734143259286</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18463,35 +18463,35 @@
       </c>
       <c r="E83" s="30" t="n">
         <f aca="false">E77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>4.80300406771389</v>
+        <v>4.77916767586565</v>
       </c>
       <c r="F83" s="30" t="n">
         <f aca="false">F77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>8.07342616002248</v>
+        <v>8.04348737254918</v>
       </c>
       <c r="G83" s="30" t="n">
         <f aca="false">G77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>13.2055328894877</v>
+        <v>13.1756848618954</v>
       </c>
       <c r="H83" s="30" t="n">
         <f aca="false">H77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>18.3572601830158</v>
+        <v>18.3534463603201</v>
       </c>
       <c r="I83" s="30" t="n">
         <f aca="false">I77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>24.4168106808756</v>
+        <v>24.4129968581798</v>
       </c>
       <c r="J83" s="30" t="n">
         <f aca="false">J77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>30.8176174468802</v>
+        <v>30.771520349344</v>
       </c>
       <c r="K83" s="30" t="n">
         <f aca="false">K77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>35.2697630539481</v>
+        <v>35.2640423199045</v>
       </c>
       <c r="L83" s="30" t="n">
         <f aca="false">L77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>40.7583632444835</v>
+        <v>40.764882282984</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18519,27 +18519,27 @@
       </c>
       <c r="G84" s="30" t="n">
         <f aca="false">G78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>7.28350875221779</v>
+        <v>7.2517016924188</v>
       </c>
       <c r="H84" s="30" t="n">
         <f aca="false">H78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>10.0375852187265</v>
+        <v>10.0247501345959</v>
       </c>
       <c r="I84" s="30" t="n">
         <f aca="false">I78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>13.4115104925438</v>
+        <v>13.3763356264132</v>
       </c>
       <c r="J84" s="30" t="n">
         <f aca="false">J78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>16.8100602555005</v>
+        <v>16.8780525233296</v>
       </c>
       <c r="K84" s="30" t="n">
         <f aca="false">K78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>19.3070295598452</v>
+        <v>19.2752225000462</v>
       </c>
       <c r="L84" s="30" t="n">
         <f aca="false">L78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>22.316872292554</v>
+        <v>22.2825206679711</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18551,43 +18551,43 @@
       </c>
       <c r="C85" s="30" t="n">
         <f aca="false">SUM(C79:C84)</f>
-        <v>13.3978078371141</v>
+        <v>13.3743231138768</v>
       </c>
       <c r="D85" s="30" t="n">
         <f aca="false">SUM(D79:D84)</f>
-        <v>22.7641574904517</v>
+        <v>22.6758122409151</v>
       </c>
       <c r="E85" s="30" t="n">
         <f aca="false">SUM(E79:E84)</f>
-        <v>40.7562821049658</v>
+        <v>40.5959835381467</v>
       </c>
       <c r="F85" s="30" t="n">
         <f aca="false">SUM(F79:F84)</f>
-        <v>78.4775986378518</v>
+        <v>78.2067368478754</v>
       </c>
       <c r="G85" s="30" t="n">
         <f aca="false">SUM(G79:G84)</f>
-        <v>133.217009429759</v>
+        <v>132.938896318167</v>
       </c>
       <c r="H85" s="30" t="n">
         <f aca="false">SUM(H79:H84)</f>
-        <v>186.551770326295</v>
+        <v>186.262623000442</v>
       </c>
       <c r="I85" s="30" t="n">
         <f aca="false">SUM(I79:I84)</f>
-        <v>253.412524547069</v>
+        <v>253.149163318861</v>
       </c>
       <c r="J85" s="30" t="n">
         <f aca="false">SUM(J79:J84)</f>
-        <v>321.677934067048</v>
+        <v>321.485636201807</v>
       </c>
       <c r="K85" s="30" t="n">
         <f aca="false">SUM(K79:K84)</f>
-        <v>364.443553741527</v>
+        <v>364.211973070295</v>
       </c>
       <c r="L85" s="30" t="n">
         <f aca="false">SUM(L79:L84)</f>
-        <v>420.598207384379</v>
+        <v>420.381623391072</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18599,43 +18599,43 @@
       </c>
       <c r="C86" s="9" t="n">
         <f aca="false">SUMPRODUCT(C79:C84,Corte!$E$63:$E$68)*1000</f>
-        <v>16374.7000400177</v>
+        <v>16345.3309845261</v>
       </c>
       <c r="D86" s="9" t="n">
         <f aca="false">SUMPRODUCT(D79:D84,Corte!$E$63:$E$68)*1000</f>
-        <v>27863.2521633652</v>
+        <v>27752.5776190017</v>
       </c>
       <c r="E86" s="9" t="n">
         <f aca="false">SUMPRODUCT(E79:E84,Corte!$E$63:$E$68)*1000</f>
-        <v>50072.0506987764</v>
+        <v>49874.6402667204</v>
       </c>
       <c r="F86" s="9" t="n">
         <f aca="false">SUMPRODUCT(F79:F84,Corte!$E$63:$E$68)*1000</f>
-        <v>96705.2610273449</v>
+        <v>96370.1461488651</v>
       </c>
       <c r="G86" s="9" t="n">
         <f aca="false">SUMPRODUCT(G79:G84,Corte!$E$63:$E$68)*1000</f>
-        <v>164265.68027904</v>
+        <v>163925.929813487</v>
       </c>
       <c r="H86" s="9" t="n">
         <f aca="false">SUMPRODUCT(H79:H84,Corte!$E$63:$E$68)*1000</f>
-        <v>230077.227155817</v>
+        <v>229717.429243344</v>
       </c>
       <c r="I86" s="9" t="n">
         <f aca="false">SUMPRODUCT(I79:I84,Corte!$E$63:$E$68)*1000</f>
-        <v>312657.188057591</v>
+        <v>312332.856507407</v>
       </c>
       <c r="J86" s="9" t="n">
         <f aca="false">SUMPRODUCT(J79:J84,Corte!$E$63:$E$68)*1000</f>
-        <v>396945.601754709</v>
+        <v>396701.72848151</v>
       </c>
       <c r="K86" s="9" t="n">
         <f aca="false">SUMPRODUCT(K79:K84,Corte!$E$63:$E$68)*1000</f>
-        <v>449624.237437893</v>
+        <v>449339.542371149</v>
       </c>
       <c r="L86" s="9" t="n">
         <f aca="false">SUMPRODUCT(L79:L84,Corte!$E$63:$E$68)*1000</f>
-        <v>518892.403090133</v>
+        <v>518625.001507345</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18647,43 +18647,43 @@
       </c>
       <c r="C87" s="30" t="n">
         <f aca="false">C85-C25</f>
-        <v>1.43433476887398</v>
+        <v>1.42934564167909</v>
       </c>
       <c r="D87" s="30" t="n">
         <f aca="false">D85-D25</f>
-        <v>2.74587002826572</v>
+        <v>2.73190990189915</v>
       </c>
       <c r="E87" s="30" t="n">
         <f aca="false">E85-E25</f>
-        <v>4.57737641389006</v>
+        <v>4.54761940790613</v>
       </c>
       <c r="F87" s="30" t="n">
         <f aca="false">F85-F25</f>
-        <v>8.22563264305329</v>
+        <v>8.15465666148751</v>
       </c>
       <c r="G87" s="30" t="n">
         <f aca="false">G85-G25</f>
-        <v>13.5323209670392</v>
+        <v>13.5170299080291</v>
       </c>
       <c r="H87" s="30" t="n">
         <f aca="false">H85-H25</f>
-        <v>19.0050310387103</v>
+        <v>18.9628164593356</v>
       </c>
       <c r="I87" s="30" t="n">
         <f aca="false">I85-I25</f>
-        <v>26.0882979811649</v>
+        <v>26.0527339856737</v>
       </c>
       <c r="J87" s="30" t="n">
         <f aca="false">J85-J25</f>
-        <v>33.3311173034924</v>
+        <v>33.2710299221779</v>
       </c>
       <c r="K87" s="30" t="n">
         <f aca="false">K85-K25</f>
-        <v>37.1513176083752</v>
+        <v>37.0891863825078</v>
       </c>
       <c r="L87" s="30" t="n">
         <f aca="false">L85-L25</f>
-        <v>42.7677670865956</v>
+        <v>42.7420743304519</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18695,43 +18695,43 @@
       </c>
       <c r="C88" s="9" t="n">
         <f aca="false">-C87*Datos!$B$9</f>
-        <v>-358.583692218495</v>
+        <v>-357.336410419773</v>
       </c>
       <c r="D88" s="9" t="n">
         <f aca="false">-D87*Datos!$B$9</f>
-        <v>-686.467507066429</v>
+        <v>-682.977475474787</v>
       </c>
       <c r="E88" s="9" t="n">
         <f aca="false">-E87*Datos!$B$9</f>
-        <v>-1144.34410347252</v>
+        <v>-1136.90485197653</v>
       </c>
       <c r="F88" s="9" t="n">
         <f aca="false">-F87*Datos!$B$9</f>
-        <v>-2056.40816076332</v>
+        <v>-2038.66416537188</v>
       </c>
       <c r="G88" s="9" t="n">
         <f aca="false">-G87*Datos!$B$9</f>
-        <v>-3383.08024175981</v>
+        <v>-3379.25747700727</v>
       </c>
       <c r="H88" s="9" t="n">
         <f aca="false">-H87*Datos!$B$9</f>
-        <v>-4751.25775967758</v>
+        <v>-4740.7041148339</v>
       </c>
       <c r="I88" s="9" t="n">
         <f aca="false">-I87*Datos!$B$9</f>
-        <v>-6522.07449529122</v>
+        <v>-6513.18349641842</v>
       </c>
       <c r="J88" s="9" t="n">
         <f aca="false">-J87*Datos!$B$9</f>
-        <v>-8332.77932587309</v>
+        <v>-8317.75748054447</v>
       </c>
       <c r="K88" s="9" t="n">
         <f aca="false">-K87*Datos!$B$9</f>
-        <v>-9287.82940209379</v>
+        <v>-9272.29659562696</v>
       </c>
       <c r="L88" s="9" t="n">
         <f aca="false">-L87*Datos!$B$9</f>
-        <v>-10691.9417716489</v>
+        <v>-10685.518582613</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18743,43 +18743,43 @@
       </c>
       <c r="C89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+C79:C84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-C79:C84*Datos!$B$53/12))/2+C79:C84*Datos!$B$50/52)</f>
-        <v>3.86475226070599</v>
+        <v>3.85797782131062</v>
       </c>
       <c r="D89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+D79:D84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-D79:D84*Datos!$B$53/12))/2+D79:D84*Datos!$B$50/52)</f>
-        <v>6.56658389147646</v>
+        <v>6.54109968487937</v>
       </c>
       <c r="E89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+E79:E84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-E79:E84*Datos!$B$53/12))/2+E79:E84*Datos!$B$50/52)</f>
-        <v>11.7566198379709</v>
+        <v>11.7103798667731</v>
       </c>
       <c r="F89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+F79:F84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-F79:F84*Datos!$B$53/12))/2+F79:F84*Datos!$B$50/52)</f>
-        <v>22.6377688378419</v>
+        <v>22.5596356291948</v>
       </c>
       <c r="G89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+G79:G84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-G79:G84*Datos!$B$53/12))/2+G79:G84*Datos!$B$50/52)</f>
-        <v>35.0092013876862</v>
+        <v>34.9705048665371</v>
       </c>
       <c r="H89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+H79:H84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-H79:H84*Datos!$B$53/12))/2+H79:H84*Datos!$B$50/52)</f>
-        <v>39.1750680894729</v>
+        <v>39.1639470384785</v>
       </c>
       <c r="I89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+I79:I84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-I79:I84*Datos!$B$53/12))/2+I79:I84*Datos!$B$50/52)</f>
-        <v>41.7466355595027</v>
+        <v>41.7365062814947</v>
       </c>
       <c r="J89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+J79:J84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-J79:J84*Datos!$B$53/12))/2+J79:J84*Datos!$B$50/52)</f>
-        <v>44.372228233348</v>
+        <v>44.364832161608</v>
       </c>
       <c r="K89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+K79:K84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-K79:K84*Datos!$B$53/12))/2+K79:K84*Datos!$B$50/52)</f>
-        <v>46.0170597592895</v>
+        <v>46.008152810396</v>
       </c>
       <c r="L89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+L79:L84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-L79:L84*Datos!$B$53/12))/2+L79:L84*Datos!$B$50/52)</f>
-        <v>48.1768541301684</v>
+        <v>48.1685239765797</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18791,43 +18791,43 @@
       </c>
       <c r="C90" s="9" t="n">
         <f aca="false">IF(C85=0,0,C89*C86/C85*Datos!$B$7)</f>
-        <v>566.816539846767</v>
+        <v>565.799918695133</v>
       </c>
       <c r="D90" s="9" t="n">
         <f aca="false">IF(D85=0,0,D89*D86/D85*Datos!$B$7)</f>
-        <v>964.497190270335</v>
+        <v>960.66614835006</v>
       </c>
       <c r="E90" s="9" t="n">
         <f aca="false">IF(E85=0,0,E89*E86/E85*Datos!$B$7)</f>
-        <v>1733.26329341918</v>
+        <v>1726.42985538648</v>
       </c>
       <c r="F90" s="9" t="n">
         <f aca="false">IF(F85=0,0,F89*F86/F85*Datos!$B$7)</f>
-        <v>3347.48980479271</v>
+        <v>3335.88967438379</v>
       </c>
       <c r="G90" s="9" t="n">
         <f aca="false">IF(G85=0,0,G89*G86/G85*Datos!$B$7)</f>
-        <v>5180.24865436398</v>
+        <v>5174.62324577232</v>
       </c>
       <c r="H90" s="9" t="n">
         <f aca="false">IF(H85=0,0,H89*H86/H85*Datos!$B$7)</f>
-        <v>5797.82718152794</v>
+        <v>5796.10085229848</v>
       </c>
       <c r="I90" s="9" t="n">
         <f aca="false">IF(I85=0,0,I89*I86/I85*Datos!$B$7)</f>
-        <v>6180.77691695532</v>
+        <v>6179.28910685078</v>
       </c>
       <c r="J90" s="9" t="n">
         <f aca="false">IF(J85=0,0,J89*J86/J85*Datos!$B$7)</f>
-        <v>6570.5573078988</v>
+        <v>6569.35313573542</v>
       </c>
       <c r="K90" s="9" t="n">
         <f aca="false">IF(K85=0,0,K89*K86/K85*Datos!$B$7)</f>
-        <v>6812.7045269936</v>
+        <v>6811.40122491529</v>
       </c>
       <c r="L90" s="9" t="n">
         <f aca="false">IF(L85=0,0,L89*L86/L85*Datos!$B$7)</f>
-        <v>7132.29961726774</v>
+        <v>7131.06361361203</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18839,43 +18839,43 @@
       </c>
       <c r="C91" s="30" t="n">
         <f aca="false">SUM(C73:C78)/(Datos!$B$42*60)+SUMPRODUCT(C79:C84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>2.22071320333608</v>
+        <v>2.21757927673225</v>
       </c>
       <c r="D91" s="30" t="n">
         <f aca="false">SUM(D73:D78)/(Datos!$B$42*60)+SUMPRODUCT(D79:D84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>3.81137458115324</v>
+        <v>3.79581578966439</v>
       </c>
       <c r="E91" s="30" t="n">
         <f aca="false">SUM(E73:E78)/(Datos!$B$42*60)+SUMPRODUCT(E79:E84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>6.72039785684027</v>
+        <v>6.6934567217773</v>
       </c>
       <c r="F91" s="30" t="n">
         <f aca="false">SUM(F73:F78)/(Datos!$B$42*60)+SUMPRODUCT(F79:F84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>12.7868173550103</v>
+        <v>12.7393113341347</v>
       </c>
       <c r="G91" s="30" t="n">
         <f aca="false">SUM(G73:G78)/(Datos!$B$42*60)+SUMPRODUCT(G79:G84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>21.6385865613947</v>
+        <v>21.5862972346443</v>
       </c>
       <c r="H91" s="30" t="n">
         <f aca="false">SUM(H73:H78)/(Datos!$B$42*60)+SUMPRODUCT(H79:H84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>30.3743129415377</v>
+        <v>30.3239532590401</v>
       </c>
       <c r="I91" s="30" t="n">
         <f aca="false">SUM(I73:I78)/(Datos!$B$42*60)+SUMPRODUCT(I79:I84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>41.1943120510018</v>
+        <v>41.1448966996117</v>
       </c>
       <c r="J91" s="30" t="n">
         <f aca="false">SUM(J73:J78)/(Datos!$B$42*60)+SUMPRODUCT(J79:J84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>52.2725127894285</v>
+        <v>52.2505335002338</v>
       </c>
       <c r="K91" s="30" t="n">
         <f aca="false">SUM(K73:K78)/(Datos!$B$42*60)+SUMPRODUCT(K79:K84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>59.2798415209734</v>
+        <v>59.2339594987884</v>
       </c>
       <c r="L91" s="30" t="n">
         <f aca="false">SUM(L73:L78)/(Datos!$B$42*60)+SUMPRODUCT(L79:L84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>68.4840396157632</v>
+        <v>68.4424110415692</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18887,43 +18887,43 @@
       </c>
       <c r="C92" s="30" t="n">
         <f aca="false">SUMPRODUCT(C79:C84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>2.90367203656156</v>
+        <v>2.89279690213649</v>
       </c>
       <c r="D92" s="30" t="n">
         <f aca="false">SUMPRODUCT(D79:D84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>5.92650643196716</v>
+        <v>5.89187831298669</v>
       </c>
       <c r="E92" s="30" t="n">
         <f aca="false">SUMPRODUCT(E79:E84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>10.922182713573</v>
+        <v>10.8724487266465</v>
       </c>
       <c r="F92" s="30" t="n">
         <f aca="false">SUMPRODUCT(F79:F84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>21.6451012916148</v>
+        <v>21.5578300794564</v>
       </c>
       <c r="G92" s="30" t="n">
         <f aca="false">SUMPRODUCT(G79:G84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>36.4390603364961</v>
+        <v>36.3864197622234</v>
       </c>
       <c r="H92" s="30" t="n">
         <f aca="false">SUMPRODUCT(H79:H84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>51.5395196253966</v>
+        <v>51.4483670206452</v>
       </c>
       <c r="I92" s="30" t="n">
         <f aca="false">SUMPRODUCT(I79:I84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>70.6393061011088</v>
+        <v>70.5707624826328</v>
       </c>
       <c r="J92" s="30" t="n">
         <f aca="false">SUMPRODUCT(J79:J84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>90.251901371782</v>
+        <v>90.1741857305923</v>
       </c>
       <c r="K92" s="30" t="n">
         <f aca="false">SUMPRODUCT(K79:K84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>101.691761953341</v>
+        <v>101.613783148861</v>
       </c>
       <c r="L92" s="30" t="n">
         <f aca="false">SUMPRODUCT(L79:L84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>117.926144510026</v>
+        <v>117.901789395002</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18935,43 +18935,43 @@
       </c>
       <c r="C93" s="9" t="n">
         <f aca="false">C91*Datos!$B$44+SUM(C$8:C$15)/Datos!$B$41+C92*Datos!$B$46/60</f>
-        <v>11.0061613092959</v>
+        <v>10.9905080058153</v>
       </c>
       <c r="D93" s="9" t="n">
         <f aca="false">D91*Datos!$B$44+SUM(D$8:D$15)/Datos!$B$41+D92*Datos!$B$46/60</f>
-        <v>18.3418975993149</v>
+        <v>18.2790896532588</v>
       </c>
       <c r="E93" s="9" t="n">
         <f aca="false">E91*Datos!$B$44+SUM(E$8:E$15)/Datos!$B$41+E92*Datos!$B$46/60</f>
-        <v>35.5756466807071</v>
+        <v>35.4719975805162</v>
       </c>
       <c r="F93" s="9" t="n">
         <f aca="false">F91*Datos!$B$44+SUM(F$8:F$15)/Datos!$B$41+F92*Datos!$B$46/60</f>
-        <v>73.7365674844659</v>
+        <v>73.5562709730085</v>
       </c>
       <c r="G93" s="9" t="n">
         <f aca="false">G91*Datos!$B$44+SUM(G$8:G$15)/Datos!$B$41+G92*Datos!$B$46/60</f>
-        <v>126.766896158489</v>
+        <v>126.582690694753</v>
       </c>
       <c r="H93" s="9" t="n">
         <f aca="false">H91*Datos!$B$44+SUM(H$8:H$15)/Datos!$B$41+H92*Datos!$B$46/60</f>
-        <v>178.050530814316</v>
+        <v>177.853523298133</v>
       </c>
       <c r="I93" s="9" t="n">
         <f aca="false">I91*Datos!$B$44+SUM(I$8:I$15)/Datos!$B$41+I92*Datos!$B$46/60</f>
-        <v>243.959269045289</v>
+        <v>243.780069104557</v>
       </c>
       <c r="J93" s="9" t="n">
         <f aca="false">J91*Datos!$B$44+SUM(J$8:J$15)/Datos!$B$41+J92*Datos!$B$46/60</f>
-        <v>310.925410031636</v>
+        <v>310.809422542949</v>
       </c>
       <c r="K93" s="9" t="n">
         <f aca="false">K91*Datos!$B$44+SUM(K$8:K$15)/Datos!$B$41+K92*Datos!$B$46/60</f>
-        <v>351.421745738115</v>
+        <v>351.262986992626</v>
       </c>
       <c r="L93" s="9" t="n">
         <f aca="false">L91*Datos!$B$44+SUM(L$8:L$15)/Datos!$B$41+L92*Datos!$B$46/60</f>
-        <v>406.129287447283</v>
+        <v>405.986474853472</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18983,43 +18983,43 @@
       </c>
       <c r="C94" s="9" t="n">
         <f aca="false">C93*Datos!$B$15</f>
-        <v>69.1332645598863</v>
+        <v>69.0349410899362</v>
       </c>
       <c r="D94" s="9" t="n">
         <f aca="false">D93*Datos!$B$15</f>
-        <v>115.211400562773</v>
+        <v>114.816883507358</v>
       </c>
       <c r="E94" s="9" t="n">
         <f aca="false">E93*Datos!$B$15</f>
-        <v>223.462161306784</v>
+        <v>222.811107732016</v>
       </c>
       <c r="F94" s="9" t="n">
         <f aca="false">F93*Datos!$B$15</f>
-        <v>463.163266863623</v>
+        <v>462.030766069246</v>
       </c>
       <c r="G94" s="9" t="n">
         <f aca="false">G93*Datos!$B$15</f>
-        <v>796.263940104025</v>
+        <v>795.106885914108</v>
       </c>
       <c r="H94" s="9" t="n">
         <f aca="false">H93*Datos!$B$15</f>
-        <v>1118.39306238569</v>
+        <v>1117.15559435721</v>
       </c>
       <c r="I94" s="9" t="n">
         <f aca="false">I93*Datos!$B$15</f>
-        <v>1532.38719793245</v>
+        <v>1531.26158505402</v>
       </c>
       <c r="J94" s="9" t="n">
         <f aca="false">J93*Datos!$B$15</f>
-        <v>1953.02322272463</v>
+        <v>1952.29466773478</v>
       </c>
       <c r="K94" s="9" t="n">
         <f aca="false">K93*Datos!$B$15</f>
-        <v>2207.39382582831</v>
+        <v>2206.396610719</v>
       </c>
       <c r="L94" s="9" t="n">
         <f aca="false">L93*Datos!$B$15</f>
-        <v>2551.02961746499</v>
+        <v>2550.13256530003</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19079,43 +19079,43 @@
       </c>
       <c r="C96" s="11" t="n">
         <f aca="false">C86+C88+C90+C94+C95</f>
-        <v>22382.0661522059</v>
+        <v>22352.8294338914</v>
       </c>
       <c r="D96" s="11" t="n">
         <f aca="false">D86+D88+D90+D94+D95</f>
-        <v>33986.4932471319</v>
+        <v>33875.0831753844</v>
       </c>
       <c r="E96" s="11" t="n">
         <f aca="false">E86+E88+E90+E94+E95</f>
-        <v>56614.4320500298</v>
+        <v>56416.9763778624</v>
       </c>
       <c r="F96" s="11" t="n">
         <f aca="false">F86+F88+F90+F94+F95</f>
-        <v>104189.505938238</v>
+        <v>103859.402423946</v>
       </c>
       <c r="G96" s="11" t="n">
         <f aca="false">G86+G88+G90+G94+G95</f>
-        <v>172589.112631748</v>
+        <v>172246.402468166</v>
       </c>
       <c r="H96" s="11" t="n">
         <f aca="false">H86+H88+H90+H94+H95</f>
-        <v>237972.189640053</v>
+        <v>237619.981575166</v>
       </c>
       <c r="I96" s="11" t="n">
         <f aca="false">I86+I88+I90+I94+I95</f>
-        <v>319578.277677188</v>
+        <v>319260.223702893</v>
       </c>
       <c r="J96" s="11" t="n">
         <f aca="false">J86+J88+J90+J94+J95</f>
-        <v>402866.402959459</v>
+        <v>402635.618804436</v>
       </c>
       <c r="K96" s="11" t="n">
         <f aca="false">K86+K88+K90+K94+K95</f>
-        <v>455086.506388621</v>
+        <v>454815.043611156</v>
       </c>
       <c r="L96" s="11" t="n">
         <f aca="false">L86+L88+L90+L94+L95</f>
-        <v>523613.790553217</v>
+        <v>523350.679103644</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19132,43 +19132,43 @@
       </c>
       <c r="C99" s="30" t="n">
         <f aca="false">C54+C30</f>
-        <v>13.7169286836621</v>
+        <v>13.6958369641341</v>
       </c>
       <c r="D99" s="30" t="n">
         <f aca="false">D54+D30</f>
-        <v>22.9320178976016</v>
+        <v>22.847377266859</v>
       </c>
       <c r="E99" s="30" t="n">
         <f aca="false">E54+E30</f>
-        <v>41.3655348215154</v>
+        <v>41.2162748045226</v>
       </c>
       <c r="F99" s="30" t="n">
         <f aca="false">F54+F30</f>
-        <v>80.195277153377</v>
+        <v>79.9710464542093</v>
       </c>
       <c r="G99" s="30" t="n">
         <f aca="false">G54+G30</f>
-        <v>136.598653943184</v>
+        <v>136.296056096951</v>
       </c>
       <c r="H99" s="30" t="n">
         <f aca="false">H54+H30</f>
-        <v>191.202797913017</v>
+        <v>190.914260271651</v>
       </c>
       <c r="I99" s="30" t="n">
         <f aca="false">I54+I30</f>
-        <v>259.373576798051</v>
+        <v>259.111166829282</v>
       </c>
       <c r="J99" s="30" t="n">
         <f aca="false">J54+J30</f>
-        <v>328.957295418818</v>
+        <v>328.820116967212</v>
       </c>
       <c r="K99" s="30" t="n">
         <f aca="false">K54+K30</f>
-        <v>373.428727727614</v>
+        <v>373.230995568367</v>
       </c>
       <c r="L99" s="30" t="n">
         <f aca="false">L54+L30</f>
-        <v>431.090008067307</v>
+        <v>430.870850884214</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19180,43 +19180,43 @@
       </c>
       <c r="C100" s="9" t="n">
         <f aca="false">C55+C31</f>
-        <v>17092.2719697565</v>
+        <v>17065.2489143294</v>
       </c>
       <c r="D100" s="9" t="n">
         <f aca="false">D55+D31</f>
-        <v>28585.8332796281</v>
+        <v>28477.7195964164</v>
       </c>
       <c r="E100" s="9" t="n">
         <f aca="false">E55+E31</f>
-        <v>51894.1087187689</v>
+        <v>51706.5484103962</v>
       </c>
       <c r="F100" s="9" t="n">
         <f aca="false">F55+F31</f>
-        <v>101142.983807276</v>
+        <v>100855.02506432</v>
       </c>
       <c r="G100" s="9" t="n">
         <f aca="false">G55+G31</f>
-        <v>172459.11466377</v>
+        <v>172086.078263786</v>
       </c>
       <c r="H100" s="9" t="n">
         <f aca="false">H55+H31</f>
-        <v>241453.753246655</v>
+        <v>241089.624429238</v>
       </c>
       <c r="I100" s="9" t="n">
         <f aca="false">I55+I31</f>
-        <v>327760.145575775</v>
+        <v>327433.096325883</v>
       </c>
       <c r="J100" s="9" t="n">
         <f aca="false">J55+J31</f>
-        <v>415811.100567914</v>
+        <v>415625.374030073</v>
       </c>
       <c r="K100" s="9" t="n">
         <f aca="false">K55+K31</f>
-        <v>471863.617207206</v>
+        <v>471617.136451018</v>
       </c>
       <c r="L100" s="9" t="n">
         <f aca="false">L55+L31</f>
-        <v>544701.614759793</v>
+        <v>544426.602978224</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19228,43 +19228,43 @@
       </c>
       <c r="C101" s="30" t="n">
         <f aca="false">C99-C25</f>
-        <v>1.75345561542195</v>
+        <v>1.75085949193642</v>
       </c>
       <c r="D101" s="30" t="n">
         <f aca="false">D99-D25</f>
-        <v>2.91373043541558</v>
+        <v>2.90347492784298</v>
       </c>
       <c r="E101" s="30" t="n">
         <f aca="false">E99-E25</f>
-        <v>5.18662913043973</v>
+        <v>5.16791067428202</v>
       </c>
       <c r="F101" s="30" t="n">
         <f aca="false">F99-F25</f>
-        <v>9.9433111585785</v>
+        <v>9.91896626782135</v>
       </c>
       <c r="G101" s="30" t="n">
         <f aca="false">G99-G25</f>
-        <v>16.913965480464</v>
+        <v>16.8741896868139</v>
       </c>
       <c r="H101" s="30" t="n">
         <f aca="false">H99-H25</f>
-        <v>23.6560586254323</v>
+        <v>23.6144537305448</v>
       </c>
       <c r="I101" s="30" t="n">
         <f aca="false">I99-I25</f>
-        <v>32.0493502321467</v>
+        <v>32.0147374960949</v>
       </c>
       <c r="J101" s="30" t="n">
         <f aca="false">J99-J25</f>
-        <v>40.6104786552619</v>
+        <v>40.6055106875828</v>
       </c>
       <c r="K101" s="30" t="n">
         <f aca="false">K99-K25</f>
-        <v>46.1364915944617</v>
+        <v>46.1082088805801</v>
       </c>
       <c r="L101" s="30" t="n">
         <f aca="false">L99-L25</f>
-        <v>53.2595677695233</v>
+        <v>53.2313018235947</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19276,43 +19276,43 @@
       </c>
       <c r="C102" s="9" t="n">
         <f aca="false">-C101*Datos!$B$9</f>
-        <v>-438.363903855489</v>
+        <v>-437.714872984104</v>
       </c>
       <c r="D102" s="9" t="n">
         <f aca="false">-D101*Datos!$B$9</f>
-        <v>-728.432608853896</v>
+        <v>-725.868731960745</v>
       </c>
       <c r="E102" s="9" t="n">
         <f aca="false">-E101*Datos!$B$9</f>
-        <v>-1296.65728260993</v>
+        <v>-1291.9776685705</v>
       </c>
       <c r="F102" s="9" t="n">
         <f aca="false">-F101*Datos!$B$9</f>
-        <v>-2485.82778964462</v>
+        <v>-2479.74156695534</v>
       </c>
       <c r="G102" s="9" t="n">
         <f aca="false">-G101*Datos!$B$9</f>
-        <v>-4228.491370116</v>
+        <v>-4218.54742170347</v>
       </c>
       <c r="H102" s="9" t="n">
         <f aca="false">-H101*Datos!$B$9</f>
-        <v>-5914.01465635806</v>
+        <v>-5903.61343263619</v>
       </c>
       <c r="I102" s="9" t="n">
         <f aca="false">-I101*Datos!$B$9</f>
-        <v>-8012.33755803668</v>
+        <v>-8003.68437402372</v>
       </c>
       <c r="J102" s="9" t="n">
         <f aca="false">-J101*Datos!$B$9</f>
-        <v>-10152.6196638155</v>
+        <v>-10151.3776718957</v>
       </c>
       <c r="K102" s="9" t="n">
         <f aca="false">-K101*Datos!$B$9</f>
-        <v>-11534.1228986154</v>
+        <v>-11527.052220145</v>
       </c>
       <c r="L102" s="9" t="n">
         <f aca="false">-L101*Datos!$B$9</f>
-        <v>-13314.8919423808</v>
+        <v>-13307.8254558987</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19324,43 +19324,43 @@
       </c>
       <c r="C103" s="30" t="n">
         <f aca="false">C54*(Datos!$B$51/2/12+Datos!$B$50/52)+C37</f>
-        <v>1.34763534204348</v>
+        <v>1.34541775755274</v>
       </c>
       <c r="D103" s="30" t="n">
         <f aca="false">D54*(Datos!$B$51/2/12+Datos!$B$50/52)+D37</f>
-        <v>2.2603738100287</v>
+        <v>2.25159203698153</v>
       </c>
       <c r="E103" s="30" t="n">
         <f aca="false">E54*(Datos!$B$51/2/12+Datos!$B$50/52)+E37</f>
-        <v>4.10012841188462</v>
+        <v>4.08503371284284</v>
       </c>
       <c r="F103" s="30" t="n">
         <f aca="false">F54*(Datos!$B$51/2/12+Datos!$B$50/52)+F37</f>
-        <v>7.98112843231891</v>
+        <v>7.95764630498611</v>
       </c>
       <c r="G103" s="30" t="n">
         <f aca="false">G54*(Datos!$B$51/2/12+Datos!$B$50/52)+G37</f>
-        <v>13.2779266849172</v>
+        <v>13.2518249900995</v>
       </c>
       <c r="H103" s="30" t="n">
         <f aca="false">H54*(Datos!$B$51/2/12+Datos!$B$50/52)+H37</f>
-        <v>17.3527452206496</v>
+        <v>17.3305867912496</v>
       </c>
       <c r="I103" s="30" t="n">
         <f aca="false">I54*(Datos!$B$51/2/12+Datos!$B$50/52)+I37</f>
-        <v>22.3537063897181</v>
+        <v>22.3340734789705</v>
       </c>
       <c r="J103" s="30" t="n">
         <f aca="false">J54*(Datos!$B$51/2/12+Datos!$B$50/52)+J37</f>
-        <v>27.3811844311315</v>
+        <v>27.3719646463186</v>
       </c>
       <c r="K103" s="30" t="n">
         <f aca="false">K54*(Datos!$B$51/2/12+Datos!$B$50/52)+K37</f>
-        <v>30.5259523878606</v>
+        <v>30.5120883725126</v>
       </c>
       <c r="L103" s="30" t="n">
         <f aca="false">L54*(Datos!$B$51/2/12+Datos!$B$50/52)+L37</f>
-        <v>34.5843001808279</v>
+        <v>34.5690370686019</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19372,43 +19372,43 @@
       </c>
       <c r="C104" s="9" t="n">
         <f aca="false">IF(C99=0,0,C103*C100/C99*Datos!$B$7)</f>
-        <v>201.509976294023</v>
+        <v>201.169645811547</v>
       </c>
       <c r="D104" s="9" t="n">
         <f aca="false">IF(D99=0,0,D103*D100/D99*Datos!$B$7)</f>
-        <v>338.119405828004</v>
+        <v>336.77497032113</v>
       </c>
       <c r="E104" s="9" t="n">
         <f aca="false">IF(E99=0,0,E103*E100/E99*Datos!$B$7)</f>
-        <v>617.245764094174</v>
+        <v>614.969677195665</v>
       </c>
       <c r="F104" s="9" t="n">
         <f aca="false">IF(F99=0,0,F103*F100/F99*Datos!$B$7)</f>
-        <v>1207.90426436203</v>
+        <v>1204.28878169338</v>
       </c>
       <c r="G104" s="9" t="n">
         <f aca="false">IF(G99=0,0,G103*G100/G99*Datos!$B$7)</f>
-        <v>2011.64454953156</v>
+        <v>2007.79508169667</v>
       </c>
       <c r="H104" s="9" t="n">
         <f aca="false">IF(H99=0,0,H103*H100/H99*Datos!$B$7)</f>
-        <v>2629.59674757369</v>
+        <v>2626.24153147838</v>
       </c>
       <c r="I104" s="9" t="n">
         <f aca="false">IF(I99=0,0,I103*I100/I99*Datos!$B$7)</f>
-        <v>3389.69951414443</v>
+        <v>3386.76943442146</v>
       </c>
       <c r="J104" s="9" t="n">
         <f aca="false">IF(J99=0,0,J103*J100/J99*Datos!$B$7)</f>
-        <v>4153.26874036935</v>
+        <v>4151.74709467006</v>
       </c>
       <c r="K104" s="9" t="n">
         <f aca="false">IF(K99=0,0,K103*K100/K99*Datos!$B$7)</f>
-        <v>4628.70215692804</v>
+        <v>4626.63302338154</v>
       </c>
       <c r="L104" s="9" t="n">
         <f aca="false">IF(L99=0,0,L103*L100/L99*Datos!$B$7)</f>
-        <v>5243.85825733909</v>
+        <v>5241.56230504757</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19420,43 +19420,43 @@
       </c>
       <c r="C105" s="9" t="n">
         <f aca="false">C56+C57+C40*Datos!$B$46/60</f>
-        <v>3.00781189147347</v>
+        <v>3.00309579676457</v>
       </c>
       <c r="D105" s="9" t="n">
         <f aca="false">D56+D57+D40*Datos!$B$46/60</f>
-        <v>4.95956645633449</v>
+        <v>4.94156887027411</v>
       </c>
       <c r="E105" s="9" t="n">
         <f aca="false">E56+E57+E40*Datos!$B$46/60</f>
-        <v>9.80534815551962</v>
+        <v>9.77687571910761</v>
       </c>
       <c r="F105" s="9" t="n">
         <f aca="false">F56+F57+F40*Datos!$B$46/60</f>
-        <v>20.5721035515252</v>
+        <v>20.5229612761976</v>
       </c>
       <c r="G105" s="9" t="n">
         <f aca="false">G56+G57+G40*Datos!$B$46/60</f>
-        <v>35.5006862986293</v>
+        <v>35.4492627482788</v>
       </c>
       <c r="H105" s="9" t="n">
         <f aca="false">H56+H57+H40*Datos!$B$46/60</f>
-        <v>49.8321242572736</v>
+        <v>49.7756443734183</v>
       </c>
       <c r="I105" s="9" t="n">
         <f aca="false">I56+I57+I40*Datos!$B$46/60</f>
-        <v>68.2309094832047</v>
+        <v>68.1828056112613</v>
       </c>
       <c r="J105" s="9" t="n">
         <f aca="false">J56+J57+J40*Datos!$B$46/60</f>
-        <v>86.9143889324121</v>
+        <v>86.8741947465183</v>
       </c>
       <c r="K105" s="9" t="n">
         <f aca="false">K56+K57+K40*Datos!$B$46/60</f>
-        <v>98.3449059696079</v>
+        <v>98.3090072583123</v>
       </c>
       <c r="L105" s="9" t="n">
         <f aca="false">L56+L57+L40*Datos!$B$46/60</f>
-        <v>113.636671133687</v>
+        <v>113.59536747308</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19468,43 +19468,43 @@
       </c>
       <c r="C106" s="9" t="n">
         <f aca="false">C105*Datos!$B$15</f>
-        <v>18.8930408519435</v>
+        <v>18.8634175333279</v>
       </c>
       <c r="D106" s="9" t="n">
         <f aca="false">D105*Datos!$B$15</f>
-        <v>31.1526435323566</v>
+        <v>31.0395948641074</v>
       </c>
       <c r="E106" s="9" t="n">
         <f aca="false">E105*Datos!$B$15</f>
-        <v>61.5905681452071</v>
+        <v>61.411723548638</v>
       </c>
       <c r="F106" s="9" t="n">
         <f aca="false">F105*Datos!$B$15</f>
-        <v>129.220046609689</v>
+        <v>128.911368059027</v>
       </c>
       <c r="G106" s="9" t="n">
         <f aca="false">G105*Datos!$B$15</f>
-        <v>222.991310864013</v>
+        <v>222.668302885928</v>
       </c>
       <c r="H106" s="9" t="n">
         <f aca="false">H105*Datos!$B$15</f>
-        <v>313.011715260751</v>
+        <v>312.656946813955</v>
       </c>
       <c r="I106" s="9" t="n">
         <f aca="false">I105*Datos!$B$15</f>
-        <v>428.580445434687</v>
+        <v>428.278289432065</v>
       </c>
       <c r="J106" s="9" t="n">
         <f aca="false">J105*Datos!$B$15</f>
-        <v>545.937432249909</v>
+        <v>545.684959547659</v>
       </c>
       <c r="K106" s="9" t="n">
         <f aca="false">K105*Datos!$B$15</f>
-        <v>617.736212604083</v>
+        <v>617.510721169276</v>
       </c>
       <c r="L106" s="9" t="n">
         <f aca="false">L105*Datos!$B$15</f>
-        <v>713.788743270069</v>
+        <v>713.529301597739</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19564,43 +19564,43 @@
       </c>
       <c r="C108" s="11" t="n">
         <f aca="false">C100+C102+C104+C106+C107</f>
-        <v>19454.4988624807</v>
+        <v>19427.7548841238</v>
       </c>
       <c r="D108" s="11" t="n">
         <f aca="false">D100+D102+D104+D106+D107</f>
-        <v>30806.8604995683</v>
+        <v>30699.8532090746</v>
       </c>
       <c r="E108" s="11" t="n">
         <f aca="false">E100+E102+E104+E106+E107</f>
-        <v>53856.4755478321</v>
+        <v>53671.1399220037</v>
       </c>
       <c r="F108" s="11" t="n">
         <f aca="false">F100+F102+F104+F106+F107</f>
-        <v>102574.468108037</v>
+        <v>102288.671426551</v>
       </c>
       <c r="G108" s="11" t="n">
         <f aca="false">G100+G102+G104+G106+G107</f>
-        <v>173045.446933484</v>
+        <v>172678.182006099</v>
       </c>
       <c r="H108" s="11" t="n">
         <f aca="false">H100+H102+H104+H106+H107</f>
-        <v>241062.534832565</v>
+        <v>240705.097254328</v>
       </c>
       <c r="I108" s="11" t="n">
         <f aca="false">I100+I102+I104+I106+I107</f>
-        <v>326146.275756751</v>
+        <v>325824.647455147</v>
       </c>
       <c r="J108" s="11" t="n">
         <f aca="false">J100+J102+J104+J106+J107</f>
-        <v>412937.874856152</v>
+        <v>412751.616191828</v>
       </c>
       <c r="K108" s="11" t="n">
         <f aca="false">K100+K102+K104+K106+K107</f>
-        <v>468156.120457556</v>
+        <v>467914.415754858</v>
       </c>
       <c r="L108" s="11" t="n">
         <f aca="false">L100+L102+L104+L106+L107</f>
-        <v>539924.557597455</v>
+        <v>539654.056908405</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19617,43 +19617,43 @@
       </c>
       <c r="C111" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>9.75815679409689</v>
+        <v>9.74436245386314</v>
       </c>
       <c r="D111" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>16.2632510037798</v>
+        <v>16.2066883707767</v>
       </c>
       <c r="E111" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>29.2104736361371</v>
+        <v>29.1078692763175</v>
       </c>
       <c r="F111" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>56.470631955553</v>
+        <v>56.319897511078</v>
       </c>
       <c r="G111" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>96.1219776435812</v>
+        <v>95.9075832845086</v>
       </c>
       <c r="H111" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>134.523459912545</v>
+        <v>134.332583077155</v>
       </c>
       <c r="I111" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>182.43893470904</v>
+        <v>182.257743808154</v>
       </c>
       <c r="J111" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>231.371801469011</v>
+        <v>231.280035549904</v>
       </c>
       <c r="K111" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>262.694691724471</v>
+        <v>262.560532780319</v>
       </c>
       <c r="L111" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>303.277540090901</v>
+        <v>303.127601765745</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19665,43 +19665,43 @@
       </c>
       <c r="C112" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15,Corte!$I$32:$I$39)</f>
-        <v>13426.3489312009</v>
+        <v>13406.3605354273</v>
       </c>
       <c r="D112" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15,Corte!$I$32:$I$39)</f>
-        <v>22446.1917360546</v>
+        <v>22364.4626749836</v>
       </c>
       <c r="E112" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15,Corte!$I$32:$I$39)</f>
-        <v>40377.3967056522</v>
+        <v>40232.0208714075</v>
       </c>
       <c r="F112" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15,Corte!$I$32:$I$39)</f>
-        <v>78096.9853372748</v>
+        <v>77878.3049898693</v>
       </c>
       <c r="G112" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15,Corte!$I$32:$I$39)</f>
-        <v>132956.045701458</v>
+        <v>132658.745284838</v>
       </c>
       <c r="H112" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15,Corte!$I$32:$I$39)</f>
-        <v>186102.529725481</v>
+        <v>185829.776912118</v>
       </c>
       <c r="I112" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15,Corte!$I$32:$I$39)</f>
-        <v>252380.77693027</v>
+        <v>252126.496622955</v>
       </c>
       <c r="J112" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15,Corte!$I$32:$I$39)</f>
-        <v>320065.935322803</v>
+        <v>319925.209559701</v>
       </c>
       <c r="K112" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15,Corte!$I$32:$I$39)</f>
-        <v>363372.163237751</v>
+        <v>363183.583455873</v>
       </c>
       <c r="L112" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15,Corte!$I$32:$I$39)</f>
-        <v>419481.831270372</v>
+        <v>419269.833373514</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19713,43 +19713,43 @@
       </c>
       <c r="C113" s="30" t="n">
         <f aca="false">C111+C30</f>
-        <v>12.7404263950974</v>
+        <v>12.7203015405208</v>
       </c>
       <c r="D113" s="30" t="n">
         <f aca="false">D111+D30</f>
-        <v>21.3377195148919</v>
+        <v>21.2571608271907</v>
       </c>
       <c r="E113" s="30" t="n">
         <f aca="false">E111+E30</f>
-        <v>38.6374618657569</v>
+        <v>38.4972403645445</v>
       </c>
       <c r="F113" s="30" t="n">
         <f aca="false">F111+F30</f>
-        <v>75.1333297266714</v>
+        <v>74.9164161957101</v>
       </c>
       <c r="G113" s="30" t="n">
         <f aca="false">G111+G30</f>
-        <v>128.036602152218</v>
+        <v>127.757002574009</v>
       </c>
       <c r="H113" s="30" t="n">
         <f aca="false">H111+H30</f>
-        <v>179.25257076729</v>
+        <v>178.986217454328</v>
       </c>
       <c r="I113" s="30" t="n">
         <f aca="false">I111+I30</f>
-        <v>243.2439151557</v>
+        <v>242.999970461348</v>
       </c>
       <c r="J113" s="30" t="n">
         <f aca="false">J111+J30</f>
-        <v>308.559463246909</v>
+        <v>308.413241565485</v>
       </c>
       <c r="K113" s="30" t="n">
         <f aca="false">K111+K30</f>
-        <v>350.204003122767</v>
+        <v>350.022326394569</v>
       </c>
       <c r="L113" s="30" t="n">
         <f aca="false">L111+L30</f>
-        <v>404.273582034313</v>
+        <v>404.06850228125</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19761,43 +19761,43 @@
       </c>
       <c r="C114" s="9" t="n">
         <f aca="false">C112+C31</f>
-        <v>16983.2739308602</v>
+        <v>16955.7775450761</v>
       </c>
       <c r="D114" s="9" t="n">
         <f aca="false">D112+D31</f>
-        <v>28493.5228923199</v>
+        <v>28383.3112781369</v>
       </c>
       <c r="E114" s="9" t="n">
         <f aca="false">E112+E31</f>
-        <v>51627.3165330636</v>
+        <v>51437.3016783078</v>
       </c>
       <c r="F114" s="9" t="n">
         <f aca="false">F112+F31</f>
-        <v>100398.034460587</v>
+        <v>100100.80779089</v>
       </c>
       <c r="G114" s="9" t="n">
         <f aca="false">G112+G31</f>
-        <v>171101.81428929</v>
+        <v>170727.133708532</v>
       </c>
       <c r="H114" s="9" t="n">
         <f aca="false">H112+H31</f>
-        <v>239566.265974252</v>
+        <v>239203.940442532</v>
       </c>
       <c r="I114" s="9" t="n">
         <f aca="false">I112+I31</f>
-        <v>325073.202859069</v>
+        <v>324744.45845183</v>
       </c>
       <c r="J114" s="9" t="n">
         <f aca="false">J112+J31</f>
-        <v>412351.493513547</v>
+        <v>412146.135512804</v>
       </c>
       <c r="K114" s="9" t="n">
         <f aca="false">K112+K31</f>
-        <v>467990.884981959</v>
+        <v>467745.922158803</v>
       </c>
       <c r="L114" s="9" t="n">
         <f aca="false">L112+L31</f>
-        <v>540224.987083676</v>
+        <v>539947.548396235</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19809,43 +19809,43 @@
       </c>
       <c r="C115" s="30" t="n">
         <f aca="false">C113-C25</f>
-        <v>0.776953326857221</v>
+        <v>0.775324068323117</v>
       </c>
       <c r="D115" s="30" t="n">
         <f aca="false">D113-D25</f>
-        <v>1.31943205270595</v>
+        <v>1.31325848817471</v>
       </c>
       <c r="E115" s="30" t="n">
         <f aca="false">E113-E25</f>
-        <v>2.45855617468116</v>
+        <v>2.44887623430387</v>
       </c>
       <c r="F115" s="30" t="n">
         <f aca="false">F113-F25</f>
-        <v>4.88136373187288</v>
+        <v>4.86433600932222</v>
       </c>
       <c r="G115" s="30" t="n">
         <f aca="false">G113-G25</f>
-        <v>8.35191368949839</v>
+        <v>8.33513616387194</v>
       </c>
       <c r="H115" s="30" t="n">
         <f aca="false">H113-H25</f>
-        <v>11.705831479706</v>
+        <v>11.6864109132216</v>
       </c>
       <c r="I115" s="30" t="n">
         <f aca="false">I113-I25</f>
-        <v>15.9196885897956</v>
+        <v>15.903541128161</v>
       </c>
       <c r="J115" s="30" t="n">
         <f aca="false">J113-J25</f>
-        <v>20.212646483353</v>
+        <v>20.1986352858556</v>
       </c>
       <c r="K115" s="30" t="n">
         <f aca="false">K113-K25</f>
-        <v>22.9117669896149</v>
+        <v>22.8995397067815</v>
       </c>
       <c r="L115" s="30" t="n">
         <f aca="false">L113-L25</f>
-        <v>26.4431417365297</v>
+        <v>26.4289532206306</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19857,43 +19857,43 @@
       </c>
       <c r="C116" s="9" t="n">
         <f aca="false">-C115*Datos!$B$9</f>
-        <v>-194.238331714305</v>
+        <v>-193.831017080779</v>
       </c>
       <c r="D116" s="9" t="n">
         <f aca="false">-D115*Datos!$B$9</f>
-        <v>-329.858013176487</v>
+        <v>-328.314622043679</v>
       </c>
       <c r="E116" s="9" t="n">
         <f aca="false">-E115*Datos!$B$9</f>
-        <v>-614.639043670289</v>
+        <v>-612.219058575969</v>
       </c>
       <c r="F116" s="9" t="n">
         <f aca="false">-F115*Datos!$B$9</f>
-        <v>-1220.34093296822</v>
+        <v>-1216.08400233055</v>
       </c>
       <c r="G116" s="9" t="n">
         <f aca="false">-G115*Datos!$B$9</f>
-        <v>-2087.9784223746</v>
+        <v>-2083.78404096798</v>
       </c>
       <c r="H116" s="9" t="n">
         <f aca="false">-H115*Datos!$B$9</f>
-        <v>-2926.45786992651</v>
+        <v>-2921.60272830539</v>
       </c>
       <c r="I116" s="9" t="n">
         <f aca="false">-I115*Datos!$B$9</f>
-        <v>-3979.9221474489</v>
+        <v>-3975.88528204025</v>
       </c>
       <c r="J116" s="9" t="n">
         <f aca="false">-J115*Datos!$B$9</f>
-        <v>-5053.16162083825</v>
+        <v>-5049.65882146391</v>
       </c>
       <c r="K116" s="9" t="n">
         <f aca="false">-K115*Datos!$B$9</f>
-        <v>-5727.94174740373</v>
+        <v>-5724.88492669537</v>
       </c>
       <c r="L116" s="9" t="n">
         <f aca="false">-L115*Datos!$B$9</f>
-        <v>-6610.78543413242</v>
+        <v>-6607.23830515765</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19905,43 +19905,43 @@
       </c>
       <c r="C117" s="30" t="n">
         <f aca="false">C111*(Datos!$B$51/2/12+Datos!$B$50/52)+C37</f>
-        <v>1.2693899663572</v>
+        <v>1.26724985501962</v>
       </c>
       <c r="D117" s="30" t="n">
         <f aca="false">D111*(Datos!$B$51/2/12+Datos!$B$50/52)+D37</f>
-        <v>2.13262554218338</v>
+        <v>2.12417084790555</v>
       </c>
       <c r="E117" s="30" t="n">
         <f aca="false">E111*(Datos!$B$51/2/12+Datos!$B$50/52)+E37</f>
-        <v>3.88153282248089</v>
+        <v>3.86716236348562</v>
       </c>
       <c r="F117" s="30" t="n">
         <f aca="false">F111*(Datos!$B$51/2/12+Datos!$B$50/52)+F37</f>
-        <v>7.57552367056366</v>
+        <v>7.55262785478586</v>
       </c>
       <c r="G117" s="30" t="n">
         <f aca="false">G111*(Datos!$B$51/2/12+Datos!$B$50/52)+G37</f>
-        <v>12.5918648426924</v>
+        <v>12.5676059578125</v>
       </c>
       <c r="H117" s="30" t="n">
         <f aca="false">H111*(Datos!$B$51/2/12+Datos!$B$50/52)+H37</f>
-        <v>16.3951949685882</v>
+        <v>16.3748141296051</v>
       </c>
       <c r="I117" s="30" t="n">
         <f aca="false">I111*(Datos!$B$51/2/12+Datos!$B$50/52)+I37</f>
-        <v>21.0612655529912</v>
+        <v>21.0431122315399</v>
       </c>
       <c r="J117" s="30" t="n">
         <f aca="false">J111*(Datos!$B$51/2/12+Datos!$B$50/52)+J37</f>
-        <v>25.7467427506901</v>
+        <v>25.7367983481033</v>
       </c>
       <c r="K117" s="30" t="n">
         <f aca="false">K111*(Datos!$B$51/2/12+Datos!$B$50/52)+K37</f>
-        <v>28.6649968906773</v>
+        <v>28.6524193682018</v>
       </c>
       <c r="L117" s="30" t="n">
         <f aca="false">L111*(Datos!$B$51/2/12+Datos!$B$50/52)+L37</f>
-        <v>32.4355480948509</v>
+        <v>32.4214129818259</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19953,43 +19953,43 @@
       </c>
       <c r="C118" s="9" t="n">
         <f aca="false">IF(C113=0,0,C117*C114/C113*Datos!$B$7)</f>
-        <v>203.055033059418</v>
+        <v>202.704691242998</v>
       </c>
       <c r="D118" s="9" t="n">
         <f aca="false">IF(D113=0,0,D117*D114/D113*Datos!$B$7)</f>
-        <v>341.738570503967</v>
+        <v>340.352145091326</v>
       </c>
       <c r="E118" s="9" t="n">
         <f aca="false">IF(E113=0,0,E117*E114/E113*Datos!$B$7)</f>
-        <v>622.379775429188</v>
+        <v>620.043603892628</v>
       </c>
       <c r="F118" s="9" t="n">
         <f aca="false">IF(F113=0,0,F117*F114/F113*Datos!$B$7)</f>
-        <v>1214.74880344229</v>
+        <v>1210.9882254373</v>
       </c>
       <c r="G118" s="9" t="n">
         <f aca="false">IF(G113=0,0,G117*G114/G113*Datos!$B$7)</f>
-        <v>2019.25782189266</v>
+        <v>2015.35536951501</v>
       </c>
       <c r="H118" s="9" t="n">
         <f aca="false">IF(H113=0,0,H117*H114/H113*Datos!$B$7)</f>
-        <v>2629.40874213308</v>
+        <v>2626.07039996143</v>
       </c>
       <c r="I118" s="9" t="n">
         <f aca="false">IF(I113=0,0,I117*I114/I113*Datos!$B$7)</f>
-        <v>3377.57417456161</v>
+        <v>3374.63452664549</v>
       </c>
       <c r="J118" s="9" t="n">
         <f aca="false">IF(J113=0,0,J117*J114/J113*Datos!$B$7)</f>
-        <v>4128.8798138182</v>
+        <v>4127.18543178018</v>
       </c>
       <c r="K118" s="9" t="n">
         <f aca="false">IF(K113=0,0,K117*K114/K113*Datos!$B$7)</f>
-        <v>4596.73463806881</v>
+        <v>4594.69627238097</v>
       </c>
       <c r="L118" s="9" t="n">
         <f aca="false">IF(L113=0,0,L117*L114/L113*Datos!$B$7)</f>
-        <v>5201.17890338098</v>
+        <v>5198.87960271466</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20001,43 +20001,43 @@
       </c>
       <c r="C119" s="9" t="n">
         <f aca="false">C40*Datos!$B$46/60</f>
-        <v>0.525054710757036</v>
+        <v>0.523996023455547</v>
       </c>
       <c r="D119" s="9" t="n">
         <f aca="false">D40*Datos!$B$46/60</f>
-        <v>0.91952703527801</v>
+        <v>0.914368338106516</v>
       </c>
       <c r="E119" s="9" t="n">
         <f aca="false">E40*Datos!$B$46/60</f>
-        <v>1.78266992545758</v>
+        <v>1.77544748904557</v>
       </c>
       <c r="F119" s="9" t="n">
         <f aca="false">F40*Datos!$B$46/60</f>
-        <v>3.66031940911966</v>
+        <v>3.6467086152735</v>
       </c>
       <c r="G119" s="9" t="n">
         <f aca="false">G40*Datos!$B$46/60</f>
-        <v>6.28876842829598</v>
+        <v>6.27567265572325</v>
       </c>
       <c r="H119" s="9" t="n">
         <f aca="false">H40*Datos!$B$46/60</f>
-        <v>8.86281735433888</v>
+        <v>8.84766154455763</v>
       </c>
       <c r="I119" s="9" t="n">
         <f aca="false">I40*Datos!$B$46/60</f>
-        <v>12.0632063559608</v>
+        <v>12.0509571136469</v>
       </c>
       <c r="J119" s="9" t="n">
         <f aca="false">J40*Datos!$B$46/60</f>
-        <v>15.33714333675</v>
+        <v>15.3258972990045</v>
       </c>
       <c r="K119" s="9" t="n">
         <f aca="false">K40*Datos!$B$46/60</f>
-        <v>17.4153512312884</v>
+        <v>17.4061978903632</v>
       </c>
       <c r="L119" s="9" t="n">
         <f aca="false">L40*Datos!$B$46/60</f>
-        <v>20.155450074562</v>
+        <v>20.1444510435848</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20049,43 +20049,43 @@
       </c>
       <c r="C120" s="9" t="n">
         <f aca="false">C119*Datos!$B$15</f>
-        <v>3.29803872641068</v>
+        <v>3.29138876851499</v>
       </c>
       <c r="D120" s="9" t="n">
         <f aca="false">D119*Datos!$B$15</f>
-        <v>5.77584718353627</v>
+        <v>5.74344373547486</v>
       </c>
       <c r="E120" s="9" t="n">
         <f aca="false">E119*Datos!$B$15</f>
-        <v>11.1975272864228</v>
+        <v>11.1521608236565</v>
       </c>
       <c r="F120" s="9" t="n">
         <f aca="false">F119*Datos!$B$15</f>
-        <v>22.991651945954</v>
+        <v>22.9061581406758</v>
       </c>
       <c r="G120" s="9" t="n">
         <f aca="false">G119*Datos!$B$15</f>
-        <v>39.501791704801</v>
+        <v>39.4195329149792</v>
       </c>
       <c r="H120" s="9" t="n">
         <f aca="false">H119*Datos!$B$15</f>
-        <v>55.6702268561117</v>
+        <v>55.5750283052471</v>
       </c>
       <c r="I120" s="9" t="n">
         <f aca="false">I119*Datos!$B$15</f>
-        <v>75.7729069210317</v>
+        <v>75.6959654619939</v>
       </c>
       <c r="J120" s="9" t="n">
         <f aca="false">J119*Datos!$B$15</f>
-        <v>96.3375656685035</v>
+        <v>96.2669256623411</v>
       </c>
       <c r="K120" s="9" t="n">
         <f aca="false">K119*Datos!$B$15</f>
-        <v>109.391462676375</v>
+        <v>109.333967576857</v>
       </c>
       <c r="L120" s="9" t="n">
         <f aca="false">L119*Datos!$B$15</f>
-        <v>126.60291114863</v>
+        <v>126.533822671995</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20145,43 +20145,43 @@
       </c>
       <c r="C122" s="11" t="n">
         <f aca="false">C114+C116+C118+C120+C121</f>
-        <v>17445.3886709318</v>
+        <v>17417.9426080068</v>
       </c>
       <c r="D122" s="11" t="n">
         <f aca="false">D114+D116+D118+D120+D121</f>
-        <v>28961.1792968309</v>
+        <v>28851.09224492</v>
       </c>
       <c r="E122" s="11" t="n">
         <f aca="false">E114+E116+E118+E120+E121</f>
-        <v>52096.2547921089</v>
+        <v>51906.2783844481</v>
       </c>
       <c r="F122" s="11" t="n">
         <f aca="false">F114+F116+F118+F120+F121</f>
-        <v>100865.433983007</v>
+        <v>100568.618172138</v>
       </c>
       <c r="G122" s="11" t="n">
         <f aca="false">G114+G116+G118+G120+G121</f>
-        <v>171522.595480513</v>
+        <v>171148.124569994</v>
       </c>
       <c r="H122" s="11" t="n">
         <f aca="false">H114+H116+H118+H120+H121</f>
-        <v>239774.887073314</v>
+        <v>239413.983142493</v>
       </c>
       <c r="I122" s="11" t="n">
         <f aca="false">I114+I116+I118+I120+I121</f>
-        <v>324996.627793102</v>
+        <v>324668.903661897</v>
       </c>
       <c r="J122" s="11" t="n">
         <f aca="false">J114+J116+J118+J120+J121</f>
-        <v>411973.549272195</v>
+        <v>411769.929048782</v>
       </c>
       <c r="K122" s="11" t="n">
         <f aca="false">K114+K116+K118+K120+K121</f>
-        <v>467419.0693353</v>
+        <v>467175.067472066</v>
       </c>
       <c r="L122" s="11" t="n">
         <f aca="false">L114+L116+L118+L120+L121</f>
-        <v>539391.983464073</v>
+        <v>539115.723516464</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20246,43 +20246,43 @@
       </c>
       <c r="C126" s="9" t="n">
         <f aca="false">C9/Corte!$I$7</f>
-        <v>11.1863095259259</v>
+        <v>11.1122354518519</v>
       </c>
       <c r="D126" s="9" t="n">
         <f aca="false">D9/Corte!$I$7</f>
-        <v>26.9365722333333</v>
+        <v>26.7454611222222</v>
       </c>
       <c r="E126" s="9" t="n">
         <f aca="false">E9/Corte!$I$7</f>
-        <v>48.7921502814815</v>
+        <v>48.5121502814815</v>
       </c>
       <c r="F126" s="9" t="n">
         <f aca="false">F9/Corte!$I$7</f>
-        <v>96.0251175555555</v>
+        <v>95.5391916296296</v>
       </c>
       <c r="G126" s="9" t="n">
         <f aca="false">G9/Corte!$I$7</f>
-        <v>159.16250837037</v>
+        <v>158.603989851852</v>
       </c>
       <c r="H126" s="9" t="n">
         <f aca="false">H9/Corte!$I$7</f>
-        <v>226.412958777778</v>
+        <v>225.815921740741</v>
       </c>
       <c r="I126" s="9" t="n">
         <f aca="false">I9/Corte!$I$7</f>
-        <v>300.639834222222</v>
+        <v>300.078352740741</v>
       </c>
       <c r="J126" s="9" t="n">
         <f aca="false">J9/Corte!$I$7</f>
-        <v>380.378762481481</v>
+        <v>379.969873592593</v>
       </c>
       <c r="K126" s="9" t="n">
         <f aca="false">K9/Corte!$I$7</f>
-        <v>443.574305296296</v>
+        <v>443.14763862963</v>
       </c>
       <c r="L126" s="9" t="n">
         <f aca="false">L9/Corte!$I$7</f>
-        <v>523.532534962963</v>
+        <v>523.125127555556</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20294,43 +20294,43 @@
       </c>
       <c r="C127" s="9" t="n">
         <f aca="false">C10/Corte!$I$8</f>
-        <v>190.56441875</v>
+        <v>190.06441875</v>
       </c>
       <c r="D127" s="9" t="n">
         <f aca="false">D10/Corte!$I$8</f>
-        <v>328.371573416667</v>
+        <v>326.748240083333</v>
       </c>
       <c r="E127" s="9" t="n">
         <f aca="false">E10/Corte!$I$8</f>
-        <v>561.091465916667</v>
+        <v>558.341465916667</v>
       </c>
       <c r="F127" s="9" t="n">
         <f aca="false">F10/Corte!$I$8</f>
-        <v>1020.07960941667</v>
+        <v>1015.45627608333</v>
       </c>
       <c r="G127" s="9" t="n">
         <f aca="false">G10/Corte!$I$8</f>
-        <v>1719.03891166667</v>
+        <v>1714.40891166667</v>
       </c>
       <c r="H127" s="9" t="n">
         <f aca="false">H10/Corte!$I$8</f>
-        <v>2395.3903425</v>
+        <v>2390.0303425</v>
       </c>
       <c r="I127" s="9" t="n">
         <f aca="false">I10/Corte!$I$8</f>
-        <v>3224.95665333333</v>
+        <v>3220.41665333333</v>
       </c>
       <c r="J127" s="9" t="n">
         <f aca="false">J10/Corte!$I$8</f>
-        <v>4072.66886416667</v>
+        <v>4068.87553083333</v>
       </c>
       <c r="K127" s="9" t="n">
         <f aca="false">K10/Corte!$I$8</f>
-        <v>4625.7937125</v>
+        <v>4622.32704583333</v>
       </c>
       <c r="L127" s="9" t="n">
         <f aca="false">L10/Corte!$I$8</f>
-        <v>5323.57822666667</v>
+        <v>5319.64489333333</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20346,39 +20346,39 @@
       </c>
       <c r="D128" s="9" t="n">
         <f aca="false">D11/Corte!$I$9</f>
-        <v>12.2991531133333</v>
+        <v>12.0991531133333</v>
       </c>
       <c r="E128" s="9" t="n">
         <f aca="false">E11/Corte!$I$9</f>
-        <v>23.7452519866667</v>
+        <v>23.5292519866667</v>
       </c>
       <c r="F128" s="9" t="n">
         <f aca="false">F11/Corte!$I$9</f>
-        <v>46.25203294</v>
+        <v>45.7533662733333</v>
       </c>
       <c r="G128" s="9" t="n">
         <f aca="false">G11/Corte!$I$9</f>
-        <v>80.42654346</v>
+        <v>80.0238767933333</v>
       </c>
       <c r="H128" s="9" t="n">
         <f aca="false">H11/Corte!$I$9</f>
-        <v>116.203002133333</v>
+        <v>115.707002133333</v>
       </c>
       <c r="I128" s="9" t="n">
         <f aca="false">I11/Corte!$I$9</f>
-        <v>155.986703</v>
+        <v>155.658703</v>
       </c>
       <c r="J128" s="9" t="n">
         <f aca="false">J11/Corte!$I$9</f>
-        <v>197.170987466667</v>
+        <v>196.7603208</v>
       </c>
       <c r="K128" s="9" t="n">
         <f aca="false">K11/Corte!$I$9</f>
-        <v>223.911336933333</v>
+        <v>223.679336933333</v>
       </c>
       <c r="L128" s="9" t="n">
         <f aca="false">L11/Corte!$I$9</f>
-        <v>257.8885386</v>
+        <v>257.517871933333</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20446,35 +20446,35 @@
       </c>
       <c r="E130" s="9" t="n">
         <f aca="false">E51</f>
-        <v>26.019086335</v>
+        <v>25.8524196683333</v>
       </c>
       <c r="F130" s="9" t="n">
         <f aca="false">F51</f>
-        <v>43.256791675</v>
+        <v>43.4934583416667</v>
       </c>
       <c r="G130" s="9" t="n">
         <f aca="false">G51</f>
-        <v>71.3882009916667</v>
+        <v>71.061534325</v>
       </c>
       <c r="H130" s="9" t="n">
         <f aca="false">H51</f>
-        <v>99.2247701083333</v>
+        <v>99.2047701083333</v>
       </c>
       <c r="I130" s="9" t="n">
         <f aca="false">I51</f>
-        <v>131.935999383333</v>
+        <v>131.915999383333</v>
       </c>
       <c r="J130" s="9" t="n">
         <f aca="false">J51</f>
-        <v>166.373790041667</v>
+        <v>166.270456708333</v>
       </c>
       <c r="K130" s="9" t="n">
         <f aca="false">K51</f>
-        <v>190.63776775</v>
+        <v>190.52776775</v>
       </c>
       <c r="L130" s="9" t="n">
         <f aca="false">L51</f>
-        <v>220.129984416667</v>
+        <v>220.26331775</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20550,27 +20550,27 @@
       </c>
       <c r="G132" s="9" t="n">
         <f aca="false">G49</f>
-        <v>13.2956090766667</v>
+        <v>13.4067201877778</v>
       </c>
       <c r="H132" s="9" t="n">
         <f aca="false">H49</f>
-        <v>18.6720613011111</v>
+        <v>18.2365057455556</v>
       </c>
       <c r="I132" s="9" t="n">
         <f aca="false">I49</f>
-        <v>24.7156391033333</v>
+        <v>24.8000835477778</v>
       </c>
       <c r="J132" s="9" t="n">
         <f aca="false">J49</f>
-        <v>30.8763735444444</v>
+        <v>31.0808179888889</v>
       </c>
       <c r="K132" s="9" t="n">
         <f aca="false">K49</f>
-        <v>35.3401288333333</v>
+        <v>35.4512399444444</v>
       </c>
       <c r="L132" s="9" t="n">
         <f aca="false">L49</f>
-        <v>40.9122062</v>
+        <v>41.0322062</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20594,31 +20594,31 @@
       </c>
       <c r="F133" s="9" t="n">
         <f aca="false">F50</f>
-        <v>25.66164215</v>
+        <v>25.4949754833333</v>
       </c>
       <c r="G133" s="9" t="n">
         <f aca="false">G50</f>
-        <v>41.89266725</v>
+        <v>41.8793339166667</v>
       </c>
       <c r="H133" s="9" t="n">
         <f aca="false">H50</f>
-        <v>58.2624137833333</v>
+        <v>58.24908045</v>
       </c>
       <c r="I133" s="9" t="n">
         <f aca="false">I50</f>
-        <v>77.5780388666667</v>
+        <v>77.5647055333333</v>
       </c>
       <c r="J133" s="9" t="n">
         <f aca="false">J50</f>
-        <v>97.95477845</v>
+        <v>97.77477845</v>
       </c>
       <c r="K133" s="9" t="n">
         <f aca="false">K50</f>
-        <v>111.944569266667</v>
+        <v>112.084569266667</v>
       </c>
       <c r="L133" s="9" t="n">
         <f aca="false">L50</f>
-        <v>129.551755533333</v>
+        <v>129.5384222</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20646,27 +20646,27 @@
       </c>
       <c r="G134" s="9" t="n">
         <f aca="false">G47</f>
-        <v>40.75349389</v>
+        <v>40.4201605566667</v>
       </c>
       <c r="H134" s="9" t="n">
         <f aca="false">H47</f>
-        <v>55.8428505666667</v>
+        <v>56.1495172333333</v>
       </c>
       <c r="I134" s="9" t="n">
         <f aca="false">I47</f>
-        <v>74.8269173</v>
+        <v>74.4935839666667</v>
       </c>
       <c r="J134" s="9" t="n">
         <f aca="false">J47</f>
-        <v>93.8824539666667</v>
+        <v>94.1891206333334</v>
       </c>
       <c r="K134" s="9" t="n">
         <f aca="false">K47</f>
-        <v>107.9403865</v>
+        <v>107.607053166667</v>
       </c>
       <c r="L134" s="9" t="n">
         <f aca="false">L47</f>
-        <v>124.709952</v>
+        <v>124.349952</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20774,43 +20774,43 @@
       </c>
       <c r="C137" s="30" t="n">
         <f aca="false">C18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>0.153348267420575</v>
+        <v>0.152332818054212</v>
       </c>
       <c r="D137" s="30" t="n">
         <f aca="false">D18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>0.369261790285472</v>
+        <v>0.366641930920256</v>
       </c>
       <c r="E137" s="30" t="n">
         <f aca="false">E18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>0.668870434172095</v>
+        <v>0.665032035567242</v>
       </c>
       <c r="F137" s="30" t="n">
         <f aca="false">F18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>1.31636670448582</v>
+        <v>1.30970535664248</v>
       </c>
       <c r="G137" s="30" t="n">
         <f aca="false">G18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>2.18188982169156</v>
+        <v>2.17423333346918</v>
       </c>
       <c r="H137" s="30" t="n">
         <f aca="false">H18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>3.1037970896183</v>
+        <v>3.09561256772541</v>
       </c>
       <c r="I137" s="30" t="n">
         <f aca="false">I18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>4.12134114372011</v>
+        <v>4.11364403752308</v>
       </c>
       <c r="J137" s="30" t="n">
         <f aca="false">J18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>5.21444754008713</v>
+        <v>5.2088422595848</v>
       </c>
       <c r="K137" s="30" t="n">
         <f aca="false">K18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>6.08076783784882</v>
+        <v>6.07491884949857</v>
       </c>
       <c r="L137" s="30" t="n">
         <f aca="false">L18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>7.17688054213097</v>
+        <v>7.17129557061597</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20822,43 +20822,43 @@
       </c>
       <c r="C138" s="30" t="n">
         <f aca="false">C19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>0.124251178839693</v>
+        <v>0.123428406056245</v>
       </c>
       <c r="D138" s="30" t="n">
         <f aca="false">D19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>0.299196159925244</v>
+        <v>0.297073406143947</v>
       </c>
       <c r="E138" s="30" t="n">
         <f aca="false">E19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>0.541955519516678</v>
+        <v>0.538845438395242</v>
       </c>
       <c r="F138" s="30" t="n">
         <f aca="false">F19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>1.06659251890407</v>
+        <v>1.06119512944465</v>
       </c>
       <c r="G138" s="30" t="n">
         <f aca="false">G19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>1.7678868304392</v>
+        <v>1.761683123652</v>
       </c>
       <c r="H138" s="30" t="n">
         <f aca="false">H19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>2.51486667408241</v>
+        <v>2.50823512544782</v>
       </c>
       <c r="I138" s="30" t="n">
         <f aca="false">I19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>3.3393366884499</v>
+        <v>3.33310007075136</v>
       </c>
       <c r="J138" s="30" t="n">
         <f aca="false">J19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>4.22503145781635</v>
+        <v>4.22048975205171</v>
       </c>
       <c r="K138" s="30" t="n">
         <f aca="false">K19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>4.92697168877068</v>
+        <v>4.92223251753802</v>
       </c>
       <c r="L138" s="30" t="n">
         <f aca="false">L19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>5.81510233373385</v>
+        <v>5.81057708342489</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20870,43 +20870,43 @@
       </c>
       <c r="C139" s="30" t="n">
         <f aca="false">C20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>0.471341389662887</v>
+        <v>0.470104691351747</v>
       </c>
       <c r="D139" s="30" t="n">
         <f aca="false">D20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>0.812193140541355</v>
+        <v>0.808177993357854</v>
       </c>
       <c r="E139" s="30" t="n">
         <f aca="false">E20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>1.38780173658808</v>
+        <v>1.38099989587681</v>
       </c>
       <c r="F139" s="30" t="n">
         <f aca="false">F20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>2.52306146038727</v>
+        <v>2.51162612333693</v>
       </c>
       <c r="G139" s="30" t="n">
         <f aca="false">G20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>4.25186503768318</v>
+        <v>4.24041321132203</v>
       </c>
       <c r="H139" s="30" t="n">
         <f aca="false">H20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>5.92475038218019</v>
+        <v>5.91149297628477</v>
       </c>
       <c r="I139" s="30" t="n">
         <f aca="false">I20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>7.97659689335214</v>
+        <v>7.96536767268699</v>
       </c>
       <c r="J139" s="30" t="n">
         <f aca="false">J20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>10.0733254122923</v>
+        <v>10.0639429944385</v>
       </c>
       <c r="K139" s="30" t="n">
         <f aca="false">K20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>11.4414225438588</v>
+        <v>11.4328481022349</v>
       </c>
       <c r="L139" s="30" t="n">
         <f aca="false">L20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>13.1673204042775</v>
+        <v>13.1575917108965</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20918,43 +20918,43 @@
       </c>
       <c r="C140" s="30" t="n">
         <f aca="false">C21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>0.442044181282849</v>
+        <v>0.440884352537844</v>
       </c>
       <c r="D140" s="30" t="n">
         <f aca="false">D21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>0.761709579782356</v>
+        <v>0.757944002456906</v>
       </c>
       <c r="E140" s="30" t="n">
         <f aca="false">E21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>1.30154002149431</v>
+        <v>1.29516096339679</v>
       </c>
       <c r="F140" s="30" t="n">
         <f aca="false">F21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>2.3662353063899</v>
+        <v>2.35551075659442</v>
       </c>
       <c r="G140" s="30" t="n">
         <f aca="false">G21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>3.98758148706631</v>
+        <v>3.97684147288756</v>
       </c>
       <c r="H140" s="30" t="n">
         <f aca="false">H21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>5.55648514947786</v>
+        <v>5.54405178533141</v>
       </c>
       <c r="I140" s="30" t="n">
         <f aca="false">I21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>7.48079485586241</v>
+        <v>7.47026361085776</v>
       </c>
       <c r="J140" s="30" t="n">
         <f aca="false">J21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>9.44719683509493</v>
+        <v>9.43839760101616</v>
       </c>
       <c r="K140" s="30" t="n">
         <f aca="false">K21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>10.730257032442</v>
+        <v>10.7222155531433</v>
       </c>
       <c r="L140" s="30" t="n">
         <f aca="false">L21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>12.3488781071418</v>
+        <v>12.3397541210144</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20970,39 +20970,39 @@
       </c>
       <c r="D141" s="30" t="n">
         <f aca="false">D22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>0.260705826873141</v>
+        <v>0.256466415842629</v>
       </c>
       <c r="E141" s="30" t="n">
         <f aca="false">E22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>0.503329415972875</v>
+        <v>0.498750852059921</v>
       </c>
       <c r="F141" s="30" t="n">
         <f aca="false">F22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>0.980406893147332</v>
+        <v>0.969836628311254</v>
       </c>
       <c r="G141" s="30" t="n">
         <f aca="false">G22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>1.70480587745161</v>
+        <v>1.69627052991018</v>
       </c>
       <c r="H141" s="30" t="n">
         <f aca="false">H22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>2.46316144511364</v>
+        <v>2.45264770575797</v>
       </c>
       <c r="I141" s="30" t="n">
         <f aca="false">I22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>3.30645874655744</v>
+        <v>3.2995061124674</v>
       </c>
       <c r="J141" s="30" t="n">
         <f aca="false">J22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>4.1794442958162</v>
+        <v>4.17073937183355</v>
       </c>
       <c r="K141" s="30" t="n">
         <f aca="false">K22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>4.74626095825994</v>
+        <v>4.74134324146455</v>
       </c>
       <c r="L141" s="30" t="n">
         <f aca="false">L22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>5.46647757591802</v>
+        <v>5.45862053414147</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21018,39 +21018,39 @@
       </c>
       <c r="D142" s="30" t="n">
         <f aca="false">D23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>0.238114064104756</v>
+        <v>0.234242024104756</v>
       </c>
       <c r="E142" s="30" t="n">
         <f aca="false">E23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>0.459712827512264</v>
+        <v>0.455531024312264</v>
       </c>
       <c r="F142" s="30" t="n">
         <f aca="false">F23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>0.895448608124988</v>
+        <v>0.885794321724988</v>
       </c>
       <c r="G142" s="30" t="n">
         <f aca="false">G23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>1.55707396669429</v>
+        <v>1.54927825949429</v>
       </c>
       <c r="H142" s="30" t="n">
         <f aca="false">H23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>2.24971336190176</v>
+        <v>2.24011070270176</v>
       </c>
       <c r="I142" s="30" t="n">
         <f aca="false">I23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>3.0199337674206</v>
+        <v>3.0135836218206</v>
       </c>
       <c r="J142" s="30" t="n">
         <f aca="false">J23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>3.81726975155216</v>
+        <v>3.80931916275216</v>
       </c>
       <c r="K142" s="30" t="n">
         <f aca="false">K23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>4.33496826529672</v>
+        <v>4.33047669889672</v>
       </c>
       <c r="L142" s="30" t="n">
         <f aca="false">L23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>4.99277368500372</v>
+        <v>4.98559750420372</v>
       </c>
     </row>
   </sheetData>

--- a/salida/Analisis_alternativas_corte_chapa.xlsx
+++ b/salida/Analisis_alternativas_corte_chapa.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">Indexado Dim Técnico B3:K10 y B15:K22 → Demanda</t>
   </si>
   <si>
-    <t xml:space="preserve">Dimensionamiento Recargas Planta Comercial</t>
+    <t xml:space="preserve">Aprovechamiento Recargas Planta Comercial</t>
   </si>
   <si>
     <t xml:space="preserve">PEGAR ACÁ EL LINK DEL GOOGLE SHEET</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">sobrestock_sustitutos B73:K76 y B86:K89 → Demanda</t>
   </si>
   <si>
-    <t xml:space="preserve">Dimensionamiento Recargas Planta Industrial</t>
+    <t xml:space="preserve">Aprovechamiento Recargas Planta Industrial</t>
   </si>
   <si>
     <t xml:space="preserve">Sin link, esa fuente suma 0 en Demanda (la columna Estado lo avisa).</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">golpes/min</t>
   </si>
   <si>
-    <t xml:space="preserve">Dimensionamiento Manuales del grupo. La ficha de la máquina (resale.info, 2018) da 24.</t>
+    <t xml:space="preserve">Aprovechamiento Manuales del grupo. La ficha de la máquina (resale.info, 2018) da 24.</t>
   </si>
   <si>
     <t xml:space="preserve">Guillotina 1: largo de corte</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">1.er corte por el lado corto (franjas de hasta 1.500 mm de largo). G1 hace solo el 1.er corte y G2 solo el 2.º: la pieza, o la orilla si la pieza supera el tope. Franjas en paralelo: hojas enteras, con el ciclo que da menos tandas por hoja (Datos, «Hojas por ciclo»).</t>
   </si>
   <si>
-    <t xml:space="preserve">Para los Dimensionamientos de Manuales (1 a 10 kg) y Carros (25 a 100 kg): IMPORTRANGE</t>
+    <t xml:space="preserve">Para los Aprovechamientos de Manuales (1 a 10 kg) y Carros (25 a 100 kg): IMPORTRANGE</t>
   </si>
   <si>
     <t xml:space="preserve">Tandas de G2 por hoja</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">Plan: P1 hasta cubrir el 25 kg (o el 50 kg, si es menos de la mitad) y el resto en P3 o P4. Es el mínimo de hojas (Word «Esquema de corte en guillotina», 5.2).</t>
   </si>
   <si>
-    <t xml:space="preserve">Promedio por hoja de 3,2 mm con el plan elegido (va a Corte, tabla para los Dimensionamientos)</t>
+    <t xml:space="preserve">Promedio por hoja de 3,2 mm con el plan elegido (va a Corte, tabla para los Aprovechamientos)</t>
   </si>
   <si>
     <t xml:space="preserve">C) 4,75 mm: 70 y 100 kg en la hoja de 1.500 × 3.000</t>
@@ -2517,19 +2517,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1139515.48976354</c:v>
+                  <c:v>1139875.83132641</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1140050.0842414</c:v>
+                  <c:v>1140454.43915057</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1201797.48321688</c:v>
+                  <c:v>1202188.26797316</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1107544.2636078</c:v>
+                  <c:v>1107926.94786553</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1028038.84321599</c:v>
+                  <c:v>1028430.05119185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2537,11 +2537,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="96473633"/>
-        <c:axId val="92612424"/>
+        <c:axId val="23936482"/>
+        <c:axId val="83372265"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="96473633"/>
+        <c:axId val="23936482"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2573,7 +2573,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92612424"/>
+        <c:crossAx val="83372265"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2581,7 +2581,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92612424"/>
+        <c:axId val="83372265"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2658,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96473633"/>
+        <c:crossAx val="23936482"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3972,40 +3972,40 @@
         <v>2</v>
       </c>
       <c r="D34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.16)</f>
-        <v>4.16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.16)</f>
+        <v>5.16</v>
       </c>
       <c r="E34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.48)</f>
-        <v>8.48</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.56)</f>
+        <v>7.56</v>
       </c>
       <c r="F34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.12)</f>
-        <v>12.12</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.12)</f>
+        <v>13.12</v>
       </c>
       <c r="G34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13)</f>
-        <v>13</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.08)</f>
+        <v>13.08</v>
       </c>
       <c r="H34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.88)</f>
-        <v>13.88</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.96)</f>
+        <v>14.96</v>
       </c>
       <c r="I34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.76)</f>
-        <v>12.76</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.92)</f>
+        <v>13.92</v>
       </c>
       <c r="J34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.48)</f>
-        <v>11.48</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.72)</f>
+        <v>10.72</v>
       </c>
       <c r="K34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.04)</f>
-        <v>10.04</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.2)</f>
+        <v>10.2</v>
       </c>
       <c r="L34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.44)</f>
-        <v>10.44</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.6)</f>
+        <v>11.6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4020,40 +4020,40 @@
         <v>9</v>
       </c>
       <c r="D35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.72)</f>
-        <v>25.72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.72)</f>
+        <v>27.72</v>
       </c>
       <c r="E35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.72)</f>
-        <v>44.72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.88)</f>
+        <v>47.88</v>
       </c>
       <c r="F35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.08)</f>
-        <v>73.08</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.48)</f>
+        <v>78.48</v>
       </c>
       <c r="G35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.44)</f>
-        <v>74.44</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.24)</f>
+        <v>80.24</v>
       </c>
       <c r="H35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.48)</f>
-        <v>83.48</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.68)</f>
+        <v>89.68</v>
       </c>
       <c r="I35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.84)</f>
-        <v>71.84</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),77.44)</f>
+        <v>77.44</v>
       </c>
       <c r="J35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.84)</f>
-        <v>60.84</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.76)</f>
+        <v>65.76</v>
       </c>
       <c r="K35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.64)</f>
-        <v>57.64</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.8)</f>
+        <v>60.8</v>
       </c>
       <c r="L35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.96)</f>
-        <v>58.96</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.2)</f>
+        <v>64.2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4132,24 +4132,24 @@
         <v>1.16</v>
       </c>
       <c r="H37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
-        <v>0.24</v>
-      </c>
-      <c r="I37" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
         <v>1.24</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
+        <v>0.32</v>
       </c>
       <c r="J37" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
         <v>0.32</v>
       </c>
       <c r="K37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
-        <v>0.32</v>
-      </c>
-      <c r="L37" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
         <v>1.32</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
+        <v>0.4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4176,28 +4176,28 @@
         <v>2.16</v>
       </c>
       <c r="G38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
-        <v>1.32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.32)</f>
+        <v>2.32</v>
       </c>
       <c r="H38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.48)</f>
+        <v>1.48</v>
       </c>
       <c r="I38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.56)</f>
-        <v>0.56</v>
-      </c>
-      <c r="J38" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.56)</f>
         <v>1.56</v>
       </c>
-      <c r="K38" s="9" t="n">
+      <c r="J38" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.64)</f>
         <v>1.64</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="K38" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.72)</f>
         <v>1.72</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4240,12 +4240,12 @@
         <v>0.16</v>
       </c>
       <c r="K39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
+        <v>1.16</v>
       </c>
       <c r="L39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
+        <v>0.24</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4399,40 +4399,40 @@
         <v>3</v>
       </c>
       <c r="D45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.24)</f>
-        <v>8.24</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.24)</f>
+        <v>9.24</v>
       </c>
       <c r="E45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.88)</f>
-        <v>14.88</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.96)</f>
+        <v>15.96</v>
       </c>
       <c r="F45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23)</f>
-        <v>23</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.16)</f>
+        <v>24.16</v>
       </c>
       <c r="G45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.68)</f>
-        <v>23.68</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.92)</f>
+        <v>25.92</v>
       </c>
       <c r="H45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.28)</f>
-        <v>27.28</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.68)</f>
+        <v>28.68</v>
       </c>
       <c r="I45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.04)</f>
-        <v>24.04</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.52)</f>
+        <v>26.52</v>
       </c>
       <c r="J45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.4)</f>
-        <v>20.4</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.04)</f>
+        <v>21.04</v>
       </c>
       <c r="K45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.36)</f>
-        <v>18.36</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21)</f>
+        <v>21</v>
       </c>
       <c r="L45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.08)</f>
-        <v>20.08</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.88)</f>
+        <v>20.88</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4443,44 +4443,44 @@
         <v>39</v>
       </c>
       <c r="C46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16)</f>
-        <v>16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17)</f>
+        <v>17</v>
       </c>
       <c r="D46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.28)</f>
-        <v>48.28</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.36)</f>
+        <v>53.36</v>
       </c>
       <c r="E46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.04)</f>
-        <v>83.04</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.52)</f>
+        <v>91.52</v>
       </c>
       <c r="F46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.28)</f>
-        <v>137.28</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.4)</f>
+        <v>150.4</v>
       </c>
       <c r="G46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.36)</f>
-        <v>138.36</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),152.44)</f>
+        <v>152.44</v>
       </c>
       <c r="H46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),156.72)</f>
-        <v>156.72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),171.76)</f>
+        <v>171.76</v>
       </c>
       <c r="I46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),136.8)</f>
-        <v>136.8</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.8)</f>
+        <v>150.8</v>
       </c>
       <c r="J46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.48)</f>
-        <v>114.48</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),125.28)</f>
+        <v>125.28</v>
       </c>
       <c r="K46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.76)</f>
-        <v>106.76</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.04)</f>
+        <v>117.04</v>
       </c>
       <c r="L46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111)</f>
-        <v>111</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),122.68)</f>
+        <v>122.68</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4495,40 +4495,40 @@
         <v>2</v>
       </c>
       <c r="D47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.16)</f>
-        <v>2.16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.16)</f>
+        <v>3.16</v>
       </c>
       <c r="E47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.32)</f>
-        <v>6.32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.4)</f>
+        <v>5.4</v>
       </c>
       <c r="F47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.8)</f>
-        <v>8.8</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.8)</f>
+        <v>9.8</v>
       </c>
       <c r="G47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.44)</f>
-        <v>9.44</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.52)</f>
+        <v>9.52</v>
       </c>
       <c r="H47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.08)</f>
-        <v>11.08</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.16)</f>
+        <v>11.16</v>
       </c>
       <c r="I47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.8)</f>
-        <v>7.8</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.88)</f>
+        <v>8.88</v>
       </c>
       <c r="J47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.2)</f>
-        <v>7.2</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.36)</f>
+        <v>7.36</v>
       </c>
       <c r="K47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.52)</f>
-        <v>7.52</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.68)</f>
+        <v>7.68</v>
       </c>
       <c r="L47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.84)</f>
-        <v>6.84</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4555,28 +4555,28 @@
         <v>1.16</v>
       </c>
       <c r="G48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
-        <v>1.24</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.24)</f>
+        <v>2.24</v>
       </c>
       <c r="H48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.32)</f>
-        <v>2.32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
       </c>
       <c r="I48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.48)</f>
-        <v>0.48</v>
-      </c>
-      <c r="J48" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.48)</f>
         <v>1.48</v>
       </c>
-      <c r="K48" s="9" t="n">
+      <c r="J48" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.56)</f>
         <v>1.56</v>
       </c>
-      <c r="L48" s="9" t="n">
+      <c r="K48" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.64)</f>
         <v>0.64</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.64)</f>
+        <v>1.64</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4603,28 +4603,28 @@
         <v>3.32</v>
       </c>
       <c r="G49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.56)</f>
-        <v>2.56</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.56)</f>
+        <v>3.56</v>
       </c>
       <c r="H49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.72)</f>
-        <v>3.72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="I49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.96)</f>
-        <v>2.96</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.04)</f>
+        <v>3.04</v>
       </c>
       <c r="J49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.12)</f>
-        <v>2.12</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="K49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.36)</f>
+        <v>2.36</v>
       </c>
       <c r="L49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.28)</f>
-        <v>3.28</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.44)</f>
+        <v>2.44</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4651,28 +4651,28 @@
         <v>1.08</v>
       </c>
       <c r="G50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
-      </c>
-      <c r="H50" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
         <v>1.16</v>
       </c>
-      <c r="I50" s="9" t="n">
+      <c r="H50" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
         <v>0.24</v>
       </c>
-      <c r="J50" s="9" t="n">
+      <c r="I50" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
         <v>1.24</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
+        <v>0.32</v>
       </c>
       <c r="K50" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
         <v>0.32</v>
       </c>
       <c r="L50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
-        <v>0.32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
+        <v>1.32</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4707,12 +4707,12 @@
         <v>0.16</v>
       </c>
       <c r="I51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
-      </c>
-      <c r="J51" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
         <v>1.16</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
+        <v>0.24</v>
       </c>
       <c r="K51" s="9" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
@@ -4859,23 +4859,23 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$32:$L$32)</f>
-        <v>1816.95312368953</v>
+        <v>1817.54320540384</v>
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$61:$L$61)</f>
-        <v>1924.11199317846</v>
+        <v>1924.74727831533</v>
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$85:$L$85)</f>
-        <v>1833.28277104146</v>
+        <v>1833.93078164875</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$99:$L$99)</f>
-        <v>1876.9739821074</v>
+        <v>1877.59001341101</v>
       </c>
       <c r="F8" s="9" t="n">
         <f aca="false">SUM(Cálculo!$C$113:$L$113)</f>
-        <v>1759.63837965896</v>
+        <v>1760.21256110205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4884,23 +4884,23 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/B8</f>
-        <v>0.905243149641851</v>
+        <v>0.905244967114225</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/C8</f>
-        <v>0.854827772121138</v>
+        <v>0.854824868563825</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/D8</f>
-        <v>0.897179853769059</v>
+        <v>0.897155909954955</v>
       </c>
       <c r="E9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/E8</f>
-        <v>0.876295774006202</v>
+        <v>0.876294519811295</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">SUM(Cálculo!$C$25:$L$25)/F8</f>
-        <v>0.934728628025886</v>
+        <v>0.934729063729875</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4909,23 +4909,23 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$41:$L$41,Datos!$B$6-2025)</f>
-        <v>318.251396835488</v>
+        <v>318.274511570836</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$67:$L$67,Datos!$B$6-2025)</f>
-        <v>399.343543865388</v>
+        <v>399.386281854806</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$93:$L$93,Datos!$B$6-2025)</f>
-        <v>405.986474853472</v>
+        <v>406.038524982844</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$105:$L$105,Datos!$B$6-2025)</f>
-        <v>113.59536747308</v>
+        <v>113.606394245466</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$119:$L$119,Datos!$B$6-2025)</f>
-        <v>20.1444510435848</v>
+        <v>20.1466991122665</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4934,23 +4934,23 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$44:$L$44,Datos!$B$6-2025)</f>
-        <v>510774.458819745</v>
+        <v>510842.200866098</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$70:$L$70,Datos!$B$6-2025)</f>
-        <v>565439.483307224</v>
+        <v>565521.545743233</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$96:$L$96,Datos!$B$6-2025)</f>
-        <v>523350.679103644</v>
+        <v>523443.217467392</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$108:$L$108,Datos!$B$6-2025)</f>
-        <v>539654.056908405</v>
+        <v>539731.104274726</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$122:$L$122,Datos!$B$6-2025)</f>
-        <v>539115.723516464</v>
+        <v>539193.472175174</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4959,23 +4959,23 @@
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B7+SUMPRODUCT(Cálculo!$C$44:$L$44,Cálculo!$C$6:$L$6)</f>
-        <v>1139515.48976354</v>
+        <v>1139875.83132641</v>
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">C7+SUMPRODUCT(Cálculo!$C$70:$L$70,Cálculo!$C$6:$L$6)</f>
-        <v>1140050.0842414</v>
+        <v>1140454.43915057</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">D7+SUMPRODUCT(Cálculo!$C$96:$L$96,Cálculo!$C$6:$L$6)</f>
-        <v>1201797.48321688</v>
+        <v>1202188.26797316</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">E7+SUMPRODUCT(Cálculo!$C$108:$L$108,Cálculo!$C$6:$L$6)</f>
-        <v>1107544.2636078</v>
+        <v>1107926.94786553</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">F7+SUMPRODUCT(Cálculo!$C$122:$L$122,Cálculo!$C$6:$L$6)</f>
-        <v>1028038.84321599</v>
+        <v>1028430.05119185</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5008,15 +5008,15 @@
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">B12-MIN($B$12:$E$12)</f>
-        <v>31971.2261557409</v>
+        <v>31948.8834608789</v>
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">C12-MIN($B$12:$E$12)</f>
-        <v>32505.8206336012</v>
+        <v>32527.4912850342</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">D12-MIN($B$12:$E$12)</f>
-        <v>94253.2196090804</v>
+        <v>94261.3201076263</v>
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">E12-MIN($B$12:$E$12)</f>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">F12-MIN($B$12:$E$12)</f>
-        <v>-79505.4203918114</v>
+        <v>-79496.8966736835</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">($B$12-$E$12)/SUMPRODUCT(Cálculo!$C$55:$L$55,Cálculo!$C$6:$L$6)</f>
-        <v>0.0402355014547532</v>
+        <v>0.0401921184457539</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="B18" s="10" t="n">
         <f aca="false">($C$12-$E$12)/SUMPRODUCT(Cálculo!$C$31:$L$31,Cálculo!$C$6:$L$6)</f>
-        <v>0.144236820127873</v>
+        <v>0.14427752929513</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7722,39 +7722,39 @@
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false">IFERROR(Links!D12,0)+IFERROR(Links!D23,0)+IFERROR(Links!D34,0)+IFERROR(Links!D45,0)</f>
-        <v>722.1274503</v>
+        <v>724.1274503</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">IFERROR(Links!E12,0)+IFERROR(Links!E23,0)+IFERROR(Links!E34,0)+IFERROR(Links!E45,0)</f>
-        <v>1309.8280576</v>
+        <v>1309.9880576</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">IFERROR(Links!F12,0)+IFERROR(Links!F23,0)+IFERROR(Links!F34,0)+IFERROR(Links!F45,0)</f>
-        <v>2579.558174</v>
+        <v>2581.718174</v>
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">IFERROR(Links!G12,0)+IFERROR(Links!G23,0)+IFERROR(Links!G34,0)+IFERROR(Links!G45,0)</f>
-        <v>4282.307726</v>
+        <v>4284.627726</v>
       </c>
       <c r="H7" s="11" t="n">
         <f aca="false">IFERROR(Links!H12,0)+IFERROR(Links!H23,0)+IFERROR(Links!H34,0)+IFERROR(Links!H45,0)</f>
-        <v>6097.029887</v>
+        <v>6099.509887</v>
       </c>
       <c r="I7" s="11" t="n">
         <f aca="false">IFERROR(Links!I12,0)+IFERROR(Links!I23,0)+IFERROR(Links!I34,0)+IFERROR(Links!I45,0)</f>
-        <v>8102.115524</v>
+        <v>8105.755524</v>
       </c>
       <c r="J7" s="11" t="n">
         <f aca="false">IFERROR(Links!J12,0)+IFERROR(Links!J23,0)+IFERROR(Links!J34,0)+IFERROR(Links!J45,0)</f>
-        <v>10259.186587</v>
+        <v>10259.066587</v>
       </c>
       <c r="K7" s="11" t="n">
         <f aca="false">IFERROR(Links!K12,0)+IFERROR(Links!K23,0)+IFERROR(Links!K34,0)+IFERROR(Links!K45,0)</f>
-        <v>11964.986243</v>
+        <v>11967.786243</v>
       </c>
       <c r="L7" s="11" t="n">
         <f aca="false">IFERROR(Links!L12,0)+IFERROR(Links!L23,0)+IFERROR(Links!L34,0)+IFERROR(Links!L45,0)</f>
-        <v>14124.378444</v>
+        <v>14126.338444</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7766,43 +7766,43 @@
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">IFERROR(Links!C13,0)+IFERROR(Links!C24,0)+IFERROR(Links!C35,0)+IFERROR(Links!C46,0)</f>
-        <v>2280.773025</v>
+        <v>2281.773025</v>
       </c>
       <c r="D8" s="11" t="n">
         <f aca="false">IFERROR(Links!D13,0)+IFERROR(Links!D24,0)+IFERROR(Links!D35,0)+IFERROR(Links!D46,0)</f>
-        <v>3920.978881</v>
+        <v>3928.058881</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">IFERROR(Links!E13,0)+IFERROR(Links!E24,0)+IFERROR(Links!E35,0)+IFERROR(Links!E46,0)</f>
-        <v>6700.097591</v>
+        <v>6711.737591</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">IFERROR(Links!F13,0)+IFERROR(Links!F24,0)+IFERROR(Links!F35,0)+IFERROR(Links!F46,0)</f>
-        <v>12185.475313</v>
+        <v>12203.995313</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">IFERROR(Links!G13,0)+IFERROR(Links!G24,0)+IFERROR(Links!G35,0)+IFERROR(Links!G46,0)</f>
-        <v>20572.90694</v>
+        <v>20592.78694</v>
       </c>
       <c r="H8" s="11" t="n">
         <f aca="false">IFERROR(Links!H13,0)+IFERROR(Links!H24,0)+IFERROR(Links!H35,0)+IFERROR(Links!H46,0)</f>
-        <v>28680.36411</v>
+        <v>28701.60411</v>
       </c>
       <c r="I8" s="11" t="n">
         <f aca="false">IFERROR(Links!I13,0)+IFERROR(Links!I24,0)+IFERROR(Links!I35,0)+IFERROR(Links!I46,0)</f>
-        <v>38644.99984</v>
+        <v>38664.59984</v>
       </c>
       <c r="J8" s="11" t="n">
         <f aca="false">IFERROR(Links!J13,0)+IFERROR(Links!J24,0)+IFERROR(Links!J35,0)+IFERROR(Links!J46,0)</f>
-        <v>48826.50637</v>
+        <v>48842.22637</v>
       </c>
       <c r="K8" s="11" t="n">
         <f aca="false">IFERROR(Links!K13,0)+IFERROR(Links!K24,0)+IFERROR(Links!K35,0)+IFERROR(Links!K46,0)</f>
-        <v>55467.92455</v>
+        <v>55481.36455</v>
       </c>
       <c r="L8" s="11" t="n">
         <f aca="false">IFERROR(Links!L13,0)+IFERROR(Links!L24,0)+IFERROR(Links!L35,0)+IFERROR(Links!L46,0)</f>
-        <v>63835.73872</v>
+        <v>63852.65872</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7818,39 +7818,39 @@
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">IFERROR(Links!D14,0)+IFERROR(Links!D25,0)+IFERROR(Links!D36,0)+IFERROR(Links!D47,0)</f>
-        <v>181.4872967</v>
+        <v>182.4872967</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">IFERROR(Links!E14,0)+IFERROR(Links!E25,0)+IFERROR(Links!E36,0)+IFERROR(Links!E47,0)</f>
-        <v>352.9387798</v>
+        <v>352.0187798</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">IFERROR(Links!F14,0)+IFERROR(Links!F25,0)+IFERROR(Links!F36,0)+IFERROR(Links!F47,0)</f>
-        <v>686.3004941</v>
+        <v>687.3004941</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">IFERROR(Links!G14,0)+IFERROR(Links!G25,0)+IFERROR(Links!G36,0)+IFERROR(Links!G47,0)</f>
-        <v>1200.3581519</v>
+        <v>1200.4381519</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">IFERROR(Links!H14,0)+IFERROR(Links!H25,0)+IFERROR(Links!H36,0)+IFERROR(Links!H47,0)</f>
-        <v>1735.605032</v>
+        <v>1735.685032</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">IFERROR(Links!I14,0)+IFERROR(Links!I25,0)+IFERROR(Links!I36,0)+IFERROR(Links!I47,0)</f>
-        <v>2334.880545</v>
+        <v>2335.960545</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">IFERROR(Links!J14,0)+IFERROR(Links!J25,0)+IFERROR(Links!J36,0)+IFERROR(Links!J47,0)</f>
-        <v>2951.404812</v>
+        <v>2951.564812</v>
       </c>
       <c r="K9" s="11" t="n">
         <f aca="false">IFERROR(Links!K14,0)+IFERROR(Links!K25,0)+IFERROR(Links!K36,0)+IFERROR(Links!K47,0)</f>
-        <v>3355.190054</v>
+        <v>3355.350054</v>
       </c>
       <c r="L9" s="11" t="n">
         <f aca="false">IFERROR(Links!L14,0)+IFERROR(Links!L25,0)+IFERROR(Links!L36,0)+IFERROR(Links!L47,0)</f>
-        <v>3862.768079</v>
+        <v>3862.928079</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7878,27 +7878,27 @@
       </c>
       <c r="G10" s="11" t="n">
         <f aca="false">IFERROR(Links!G15,0)+IFERROR(Links!G26,0)+IFERROR(Links!G37,0)+IFERROR(Links!G48,0)</f>
-        <v>251.2760035</v>
+        <v>252.2760035</v>
       </c>
       <c r="H10" s="11" t="n">
         <f aca="false">IFERROR(Links!H15,0)+IFERROR(Links!H26,0)+IFERROR(Links!H37,0)+IFERROR(Links!H48,0)</f>
-        <v>349.4944827</v>
+        <v>349.5744827</v>
       </c>
       <c r="I10" s="11" t="n">
         <f aca="false">IFERROR(Links!I15,0)+IFERROR(Links!I26,0)+IFERROR(Links!I37,0)+IFERROR(Links!I48,0)</f>
-        <v>465.3882332</v>
+        <v>465.4682332</v>
       </c>
       <c r="J10" s="11" t="n">
         <f aca="false">IFERROR(Links!J15,0)+IFERROR(Links!J26,0)+IFERROR(Links!J37,0)+IFERROR(Links!J48,0)</f>
-        <v>586.6486707</v>
+        <v>586.7286707</v>
       </c>
       <c r="K10" s="11" t="n">
         <f aca="false">IFERROR(Links!K15,0)+IFERROR(Links!K26,0)+IFERROR(Links!K37,0)+IFERROR(Links!K48,0)</f>
-        <v>672.5074156</v>
+        <v>672.5874156</v>
       </c>
       <c r="L10" s="11" t="n">
         <f aca="false">IFERROR(Links!L15,0)+IFERROR(Links!L26,0)+IFERROR(Links!L37,0)+IFERROR(Links!L48,0)</f>
-        <v>777.2305332</v>
+        <v>777.3105332</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7926,27 +7926,27 @@
       </c>
       <c r="G11" s="11" t="n">
         <f aca="false">IFERROR(Links!G16,0)+IFERROR(Links!G27,0)+IFERROR(Links!G38,0)+IFERROR(Links!G49,0)</f>
-        <v>552.0072077</v>
+        <v>554.0072077</v>
       </c>
       <c r="H11" s="11" t="n">
         <f aca="false">IFERROR(Links!H16,0)+IFERROR(Links!H27,0)+IFERROR(Links!H38,0)+IFERROR(Links!H49,0)</f>
-        <v>769.975862</v>
+        <v>769.135862</v>
       </c>
       <c r="I11" s="11" t="n">
         <f aca="false">IFERROR(Links!I16,0)+IFERROR(Links!I27,0)+IFERROR(Links!I38,0)+IFERROR(Links!I49,0)</f>
-        <v>1024.1901129</v>
+        <v>1025.2701129</v>
       </c>
       <c r="J11" s="11" t="n">
         <f aca="false">IFERROR(Links!J16,0)+IFERROR(Links!J27,0)+IFERROR(Links!J38,0)+IFERROR(Links!J49,0)</f>
-        <v>1290.9470756</v>
+        <v>1292.1070756</v>
       </c>
       <c r="K11" s="11" t="n">
         <f aca="false">IFERROR(Links!K16,0)+IFERROR(Links!K27,0)+IFERROR(Links!K38,0)+IFERROR(Links!K49,0)</f>
-        <v>1479.4203143</v>
+        <v>1479.6603143</v>
       </c>
       <c r="L11" s="11" t="n">
         <f aca="false">IFERROR(Links!L16,0)+IFERROR(Links!L27,0)+IFERROR(Links!L38,0)+IFERROR(Links!L49,0)</f>
-        <v>1710.1951731</v>
+        <v>1708.4351731</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7974,27 +7974,27 @@
       </c>
       <c r="G12" s="11" t="n">
         <f aca="false">IFERROR(Links!G17,0)+IFERROR(Links!G28,0)+IFERROR(Links!G39,0)+IFERROR(Links!G50,0)</f>
-        <v>121.26048167</v>
+        <v>122.26048167</v>
       </c>
       <c r="H12" s="11" t="n">
         <f aca="false">IFERROR(Links!H17,0)+IFERROR(Links!H28,0)+IFERROR(Links!H39,0)+IFERROR(Links!H50,0)</f>
-        <v>168.4485517</v>
+        <v>167.5285517</v>
       </c>
       <c r="I12" s="11" t="n">
         <f aca="false">IFERROR(Links!I17,0)+IFERROR(Links!I28,0)+IFERROR(Links!I39,0)+IFERROR(Links!I50,0)</f>
-        <v>223.4807519</v>
+        <v>224.4807519</v>
       </c>
       <c r="J12" s="11" t="n">
         <f aca="false">IFERROR(Links!J17,0)+IFERROR(Links!J28,0)+IFERROR(Links!J39,0)+IFERROR(Links!J50,0)</f>
-        <v>282.5673619</v>
+        <v>281.6473619</v>
       </c>
       <c r="K12" s="11" t="n">
         <f aca="false">IFERROR(Links!K17,0)+IFERROR(Links!K28,0)+IFERROR(Links!K39,0)+IFERROR(Links!K50,0)</f>
-        <v>322.8211595</v>
+        <v>323.8211595</v>
       </c>
       <c r="L12" s="11" t="n">
         <f aca="false">IFERROR(Links!L17,0)+IFERROR(Links!L28,0)+IFERROR(Links!L39,0)+IFERROR(Links!L50,0)</f>
-        <v>373.049856</v>
+        <v>374.129856</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8030,11 +8030,11 @@
       </c>
       <c r="I13" s="11" t="n">
         <f aca="false">IFERROR(Links!I18,0)+IFERROR(Links!I29,0)+IFERROR(Links!I40,0)+IFERROR(Links!I51,0)</f>
-        <v>148.89383461</v>
+        <v>149.89383461</v>
       </c>
       <c r="J13" s="11" t="n">
         <f aca="false">IFERROR(Links!J18,0)+IFERROR(Links!J29,0)+IFERROR(Links!J40,0)+IFERROR(Links!J51,0)</f>
-        <v>187.4315746</v>
+        <v>186.5115746</v>
       </c>
       <c r="K13" s="11" t="n">
         <f aca="false">IFERROR(Links!K18,0)+IFERROR(Links!K29,0)+IFERROR(Links!K40,0)+IFERROR(Links!K51,0)</f>
@@ -8051,43 +8051,43 @@
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">SUM(C6:C13)</f>
-        <v>6998.58027218</v>
+        <v>6999.58027218</v>
       </c>
       <c r="D14" s="11" t="n">
         <f aca="false">SUM(D6:D13)</f>
-        <v>11057.38619482</v>
+        <v>11067.46619482</v>
       </c>
       <c r="E14" s="11" t="n">
         <f aca="false">SUM(E6:E13)</f>
-        <v>23240.36634636</v>
+        <v>23251.24634636</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">SUM(F6:F13)</f>
-        <v>51225.82894185</v>
+        <v>51247.50894185</v>
       </c>
       <c r="G14" s="11" t="n">
         <f aca="false">SUM(G6:G13)</f>
-        <v>89176.18954189</v>
+        <v>89202.46954189</v>
       </c>
       <c r="H14" s="11" t="n">
         <f aca="false">SUM(H6:H13)</f>
-        <v>125212.23002987</v>
+        <v>125234.35002987</v>
       </c>
       <c r="I14" s="11" t="n">
         <f aca="false">SUM(I6:I13)</f>
-        <v>172617.10210161</v>
+        <v>172644.58210161</v>
       </c>
       <c r="J14" s="11" t="n">
         <f aca="false">SUM(J6:J13)</f>
-        <v>220517.7709318</v>
+        <v>220532.9309318</v>
       </c>
       <c r="K14" s="11" t="n">
         <f aca="false">SUM(K6:K13)</f>
-        <v>248869.9466494</v>
+        <v>248887.6666494</v>
       </c>
       <c r="L14" s="11" t="n">
         <f aca="false">SUM(L6:L13)</f>
-        <v>287551.4465059</v>
+        <v>287569.8865059</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="B23" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$52,I10)</f>
-        <v>7.11095864376074</v>
+        <v>7.11198427852906</v>
       </c>
       <c r="C23" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$53,P10)</f>
@@ -10595,11 +10595,11 @@
       </c>
       <c r="D23" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$54,R10)</f>
-        <v>4.11095864376074</v>
+        <v>4.11198427852906</v>
       </c>
       <c r="E23" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$55,O10/N10)</f>
-        <v>2.05547932188037</v>
+        <v>2.05599213926453</v>
       </c>
       <c r="F23" s="9" t="n">
         <f aca="false">Datos!$B$32</f>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B24" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$52,I11)</f>
-        <v>7.11095864376074</v>
+        <v>7.11198427852906</v>
       </c>
       <c r="C24" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$53,P11)</f>
@@ -10625,11 +10625,11 @@
       </c>
       <c r="D24" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$54,R11)</f>
-        <v>4.11095864376074</v>
+        <v>4.11198427852906</v>
       </c>
       <c r="E24" s="20" t="n">
         <f aca="false">IF(Datos!$B$27="SI",Nesting!$B$55,O11/N11)</f>
-        <v>2.05547932188037</v>
+        <v>2.05599213926453</v>
       </c>
       <c r="F24" s="9" t="n">
         <f aca="false">Datos!$B$32</f>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="F64" s="20" t="n">
         <f aca="false">H82+H83+H84</f>
-        <v>5.7717</v>
+        <v>5.7712</v>
       </c>
       <c r="G64" s="28" t="n">
         <f aca="false">MIN(ROUNDDOWN(MIN(B64*Datos!$B$57,Datos!$B$60)*2,0)/2,MAX(Datos!$B$54,ROUNDUP(INDEX(Cálculo!$C$80:$L$80,Datos!$B$6-2025)/12*Datos!$B$52*2,0)/2))</f>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="H81" s="22" t="n">
         <f aca="false">E81*$E$85+F81*$F$85+G81*$G$85</f>
-        <v>0.9061</v>
+        <v>0.9062</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="H82" s="22" t="n">
         <f aca="false">E82*$E$85+F82*$F$85+G82*$G$85</f>
-        <v>0.5367</v>
+        <v>0.5365</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="H83" s="22" t="n">
         <f aca="false">E83*$E$85+F83*$F$85+G83*$G$85</f>
-        <v>0.4833</v>
+        <v>0.4839</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H84" s="22" t="n">
         <f aca="false">E84*$E$85+F84*$F$85+G84*$G$85</f>
-        <v>4.7517</v>
+        <v>4.7508</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12578,13 +12578,13 @@
         <v>486</v>
       </c>
       <c r="E85" s="17" t="n">
-        <v>0.745</v>
+        <v>0.7449</v>
       </c>
       <c r="F85" s="17" t="n">
-        <v>0.1611</v>
+        <v>0.1613</v>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.0939</v>
+        <v>0.0938</v>
       </c>
       <c r="H85" s="7" t="str">
         <f aca="false">IF(ABS(SUM(E85:G85)-1)&lt;0.001,"Suma 100 %","Revisar: no suma 100 %")</f>
@@ -14438,11 +14438,11 @@
       </c>
       <c r="B43" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)</f>
-        <v>777.2305332</v>
+        <v>777.3105332</v>
       </c>
       <c r="C43" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)</f>
-        <v>777.2305332</v>
+        <v>777.3105332</v>
       </c>
       <c r="D43" s="9" t="n">
         <f aca="false">C43-B43</f>
@@ -14455,11 +14455,11 @@
       </c>
       <c r="B44" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)</f>
-        <v>1710.1951731</v>
+        <v>1708.4351731</v>
       </c>
       <c r="C44" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)</f>
-        <v>1710.1951731</v>
+        <v>1708.4351731</v>
       </c>
       <c r="D44" s="9" t="n">
         <f aca="false">C44-B44</f>
@@ -14472,15 +14472,15 @@
       </c>
       <c r="B45" s="30" t="n">
         <f aca="false">INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)/Corte!$I$10+INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)/Corte!$I$11</f>
-        <v>371.391476983333</v>
+        <v>371.107032538889</v>
       </c>
       <c r="C45" s="30" t="n">
         <f aca="false">INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)</f>
-        <v>349.80173995</v>
+        <v>349.515073283333</v>
       </c>
       <c r="D45" s="30" t="n">
         <f aca="false">C45-B45</f>
-        <v>-21.5897370333334</v>
+        <v>-21.5919592555555</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14489,15 +14489,15 @@
       </c>
       <c r="B46" s="30" t="n">
         <f aca="false">B45*Corte!$W$10/1000</f>
-        <v>42.0890533035672</v>
+        <v>42.0568177835672</v>
       </c>
       <c r="C46" s="30" t="n">
         <f aca="false">C45*Corte!$W$10/1000</f>
-        <v>39.6423315850536</v>
+        <v>39.6098442250536</v>
       </c>
       <c r="D46" s="30" t="n">
         <f aca="false">C46-B46</f>
-        <v>-2.44672171851361</v>
+        <v>-2.4469735585136</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14506,15 +14506,15 @@
       </c>
       <c r="B47" s="10" t="n">
         <f aca="false">(INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)*Piezas!$F$10*Piezas!$G$10+INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)*Piezas!$F$11*Piezas!$G$11)/(B45*Corte!$B$10*Corte!$C$10)</f>
-        <v>0.848792881238399</v>
+        <v>0.848792272206547</v>
       </c>
       <c r="C47" s="10" t="n">
         <f aca="false">(INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)*Piezas!$F$10*Piezas!$G$10+INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025)*Piezas!$F$11*Piezas!$G$11)/(C45*Corte!$B$10*Corte!$C$10)</f>
-        <v>0.901180313914754</v>
+        <v>0.901228031230472</v>
       </c>
       <c r="D47" s="10" t="n">
         <f aca="false">C47-B47</f>
-        <v>0.0523874326763549</v>
+        <v>0.0524357590239243</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14523,15 +14523,15 @@
       </c>
       <c r="B48" s="9" t="n">
         <f aca="false">B46*1000*INDEX(Datos!$C$95:$C$100,MATCH(Piezas!$E$10,Datos!$A$95:$A$100,0))</f>
-        <v>46379.4125299613</v>
+        <v>46343.8910733627</v>
       </c>
       <c r="C48" s="9" t="n">
         <f aca="false">C46*1000*INDEX(Datos!$C$95:$C$100,MATCH(Piezas!$E$10,Datos!$A$95:$A$100,0))</f>
-        <v>43683.2835600245</v>
+        <v>43647.4845920463</v>
       </c>
       <c r="D48" s="9" t="n">
         <f aca="false">C48-B48</f>
-        <v>-2696.12896993672</v>
+        <v>-2696.40648131638</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="B52" s="20" t="n">
         <f aca="false">IF((INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025))=0,0,(INDEX(Cálculo!$C$12:$L$12,Datos!$B$6-2025)+INDEX(Cálculo!$C$13:$L$13,Datos!$B$6-2025))/(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)))</f>
-        <v>7.11095864376074</v>
+        <v>7.11198427852906</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B54" s="20" t="n">
         <f aca="false">IF((INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025))=0,0,(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)*H26+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)*H28+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)*H29)/(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)))</f>
-        <v>4.11095864376074</v>
+        <v>4.11198427852906</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="B55" s="20" t="n">
         <f aca="false">IF((INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025))=0,0,(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)*I26+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)*I28+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)*I29)/(INDEX(Cálculo!$C$50:$L$50,Datos!$B$6-2025)+INDEX(Cálculo!$C$51:$L$51,Datos!$B$6-2025)+INDEX(Cálculo!$C$52:$L$52,Datos!$B$6-2025)))</f>
-        <v>2.05547932188037</v>
+        <v>2.05599213926453</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14799,15 +14799,15 @@
       </c>
       <c r="F69" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$18:$L$18,Datos!$B$6-2025)*Corte!$X$46</f>
-        <v>3585.64778530799</v>
+        <v>3586.1453554975</v>
       </c>
       <c r="G69" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$18:$L$18,Datos!$B$6-2025)*Corte!$Y$46</f>
-        <v>3309.54210548509</v>
+        <v>3310.00136127128</v>
       </c>
       <c r="H69" s="9" t="n">
         <f aca="false">F69-G69</f>
-        <v>276.105679822898</v>
+        <v>276.143994226225</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14833,15 +14833,15 @@
       </c>
       <c r="F70" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$19:$L$19,Datos!$B$6-2025)*Corte!$X$47</f>
-        <v>2905.28854171244</v>
+        <v>2905.69170037633</v>
       </c>
       <c r="G70" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$19:$L$19,Datos!$B$6-2025)*Corte!$Y$47</f>
-        <v>2678.38641983267</v>
+        <v>2678.75809193163</v>
       </c>
       <c r="H70" s="9" t="n">
         <f aca="false">F70-G70</f>
-        <v>226.902121879776</v>
+        <v>226.9336084447</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14867,15 +14867,15 @@
       </c>
       <c r="F71" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$20:$L$20,Datos!$B$6-2025)*Corte!$X$48</f>
-        <v>32893.9792772413</v>
+        <v>32902.6980003348</v>
       </c>
       <c r="G71" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$20:$L$20,Datos!$B$6-2025)*Corte!$Y$48</f>
-        <v>30355.6872980687</v>
+        <v>30363.7332334551</v>
       </c>
       <c r="H71" s="9" t="n">
         <f aca="false">F71-G71</f>
-        <v>2538.29197917261</v>
+        <v>2538.96476687976</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14901,15 +14901,15 @@
       </c>
       <c r="F72" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$21:$L$21,Datos!$B$6-2025)*Corte!$X$49</f>
-        <v>24679.5082420288</v>
+        <v>24686.0496761506</v>
       </c>
       <c r="G72" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$21:$L$21,Datos!$B$6-2025)*Corte!$Y$49</f>
-        <v>22736.8172700069</v>
+        <v>22742.843783617</v>
       </c>
       <c r="H72" s="9" t="n">
         <f aca="false">F72-G72</f>
-        <v>1942.69097202186</v>
+        <v>1943.20589253356</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14935,15 +14935,15 @@
       </c>
       <c r="F73" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$22:$L$22,Datos!$B$6-2025)*Corte!$X$50</f>
-        <v>2729.31026707074</v>
+        <v>2729.42331803155</v>
       </c>
       <c r="G73" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$22:$L$22,Datos!$B$6-2025)*Corte!$Y$50</f>
-        <v>2522.7158978905</v>
+        <v>2522.82039149079</v>
       </c>
       <c r="H73" s="9" t="n">
         <f aca="false">F73-G73</f>
-        <v>206.594369180234</v>
+        <v>206.602926540758</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14969,15 +14969,15 @@
       </c>
       <c r="F74" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$23:$L$23,Datos!$B$6-2025)*Corte!$X$51</f>
-        <v>2492.79875210186</v>
+        <v>2492.90200650186</v>
       </c>
       <c r="G74" s="9" t="n">
         <f aca="false">INDEX(Cálculo!$C$23:$L$23,Datos!$B$6-2025)*Corte!$Y$51</f>
-        <v>2294.22030805734</v>
+        <v>2294.31533712504</v>
       </c>
       <c r="H74" s="9" t="n">
         <f aca="false">F74-G74</f>
-        <v>198.578444044516</v>
+        <v>198.586669376817</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14986,15 +14986,15 @@
       </c>
       <c r="F75" s="11" t="n">
         <f aca="false">SUM(F67:F74)</f>
-        <v>100940.900515505</v>
+        <v>100957.277706935</v>
       </c>
       <c r="G75" s="11" t="n">
         <f aca="false">SUM(G67:G74)</f>
-        <v>92963.8071547285</v>
+        <v>92978.9100542782</v>
       </c>
       <c r="H75" s="11" t="n">
         <f aca="false">SUM(H67:H74)</f>
-        <v>7977.09336077672</v>
+        <v>7978.36765265665</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15228,39 +15228,39 @@
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">Demanda!D7</f>
-        <v>722.1274503</v>
+        <v>724.1274503</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">Demanda!E7</f>
-        <v>1309.8280576</v>
+        <v>1309.9880576</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">Demanda!F7</f>
-        <v>2579.558174</v>
+        <v>2581.718174</v>
       </c>
       <c r="G9" s="9" t="n">
         <f aca="false">Demanda!G7</f>
-        <v>4282.307726</v>
+        <v>4284.627726</v>
       </c>
       <c r="H9" s="9" t="n">
         <f aca="false">Demanda!H7</f>
-        <v>6097.029887</v>
+        <v>6099.509887</v>
       </c>
       <c r="I9" s="9" t="n">
         <f aca="false">Demanda!I7</f>
-        <v>8102.115524</v>
+        <v>8105.755524</v>
       </c>
       <c r="J9" s="9" t="n">
         <f aca="false">Demanda!J7</f>
-        <v>10259.186587</v>
+        <v>10259.066587</v>
       </c>
       <c r="K9" s="9" t="n">
         <f aca="false">Demanda!K7</f>
-        <v>11964.986243</v>
+        <v>11967.786243</v>
       </c>
       <c r="L9" s="9" t="n">
         <f aca="false">Demanda!L7</f>
-        <v>14124.378444</v>
+        <v>14126.338444</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15272,43 +15272,43 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">Demanda!C8</f>
-        <v>2280.773025</v>
+        <v>2281.773025</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">Demanda!D8</f>
-        <v>3920.978881</v>
+        <v>3928.058881</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">Demanda!E8</f>
-        <v>6700.097591</v>
+        <v>6711.737591</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">Demanda!F8</f>
-        <v>12185.475313</v>
+        <v>12203.995313</v>
       </c>
       <c r="G10" s="9" t="n">
         <f aca="false">Demanda!G8</f>
-        <v>20572.90694</v>
+        <v>20592.78694</v>
       </c>
       <c r="H10" s="9" t="n">
         <f aca="false">Demanda!H8</f>
-        <v>28680.36411</v>
+        <v>28701.60411</v>
       </c>
       <c r="I10" s="9" t="n">
         <f aca="false">Demanda!I8</f>
-        <v>38644.99984</v>
+        <v>38664.59984</v>
       </c>
       <c r="J10" s="9" t="n">
         <f aca="false">Demanda!J8</f>
-        <v>48826.50637</v>
+        <v>48842.22637</v>
       </c>
       <c r="K10" s="9" t="n">
         <f aca="false">Demanda!K8</f>
-        <v>55467.92455</v>
+        <v>55481.36455</v>
       </c>
       <c r="L10" s="9" t="n">
         <f aca="false">Demanda!L8</f>
-        <v>63835.73872</v>
+        <v>63852.65872</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15324,39 +15324,39 @@
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">Demanda!D9</f>
-        <v>181.4872967</v>
+        <v>182.4872967</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">Demanda!E9</f>
-        <v>352.9387798</v>
+        <v>352.0187798</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">Demanda!F9</f>
-        <v>686.3004941</v>
+        <v>687.3004941</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">Demanda!G9</f>
-        <v>1200.3581519</v>
+        <v>1200.4381519</v>
       </c>
       <c r="H11" s="9" t="n">
         <f aca="false">Demanda!H9</f>
-        <v>1735.605032</v>
+        <v>1735.685032</v>
       </c>
       <c r="I11" s="9" t="n">
         <f aca="false">Demanda!I9</f>
-        <v>2334.880545</v>
+        <v>2335.960545</v>
       </c>
       <c r="J11" s="9" t="n">
         <f aca="false">Demanda!J9</f>
-        <v>2951.404812</v>
+        <v>2951.564812</v>
       </c>
       <c r="K11" s="9" t="n">
         <f aca="false">Demanda!K9</f>
-        <v>3355.190054</v>
+        <v>3355.350054</v>
       </c>
       <c r="L11" s="9" t="n">
         <f aca="false">Demanda!L9</f>
-        <v>3862.768079</v>
+        <v>3862.928079</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15384,27 +15384,27 @@
       </c>
       <c r="G12" s="9" t="n">
         <f aca="false">Demanda!G10</f>
-        <v>251.2760035</v>
+        <v>252.2760035</v>
       </c>
       <c r="H12" s="9" t="n">
         <f aca="false">Demanda!H10</f>
-        <v>349.4944827</v>
+        <v>349.5744827</v>
       </c>
       <c r="I12" s="9" t="n">
         <f aca="false">Demanda!I10</f>
-        <v>465.3882332</v>
+        <v>465.4682332</v>
       </c>
       <c r="J12" s="9" t="n">
         <f aca="false">Demanda!J10</f>
-        <v>586.6486707</v>
+        <v>586.7286707</v>
       </c>
       <c r="K12" s="9" t="n">
         <f aca="false">Demanda!K10</f>
-        <v>672.5074156</v>
+        <v>672.5874156</v>
       </c>
       <c r="L12" s="9" t="n">
         <f aca="false">Demanda!L10</f>
-        <v>777.2305332</v>
+        <v>777.3105332</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15432,27 +15432,27 @@
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">Demanda!G11</f>
-        <v>552.0072077</v>
+        <v>554.0072077</v>
       </c>
       <c r="H13" s="9" t="n">
         <f aca="false">Demanda!H11</f>
-        <v>769.975862</v>
+        <v>769.135862</v>
       </c>
       <c r="I13" s="9" t="n">
         <f aca="false">Demanda!I11</f>
-        <v>1024.1901129</v>
+        <v>1025.2701129</v>
       </c>
       <c r="J13" s="9" t="n">
         <f aca="false">Demanda!J11</f>
-        <v>1290.9470756</v>
+        <v>1292.1070756</v>
       </c>
       <c r="K13" s="9" t="n">
         <f aca="false">Demanda!K11</f>
-        <v>1479.4203143</v>
+        <v>1479.6603143</v>
       </c>
       <c r="L13" s="9" t="n">
         <f aca="false">Demanda!L11</f>
-        <v>1710.1951731</v>
+        <v>1708.4351731</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15480,27 +15480,27 @@
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">Demanda!G12</f>
-        <v>121.26048167</v>
+        <v>122.26048167</v>
       </c>
       <c r="H14" s="9" t="n">
         <f aca="false">Demanda!H12</f>
-        <v>168.4485517</v>
+        <v>167.5285517</v>
       </c>
       <c r="I14" s="9" t="n">
         <f aca="false">Demanda!I12</f>
-        <v>223.4807519</v>
+        <v>224.4807519</v>
       </c>
       <c r="J14" s="9" t="n">
         <f aca="false">Demanda!J12</f>
-        <v>282.5673619</v>
+        <v>281.6473619</v>
       </c>
       <c r="K14" s="9" t="n">
         <f aca="false">Demanda!K12</f>
-        <v>322.8211595</v>
+        <v>323.8211595</v>
       </c>
       <c r="L14" s="9" t="n">
         <f aca="false">Demanda!L12</f>
-        <v>373.049856</v>
+        <v>374.129856</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15536,11 +15536,11 @@
       </c>
       <c r="I15" s="9" t="n">
         <f aca="false">Demanda!I13</f>
-        <v>148.89383461</v>
+        <v>149.89383461</v>
       </c>
       <c r="J15" s="9" t="n">
         <f aca="false">Demanda!J13</f>
-        <v>187.4315746</v>
+        <v>186.5115746</v>
       </c>
       <c r="K15" s="9" t="n">
         <f aca="false">Demanda!K13</f>
@@ -15660,39 +15660,39 @@
       </c>
       <c r="D18" s="9" t="n">
         <f aca="false">D9</f>
-        <v>722.1274503</v>
+        <v>724.1274503</v>
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">E9</f>
-        <v>1309.8280576</v>
+        <v>1309.9880576</v>
       </c>
       <c r="F18" s="9" t="n">
         <f aca="false">F9</f>
-        <v>2579.558174</v>
+        <v>2581.718174</v>
       </c>
       <c r="G18" s="9" t="n">
         <f aca="false">G9</f>
-        <v>4282.307726</v>
+        <v>4284.627726</v>
       </c>
       <c r="H18" s="9" t="n">
         <f aca="false">H9</f>
-        <v>6097.029887</v>
+        <v>6099.509887</v>
       </c>
       <c r="I18" s="9" t="n">
         <f aca="false">I9</f>
-        <v>8102.115524</v>
+        <v>8105.755524</v>
       </c>
       <c r="J18" s="9" t="n">
         <f aca="false">J9</f>
-        <v>10259.186587</v>
+        <v>10259.066587</v>
       </c>
       <c r="K18" s="9" t="n">
         <f aca="false">K9</f>
-        <v>11964.986243</v>
+        <v>11967.786243</v>
       </c>
       <c r="L18" s="9" t="n">
         <f aca="false">L9</f>
-        <v>14124.378444</v>
+        <v>14126.338444</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15708,39 +15708,39 @@
       </c>
       <c r="D19" s="9" t="n">
         <f aca="false">D9</f>
-        <v>722.1274503</v>
+        <v>724.1274503</v>
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">E9</f>
-        <v>1309.8280576</v>
+        <v>1309.9880576</v>
       </c>
       <c r="F19" s="9" t="n">
         <f aca="false">F9</f>
-        <v>2579.558174</v>
+        <v>2581.718174</v>
       </c>
       <c r="G19" s="9" t="n">
         <f aca="false">G9</f>
-        <v>4282.307726</v>
+        <v>4284.627726</v>
       </c>
       <c r="H19" s="9" t="n">
         <f aca="false">H9</f>
-        <v>6097.029887</v>
+        <v>6099.509887</v>
       </c>
       <c r="I19" s="9" t="n">
         <f aca="false">I9</f>
-        <v>8102.115524</v>
+        <v>8105.755524</v>
       </c>
       <c r="J19" s="9" t="n">
         <f aca="false">J9</f>
-        <v>10259.186587</v>
+        <v>10259.066587</v>
       </c>
       <c r="K19" s="9" t="n">
         <f aca="false">K9</f>
-        <v>11964.986243</v>
+        <v>11967.786243</v>
       </c>
       <c r="L19" s="9" t="n">
         <f aca="false">L9</f>
-        <v>14124.378444</v>
+        <v>14126.338444</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15752,43 +15752,43 @@
       </c>
       <c r="C20" s="9" t="n">
         <f aca="false">C10</f>
-        <v>2280.773025</v>
+        <v>2281.773025</v>
       </c>
       <c r="D20" s="9" t="n">
         <f aca="false">D10</f>
-        <v>3920.978881</v>
+        <v>3928.058881</v>
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">E10</f>
-        <v>6700.097591</v>
+        <v>6711.737591</v>
       </c>
       <c r="F20" s="9" t="n">
         <f aca="false">F10</f>
-        <v>12185.475313</v>
+        <v>12203.995313</v>
       </c>
       <c r="G20" s="9" t="n">
         <f aca="false">G10</f>
-        <v>20572.90694</v>
+        <v>20592.78694</v>
       </c>
       <c r="H20" s="9" t="n">
         <f aca="false">H10</f>
-        <v>28680.36411</v>
+        <v>28701.60411</v>
       </c>
       <c r="I20" s="9" t="n">
         <f aca="false">I10</f>
-        <v>38644.99984</v>
+        <v>38664.59984</v>
       </c>
       <c r="J20" s="9" t="n">
         <f aca="false">J10</f>
-        <v>48826.50637</v>
+        <v>48842.22637</v>
       </c>
       <c r="K20" s="9" t="n">
         <f aca="false">K10</f>
-        <v>55467.92455</v>
+        <v>55481.36455</v>
       </c>
       <c r="L20" s="9" t="n">
         <f aca="false">L10</f>
-        <v>63835.73872</v>
+        <v>63852.65872</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15800,43 +15800,43 @@
       </c>
       <c r="C21" s="9" t="n">
         <f aca="false">C10</f>
-        <v>2280.773025</v>
+        <v>2281.773025</v>
       </c>
       <c r="D21" s="9" t="n">
         <f aca="false">D10</f>
-        <v>3920.978881</v>
+        <v>3928.058881</v>
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">E10</f>
-        <v>6700.097591</v>
+        <v>6711.737591</v>
       </c>
       <c r="F21" s="9" t="n">
         <f aca="false">F10</f>
-        <v>12185.475313</v>
+        <v>12203.995313</v>
       </c>
       <c r="G21" s="9" t="n">
         <f aca="false">G10</f>
-        <v>20572.90694</v>
+        <v>20592.78694</v>
       </c>
       <c r="H21" s="9" t="n">
         <f aca="false">H10</f>
-        <v>28680.36411</v>
+        <v>28701.60411</v>
       </c>
       <c r="I21" s="9" t="n">
         <f aca="false">I10</f>
-        <v>38644.99984</v>
+        <v>38664.59984</v>
       </c>
       <c r="J21" s="9" t="n">
         <f aca="false">J10</f>
-        <v>48826.50637</v>
+        <v>48842.22637</v>
       </c>
       <c r="K21" s="9" t="n">
         <f aca="false">K10</f>
-        <v>55467.92455</v>
+        <v>55481.36455</v>
       </c>
       <c r="L21" s="9" t="n">
         <f aca="false">L10</f>
-        <v>63835.73872</v>
+        <v>63852.65872</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15852,39 +15852,39 @@
       </c>
       <c r="D22" s="9" t="n">
         <f aca="false">D11</f>
-        <v>181.4872967</v>
+        <v>182.4872967</v>
       </c>
       <c r="E22" s="9" t="n">
         <f aca="false">E11</f>
-        <v>352.9387798</v>
+        <v>352.0187798</v>
       </c>
       <c r="F22" s="9" t="n">
         <f aca="false">F11</f>
-        <v>686.3004941</v>
+        <v>687.3004941</v>
       </c>
       <c r="G22" s="9" t="n">
         <f aca="false">G11</f>
-        <v>1200.3581519</v>
+        <v>1200.4381519</v>
       </c>
       <c r="H22" s="9" t="n">
         <f aca="false">H11</f>
-        <v>1735.605032</v>
+        <v>1735.685032</v>
       </c>
       <c r="I22" s="9" t="n">
         <f aca="false">I11</f>
-        <v>2334.880545</v>
+        <v>2335.960545</v>
       </c>
       <c r="J22" s="9" t="n">
         <f aca="false">J11</f>
-        <v>2951.404812</v>
+        <v>2951.564812</v>
       </c>
       <c r="K22" s="9" t="n">
         <f aca="false">K11</f>
-        <v>3355.190054</v>
+        <v>3355.350054</v>
       </c>
       <c r="L22" s="9" t="n">
         <f aca="false">L11</f>
-        <v>3862.768079</v>
+        <v>3862.928079</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15900,39 +15900,39 @@
       </c>
       <c r="D23" s="9" t="n">
         <f aca="false">D11</f>
-        <v>181.4872967</v>
+        <v>182.4872967</v>
       </c>
       <c r="E23" s="9" t="n">
         <f aca="false">E11</f>
-        <v>352.9387798</v>
+        <v>352.0187798</v>
       </c>
       <c r="F23" s="9" t="n">
         <f aca="false">F11</f>
-        <v>686.3004941</v>
+        <v>687.3004941</v>
       </c>
       <c r="G23" s="9" t="n">
         <f aca="false">G11</f>
-        <v>1200.3581519</v>
+        <v>1200.4381519</v>
       </c>
       <c r="H23" s="9" t="n">
         <f aca="false">H11</f>
-        <v>1735.605032</v>
+        <v>1735.685032</v>
       </c>
       <c r="I23" s="9" t="n">
         <f aca="false">I11</f>
-        <v>2334.880545</v>
+        <v>2335.960545</v>
       </c>
       <c r="J23" s="9" t="n">
         <f aca="false">J11</f>
-        <v>2951.404812</v>
+        <v>2951.564812</v>
       </c>
       <c r="K23" s="9" t="n">
         <f aca="false">K11</f>
-        <v>3355.190054</v>
+        <v>3355.350054</v>
       </c>
       <c r="L23" s="9" t="n">
         <f aca="false">L11</f>
-        <v>3862.768079</v>
+        <v>3862.928079</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15944,43 +15944,43 @@
       </c>
       <c r="C25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(C$8:C$15,Piezas!$H$6:$H$13)+SUMPRODUCT(C$16:C$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>11.9449774721977</v>
+        <v>11.947608001115</v>
       </c>
       <c r="D25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(D$8:D$15,Piezas!$H$6:$H$13)+SUMPRODUCT(D$16:D$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>19.943902339016</v>
+        <v>19.9706203628595</v>
       </c>
       <c r="E25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(E$8:E$15,Piezas!$H$6:$H$13)+SUMPRODUCT(E$16:E$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>36.0483641302406</v>
+        <v>36.0742495405962</v>
       </c>
       <c r="F25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(F$8:F$15,Piezas!$H$6:$H$13)+SUMPRODUCT(F$16:F$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>70.0520801863879</v>
+        <v>70.1091084548485</v>
       </c>
       <c r="G25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(G$8:G$15,Piezas!$H$6:$H$13)+SUMPRODUCT(G$16:G$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>119.421866410137</v>
+        <v>119.551258631646</v>
       </c>
       <c r="H25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(H$8:H$15,Piezas!$H$6:$H$13)+SUMPRODUCT(H$16:H$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>167.299806541106</v>
+        <v>167.31853826505</v>
       </c>
       <c r="I25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(I$8:I$15,Piezas!$H$6:$H$13)+SUMPRODUCT(I$16:I$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>227.096429333187</v>
+        <v>227.248415237344</v>
       </c>
       <c r="J25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(J$8:J$15,Piezas!$H$6:$H$13)+SUMPRODUCT(J$16:J$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>288.214606279629</v>
+        <v>288.21034405588</v>
       </c>
       <c r="K25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(K$8:K$15,Piezas!$H$6:$H$13)+SUMPRODUCT(K$16:K$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>327.122786687787</v>
+        <v>327.198274018411</v>
       </c>
       <c r="L25" s="32" t="n">
         <f aca="false">(SUMPRODUCT(L$8:L$15,Piezas!$H$6:$H$13)+SUMPRODUCT(L$16:L$23,Piezas!$S$18:$S$25))/1000</f>
-        <v>377.63954906062</v>
+        <v>377.693422636733</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15997,43 +15997,43 @@
       </c>
       <c r="C28" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15,Corte!$F$32:$F$39)/1000</f>
-        <v>10.2047701967592</v>
+        <v>10.2067760580657</v>
       </c>
       <c r="D28" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15,Corte!$F$32:$F$39)/1000</f>
-        <v>16.97739121086</v>
+        <v>16.9982047612553</v>
       </c>
       <c r="E28" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15,Corte!$F$32:$F$39)/1000</f>
-        <v>30.4301574679783</v>
+        <v>30.4495736728494</v>
       </c>
       <c r="F28" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15,Corte!$F$32:$F$39)/1000</f>
-        <v>58.7925651485816</v>
+        <v>58.8364978377172</v>
       </c>
       <c r="G28" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15,Corte!$F$32:$F$39)/1000</f>
-        <v>100.069365182897</v>
+        <v>100.19256042016</v>
       </c>
       <c r="H28" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15,Corte!$F$32:$F$39)/1000</f>
-        <v>140.157283249732</v>
+        <v>140.158644722821</v>
       </c>
       <c r="I28" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15,Corte!$F$32:$F$39)/1000</f>
-        <v>190.121382063911</v>
+        <v>190.264612846044</v>
       </c>
       <c r="J28" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15,Corte!$F$32:$F$39)/1000</f>
-        <v>241.246290761434</v>
+        <v>241.233205581359</v>
       </c>
       <c r="K28" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15,Corte!$F$32:$F$39)/1000</f>
-        <v>273.91063527891</v>
+        <v>273.978530928977</v>
       </c>
       <c r="L28" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15,Corte!$F$32:$F$39)/1000</f>
-        <v>316.249801347332</v>
+        <v>316.288523528298</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16045,43 +16045,43 @@
       </c>
       <c r="C29" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15,Corte!$G$32:$G$39)</f>
-        <v>12383.7807740959</v>
+        <v>12386.2892240114</v>
       </c>
       <c r="D29" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15,Corte!$G$32:$G$39)</f>
-        <v>20620.7050377513</v>
+        <v>20646.7884568384</v>
       </c>
       <c r="E29" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15,Corte!$G$32:$G$39)</f>
-        <v>37148.0310270457</v>
+        <v>37172.2617167448</v>
       </c>
       <c r="F29" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15,Corte!$G$32:$G$39)</f>
-        <v>72059.4473710889</v>
+        <v>72114.4426603191</v>
       </c>
       <c r="G29" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15,Corte!$G$32:$G$39)</f>
-        <v>122764.804323169</v>
+        <v>122907.861500587</v>
       </c>
       <c r="H29" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15,Corte!$G$32:$G$39)</f>
-        <v>171979.101486817</v>
+        <v>171986.865560829</v>
       </c>
       <c r="I29" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15,Corte!$G$32:$G$39)</f>
-        <v>233400.186573223</v>
+        <v>233566.340568906</v>
       </c>
       <c r="J29" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15,Corte!$G$32:$G$39)</f>
-        <v>296213.417553126</v>
+        <v>296203.247513899</v>
       </c>
       <c r="K29" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15,Corte!$G$32:$G$39)</f>
-        <v>336249.628657763</v>
+        <v>336329.453347735</v>
       </c>
       <c r="L29" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15,Corte!$G$32:$G$39)</f>
-        <v>388214.382638995</v>
+        <v>388262.547470161</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16093,43 +16093,43 @@
       </c>
       <c r="C30" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$16:C$23,Corte!$I$44:$I$51)/1000</f>
-        <v>2.97593908665771</v>
+        <v>2.97684098720235</v>
       </c>
       <c r="D30" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$16:D$23,Corte!$I$44:$I$51)/1000</f>
-        <v>5.05047245641396</v>
+        <v>5.05912893185002</v>
       </c>
       <c r="E30" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$16:E$23,Corte!$I$44:$I$51)/1000</f>
-        <v>9.38937108822696</v>
+        <v>9.39869898362792</v>
       </c>
       <c r="F30" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$16:F$23,Corte!$I$44:$I$51)/1000</f>
-        <v>18.5965186846321</v>
+        <v>18.6155664311849</v>
       </c>
       <c r="G30" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$16:G$23,Corte!$I$44:$I$51)/1000</f>
-        <v>31.8494192895008</v>
+        <v>31.8685233938556</v>
       </c>
       <c r="H30" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$16:H$23,Corte!$I$44:$I$51)/1000</f>
-        <v>44.6536343771726</v>
+        <v>44.6740385951541</v>
       </c>
       <c r="I30" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$16:I$23,Corte!$I$44:$I$51)/1000</f>
-        <v>60.7422266531947</v>
+        <v>60.7630367472115</v>
       </c>
       <c r="J30" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$16:J$23,Corte!$I$44:$I$51)/1000</f>
-        <v>77.1332060155806</v>
+        <v>77.1475450508387</v>
       </c>
       <c r="K30" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$16:K$23,Corte!$I$44:$I$51)/1000</f>
-        <v>87.4617936142496</v>
+        <v>87.4754182184353</v>
       </c>
       <c r="L30" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$16:L$23,Corte!$I$44:$I$51)/1000</f>
-        <v>100.940900515505</v>
+        <v>100.957277706935</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16141,43 +16141,43 @@
       </c>
       <c r="C31" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$16:C$23,Corte!$J$44:$J$51)</f>
-        <v>3549.41700964878</v>
+        <v>3550.48666369473</v>
       </c>
       <c r="D31" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$16:D$23,Corte!$J$44:$J$51)</f>
-        <v>6018.8486031533</v>
+        <v>6029.12292710047</v>
       </c>
       <c r="E31" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$16:E$23,Corte!$J$44:$J$51)</f>
-        <v>11205.2808069003</v>
+        <v>11216.3365662922</v>
       </c>
       <c r="F31" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$16:F$23,Corte!$J$44:$J$51)</f>
-        <v>22222.5028010211</v>
+        <v>22245.1011725127</v>
       </c>
       <c r="G31" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$16:G$23,Corte!$J$44:$J$51)</f>
-        <v>38068.3884236941</v>
+        <v>38091.0465109853</v>
       </c>
       <c r="H31" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$16:H$23,Corte!$J$44:$J$51)</f>
-        <v>53374.1635304143</v>
+        <v>53398.3635524667</v>
       </c>
       <c r="I31" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$16:I$23,Corte!$J$44:$J$51)</f>
-        <v>72617.961828875</v>
+        <v>72642.6509639854</v>
       </c>
       <c r="J31" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$16:J$23,Corte!$J$44:$J$51)</f>
-        <v>92220.9259531029</v>
+        <v>92237.9332879718</v>
       </c>
       <c r="K31" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$16:K$23,Corte!$J$44:$J$51)</f>
-        <v>104562.338702931</v>
+        <v>104578.498722548</v>
       </c>
       <c r="L31" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$16:L$23,Corte!$J$44:$J$51)</f>
-        <v>120677.715022721</v>
+        <v>120697.139610809</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16189,43 +16189,43 @@
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">C28+C30</f>
-        <v>13.1807092834169</v>
+        <v>13.1836170452681</v>
       </c>
       <c r="D32" s="30" t="n">
         <f aca="false">D28+D30</f>
-        <v>22.027863667274</v>
+        <v>22.0573336931053</v>
       </c>
       <c r="E32" s="30" t="n">
         <f aca="false">E28+E30</f>
-        <v>39.8195285562053</v>
+        <v>39.8482726564773</v>
       </c>
       <c r="F32" s="30" t="n">
         <f aca="false">F28+F30</f>
-        <v>77.3890838332137</v>
+        <v>77.4520642689021</v>
       </c>
       <c r="G32" s="30" t="n">
         <f aca="false">G28+G30</f>
-        <v>131.918784472398</v>
+        <v>132.061083814016</v>
       </c>
       <c r="H32" s="30" t="n">
         <f aca="false">H28+H30</f>
-        <v>184.810917626905</v>
+        <v>184.832683317975</v>
       </c>
       <c r="I32" s="30" t="n">
         <f aca="false">I28+I30</f>
-        <v>250.863608717106</v>
+        <v>251.027649593255</v>
       </c>
       <c r="J32" s="30" t="n">
         <f aca="false">J28+J30</f>
-        <v>318.379496777015</v>
+        <v>318.380750632198</v>
       </c>
       <c r="K32" s="30" t="n">
         <f aca="false">K28+K30</f>
-        <v>361.37242889316</v>
+        <v>361.453949147413</v>
       </c>
       <c r="L32" s="30" t="n">
         <f aca="false">L28+L30</f>
-        <v>417.190701862837</v>
+        <v>417.245801235233</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16237,43 +16237,43 @@
       </c>
       <c r="C33" s="9" t="n">
         <f aca="false">C29+C31</f>
-        <v>15933.1977837446</v>
+        <v>15936.7758877061</v>
       </c>
       <c r="D33" s="9" t="n">
         <f aca="false">D29+D31</f>
-        <v>26639.5536409046</v>
+        <v>26675.9113839389</v>
       </c>
       <c r="E33" s="9" t="n">
         <f aca="false">E29+E31</f>
-        <v>48353.3118339459</v>
+        <v>48388.598283037</v>
       </c>
       <c r="F33" s="9" t="n">
         <f aca="false">F29+F31</f>
-        <v>94281.95017211</v>
+        <v>94359.5438328318</v>
       </c>
       <c r="G33" s="9" t="n">
         <f aca="false">G29+G31</f>
-        <v>160833.192746863</v>
+        <v>160998.908011572</v>
       </c>
       <c r="H33" s="9" t="n">
         <f aca="false">H29+H31</f>
-        <v>225353.265017231</v>
+        <v>225385.229113295</v>
       </c>
       <c r="I33" s="9" t="n">
         <f aca="false">I29+I31</f>
-        <v>306018.148402098</v>
+        <v>306208.991532891</v>
       </c>
       <c r="J33" s="9" t="n">
         <f aca="false">J29+J31</f>
-        <v>388434.343506229</v>
+        <v>388441.180801871</v>
       </c>
       <c r="K33" s="9" t="n">
         <f aca="false">K29+K31</f>
-        <v>440811.967360693</v>
+        <v>440907.952070283</v>
       </c>
       <c r="L33" s="9" t="n">
         <f aca="false">L29+L31</f>
-        <v>508892.097661716</v>
+        <v>508959.687080971</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16285,43 +16285,43 @@
       </c>
       <c r="C34" s="30" t="n">
         <f aca="false">C32-C25</f>
-        <v>1.23573181121919</v>
+        <v>1.23600904415307</v>
       </c>
       <c r="D34" s="30" t="n">
         <f aca="false">D32-D25</f>
-        <v>2.08396132825798</v>
+        <v>2.08671333024581</v>
       </c>
       <c r="E34" s="30" t="n">
         <f aca="false">E32-E25</f>
-        <v>3.77116442596473</v>
+        <v>3.77402311588109</v>
       </c>
       <c r="F34" s="30" t="n">
         <f aca="false">F32-F25</f>
-        <v>7.33700364682575</v>
+        <v>7.34295581405365</v>
       </c>
       <c r="G34" s="30" t="n">
         <f aca="false">G32-G25</f>
-        <v>12.4969180622603</v>
+        <v>12.5098251823697</v>
       </c>
       <c r="H34" s="30" t="n">
         <f aca="false">H32-H25</f>
-        <v>17.5111110857987</v>
+        <v>17.5141450529251</v>
       </c>
       <c r="I34" s="30" t="n">
         <f aca="false">I32-I25</f>
-        <v>23.7671793839187</v>
+        <v>23.7792343559109</v>
       </c>
       <c r="J34" s="30" t="n">
         <f aca="false">J32-J25</f>
-        <v>30.1648904973857</v>
+        <v>30.1704065763175</v>
       </c>
       <c r="K34" s="30" t="n">
         <f aca="false">K32-K25</f>
-        <v>34.2496422053726</v>
+        <v>34.2556751290021</v>
       </c>
       <c r="L34" s="30" t="n">
         <f aca="false">L32-L25</f>
-        <v>39.5511528022171</v>
+        <v>39.5523785985</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16333,43 +16333,43 @@
       </c>
       <c r="C35" s="9" t="n">
         <f aca="false">-C34*Datos!$B$9</f>
-        <v>-308.932952804798</v>
+        <v>-309.002261038267</v>
       </c>
       <c r="D35" s="9" t="n">
         <f aca="false">-D34*Datos!$B$9</f>
-        <v>-520.990332064496</v>
+        <v>-521.678332561452</v>
       </c>
       <c r="E35" s="9" t="n">
         <f aca="false">-E34*Datos!$B$9</f>
-        <v>-942.791106491182</v>
+        <v>-943.505778970271</v>
       </c>
       <c r="F35" s="9" t="n">
         <f aca="false">-F34*Datos!$B$9</f>
-        <v>-1834.25091170644</v>
+        <v>-1835.73895351341</v>
       </c>
       <c r="G35" s="9" t="n">
         <f aca="false">-G34*Datos!$B$9</f>
-        <v>-3124.22951556507</v>
+        <v>-3127.45629559243</v>
       </c>
       <c r="H35" s="9" t="n">
         <f aca="false">-H34*Datos!$B$9</f>
-        <v>-4377.77777144969</v>
+        <v>-4378.53626323127</v>
       </c>
       <c r="I35" s="9" t="n">
         <f aca="false">-I34*Datos!$B$9</f>
-        <v>-5941.79484597967</v>
+        <v>-5944.80858897772</v>
       </c>
       <c r="J35" s="9" t="n">
         <f aca="false">-J34*Datos!$B$9</f>
-        <v>-7541.22262434642</v>
+        <v>-7542.60164407938</v>
       </c>
       <c r="K35" s="9" t="n">
         <f aca="false">-K34*Datos!$B$9</f>
-        <v>-8562.41055134315</v>
+        <v>-8563.91878225053</v>
       </c>
       <c r="L35" s="9" t="n">
         <f aca="false">-L34*Datos!$B$9</f>
-        <v>-9887.78820055428</v>
+        <v>-9888.094649625</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16381,43 +16381,43 @@
       </c>
       <c r="C36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+C$8:C$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-C$8:C$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+C$8:C$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>1.66808743600872</v>
+        <v>1.66841531718382</v>
       </c>
       <c r="D36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+D$8:D$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-D$8:D$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+D$8:D$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>2.77515048639058</v>
+        <v>2.77855270135904</v>
       </c>
       <c r="E36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+E$8:E$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-E$8:E$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+E$8:E$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>4.97416035534262</v>
+        <v>4.97733415806192</v>
       </c>
       <c r="F36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+F$8:F$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-F$8:F$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+F$8:F$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>9.61032314928737</v>
+        <v>9.61750445424224</v>
       </c>
       <c r="G36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+G$8:G$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-G$8:G$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+G$8:G$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>16.1991926364354</v>
+        <v>16.2143457541028</v>
       </c>
       <c r="H36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+H$8:H$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-H$8:H$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+H$8:H$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>18.8653024841817</v>
+        <v>18.865463494079</v>
       </c>
       <c r="I36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+I$8:I$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-I$8:I$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+I$8:I$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>20.812360848612</v>
+        <v>20.8178697248478</v>
       </c>
       <c r="J36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+J$8:J$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-J$8:J$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+J$8:J$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>22.7787034908244</v>
+        <v>22.7782002146676</v>
       </c>
       <c r="K36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+K$8:K$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-K$8:K$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+K$8:K$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>24.0350244338042</v>
+        <v>24.0376358049607</v>
       </c>
       <c r="L36" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$H$32:$H$39+L$8:L$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12-ABS(Corte!$H$32:$H$39-L$8:L$15*Corte!$F$32:$F$39/1000*Datos!$B$53/12))/4+L$8:L$15*Corte!$F$32:$F$39/1000*Datos!$B$50/52)</f>
-        <v>25.6634538979743</v>
+        <v>25.6649432126269</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16429,43 +16429,43 @@
       </c>
       <c r="C37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+C$16:C$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-C$16:C$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+C$16:C$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>0.486451581472894</v>
+        <v>0.486599007523461</v>
       </c>
       <c r="D37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+D$16:D$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-D$16:D$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+D$16:D$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>0.825557997683051</v>
+        <v>0.826972998475484</v>
       </c>
       <c r="E37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+E$16:E$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-E$16:E$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+E$16:E$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>1.53480104326787</v>
+        <v>1.53632579540072</v>
       </c>
       <c r="F37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+F$16:F$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-F$16:F$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+F$16:F$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>3.03981555421871</v>
+        <v>3.04292912817445</v>
       </c>
       <c r="G37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+G$16:G$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-G$16:G$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+G$16:G$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>4.88270345104098</v>
+        <v>4.88454573928675</v>
       </c>
       <c r="H37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+H$16:H$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-H$16:H$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+H$16:H$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>5.61098535739716</v>
+        <v>5.61192611631349</v>
       </c>
       <c r="I37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+I$16:I$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-I$16:I$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+I$16:I$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>6.43912634947629</v>
+        <v>6.44020283576002</v>
       </c>
       <c r="J37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+J$16:J$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-J$16:J$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+J$16:J$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>7.20474421750203</v>
+        <v>7.20530862565811</v>
       </c>
       <c r="K37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+K$16:K$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-K$16:K$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+K$16:K$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>7.6139151390096</v>
+        <v>7.61443916224751</v>
       </c>
       <c r="L37" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$K$44:$K$51+L$16:L$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12-ABS(Corte!$K$44:$K$51-L$16:L$23*Corte!$I$44:$I$51/1000*Datos!$B$53/12))/4+L$16:L$23*Corte!$I$44:$I$51/1000*Datos!$B$50/52)</f>
-        <v>8.13234232751943</v>
+        <v>8.13297221949749</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16477,43 +16477,43 @@
       </c>
       <c r="C38" s="30" t="n">
         <f aca="false">C36+C37</f>
-        <v>2.15453901748161</v>
+        <v>2.15501432470728</v>
       </c>
       <c r="D38" s="30" t="n">
         <f aca="false">D36+D37</f>
-        <v>3.60070848407363</v>
+        <v>3.60552569983453</v>
       </c>
       <c r="E38" s="30" t="n">
         <f aca="false">E36+E37</f>
-        <v>6.50896139861048</v>
+        <v>6.51365995346263</v>
       </c>
       <c r="F38" s="30" t="n">
         <f aca="false">F36+F37</f>
-        <v>12.6501387035061</v>
+        <v>12.6604335824167</v>
       </c>
       <c r="G38" s="30" t="n">
         <f aca="false">G36+G37</f>
-        <v>21.0818960874764</v>
+        <v>21.0988914933896</v>
       </c>
       <c r="H38" s="30" t="n">
         <f aca="false">H36+H37</f>
-        <v>24.4762878415789</v>
+        <v>24.4773896103925</v>
       </c>
       <c r="I38" s="30" t="n">
         <f aca="false">I36+I37</f>
-        <v>27.2514871980883</v>
+        <v>27.2580725606078</v>
       </c>
       <c r="J38" s="30" t="n">
         <f aca="false">J36+J37</f>
-        <v>29.9834477083264</v>
+        <v>29.9835088403258</v>
       </c>
       <c r="K38" s="30" t="n">
         <f aca="false">K36+K37</f>
-        <v>31.6489395728138</v>
+        <v>31.6520749672082</v>
       </c>
       <c r="L38" s="30" t="n">
         <f aca="false">L36+L37</f>
-        <v>33.7957962254937</v>
+        <v>33.7979154321243</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16525,43 +16525,43 @@
       </c>
       <c r="C39" s="9" t="n">
         <f aca="false">IF(C32=0,0,C38*C33/C32*Datos!$B$7)</f>
-        <v>312.535802681145</v>
+        <v>312.605988566542</v>
       </c>
       <c r="D39" s="9" t="n">
         <f aca="false">IF(D32=0,0,D38*D33/D32*Datos!$B$7)</f>
-        <v>522.545090648514</v>
+        <v>523.258261761878</v>
       </c>
       <c r="E39" s="9" t="n">
         <f aca="false">IF(E32=0,0,E38*E33/E32*Datos!$B$7)</f>
-        <v>948.468809050478</v>
+        <v>949.160966321111</v>
       </c>
       <c r="F39" s="9" t="n">
         <f aca="false">IF(F32=0,0,F38*F33/F32*Datos!$B$7)</f>
-        <v>1849.37671491447</v>
+        <v>1850.89874441324</v>
       </c>
       <c r="G39" s="9" t="n">
         <f aca="false">IF(G32=0,0,G38*G33/G32*Datos!$B$7)</f>
-        <v>3084.32374097494</v>
+        <v>3086.66116550214</v>
       </c>
       <c r="H39" s="9" t="n">
         <f aca="false">IF(H32=0,0,H38*H33/H32*Datos!$B$7)</f>
-        <v>3581.48411452832</v>
+        <v>3581.73152046461</v>
       </c>
       <c r="I39" s="9" t="n">
         <f aca="false">IF(I32=0,0,I38*I33/I32*Datos!$B$7)</f>
-        <v>3989.15555566292</v>
+        <v>3989.99883404319</v>
       </c>
       <c r="J39" s="9" t="n">
         <f aca="false">IF(J32=0,0,J38*J33/J32*Datos!$B$7)</f>
-        <v>4389.70509515974</v>
+        <v>4389.77402574475</v>
       </c>
       <c r="K39" s="9" t="n">
         <f aca="false">IF(K32=0,0,K38*K33/K32*Datos!$B$7)</f>
-        <v>4632.74899882187</v>
+        <v>4633.17163986782</v>
       </c>
       <c r="L39" s="9" t="n">
         <f aca="false">IF(L32=0,0,L38*L33/L32*Datos!$B$7)</f>
-        <v>4946.92146010306</v>
+        <v>4947.23534513178</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16573,43 +16573,43 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$16:C$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>2.09598409382219</v>
+        <v>2.09638351499821</v>
       </c>
       <c r="D40" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$16:D$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>3.65747335242606</v>
+        <v>3.6648432935123</v>
       </c>
       <c r="E40" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$16:E$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>7.10178995618229</v>
+        <v>7.10409876479384</v>
       </c>
       <c r="F40" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$16:F$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>14.586834461094</v>
+        <v>14.5989208382059</v>
       </c>
       <c r="G40" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$16:G$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>25.102690622893</v>
+        <v>25.112979758927</v>
       </c>
       <c r="H40" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$16:H$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>35.3906461782305</v>
+        <v>35.4016255848358</v>
       </c>
       <c r="I40" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$16:I$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>48.2038284545877</v>
+        <v>48.2179227963214</v>
       </c>
       <c r="J40" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$16:J$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>61.3035891960178</v>
+        <v>61.3101904142976</v>
       </c>
       <c r="K40" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$16:K$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>69.6247915614529</v>
+        <v>69.63316590379</v>
       </c>
       <c r="L40" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$16:L$23*Corte!$I$44:$I$51/1000/Corte!$K$44:$K$51)</f>
-        <v>80.5778041743391</v>
+        <v>80.5867964490659</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16621,43 +16621,43 @@
       </c>
       <c r="C41" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(C$8:C$15)/(Datos!$B$32*60)+C40*Datos!$B$46/60</f>
-        <v>7.87710238427916</v>
+        <v>7.87831335068428</v>
       </c>
       <c r="D41" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(D$8:D$15)/(Datos!$B$32*60)+D40*Datos!$B$46/60</f>
-        <v>12.6033779589315</v>
+        <v>12.616559333092</v>
       </c>
       <c r="E41" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(E$8:E$15)/(Datos!$B$32*60)+E40*Datos!$B$46/60</f>
-        <v>26.1023082474067</v>
+        <v>26.1148465606707</v>
       </c>
       <c r="F41" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(F$8:F$15)/(Datos!$B$32*60)+F40*Datos!$B$46/60</f>
-        <v>56.8674592813291</v>
+        <v>56.8947086533848</v>
       </c>
       <c r="G41" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(G$8:G$15)/(Datos!$B$32*60)+G40*Datos!$B$46/60</f>
-        <v>98.8141641470955</v>
+        <v>98.8467808755484</v>
       </c>
       <c r="H41" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(H$8:H$15)/(Datos!$B$32*60)+H40*Datos!$B$46/60</f>
-        <v>138.77547946423</v>
+        <v>138.802185426992</v>
       </c>
       <c r="I41" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(I$8:I$15)/(Datos!$B$32*60)+I40*Datos!$B$46/60</f>
-        <v>191.001910337094</v>
+        <v>191.037378366972</v>
       </c>
       <c r="J41" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(J$8:J$15)/(Datos!$B$32*60)+J40*Datos!$B$46/60</f>
-        <v>243.847849007893</v>
+        <v>243.865504868019</v>
       </c>
       <c r="K41" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(K$8:K$15)/(Datos!$B$32*60)+K40*Datos!$B$46/60</f>
-        <v>275.409920443349</v>
+        <v>275.432314028934</v>
       </c>
       <c r="L41" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15/Corte!$C$32:$C$39)/Datos!$B$41+SUM(L$8:L$15)/(Datos!$B$32*60)+L40*Datos!$B$46/60</f>
-        <v>318.251396835488</v>
+        <v>318.274511570836</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16669,43 +16669,43 @@
       </c>
       <c r="C42" s="9" t="n">
         <f aca="false">C41*Datos!$B$15</f>
-        <v>49.4786318130495</v>
+        <v>49.4862382853249</v>
       </c>
       <c r="D42" s="9" t="n">
         <f aca="false">D41*Datos!$B$15</f>
-        <v>79.1658997444581</v>
+        <v>79.2486962255825</v>
       </c>
       <c r="E42" s="9" t="n">
         <f aca="false">E41*Datos!$B$15</f>
-        <v>163.957053779281</v>
+        <v>164.035810986599</v>
       </c>
       <c r="F42" s="9" t="n">
         <f aca="false">F41*Datos!$B$15</f>
-        <v>357.202933599034</v>
+        <v>357.374095732178</v>
       </c>
       <c r="G42" s="9" t="n">
         <f aca="false">G41*Datos!$B$15</f>
-        <v>620.683775230095</v>
+        <v>620.88865146749</v>
       </c>
       <c r="H42" s="9" t="n">
         <f aca="false">H41*Datos!$B$15</f>
-        <v>871.693741951837</v>
+        <v>871.861490755176</v>
       </c>
       <c r="I42" s="9" t="n">
         <f aca="false">I41*Datos!$B$15</f>
-        <v>1199.74487268557</v>
+        <v>1199.96765887087</v>
       </c>
       <c r="J42" s="9" t="n">
         <f aca="false">J41*Datos!$B$15</f>
-        <v>1531.68733258375</v>
+        <v>1531.7982347607</v>
       </c>
       <c r="K42" s="9" t="n">
         <f aca="false">K41*Datos!$B$15</f>
-        <v>1729.93892760285</v>
+        <v>1730.07958896816</v>
       </c>
       <c r="L42" s="9" t="n">
         <f aca="false">L41*Datos!$B$15</f>
-        <v>1999.04011904662</v>
+        <v>1999.18531018721</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16765,43 +16765,43 @@
       </c>
       <c r="C44" s="11" t="n">
         <f aca="false">C33+C35+C39+C42+C43</f>
-        <v>20810.4670448677</v>
+        <v>20814.0536329534</v>
       </c>
       <c r="D44" s="11" t="n">
         <f aca="false">D33+D35+D39+D42+D43</f>
-        <v>31544.4620786668</v>
+        <v>31580.9277887986</v>
       </c>
       <c r="E44" s="11" t="n">
         <f aca="false">E33+E35+E39+E42+E43</f>
-        <v>53347.1343697182</v>
+        <v>53382.4770608082</v>
       </c>
       <c r="F44" s="11" t="n">
         <f aca="false">F33+F35+F39+F42+F43</f>
-        <v>99478.4666883508</v>
+        <v>99556.2654988975</v>
       </c>
       <c r="G44" s="11" t="n">
         <f aca="false">G33+G35+G39+G42+G43</f>
-        <v>166238.158526937</v>
+        <v>166403.189312383</v>
       </c>
       <c r="H44" s="11" t="n">
         <f aca="false">H33+H35+H39+H42+H43</f>
-        <v>230252.852881695</v>
+        <v>230284.473640717</v>
       </c>
       <c r="I44" s="11" t="n">
         <f aca="false">I33+I35+I39+I42+I43</f>
-        <v>310089.4417639</v>
+        <v>310278.337216261</v>
       </c>
       <c r="J44" s="11" t="n">
         <f aca="false">J33+J35+J39+J42+J43</f>
-        <v>391638.70108906</v>
+        <v>391644.339197731</v>
       </c>
       <c r="K44" s="11" t="n">
         <f aca="false">K33+K35+K39+K42+K43</f>
-        <v>443436.432515209</v>
+        <v>443531.472296302</v>
       </c>
       <c r="L44" s="11" t="n">
         <f aca="false">L33+L35+L39+L42+L43</f>
-        <v>510774.458819745</v>
+        <v>510842.200866098</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16834,27 +16834,27 @@
       </c>
       <c r="G47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(G15/Datos!$B$25,G14/Datos!$B$26),0)</f>
-        <v>40.4201605566667</v>
+        <v>40.75349389</v>
       </c>
       <c r="H47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(H15/Datos!$B$25,H14/Datos!$B$26),0)</f>
-        <v>56.1495172333333</v>
+        <v>55.8428505666667</v>
       </c>
       <c r="I47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(I15/Datos!$B$25,I14/Datos!$B$26),0)</f>
-        <v>74.4935839666667</v>
+        <v>74.8269173</v>
       </c>
       <c r="J47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(J15/Datos!$B$25,J14/Datos!$B$26),0)</f>
-        <v>94.1891206333334</v>
+        <v>93.8824539666667</v>
       </c>
       <c r="K47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(K15/Datos!$B$25,K14/Datos!$B$26),0)</f>
-        <v>107.607053166667</v>
+        <v>107.9403865</v>
       </c>
       <c r="L47" s="30" t="n">
         <f aca="false">IF(Datos!$B$24="SI",MIN(L15/Datos!$B$25,L14/Datos!$B$26),0)</f>
-        <v>124.349952</v>
+        <v>124.709952</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16930,27 +16930,27 @@
       </c>
       <c r="G49" s="30" t="n">
         <f aca="false">(G15-Datos!$B$25*G47)/Corte!$I$13</f>
-        <v>13.4067201877778</v>
+        <v>13.2956090766667</v>
       </c>
       <c r="H49" s="30" t="n">
         <f aca="false">(H15-Datos!$B$25*H47)/Corte!$I$13</f>
-        <v>18.2365057455556</v>
+        <v>18.3387279677778</v>
       </c>
       <c r="I49" s="30" t="n">
         <f aca="false">(I15-Datos!$B$25*I47)/Corte!$I$13</f>
-        <v>24.8000835477778</v>
+        <v>25.02230577</v>
       </c>
       <c r="J49" s="30" t="n">
         <f aca="false">(J15-Datos!$B$25*J47)/Corte!$I$13</f>
-        <v>31.0808179888889</v>
+        <v>30.8763735444444</v>
       </c>
       <c r="K49" s="30" t="n">
         <f aca="false">(K15-Datos!$B$25*K47)/Corte!$I$13</f>
-        <v>35.4512399444444</v>
+        <v>35.3401288333333</v>
       </c>
       <c r="L49" s="30" t="n">
         <f aca="false">(L15-Datos!$B$25*L47)/Corte!$I$13</f>
-        <v>41.0322062</v>
+        <v>40.9122062</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16978,27 +16978,27 @@
       </c>
       <c r="G50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(G12/Nesting!$E$26,G13/Nesting!$F$26),0)</f>
-        <v>41.8793339166667</v>
+        <v>42.0460005833333</v>
       </c>
       <c r="H50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(H12/Nesting!$E$26,H13/Nesting!$F$26),0)</f>
-        <v>58.24908045</v>
+        <v>58.2624137833333</v>
       </c>
       <c r="I50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(I12/Nesting!$E$26,I13/Nesting!$F$26),0)</f>
-        <v>77.5647055333333</v>
+        <v>77.5780388666667</v>
       </c>
       <c r="J50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(J12/Nesting!$E$26,J13/Nesting!$F$26),0)</f>
-        <v>97.77477845</v>
+        <v>97.7881117833333</v>
       </c>
       <c r="K50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(K12/Nesting!$E$26,K13/Nesting!$F$26),0)</f>
-        <v>112.084569266667</v>
+        <v>112.0979026</v>
       </c>
       <c r="L50" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",MIN(L12/Nesting!$E$26,L13/Nesting!$F$26),0)</f>
-        <v>129.5384222</v>
+        <v>129.551755533333</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17026,27 +17026,27 @@
       </c>
       <c r="G51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(G13-G50*Nesting!$F$26)/Nesting!$F$28,G13/Corte!$I$11)</f>
-        <v>71.061534325</v>
+        <v>71.311534325</v>
       </c>
       <c r="H51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(H13-H50*Nesting!$F$26)/Nesting!$F$28,H13/Corte!$I$11)</f>
-        <v>99.2047701083333</v>
+        <v>99.0581034416667</v>
       </c>
       <c r="I51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(I13-I50*Nesting!$F$26)/Nesting!$F$28,I13/Corte!$I$11)</f>
-        <v>131.915999383333</v>
+        <v>132.089332716667</v>
       </c>
       <c r="J51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(J13-J50*Nesting!$F$26)/Nesting!$F$28,J13/Corte!$I$11)</f>
-        <v>166.270456708333</v>
+        <v>166.457123375</v>
       </c>
       <c r="K51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(K13-K50*Nesting!$F$26)/Nesting!$F$28,K13/Corte!$I$11)</f>
-        <v>190.52776775</v>
+        <v>190.561101083333</v>
       </c>
       <c r="L51" s="30" t="n">
         <f aca="false">IF(Datos!$B$27="SI",(L13-L50*Nesting!$F$26)/Nesting!$F$28,L13/Corte!$I$11)</f>
-        <v>220.26331775</v>
+        <v>219.96331775</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17106,43 +17106,43 @@
       </c>
       <c r="C53" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9)+C50+C51+C52+C48+C49+C47</f>
-        <v>324.558477752741</v>
+        <v>324.641811086074</v>
       </c>
       <c r="D53" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9)+D50+D51+D52+D48+D49+D47</f>
-        <v>537.941722731944</v>
+        <v>538.672463472685</v>
       </c>
       <c r="E53" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9)+E50+E51+E52+E48+E49+E47</f>
-        <v>1013.12226099981</v>
+        <v>1014.03685359241</v>
       </c>
       <c r="F53" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9)+F50+F51+F52+F48+F49+F47</f>
-        <v>2039.62664863796</v>
+        <v>2041.31664863796</v>
       </c>
       <c r="G53" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9)+G50+G51+G52+G48+G49+G47</f>
-        <v>3500.14747640907</v>
+        <v>3502.53429122389</v>
       </c>
       <c r="H53" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9)+H50+H51+H52+H48+H49+H47</f>
-        <v>4903.40320813352</v>
+        <v>4904.93261554093</v>
       </c>
       <c r="I53" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9)+I50+I51+I52+I48+I49+I47</f>
-        <v>6688.77593172741</v>
+        <v>6691.35830209778</v>
       </c>
       <c r="J53" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9)+J50+J51+J52+J48+J49+J47</f>
-        <v>8504.5448652287</v>
+        <v>8505.54997633982</v>
       </c>
       <c r="K53" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9)+K50+K51+K52+K48+K49+K47</f>
-        <v>9632.44989907963</v>
+        <v>9633.95315833889</v>
       </c>
       <c r="L53" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9)+L50+L51+L52+L48+L49+L47</f>
-        <v>11118.1526605278</v>
+        <v>11119.5992531204</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17154,43 +17154,43 @@
       </c>
       <c r="C54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(C50+C51+C52)*Corte!$W$10+C48*Corte!$W$12+C49*Corte!$W$13+C47*Corte!$W$14)/1000</f>
-        <v>10.7198978774764</v>
+        <v>10.7219965441431</v>
       </c>
       <c r="D54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(D50+D51+D52)*Corte!$W$10+D48*Corte!$W$12+D49*Corte!$W$13+D47*Corte!$W$14)/1000</f>
-        <v>17.796904810445</v>
+        <v>17.8186545756302</v>
       </c>
       <c r="E54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(E50+E51+E52)*Corte!$W$10+E48*Corte!$W$12+E49*Corte!$W$13+E47*Corte!$W$14)/1000</f>
-        <v>31.8269037162956</v>
+        <v>31.8471614927105</v>
       </c>
       <c r="F54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(F50+F51+F52)*Corte!$W$10+F48*Corte!$W$12+F49*Corte!$W$13+F47*Corte!$W$14)/1000</f>
-        <v>61.3745277695772</v>
+        <v>61.4204598178438</v>
       </c>
       <c r="G54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(G50+G51+G52)*Corte!$W$10+G48*Corte!$W$12+G49*Corte!$W$13+G47*Corte!$W$14)/1000</f>
-        <v>104.446636807451</v>
+        <v>104.575854838799</v>
       </c>
       <c r="H54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(H50+H51+H52)*Corte!$W$10+H48*Corte!$W$12+H49*Corte!$W$13+H47*Corte!$W$14)/1000</f>
-        <v>146.260625894478</v>
+        <v>146.258766848908</v>
       </c>
       <c r="I54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(I50+I51+I52)*Corte!$W$10+I48*Corte!$W$12+I49*Corte!$W$13+I47*Corte!$W$14)/1000</f>
-        <v>198.368940176088</v>
+        <v>198.533732566191</v>
       </c>
       <c r="J54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(J50+J51+J52)*Corte!$W$10+J48*Corte!$W$12+J49*Corte!$W$13+J47*Corte!$W$14)/1000</f>
-        <v>251.686910951631</v>
+        <v>251.65721320932</v>
       </c>
       <c r="K54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(K50+K51+K52)*Corte!$W$10+K48*Corte!$W$12+K49*Corte!$W$13+K47*Corte!$W$14)/1000</f>
-        <v>285.769201954118</v>
+        <v>285.843871581377</v>
       </c>
       <c r="L54" s="30" t="n">
         <f aca="false">(SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9*Corte!$W$6:$W$9)+(L50+L51+L52)*Corte!$W$10+L48*Corte!$W$12+L49*Corte!$W$13+L47*Corte!$W$14)/1000</f>
-        <v>329.929950368709</v>
+        <v>329.976226889791</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17202,43 +17202,43 @@
       </c>
       <c r="C55" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(C50+C51+C52)*Corte!$X$10+C48*Corte!$X$12+C49*Corte!$X$13+C47*Corte!$X$14</f>
-        <v>13515.8319046806</v>
+        <v>13518.6179288273</v>
       </c>
       <c r="D55" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(D50+D51+D52)*Corte!$X$10+D48*Corte!$X$12+D49*Corte!$X$13+D47*Corte!$X$14</f>
-        <v>22458.8709932631</v>
+        <v>22487.4410196709</v>
       </c>
       <c r="E55" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(E50+E51+E52)*Corte!$X$10+E48*Corte!$X$12+E49*Corte!$X$13+E47*Corte!$X$14</f>
-        <v>40501.2676034959</v>
+        <v>40528.358467687</v>
       </c>
       <c r="F55" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(F50+F51+F52)*Corte!$X$10+F48*Corte!$X$12+F49*Corte!$X$13+F47*Corte!$X$14</f>
-        <v>78632.5222632994</v>
+        <v>78693.1883195883</v>
       </c>
       <c r="G55" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(G50+G51+G52)*Corte!$X$10+G48*Corte!$X$12+G49*Corte!$X$13+G47*Corte!$X$14</f>
-        <v>134017.689840092</v>
+        <v>134169.623276681</v>
       </c>
       <c r="H55" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(H50+H51+H52)*Corte!$X$10+H48*Corte!$X$12+H49*Corte!$X$13+H47*Corte!$X$14</f>
-        <v>187715.460898824</v>
+        <v>187724.418930982</v>
       </c>
       <c r="I55" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(I50+I51+I52)*Corte!$X$10+I48*Corte!$X$12+I49*Corte!$X$13+I47*Corte!$X$14</f>
-        <v>254815.134497008</v>
+        <v>255006.633952477</v>
       </c>
       <c r="J55" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(J50+J51+J52)*Corte!$X$10+J48*Corte!$X$12+J49*Corte!$X$13+J47*Corte!$X$14</f>
-        <v>323404.44807697</v>
+        <v>323380.217874792</v>
       </c>
       <c r="K55" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(K50+K51+K52)*Corte!$X$10+K48*Corte!$X$12+K49*Corte!$X$13+K47*Corte!$X$14</f>
-        <v>367054.797748087</v>
+        <v>367143.738969776</v>
       </c>
       <c r="L55" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9*Corte!$X$6:$X$9)+(L50+L51+L52)*Corte!$X$10+L48*Corte!$X$12+L49*Corte!$X$13+L47*Corte!$X$14</f>
-        <v>423748.887955503</v>
+        <v>423807.984964498</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17250,43 +17250,43 @@
       </c>
       <c r="C56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+C50*Nesting!$G$26+C51*Nesting!$G$28+C52*Nesting!$G$29+C48*Corte!$P$12+C49*Corte!$P$13+C47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>1.50528126217222</v>
+        <v>1.50555903995</v>
       </c>
       <c r="D56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+D50*Nesting!$G$26+D51*Nesting!$G$28+D52*Nesting!$G$29+D48*Corte!$P$12+D49*Corte!$P$13+D47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>2.44524357369375</v>
+        <v>2.44804357369375</v>
       </c>
       <c r="E56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+E50*Nesting!$G$26+E51*Nesting!$G$28+E52*Nesting!$G$29+E48*Corte!$P$12+E49*Corte!$P$13+E47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>4.90456615725694</v>
+        <v>4.90758837947917</v>
       </c>
       <c r="F56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+F50*Nesting!$G$26+F51*Nesting!$G$28+F52*Nesting!$G$29+F48*Corte!$P$12+F49*Corte!$P$13+F47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>10.4266174616597</v>
+        <v>10.4326396838819</v>
       </c>
       <c r="G56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+G50*Nesting!$G$26+G51*Nesting!$G$28+G52*Nesting!$G$29+G48*Corte!$P$12+G49*Corte!$P$13+G47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>18.0408340740125</v>
+        <v>18.0488979629014</v>
       </c>
       <c r="H56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+H50*Nesting!$G$26+H51*Nesting!$G$28+H52*Nesting!$G$29+H48*Corte!$P$12+H49*Corte!$P$13+H47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>25.3189661901486</v>
+        <v>25.3244773012597</v>
       </c>
       <c r="I56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+I50*Nesting!$G$26+I51*Nesting!$G$28+I52*Nesting!$G$29+I48*Corte!$P$12+I49*Corte!$P$13+I47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>34.7467605468833</v>
+        <v>34.7556494357722</v>
       </c>
       <c r="J56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+J50*Nesting!$G$26+J51*Nesting!$G$28+J52*Nesting!$G$29+J48*Corte!$P$12+J49*Corte!$P$13+J47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>44.3064857730347</v>
+        <v>44.3098302174792</v>
       </c>
       <c r="K56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+K50*Nesting!$G$26+K51*Nesting!$G$28+K52*Nesting!$G$29+K48*Corte!$P$12+K49*Corte!$P$13+K47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>50.0993998226806</v>
+        <v>50.1049053782361</v>
       </c>
       <c r="L56" s="30" t="n">
         <f aca="false">(SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9*Corte!$P$6:$P$9)+L50*Nesting!$G$26+L51*Nesting!$G$28+L52*Nesting!$G$29+L48*Corte!$P$12+L49*Corte!$P$13+L47*Corte!$P$14)/Datos!$B$32/60</f>
-        <v>57.8902704612083</v>
+        <v>57.8957426834306</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17298,43 +17298,43 @@
       </c>
       <c r="C57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(C$8:C$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+C50*Nesting!$H$26+C51*Nesting!$H$28+C52*Nesting!$H$29+C48*Corte!$R$12+C49*Corte!$R$13+C47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>0.973818511136806</v>
+        <v>0.974026844470139</v>
       </c>
       <c r="D57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(D$8:D$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+D50*Nesting!$H$26+D51*Nesting!$H$28+D52*Nesting!$H$29+D48*Corte!$R$12+D49*Corte!$R$13+D47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>1.58195695847384</v>
+        <v>1.58382547699236</v>
       </c>
       <c r="E57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(E$8:E$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+E50*Nesting!$H$26+E51*Nesting!$H$28+E52*Nesting!$H$29+E48*Corte!$R$12+E49*Corte!$R$13+E47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>3.09686207280509</v>
+        <v>3.09911022095324</v>
       </c>
       <c r="F57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(F$8:F$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+F50*Nesting!$H$26+F51*Nesting!$H$28+F52*Nesting!$H$29+F48*Corte!$R$12+F49*Corte!$R$13+F47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>6.44963519926435</v>
+        <v>6.45390186593102</v>
       </c>
       <c r="G57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(G$8:G$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+G50*Nesting!$H$26+G51*Nesting!$H$28+G52*Nesting!$H$29+G48*Corte!$R$12+G49*Corte!$R$13+G47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>11.1327560185431</v>
+        <v>11.138818981506</v>
       </c>
       <c r="H57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(H$8:H$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+H50*Nesting!$H$26+H51*Nesting!$H$28+H52*Nesting!$H$29+H48*Corte!$R$12+H49*Corte!$R$13+H47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>15.609016638712</v>
+        <v>15.6131749720454</v>
       </c>
       <c r="I57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(I$8:I$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+I50*Nesting!$H$26+I51*Nesting!$H$28+I52*Nesting!$H$29+I48*Corte!$R$12+I49*Corte!$R$13+I47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>21.385087950731</v>
+        <v>21.3908814692495</v>
       </c>
       <c r="J57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(J$8:J$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+J50*Nesting!$H$26+J51*Nesting!$H$28+J52*Nesting!$H$29+J48*Corte!$R$12+J49*Corte!$R$13+J47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>27.2418116744792</v>
+        <v>27.2450459337384</v>
       </c>
       <c r="K57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(K$8:K$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+K50*Nesting!$H$26+K51*Nesting!$H$28+K52*Nesting!$H$29+K48*Corte!$R$12+K49*Corte!$R$13+K47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>30.8034095452685</v>
+        <v>30.8068836193426</v>
       </c>
       <c r="L57" s="30" t="n">
         <f aca="false">(SUMPRODUCT(L$8:L$11/Corte!$I$6:$I$9*Corte!$R$6:$R$9)+L50*Nesting!$H$26+L51*Nesting!$H$28+L52*Nesting!$H$29+L48*Corte!$R$12+L49*Corte!$R$13+L47*Corte!$R$14)/Datos!$B$35/60</f>
-        <v>35.5606459682871</v>
+        <v>35.5639524497685</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17346,43 +17346,43 @@
       </c>
       <c r="C58" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11,Corte!$E$55:$E$58)/1000</f>
-        <v>3.32074873524904</v>
+        <v>3.3217745635157</v>
       </c>
       <c r="D58" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11,Corte!$E$55:$E$58)/1000</f>
-        <v>5.6467936531952</v>
+        <v>5.65658163476303</v>
       </c>
       <c r="E58" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11,Corte!$E$55:$E$58)/1000</f>
-        <v>10.452198478162</v>
+        <v>10.4628313734792</v>
       </c>
       <c r="F58" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11,Corte!$E$55:$E$58)/1000</f>
-        <v>20.614687829746</v>
+        <v>20.6362925156716</v>
       </c>
       <c r="G58" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11,Corte!$E$55:$E$58)/1000</f>
-        <v>35.281357011278</v>
+        <v>35.3030490779393</v>
       </c>
       <c r="H58" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11,Corte!$E$55:$E$58)/1000</f>
-        <v>49.459517231543</v>
+        <v>49.4826856536341</v>
       </c>
       <c r="I58" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11,Corte!$E$55:$E$58)/1000</f>
-        <v>67.2434860643128</v>
+        <v>67.2670707933045</v>
       </c>
       <c r="J58" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11,Corte!$E$55:$E$58)/1000</f>
-        <v>85.3674389561632</v>
+        <v>85.3837456155912</v>
       </c>
       <c r="K58" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11,Corte!$E$55:$E$58)/1000</f>
-        <v>96.8158598211794</v>
+        <v>96.8313100211726</v>
       </c>
       <c r="L58" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11,Corte!$E$55:$E$58)/1000</f>
-        <v>111.729405071367</v>
+        <v>111.747998701546</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17394,43 +17394,43 @@
       </c>
       <c r="C59" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11,Corte!$F$55:$F$58)</f>
-        <v>4391.09787631857</v>
+        <v>4392.45968492148</v>
       </c>
       <c r="D59" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11,Corte!$F$55:$F$58)</f>
-        <v>7464.40269422972</v>
+        <v>7477.3245944859</v>
       </c>
       <c r="E59" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11,Corte!$F$55:$F$58)</f>
-        <v>13809.6816558783</v>
+        <v>13823.8253560208</v>
       </c>
       <c r="F59" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11,Corte!$F$55:$F$58)</f>
-        <v>27223.9123848681</v>
+        <v>27252.5181851195</v>
       </c>
       <c r="G59" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11,Corte!$F$55:$F$58)</f>
-        <v>46590.5748387755</v>
+        <v>46619.3249467314</v>
       </c>
       <c r="H59" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11,Corte!$F$55:$F$58)</f>
-        <v>65309.4344869033</v>
+        <v>65340.1414641371</v>
       </c>
       <c r="I59" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11,Corte!$F$55:$F$58)</f>
-        <v>88790.907881232</v>
+        <v>88822.1115374205</v>
       </c>
       <c r="J59" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11,Corte!$F$55:$F$58)</f>
-        <v>112720.083049376</v>
+        <v>112741.72730153</v>
       </c>
       <c r="K59" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11,Corte!$F$55:$F$58)</f>
-        <v>127833.554349814</v>
+        <v>127854.006453151</v>
       </c>
       <c r="L59" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11,Corte!$F$55:$F$58)</f>
-        <v>147518.992613239</v>
+        <v>147543.63356023</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17442,43 +17442,43 @@
       </c>
       <c r="C60" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$11,Corte!$G$55:$G$58)</f>
-        <v>1623.57392728239</v>
+        <v>1623.94059394906</v>
       </c>
       <c r="D60" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$11,Corte!$G$55:$G$58)</f>
-        <v>2663.52423939968</v>
+        <v>2667.04881082825</v>
       </c>
       <c r="E60" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$11,Corte!$G$55:$G$58)</f>
-        <v>5272.18898944011</v>
+        <v>5276.13841801154</v>
       </c>
       <c r="F60" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$11,Corte!$G$55:$G$58)</f>
-        <v>11063.5043170917</v>
+        <v>11071.2664123298</v>
       </c>
       <c r="G60" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$11,Corte!$G$55:$G$58)</f>
-        <v>19116.4114652437</v>
+        <v>19124.3536557199</v>
       </c>
       <c r="H60" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$11,Corte!$G$55:$G$58)</f>
-        <v>26821.5685692028</v>
+        <v>26830.0522834886</v>
       </c>
       <c r="I60" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$11,Corte!$G$55:$G$58)</f>
-        <v>36756.2200558709</v>
+        <v>36764.8060082518</v>
       </c>
       <c r="J60" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$11,Corte!$G$55:$G$58)</f>
-        <v>46831.8558842431</v>
+        <v>46837.6505985288</v>
       </c>
       <c r="K60" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$11,Corte!$G$55:$G$58)</f>
-        <v>52969.1307908091</v>
+        <v>52974.8716479519</v>
       </c>
       <c r="L60" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$11,Corte!$G$55:$G$58)</f>
-        <v>61178.5254871786</v>
+        <v>61185.3173443214</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17490,43 +17490,43 @@
       </c>
       <c r="C61" s="30" t="n">
         <f aca="false">C54+C58</f>
-        <v>14.0406466127255</v>
+        <v>14.0437711076588</v>
       </c>
       <c r="D61" s="30" t="n">
         <f aca="false">D54+D58</f>
-        <v>23.4436984636402</v>
+        <v>23.4752362103932</v>
       </c>
       <c r="E61" s="30" t="n">
         <f aca="false">E54+E58</f>
-        <v>42.2791021944577</v>
+        <v>42.3099928661896</v>
       </c>
       <c r="F61" s="30" t="n">
         <f aca="false">F54+F58</f>
-        <v>81.9892155993232</v>
+        <v>82.0567523335154</v>
       </c>
       <c r="G61" s="30" t="n">
         <f aca="false">G54+G58</f>
-        <v>139.727993818729</v>
+        <v>139.878903916738</v>
       </c>
       <c r="H61" s="30" t="n">
         <f aca="false">H54+H58</f>
-        <v>195.720143126021</v>
+        <v>195.741452502542</v>
       </c>
       <c r="I61" s="30" t="n">
         <f aca="false">I54+I58</f>
-        <v>265.6124262404</v>
+        <v>265.800803359496</v>
       </c>
       <c r="J61" s="30" t="n">
         <f aca="false">J54+J58</f>
-        <v>337.054349907794</v>
+        <v>337.040958824911</v>
       </c>
       <c r="K61" s="30" t="n">
         <f aca="false">K54+K58</f>
-        <v>382.585061775297</v>
+        <v>382.67518160255</v>
       </c>
       <c r="L61" s="30" t="n">
         <f aca="false">L54+L58</f>
-        <v>441.659355440076</v>
+        <v>441.724225591337</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17538,43 +17538,43 @@
       </c>
       <c r="C62" s="9" t="n">
         <f aca="false">C55+C59</f>
-        <v>17906.9297809991</v>
+        <v>17911.0776137488</v>
       </c>
       <c r="D62" s="9" t="n">
         <f aca="false">D55+D59</f>
-        <v>29923.2736874929</v>
+        <v>29964.7656141568</v>
       </c>
       <c r="E62" s="9" t="n">
         <f aca="false">E55+E59</f>
-        <v>54310.9492593743</v>
+        <v>54352.1838237077</v>
       </c>
       <c r="F62" s="9" t="n">
         <f aca="false">F55+F59</f>
-        <v>105856.434648167</v>
+        <v>105945.706504708</v>
       </c>
       <c r="G62" s="9" t="n">
         <f aca="false">G55+G59</f>
-        <v>180608.264678868</v>
+        <v>180788.948223412</v>
       </c>
       <c r="H62" s="9" t="n">
         <f aca="false">H55+H59</f>
-        <v>253024.895385727</v>
+        <v>253064.560395119</v>
       </c>
       <c r="I62" s="9" t="n">
         <f aca="false">I55+I59</f>
-        <v>343606.04237824</v>
+        <v>343828.745489897</v>
       </c>
       <c r="J62" s="9" t="n">
         <f aca="false">J55+J59</f>
-        <v>436124.531126346</v>
+        <v>436121.945176322</v>
       </c>
       <c r="K62" s="9" t="n">
         <f aca="false">K55+K59</f>
-        <v>494888.352097901</v>
+        <v>494997.745422927</v>
       </c>
       <c r="L62" s="9" t="n">
         <f aca="false">L55+L59</f>
-        <v>571267.880568742</v>
+        <v>571351.618524728</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17586,43 +17586,43 @@
       </c>
       <c r="C63" s="30" t="n">
         <f aca="false">C61-C25</f>
-        <v>2.09566914052775</v>
+        <v>2.09616310654378</v>
       </c>
       <c r="D63" s="30" t="n">
         <f aca="false">D61-D25</f>
-        <v>3.49979612462422</v>
+        <v>3.50461584753369</v>
       </c>
       <c r="E63" s="30" t="n">
         <f aca="false">E61-E25</f>
-        <v>6.23073806421711</v>
+        <v>6.23574332559344</v>
       </c>
       <c r="F63" s="30" t="n">
         <f aca="false">F61-F25</f>
-        <v>11.9371354129353</v>
+        <v>11.9476438786669</v>
       </c>
       <c r="G63" s="30" t="n">
         <f aca="false">G61-G25</f>
-        <v>20.3061274085911</v>
+        <v>20.3276452850922</v>
       </c>
       <c r="H63" s="30" t="n">
         <f aca="false">H61-H25</f>
-        <v>28.4203365849152</v>
+        <v>28.4229142374919</v>
       </c>
       <c r="I63" s="30" t="n">
         <f aca="false">I61-I25</f>
-        <v>38.515996907213</v>
+        <v>38.5523881221513</v>
       </c>
       <c r="J63" s="30" t="n">
         <f aca="false">J61-J25</f>
-        <v>48.8397436281654</v>
+        <v>48.8306147690315</v>
       </c>
       <c r="K63" s="30" t="n">
         <f aca="false">K61-K25</f>
-        <v>55.4622750875099</v>
+        <v>55.4769075841392</v>
       </c>
       <c r="L63" s="30" t="n">
         <f aca="false">L61-L25</f>
-        <v>64.0198063794565</v>
+        <v>64.0308029546042</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17634,43 +17634,43 @@
       </c>
       <c r="C64" s="9" t="n">
         <f aca="false">-C63*Datos!$B$9</f>
-        <v>-523.917285131936</v>
+        <v>-524.040776635945</v>
       </c>
       <c r="D64" s="9" t="n">
         <f aca="false">-D63*Datos!$B$9</f>
-        <v>-874.949031156055</v>
+        <v>-876.153961883422</v>
       </c>
       <c r="E64" s="9" t="n">
         <f aca="false">-E63*Datos!$B$9</f>
-        <v>-1557.68451605428</v>
+        <v>-1558.93583139836</v>
       </c>
       <c r="F64" s="9" t="n">
         <f aca="false">-F63*Datos!$B$9</f>
-        <v>-2984.28385323382</v>
+        <v>-2986.91096966673</v>
       </c>
       <c r="G64" s="9" t="n">
         <f aca="false">-G63*Datos!$B$9</f>
-        <v>-5076.53185214776</v>
+        <v>-5081.91132127305</v>
       </c>
       <c r="H64" s="9" t="n">
         <f aca="false">-H63*Datos!$B$9</f>
-        <v>-7105.0841462288</v>
+        <v>-7105.72855937299</v>
       </c>
       <c r="I64" s="9" t="n">
         <f aca="false">-I63*Datos!$B$9</f>
-        <v>-9628.99922680325</v>
+        <v>-9638.09703053784</v>
       </c>
       <c r="J64" s="9" t="n">
         <f aca="false">-J63*Datos!$B$9</f>
-        <v>-12209.9359070414</v>
+        <v>-12207.6536922579</v>
       </c>
       <c r="K64" s="9" t="n">
         <f aca="false">-K63*Datos!$B$9</f>
-        <v>-13865.5687718775</v>
+        <v>-13869.2268960348</v>
       </c>
       <c r="L64" s="9" t="n">
         <f aca="false">-L63*Datos!$B$9</f>
-        <v>-16004.9515948641</v>
+        <v>-16007.7007386511</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17682,43 +17682,43 @@
       </c>
       <c r="C65" s="30" t="n">
         <f aca="false">C61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>1.12505181191711</v>
+        <v>1.12530217208805</v>
       </c>
       <c r="D65" s="30" t="n">
         <f aca="false">D61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>1.87850147945835</v>
+        <v>1.88102854249946</v>
       </c>
       <c r="E65" s="30" t="n">
         <f aca="false">E61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>3.38774857327385</v>
+        <v>3.39022378735494</v>
       </c>
       <c r="F65" s="30" t="n">
         <f aca="false">F61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>6.5696486858432</v>
+        <v>6.57506028313425</v>
       </c>
       <c r="G65" s="30" t="n">
         <f aca="false">G61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>11.1961533508597</v>
+        <v>11.2082455061489</v>
       </c>
       <c r="H65" s="30" t="n">
         <f aca="false">H61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>15.6827037761235</v>
+        <v>15.6844112582165</v>
       </c>
       <c r="I65" s="30" t="n">
         <f aca="false">I61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>21.283046974391</v>
+        <v>21.2981412948314</v>
       </c>
       <c r="J65" s="30" t="n">
         <f aca="false">J61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>27.0075600887656</v>
+        <v>27.0064870853294</v>
       </c>
       <c r="K65" s="30" t="n">
         <f aca="false">K61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>30.655854308918</v>
+        <v>30.6630754489222</v>
       </c>
       <c r="L65" s="30" t="n">
         <f aca="false">L61*(Datos!$B$51/2/12+Datos!$B$50/52)</f>
-        <v>35.3893714294933</v>
+        <v>35.3945693582802</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17730,43 +17730,43 @@
       </c>
       <c r="C66" s="9" t="n">
         <f aca="false">IF(C61=0,0,C65*C62/C61*Datos!$B$7)</f>
-        <v>172.182017124992</v>
+        <v>172.2219001322</v>
       </c>
       <c r="D66" s="9" t="n">
         <f aca="false">IF(D61=0,0,D65*D62/D61*Datos!$B$7)</f>
-        <v>287.723785456662</v>
+        <v>288.122746289969</v>
       </c>
       <c r="E66" s="9" t="n">
         <f aca="false">IF(E61=0,0,E65*E62/E61*Datos!$B$7)</f>
-        <v>522.220665955522</v>
+        <v>522.617152151036</v>
       </c>
       <c r="F66" s="9" t="n">
         <f aca="false">IF(F61=0,0,F65*F62/F61*Datos!$B$7)</f>
-        <v>1017.85033315546</v>
+        <v>1018.70871639142</v>
       </c>
       <c r="G66" s="9" t="n">
         <f aca="false">IF(G61=0,0,G65*G62/G61*Datos!$B$7)</f>
-        <v>1736.6179296045</v>
+        <v>1738.35527137896</v>
       </c>
       <c r="H66" s="9" t="n">
         <f aca="false">IF(H61=0,0,H65*H62/H61*Datos!$B$7)</f>
-        <v>2432.93168640122</v>
+        <v>2433.3130807223</v>
       </c>
       <c r="I66" s="9" t="n">
         <f aca="false">IF(I61=0,0,I65*I62/I61*Datos!$B$7)</f>
-        <v>3303.90425363693</v>
+        <v>3306.04562971055</v>
       </c>
       <c r="J66" s="9" t="n">
         <f aca="false">IF(J61=0,0,J65*J62/J61*Datos!$B$7)</f>
-        <v>4193.50510698409</v>
+        <v>4193.48024208002</v>
       </c>
       <c r="K66" s="9" t="n">
         <f aca="false">IF(K61=0,0,K65*K62/K61*Datos!$B$7)</f>
-        <v>4758.5418470952</v>
+        <v>4759.59370598968</v>
       </c>
       <c r="L66" s="9" t="n">
         <f aca="false">IF(L61=0,0,L65*L62/L61*Datos!$B$7)</f>
-        <v>5492.96039008406</v>
+        <v>5493.76556273777</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17778,43 +17778,43 @@
       </c>
       <c r="C67" s="9" t="n">
         <f aca="false">C56+C57+C60/Datos!$B$32/60+C60*Datos!$B$45/3600</f>
-        <v>10.596969409721</v>
+        <v>10.5992888541654</v>
       </c>
       <c r="D67" s="9" t="n">
         <f aca="false">D56+D57+D60/Datos!$B$32/60+D60*Datos!$B$45/3600</f>
-        <v>17.344821729166</v>
+        <v>17.3671131048274</v>
       </c>
       <c r="E67" s="9" t="n">
         <f aca="false">E56+E57+E60/Datos!$B$32/60+E60*Datos!$B$45/3600</f>
-        <v>34.3623731772626</v>
+        <v>34.3873906904901</v>
       </c>
       <c r="F67" s="9" t="n">
         <f aca="false">F56+F57+F60/Datos!$B$32/60+F60*Datos!$B$45/3600</f>
-        <v>72.1937742463824</v>
+        <v>72.2428736114618</v>
       </c>
       <c r="G67" s="9" t="n">
         <f aca="false">G56+G57+G60/Datos!$B$32/60+G60*Datos!$B$45/3600</f>
-        <v>124.755647418774</v>
+        <v>124.809485223007</v>
       </c>
       <c r="H67" s="9" t="n">
         <f aca="false">H56+H57+H60/Datos!$B$32/60+H60*Datos!$B$45/3600</f>
-        <v>175.035825674875</v>
+        <v>175.087913690748</v>
       </c>
       <c r="I67" s="9" t="n">
         <f aca="false">I56+I57+I60/Datos!$B$32/60+I60*Datos!$B$45/3600</f>
-        <v>239.912948776969</v>
+        <v>239.970560946281</v>
       </c>
       <c r="J67" s="9" t="n">
         <f aca="false">J56+J57+J60/Datos!$B$32/60+J60*Datos!$B$45/3600</f>
-        <v>305.70757686873</v>
+        <v>305.743129143862</v>
       </c>
       <c r="K67" s="9" t="n">
         <f aca="false">K56+K57+K60/Datos!$B$32/60+K60*Datos!$B$45/3600</f>
-        <v>345.748463321994</v>
+        <v>345.786147237338</v>
       </c>
       <c r="L67" s="9" t="n">
         <f aca="false">L56+L57+L60/Datos!$B$32/60+L60*Datos!$B$45/3600</f>
-        <v>399.343543865388</v>
+        <v>399.386281854806</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17826,43 +17826,43 @@
       </c>
       <c r="C68" s="9" t="n">
         <f aca="false">C67*Datos!$B$15</f>
-        <v>66.5629976835339</v>
+        <v>66.5775668654587</v>
       </c>
       <c r="D68" s="9" t="n">
         <f aca="false">D67*Datos!$B$15</f>
-        <v>108.948444025959</v>
+        <v>109.088463377638</v>
       </c>
       <c r="E68" s="9" t="n">
         <f aca="false">E67*Datos!$B$15</f>
-        <v>215.841197399387</v>
+        <v>215.998340504234</v>
       </c>
       <c r="F68" s="9" t="n">
         <f aca="false">F67*Datos!$B$15</f>
-        <v>453.472482757129</v>
+        <v>453.78089177462</v>
       </c>
       <c r="G68" s="9" t="n">
         <f aca="false">G67*Datos!$B$15</f>
-        <v>783.630635238596</v>
+        <v>783.968807927397</v>
       </c>
       <c r="H68" s="9" t="n">
         <f aca="false">H67*Datos!$B$15</f>
-        <v>1099.45672281023</v>
+        <v>1099.78390451152</v>
       </c>
       <c r="I68" s="9" t="n">
         <f aca="false">I67*Datos!$B$15</f>
-        <v>1506.97094954732</v>
+        <v>1507.33283024587</v>
       </c>
       <c r="J68" s="9" t="n">
         <f aca="false">J67*Datos!$B$15</f>
-        <v>1920.24832234443</v>
+        <v>1920.47163770147</v>
       </c>
       <c r="K68" s="9" t="n">
         <f aca="false">K67*Datos!$B$15</f>
-        <v>2171.75810114878</v>
+        <v>2171.99480602852</v>
       </c>
       <c r="L68" s="9" t="n">
         <f aca="false">L67*Datos!$B$15</f>
-        <v>2508.40616382849</v>
+        <v>2508.67461498472</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17922,43 +17922,43 @@
       </c>
       <c r="C70" s="11" t="n">
         <f aca="false">C62+C64+C66+C68+C69</f>
-        <v>19796.9452901094</v>
+        <v>19801.0240835441</v>
       </c>
       <c r="D70" s="11" t="n">
         <f aca="false">D62+D64+D66+D68+D69</f>
-        <v>31620.1846652531</v>
+        <v>31661.0106413746</v>
       </c>
       <c r="E70" s="11" t="n">
         <f aca="false">E62+E64+E66+E68+E69</f>
-        <v>55666.5143861086</v>
+        <v>55707.0512643983</v>
       </c>
       <c r="F70" s="11" t="n">
         <f aca="false">F62+F64+F66+F68+F69</f>
-        <v>106518.66139028</v>
+        <v>106606.472922641</v>
       </c>
       <c r="G70" s="11" t="n">
         <f aca="false">G62+G64+G66+G68+G69</f>
-        <v>180227.169170997</v>
+        <v>180404.548760879</v>
       </c>
       <c r="H70" s="11" t="n">
         <f aca="false">H62+H64+H66+H68+H69</f>
-        <v>251627.387428144</v>
+        <v>251667.116600414</v>
       </c>
       <c r="I70" s="11" t="n">
         <f aca="false">I62+I64+I66+I68+I69</f>
-        <v>340963.106134055</v>
+        <v>341179.21469875</v>
       </c>
       <c r="J70" s="11" t="n">
         <f aca="false">J62+J64+J66+J68+J69</f>
-        <v>432203.536428067</v>
+        <v>432203.431143279</v>
       </c>
       <c r="K70" s="11" t="n">
         <f aca="false">K62+K64+K66+K68+K69</f>
-        <v>490128.271053701</v>
+        <v>490235.294818344</v>
       </c>
       <c r="L70" s="11" t="n">
         <f aca="false">L62+L64+L66+L68+L69</f>
-        <v>565439.483307224</v>
+        <v>565521.545743233</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18023,43 +18023,43 @@
       </c>
       <c r="C74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(C9&gt;0,1000000000000,0),C9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(C9&gt;0,1000000000000,0),C9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(C9&gt;0,1000000000000,0),C9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(C8&gt;0,1000000000000,0),C8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>88.5753454927712</v>
+        <v>88.5690732927307</v>
       </c>
       <c r="D74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(D9&gt;0,1000000000000,0),D9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(D9&gt;0,1000000000000,0),D9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(D9&gt;0,1000000000000,0),D9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(D8&gt;0,1000000000000,0),D8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>213.187388759795</v>
+        <v>213.762693273555</v>
       </c>
       <c r="E74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(E9&gt;0,1000000000000,0),E9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(E9&gt;0,1000000000000,0),E9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(E9&gt;0,1000000000000,0),E9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(E8&gt;0,1000000000000,0),E8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>386.689113131001</v>
+        <v>386.708962949487</v>
       </c>
       <c r="F74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(F9&gt;0,1000000000000,0),F9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(F9&gt;0,1000000000000,0),F9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(F9&gt;0,1000000000000,0),F9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(F8&gt;0,1000000000000,0),F8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>761.540460815583</v>
+        <v>762.124167394688</v>
       </c>
       <c r="G74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(G9&gt;0,1000000000000,0),G9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(G9&gt;0,1000000000000,0),G9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(G9&gt;0,1000000000000,0),G9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(G8&gt;0,1000000000000,0),G8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>1266.37467512285</v>
+        <v>1266.61457939321</v>
       </c>
       <c r="H74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(H9&gt;0,1000000000000,0),H9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(H9&gt;0,1000000000000,0),H9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(H9&gt;0,1000000000000,0),H9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(H8&gt;0,1000000000000,0),H8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>1799.9729552726</v>
+        <v>1800.57759245783</v>
       </c>
       <c r="I74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(I9&gt;0,1000000000000,0),I9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(I9&gt;0,1000000000000,0),I9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(I9&gt;0,1000000000000,0),I9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(I8&gt;0,1000000000000,0),I8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>2480.60414631869</v>
+        <v>2481.07407637924</v>
       </c>
       <c r="J74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(J9&gt;0,1000000000000,0),J9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(J9&gt;0,1000000000000,0),J9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(J9&gt;0,1000000000000,0),J9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(J8&gt;0,1000000000000,0),J8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>3183.1538139508</v>
+        <v>3183.75683626968</v>
       </c>
       <c r="K74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(K9&gt;0,1000000000000,0),K9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(K9&gt;0,1000000000000,0),K9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(K9&gt;0,1000000000000,0),K9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(K8&gt;0,1000000000000,0),K8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>3575.81708937065</v>
+        <v>3576.49449851867</v>
       </c>
       <c r="L74" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$81=0,IF(L9&gt;0,1000000000000,0),L9*Corte!$D$81/1000/Corte!$H$81),IF(Corte!$H$82=0,IF(L9&gt;0,1000000000000,0),L9*Corte!$D$82/1000/Corte!$H$82),IF(Corte!$H$83=0,IF(L9&gt;0,1000000000000,0),L9*Corte!$D$83/1000/Corte!$H$83),IF(Corte!$H$84=0,IF(L8&gt;0,1000000000000,0),L8*Corte!$D$84/1000/Corte!$H$84))</f>
-        <v>4169.8170552588</v>
+        <v>4170.10037477819</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18071,43 +18071,43 @@
       </c>
       <c r="C75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(C10&gt;0,1000000000000,0),C10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(C10&gt;0,1000000000000,0),C10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(C10&gt;0,1000000000000,0),C10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(C11&gt;0,1000000000000,0),C11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>538.832202209718</v>
+        <v>539.068452023401</v>
       </c>
       <c r="D75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(D10&gt;0,1000000000000,0),D10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(D10&gt;0,1000000000000,0),D10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(D10&gt;0,1000000000000,0),D10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(D11&gt;0,1000000000000,0),D11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>926.330530091668</v>
+        <v>928.003178772544</v>
       </c>
       <c r="E75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(E10&gt;0,1000000000000,0),E10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(E10&gt;0,1000000000000,0),E10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(E10&gt;0,1000000000000,0),E10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(E11&gt;0,1000000000000,0),E11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>1582.89680753242</v>
+        <v>1585.64675536369</v>
       </c>
       <c r="F75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(F10&gt;0,1000000000000,0),F10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(F10&gt;0,1000000000000,0),F10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(F10&gt;0,1000000000000,0),F10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(F11&gt;0,1000000000000,0),F11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>2878.81627233641</v>
+        <v>2883.19161888582</v>
       </c>
       <c r="G75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(G10&gt;0,1000000000000,0),G10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(G10&gt;0,1000000000000,0),G10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(G10&gt;0,1000000000000,0),G10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(G11&gt;0,1000000000000,0),G11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>4860.34543149501</v>
+        <v>4865.04207779103</v>
       </c>
       <c r="H75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(H10&gt;0,1000000000000,0),H10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(H10&gt;0,1000000000000,0),H10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(H10&gt;0,1000000000000,0),H10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(H11&gt;0,1000000000000,0),H11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>6775.73067735132</v>
+        <v>6780.74862339395</v>
       </c>
       <c r="I75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(I10&gt;0,1000000000000,0),I10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(I10&gt;0,1000000000000,0),I10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(I10&gt;0,1000000000000,0),I10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(I11&gt;0,1000000000000,0),I11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>9129.8740119839</v>
+        <v>9134.50450833209</v>
       </c>
       <c r="J75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(J10&gt;0,1000000000000,0),J10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(J10&gt;0,1000000000000,0),J10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(J10&gt;0,1000000000000,0),J10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(J11&gt;0,1000000000000,0),J11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>11535.2530327098</v>
+        <v>11538.9668797809</v>
       </c>
       <c r="K75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(K10&gt;0,1000000000000,0),K10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(K10&gt;0,1000000000000,0),K10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(K10&gt;0,1000000000000,0),K10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(K11&gt;0,1000000000000,0),K11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>13104.2868403264</v>
+        <v>13107.4620378223</v>
       </c>
       <c r="L75" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$91=0,IF(L10&gt;0,1000000000000,0),L10*Corte!$D$91/1000/Corte!$H$91),IF(Corte!$H$92=0,IF(L10&gt;0,1000000000000,0),L10*Corte!$D$92/1000/Corte!$H$92),IF(Corte!$H$93=0,IF(L10&gt;0,1000000000000,0),L10*Corte!$D$93/1000/Corte!$H$93),IF(Corte!$H$94=0,IF(L11&gt;0,1000000000000,0),L11*Corte!$D$94/1000/Corte!$H$94))</f>
-        <v>15081.1813789238</v>
+        <v>15085.1787257714</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18123,39 +18123,39 @@
       </c>
       <c r="D76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(D11&gt;0,1000000000000,0),D11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(D11&gt;0,1000000000000,0),D11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>60.2133578581194</v>
+        <v>60.5451351172057</v>
       </c>
       <c r="E76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(E11&gt;0,1000000000000,0),E11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(E11&gt;0,1000000000000,0),E11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>117.097060987329</v>
+        <v>116.79182590897</v>
       </c>
       <c r="F76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(F11&gt;0,1000000000000,0),F11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(F11&gt;0,1000000000000,0),F11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>227.698896842114</v>
+        <v>228.0306741012</v>
       </c>
       <c r="G76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(G11&gt;0,1000000000000,0),G11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(G11&gt;0,1000000000000,0),G11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>398.251537559353</v>
+        <v>398.27807974008</v>
       </c>
       <c r="H76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(H11&gt;0,1000000000000,0),H11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(H11&gt;0,1000000000000,0),H11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>575.834280373458</v>
+        <v>575.860822554185</v>
       </c>
       <c r="I76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(I11&gt;0,1000000000000,0),I11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(I11&gt;0,1000000000000,0),I11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>774.660267514172</v>
+        <v>775.018586953985</v>
       </c>
       <c r="J76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(J11&gt;0,1000000000000,0),J11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(J11&gt;0,1000000000000,0),J11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>979.20899897966</v>
+        <v>979.262083341114</v>
       </c>
       <c r="K76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(K11&gt;0,1000000000000,0),K11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(K11&gt;0,1000000000000,0),K11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>1113.17575982994</v>
+        <v>1113.2288441914</v>
       </c>
       <c r="L76" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$101=0,IF(L11&gt;0,1000000000000,0),L11*Corte!$D$101/1000/Corte!$H$101),IF(Corte!$H$102=0,IF(L11&gt;0,1000000000000,0),L11*Corte!$D$102/1000/Corte!$H$102))</f>
-        <v>1281.57860573691</v>
+        <v>1281.63169009837</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18183,27 +18183,27 @@
       </c>
       <c r="G77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(G12&gt;0,1000000000000,0),G12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(G13&gt;0,1000000000000,0),G13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>347.040619377011</v>
+        <v>348.421732633124</v>
       </c>
       <c r="H77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(H12&gt;0,1000000000000,0),H12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(H13&gt;0,1000000000000,0),H13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>483.420137879036</v>
+        <v>482.892753923436</v>
       </c>
       <c r="I77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(I12&gt;0,1000000000000,0),I12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(I13&gt;0,1000000000000,0),I13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>643.025515509555</v>
+        <v>643.703580595327</v>
       </c>
       <c r="J77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(J12&gt;0,1000000000000,0),J12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(J13&gt;0,1000000000000,0),J13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>810.50568476274</v>
+        <v>811.233976891902</v>
       </c>
       <c r="K77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(K12&gt;0,1000000000000,0),K12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(K13&gt;0,1000000000000,0),K13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>928.836353989437</v>
+        <v>928.987035119608</v>
       </c>
       <c r="L77" s="9" t="n">
         <f aca="false">MAX(IF(Corte!$H$109=0,IF(L12&gt;0,1000000000000,0),L12*Corte!$D$109/1000/Corte!$H$109),IF(Corte!$H$110=0,IF(L13&gt;0,1000000000000,0),L13*Corte!$D$110/1000/Corte!$H$110))</f>
-        <v>1073.72558956928</v>
+        <v>1073.55388151898</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18231,27 +18231,27 @@
       </c>
       <c r="G78" s="9" t="n">
         <f aca="false">(G14*Piezas!$F$12+G15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>155.0334165436</v>
+        <v>155.7134165436</v>
       </c>
       <c r="H78" s="9" t="n">
         <f aca="false">(H14*Piezas!$F$12+H15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>214.318146179</v>
+        <v>213.692546179</v>
       </c>
       <c r="I78" s="9" t="n">
         <f aca="false">(I14*Piezas!$F$12+I15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>285.971362441</v>
+        <v>287.551362441</v>
       </c>
       <c r="J78" s="9" t="n">
         <f aca="false">(J14*Piezas!$F$12+J15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>360.834223232</v>
+        <v>359.380623232</v>
       </c>
       <c r="K78" s="9" t="n">
         <f aca="false">(K14*Piezas!$F$12+K15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>412.08308416</v>
+        <v>412.76308416</v>
       </c>
       <c r="L78" s="9" t="n">
         <f aca="false">(L14*Piezas!$F$12+L15*Piezas!$F$13)/1000/Corte!$H$117</f>
-        <v>476.37581562</v>
+        <v>477.11021562</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18311,43 +18311,43 @@
       </c>
       <c r="C80" s="30" t="n">
         <f aca="false">C74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>0.875738654557927</v>
+        <v>0.875676641725868</v>
       </c>
       <c r="D80" s="30" t="n">
         <f aca="false">D74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>2.10776978585375</v>
+        <v>2.11345778399859</v>
       </c>
       <c r="E80" s="30" t="n">
         <f aca="false">E74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>3.82317000042836</v>
+        <v>3.82336625428702</v>
       </c>
       <c r="F80" s="30" t="n">
         <f aca="false">F74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>7.52930078720935</v>
+        <v>7.53507185602537</v>
       </c>
       <c r="G80" s="30" t="n">
         <f aca="false">G74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>12.5205636849458</v>
+        <v>12.5229356027947</v>
       </c>
       <c r="H80" s="30" t="n">
         <f aca="false">H74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>17.7962150226072</v>
+        <v>17.8021930309587</v>
       </c>
       <c r="I80" s="30" t="n">
         <f aca="false">I74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>24.5255711451358</v>
+        <v>24.5302173129455</v>
       </c>
       <c r="J80" s="30" t="n">
         <f aca="false">J74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>31.47163381381</v>
+        <v>31.4775958560834</v>
       </c>
       <c r="K80" s="30" t="n">
         <f aca="false">K74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>35.3538699665163</v>
+        <v>35.36056746651</v>
       </c>
       <c r="L80" s="30" t="n">
         <f aca="false">L74*Corte!$D$64/1000/(1-Datos!$B$20)</f>
-        <v>41.2267088252346</v>
+        <v>41.2295099868145</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18359,43 +18359,43 @@
       </c>
       <c r="C81" s="30" t="n">
         <f aca="false">C75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>6.81907044243696</v>
+        <v>6.82206024912429</v>
       </c>
       <c r="D81" s="30" t="n">
         <f aca="false">D75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>11.7229688793108</v>
+        <v>11.7441367106572</v>
       </c>
       <c r="E81" s="30" t="n">
         <f aca="false">E75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>20.031996583365</v>
+        <v>20.0667979332056</v>
       </c>
       <c r="F81" s="30" t="n">
         <f aca="false">F75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>36.4322155791559</v>
+        <v>36.4875867990053</v>
       </c>
       <c r="G81" s="30" t="n">
         <f aca="false">G75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>61.5090147471207</v>
+        <v>61.5684521040649</v>
       </c>
       <c r="H81" s="30" t="n">
         <f aca="false">H75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>85.7487444112641</v>
+        <v>85.8122479053031</v>
       </c>
       <c r="I81" s="30" t="n">
         <f aca="false">I75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>115.54107895367</v>
+        <v>115.599679164741</v>
       </c>
       <c r="J81" s="30" t="n">
         <f aca="false">J75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>145.981815264203</v>
+        <v>146.028815025328</v>
       </c>
       <c r="K81" s="30" t="n">
         <f aca="false">K75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>165.838371752151</v>
+        <v>165.878554754029</v>
       </c>
       <c r="L81" s="30" t="n">
         <f aca="false">L75*Corte!$D$65/1000/(1-Datos!$B$20)</f>
-        <v>190.856518515989</v>
+        <v>190.907106045139</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18411,39 +18411,39 @@
       </c>
       <c r="D82" s="30" t="n">
         <f aca="false">D76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>0.952520856971657</v>
+        <v>0.95776927311037</v>
       </c>
       <c r="E82" s="30" t="n">
         <f aca="false">E76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>1.85236958787996</v>
+        <v>1.84754104503234</v>
       </c>
       <c r="F82" s="30" t="n">
         <f aca="false">F76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>3.60199058924108</v>
+        <v>3.60723900537979</v>
       </c>
       <c r="G82" s="30" t="n">
         <f aca="false">G76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>6.29997909666756</v>
+        <v>6.30039896995865</v>
       </c>
       <c r="H82" s="30" t="n">
         <f aca="false">H76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>9.10917746038013</v>
+        <v>9.10959733367123</v>
       </c>
       <c r="I82" s="30" t="n">
         <f aca="false">I76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>12.2544247343448</v>
+        <v>12.2600930237746</v>
       </c>
       <c r="J82" s="30" t="n">
         <f aca="false">J76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>15.4902006471757</v>
+        <v>15.4910403937579</v>
       </c>
       <c r="K82" s="30" t="n">
         <f aca="false">K76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>17.6094336278626</v>
+        <v>17.6102733744448</v>
       </c>
       <c r="L82" s="30" t="n">
         <f aca="false">L76*Corte!$D$66/1000/(1-Datos!$B$20)</f>
-        <v>20.2734143259286</v>
+        <v>20.2742540725108</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18471,27 +18471,27 @@
       </c>
       <c r="G83" s="30" t="n">
         <f aca="false">G77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>13.1756848618954</v>
+        <v>13.2281199718079</v>
       </c>
       <c r="H83" s="30" t="n">
         <f aca="false">H77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>18.3534463603201</v>
+        <v>18.3334237911676</v>
       </c>
       <c r="I83" s="30" t="n">
         <f aca="false">I77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>24.4129968581798</v>
+        <v>24.4387401613759</v>
       </c>
       <c r="J83" s="30" t="n">
         <f aca="false">J77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>30.771520349344</v>
+        <v>30.7991705638879</v>
       </c>
       <c r="K83" s="30" t="n">
         <f aca="false">K77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>35.2640423199045</v>
+        <v>35.2697630539481</v>
       </c>
       <c r="L83" s="30" t="n">
         <f aca="false">L77*Corte!$D$67/1000/(1-Datos!$B$20)</f>
-        <v>40.764882282984</v>
+        <v>40.7583632444835</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18519,27 +18519,27 @@
       </c>
       <c r="G84" s="30" t="n">
         <f aca="false">G78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>7.2517016924188</v>
+        <v>7.28350875221779</v>
       </c>
       <c r="H84" s="30" t="n">
         <f aca="false">H78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>10.0247501345959</v>
+        <v>9.99548763958081</v>
       </c>
       <c r="I84" s="30" t="n">
         <f aca="false">I78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>13.3763356264132</v>
+        <v>13.4502402653579</v>
       </c>
       <c r="J84" s="30" t="n">
         <f aca="false">J78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>16.8780525233296</v>
+        <v>16.8100602555005</v>
       </c>
       <c r="K84" s="30" t="n">
         <f aca="false">K78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>19.2752225000462</v>
+        <v>19.3070295598452</v>
       </c>
       <c r="L84" s="30" t="n">
         <f aca="false">L78*Corte!$D$68/1000/(1-Datos!$B$20)</f>
-        <v>22.2825206679711</v>
+        <v>22.316872292554</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18551,43 +18551,43 @@
       </c>
       <c r="C85" s="30" t="n">
         <f aca="false">SUM(C79:C84)</f>
-        <v>13.3743231138768</v>
+        <v>13.3772509077321</v>
       </c>
       <c r="D85" s="30" t="n">
         <f aca="false">SUM(D79:D84)</f>
-        <v>22.6758122409151</v>
+        <v>22.707916486545</v>
       </c>
       <c r="E85" s="30" t="n">
         <f aca="false">SUM(E79:E84)</f>
-        <v>40.5959835381467</v>
+        <v>40.6261525989983</v>
       </c>
       <c r="F85" s="30" t="n">
         <f aca="false">SUM(F79:F84)</f>
-        <v>78.2067368478754</v>
+        <v>78.2731275526796</v>
       </c>
       <c r="G85" s="30" t="n">
         <f aca="false">SUM(G79:G84)</f>
-        <v>132.938896318167</v>
+        <v>133.085367635962</v>
       </c>
       <c r="H85" s="30" t="n">
         <f aca="false">SUM(H79:H84)</f>
-        <v>186.262623000442</v>
+        <v>186.283239311956</v>
       </c>
       <c r="I85" s="30" t="n">
         <f aca="false">SUM(I79:I84)</f>
-        <v>253.149163318861</v>
+        <v>253.317725929313</v>
       </c>
       <c r="J85" s="30" t="n">
         <f aca="false">SUM(J79:J84)</f>
-        <v>321.485636201807</v>
+        <v>321.499095698502</v>
       </c>
       <c r="K85" s="30" t="n">
         <f aca="false">SUM(K79:K84)</f>
-        <v>364.211973070295</v>
+        <v>364.297221112591</v>
       </c>
       <c r="L85" s="30" t="n">
         <f aca="false">SUM(L79:L84)</f>
-        <v>420.381623391072</v>
+        <v>420.463684414466</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18599,43 +18599,43 @@
       </c>
       <c r="C86" s="9" t="n">
         <f aca="false">SUMPRODUCT(C79:C84,Corte!$E$63:$E$68)*1000</f>
-        <v>16345.3309845261</v>
+        <v>16348.9923664097</v>
       </c>
       <c r="D86" s="9" t="n">
         <f aca="false">SUMPRODUCT(D79:D84,Corte!$E$63:$E$68)*1000</f>
-        <v>27752.5776190017</v>
+        <v>27792.790407451</v>
       </c>
       <c r="E86" s="9" t="n">
         <f aca="false">SUMPRODUCT(E79:E84,Corte!$E$63:$E$68)*1000</f>
-        <v>49874.6402667204</v>
+        <v>49912.3091446674</v>
       </c>
       <c r="F86" s="9" t="n">
         <f aca="false">SUMPRODUCT(F79:F84,Corte!$E$63:$E$68)*1000</f>
-        <v>96370.1461488651</v>
+        <v>96453.2362116994</v>
       </c>
       <c r="G86" s="9" t="n">
         <f aca="false">SUMPRODUCT(G79:G84,Corte!$E$63:$E$68)*1000</f>
-        <v>163925.929813487</v>
+        <v>164097.579288831</v>
       </c>
       <c r="H86" s="9" t="n">
         <f aca="false">SUMPRODUCT(H79:H84,Corte!$E$63:$E$68)*1000</f>
-        <v>229717.429243344</v>
+        <v>229749.960013443</v>
       </c>
       <c r="I86" s="9" t="n">
         <f aca="false">SUMPRODUCT(I79:I84,Corte!$E$63:$E$68)*1000</f>
-        <v>312332.856507407</v>
+        <v>312530.089000888</v>
       </c>
       <c r="J86" s="9" t="n">
         <f aca="false">SUMPRODUCT(J79:J84,Corte!$E$63:$E$68)*1000</f>
-        <v>396701.72848151</v>
+        <v>396724.090713334</v>
       </c>
       <c r="K86" s="9" t="n">
         <f aca="false">SUMPRODUCT(K79:K84,Corte!$E$63:$E$68)*1000</f>
-        <v>449339.542371149</v>
+        <v>449441.025555377</v>
       </c>
       <c r="L86" s="9" t="n">
         <f aca="false">SUMPRODUCT(L79:L84,Corte!$E$63:$E$68)*1000</f>
-        <v>518625.001507345</v>
+        <v>518723.825728492</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18647,43 +18647,43 @@
       </c>
       <c r="C87" s="30" t="n">
         <f aca="false">C85-C25</f>
-        <v>1.42934564167909</v>
+        <v>1.42964290661707</v>
       </c>
       <c r="D87" s="30" t="n">
         <f aca="false">D85-D25</f>
-        <v>2.73190990189915</v>
+        <v>2.73729612368548</v>
       </c>
       <c r="E87" s="30" t="n">
         <f aca="false">E85-E25</f>
-        <v>4.54761940790613</v>
+        <v>4.55190305840211</v>
       </c>
       <c r="F87" s="30" t="n">
         <f aca="false">F85-F25</f>
-        <v>8.15465666148751</v>
+        <v>8.16401909783113</v>
       </c>
       <c r="G87" s="30" t="n">
         <f aca="false">G85-G25</f>
-        <v>13.5170299080291</v>
+        <v>13.5341090043164</v>
       </c>
       <c r="H87" s="30" t="n">
         <f aca="false">H85-H25</f>
-        <v>18.9628164593356</v>
+        <v>18.9647010469056</v>
       </c>
       <c r="I87" s="30" t="n">
         <f aca="false">I85-I25</f>
-        <v>26.0527339856737</v>
+        <v>26.0693106919689</v>
       </c>
       <c r="J87" s="30" t="n">
         <f aca="false">J85-J25</f>
-        <v>33.2710299221779</v>
+        <v>33.2887516426223</v>
       </c>
       <c r="K87" s="30" t="n">
         <f aca="false">K85-K25</f>
-        <v>37.0891863825078</v>
+        <v>37.0989470941807</v>
       </c>
       <c r="L87" s="30" t="n">
         <f aca="false">L85-L25</f>
-        <v>42.7420743304519</v>
+        <v>42.770261777733</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18695,43 +18695,43 @@
       </c>
       <c r="C88" s="9" t="n">
         <f aca="false">-C87*Datos!$B$9</f>
-        <v>-357.336410419773</v>
+        <v>-357.410726654267</v>
       </c>
       <c r="D88" s="9" t="n">
         <f aca="false">-D87*Datos!$B$9</f>
-        <v>-682.977475474787</v>
+        <v>-684.32403092137</v>
       </c>
       <c r="E88" s="9" t="n">
         <f aca="false">-E87*Datos!$B$9</f>
-        <v>-1136.90485197653</v>
+        <v>-1137.97576460053</v>
       </c>
       <c r="F88" s="9" t="n">
         <f aca="false">-F87*Datos!$B$9</f>
-        <v>-2038.66416537188</v>
+        <v>-2041.00477445778</v>
       </c>
       <c r="G88" s="9" t="n">
         <f aca="false">-G87*Datos!$B$9</f>
-        <v>-3379.25747700727</v>
+        <v>-3383.52725107911</v>
       </c>
       <c r="H88" s="9" t="n">
         <f aca="false">-H87*Datos!$B$9</f>
-        <v>-4740.7041148339</v>
+        <v>-4741.17526172641</v>
       </c>
       <c r="I88" s="9" t="n">
         <f aca="false">-I87*Datos!$B$9</f>
-        <v>-6513.18349641842</v>
+        <v>-6517.32767299222</v>
       </c>
       <c r="J88" s="9" t="n">
         <f aca="false">-J87*Datos!$B$9</f>
-        <v>-8317.75748054447</v>
+        <v>-8322.18791065559</v>
       </c>
       <c r="K88" s="9" t="n">
         <f aca="false">-K87*Datos!$B$9</f>
-        <v>-9272.29659562696</v>
+        <v>-9274.73677354519</v>
       </c>
       <c r="L88" s="9" t="n">
         <f aca="false">-L87*Datos!$B$9</f>
-        <v>-10685.518582613</v>
+        <v>-10692.5654444333</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18743,43 +18743,43 @@
       </c>
       <c r="C89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+C79:C84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-C79:C84*Datos!$B$53/12))/2+C79:C84*Datos!$B$50/52)</f>
-        <v>3.85797782131062</v>
+        <v>3.85882237723041</v>
       </c>
       <c r="D89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+D79:D84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-D79:D84*Datos!$B$53/12))/2+D79:D84*Datos!$B$50/52)</f>
-        <v>6.54109968487937</v>
+        <v>6.55036052496491</v>
       </c>
       <c r="E89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+E79:E84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-E79:E84*Datos!$B$53/12))/2+E79:E84*Datos!$B$50/52)</f>
-        <v>11.7103798667731</v>
+        <v>11.7190824804803</v>
       </c>
       <c r="F89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+F79:F84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-F79:F84*Datos!$B$53/12))/2+F79:F84*Datos!$B$50/52)</f>
-        <v>22.5596356291948</v>
+        <v>22.5787867940422</v>
       </c>
       <c r="G89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+G79:G84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-G79:G84*Datos!$B$53/12))/2+G79:G84*Datos!$B$50/52)</f>
-        <v>34.9705048665371</v>
+        <v>34.9978968689729</v>
       </c>
       <c r="H89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+H79:H84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-H79:H84*Datos!$B$53/12))/2+H79:H84*Datos!$B$50/52)</f>
-        <v>39.1639470384785</v>
+        <v>39.1647399735368</v>
       </c>
       <c r="I89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+I79:I84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-I79:I84*Datos!$B$53/12))/2+I79:I84*Datos!$B$50/52)</f>
-        <v>41.7365062814947</v>
+        <v>41.7429894588197</v>
       </c>
       <c r="J89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+J79:J84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-J79:J84*Datos!$B$53/12))/2+J79:J84*Datos!$B$50/52)</f>
-        <v>44.364832161608</v>
+        <v>44.3653498345578</v>
       </c>
       <c r="K89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+K79:K84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-K79:K84*Datos!$B$53/12))/2+K79:K84*Datos!$B$50/52)</f>
-        <v>46.008152810396</v>
+        <v>46.0114315812535</v>
       </c>
       <c r="L89" s="30" t="n">
         <f aca="false">SUMPRODUCT((Corte!$G$63:$G$68+L79:L84*Datos!$B$53/12-ABS(Corte!$G$63:$G$68-L79:L84*Datos!$B$53/12))/2+L79:L84*Datos!$B$50/52)</f>
-        <v>48.1685239765797</v>
+        <v>48.1716801697872</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18791,43 +18791,43 @@
       </c>
       <c r="C90" s="9" t="n">
         <f aca="false">IF(C85=0,0,C89*C86/C85*Datos!$B$7)</f>
-        <v>565.799918695133</v>
+        <v>565.92665883726</v>
       </c>
       <c r="D90" s="9" t="n">
         <f aca="false">IF(D85=0,0,D89*D86/D85*Datos!$B$7)</f>
-        <v>960.66614835006</v>
+        <v>962.058129488688</v>
       </c>
       <c r="E90" s="9" t="n">
         <f aca="false">IF(E85=0,0,E89*E86/E85*Datos!$B$7)</f>
-        <v>1726.42985538648</v>
+        <v>1727.73377808464</v>
       </c>
       <c r="F90" s="9" t="n">
         <f aca="false">IF(F85=0,0,F89*F86/F85*Datos!$B$7)</f>
-        <v>3335.88967438379</v>
+        <v>3338.76586886652</v>
       </c>
       <c r="G90" s="9" t="n">
         <f aca="false">IF(G85=0,0,G89*G86/G85*Datos!$B$7)</f>
-        <v>5174.62324577232</v>
+        <v>5178.39362064929</v>
       </c>
       <c r="H90" s="9" t="n">
         <f aca="false">IF(H85=0,0,H89*H86/H85*Datos!$B$7)</f>
-        <v>5796.10085229848</v>
+        <v>5796.39744901911</v>
       </c>
       <c r="I90" s="9" t="n">
         <f aca="false">IF(I85=0,0,I89*I86/I85*Datos!$B$7)</f>
-        <v>6179.28910685078</v>
+        <v>6180.03663006281</v>
       </c>
       <c r="J90" s="9" t="n">
         <f aca="false">IF(J85=0,0,J89*J86/J85*Datos!$B$7)</f>
-        <v>6569.35313573542</v>
+        <v>6569.52506844985</v>
       </c>
       <c r="K90" s="9" t="n">
         <f aca="false">IF(K85=0,0,K89*K86/K85*Datos!$B$7)</f>
-        <v>6811.40122491529</v>
+        <v>6811.83071361119</v>
       </c>
       <c r="L90" s="9" t="n">
         <f aca="false">IF(L85=0,0,L89*L86/L85*Datos!$B$7)</f>
-        <v>7131.06361361203</v>
+        <v>7131.49767430854</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18839,43 +18839,43 @@
       </c>
       <c r="C91" s="30" t="n">
         <f aca="false">SUM(C73:C78)/(Datos!$B$42*60)+SUMPRODUCT(C79:C84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>2.21757927673225</v>
+        <v>2.21784867519188</v>
       </c>
       <c r="D91" s="30" t="n">
         <f aca="false">SUM(D73:D78)/(Datos!$B$42*60)+SUMPRODUCT(D79:D84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>3.79581578966439</v>
+        <v>3.80140067960993</v>
       </c>
       <c r="E91" s="30" t="n">
         <f aca="false">SUM(E73:E78)/(Datos!$B$42*60)+SUMPRODUCT(E79:E84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>6.6934567217773</v>
+        <v>6.69489005804418</v>
       </c>
       <c r="F91" s="30" t="n">
         <f aca="false">SUM(F73:F78)/(Datos!$B$42*60)+SUMPRODUCT(F79:F84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>12.7393113341347</v>
+        <v>12.7481813616922</v>
       </c>
       <c r="G91" s="30" t="n">
         <f aca="false">SUM(G73:G78)/(Datos!$B$42*60)+SUMPRODUCT(G79:G84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>21.5862972346443</v>
+        <v>21.6167682849551</v>
       </c>
       <c r="H91" s="30" t="n">
         <f aca="false">SUM(H73:H78)/(Datos!$B$42*60)+SUMPRODUCT(H79:H84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>30.3239532590401</v>
+        <v>30.3159700878</v>
       </c>
       <c r="I91" s="30" t="n">
         <f aca="false">SUM(I73:I78)/(Datos!$B$42*60)+SUMPRODUCT(I79:I84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>41.1448966996117</v>
+        <v>41.1881264283347</v>
       </c>
       <c r="J91" s="30" t="n">
         <f aca="false">SUM(J73:J78)/(Datos!$B$42*60)+SUMPRODUCT(J79:J84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>52.2505335002338</v>
+        <v>52.2370100187476</v>
       </c>
       <c r="K91" s="30" t="n">
         <f aca="false">SUM(K73:K78)/(Datos!$B$42*60)+SUMPRODUCT(K79:K84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>59.2339594987884</v>
+        <v>59.2533480273394</v>
       </c>
       <c r="L91" s="30" t="n">
         <f aca="false">SUM(L73:L78)/(Datos!$B$42*60)+SUMPRODUCT(L79:L84/Corte!$G$63:$G$68)*Datos!$B$43/60</f>
-        <v>68.4424110415692</v>
+        <v>68.4600130228656</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18887,43 +18887,43 @@
       </c>
       <c r="C92" s="30" t="n">
         <f aca="false">SUMPRODUCT(C79:C84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>2.89279690213649</v>
+        <v>2.89297952001173</v>
       </c>
       <c r="D92" s="30" t="n">
         <f aca="false">SUMPRODUCT(D79:D84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>5.89187831298669</v>
+        <v>5.9054328632888</v>
       </c>
       <c r="E92" s="30" t="n">
         <f aca="false">SUMPRODUCT(E79:E84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>10.8724487266465</v>
+        <v>10.8755502203916</v>
       </c>
       <c r="F92" s="30" t="n">
         <f aca="false">SUMPRODUCT(F79:F84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>21.5578300794564</v>
+        <v>21.5754372413946</v>
       </c>
       <c r="G92" s="30" t="n">
         <f aca="false">SUMPRODUCT(G79:G84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>36.3864197622234</v>
+        <v>36.3968184670649</v>
       </c>
       <c r="H92" s="30" t="n">
         <f aca="false">SUMPRODUCT(H79:H84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>51.4483670206452</v>
+        <v>51.4645157642043</v>
       </c>
       <c r="I92" s="30" t="n">
         <f aca="false">SUMPRODUCT(I79:I84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>70.5707624826328</v>
+        <v>70.5846554360306</v>
       </c>
       <c r="J92" s="30" t="n">
         <f aca="false">SUMPRODUCT(J79:J84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>90.1741857305923</v>
+        <v>90.1862173618255</v>
       </c>
       <c r="K92" s="30" t="n">
         <f aca="false">SUMPRODUCT(K79:K84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>101.613783148861</v>
+        <v>101.62553813356</v>
       </c>
       <c r="L92" s="30" t="n">
         <f aca="false">SUMPRODUCT(L79:L84/Corte!$G$63:$G$68*Corte!$F$63:$F$68)</f>
-        <v>117.901789395002</v>
+        <v>117.90770739545</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18935,43 +18935,43 @@
       </c>
       <c r="C93" s="9" t="n">
         <f aca="false">C91*Datos!$B$44+SUM(C$8:C$15)/Datos!$B$41+C92*Datos!$B$46/60</f>
-        <v>10.9905080058153</v>
+        <v>10.9919257905367</v>
       </c>
       <c r="D93" s="9" t="n">
         <f aca="false">D91*Datos!$B$44+SUM(D$8:D$15)/Datos!$B$41+D92*Datos!$B$46/60</f>
-        <v>18.2790896532588</v>
+        <v>18.3020480707254</v>
       </c>
       <c r="E93" s="9" t="n">
         <f aca="false">E91*Datos!$B$44+SUM(E$8:E$15)/Datos!$B$41+E92*Datos!$B$46/60</f>
-        <v>35.4719975805162</v>
+        <v>35.4847062931529</v>
       </c>
       <c r="F93" s="9" t="n">
         <f aca="false">F91*Datos!$B$44+SUM(F$8:F$15)/Datos!$B$41+F92*Datos!$B$46/60</f>
-        <v>73.5562709730085</v>
+        <v>73.5964794852748</v>
       </c>
       <c r="G93" s="9" t="n">
         <f aca="false">G91*Datos!$B$44+SUM(G$8:G$15)/Datos!$B$41+G92*Datos!$B$46/60</f>
-        <v>126.582690694753</v>
+        <v>126.668132471585</v>
       </c>
       <c r="H93" s="9" t="n">
         <f aca="false">H91*Datos!$B$44+SUM(H$8:H$15)/Datos!$B$41+H92*Datos!$B$46/60</f>
-        <v>177.853523298133</v>
+        <v>177.860027474876</v>
       </c>
       <c r="I93" s="9" t="n">
         <f aca="false">I91*Datos!$B$44+SUM(I$8:I$15)/Datos!$B$41+I92*Datos!$B$46/60</f>
-        <v>243.780069104557</v>
+        <v>243.892901800352</v>
       </c>
       <c r="J93" s="9" t="n">
         <f aca="false">J91*Datos!$B$44+SUM(J$8:J$15)/Datos!$B$41+J92*Datos!$B$46/60</f>
-        <v>310.809422542949</v>
+        <v>310.798016821118</v>
       </c>
       <c r="K93" s="9" t="n">
         <f aca="false">K91*Datos!$B$44+SUM(K$8:K$15)/Datos!$B$41+K92*Datos!$B$46/60</f>
-        <v>351.262986992626</v>
+        <v>351.319469462569</v>
       </c>
       <c r="L93" s="9" t="n">
         <f aca="false">L91*Datos!$B$44+SUM(L$8:L$15)/Datos!$B$41+L92*Datos!$B$46/60</f>
-        <v>405.986474853472</v>
+        <v>406.038524982844</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18983,43 +18983,43 @@
       </c>
       <c r="C94" s="9" t="n">
         <f aca="false">C93*Datos!$B$15</f>
-        <v>69.0349410899362</v>
+        <v>69.0438466550537</v>
       </c>
       <c r="D94" s="9" t="n">
         <f aca="false">D93*Datos!$B$15</f>
-        <v>114.816883507358</v>
+        <v>114.9610927647</v>
       </c>
       <c r="E94" s="9" t="n">
         <f aca="false">E93*Datos!$B$15</f>
-        <v>222.811107732016</v>
+        <v>222.890935272994</v>
       </c>
       <c r="F94" s="9" t="n">
         <f aca="false">F93*Datos!$B$15</f>
-        <v>462.030766069246</v>
+        <v>462.283328760084</v>
       </c>
       <c r="G94" s="9" t="n">
         <f aca="false">G93*Datos!$B$15</f>
-        <v>795.106885914108</v>
+        <v>795.643573392712</v>
       </c>
       <c r="H94" s="9" t="n">
         <f aca="false">H93*Datos!$B$15</f>
-        <v>1117.15559435721</v>
+        <v>1117.19644919832</v>
       </c>
       <c r="I94" s="9" t="n">
         <f aca="false">I93*Datos!$B$15</f>
-        <v>1531.26158505402</v>
+        <v>1531.97032376775</v>
       </c>
       <c r="J94" s="9" t="n">
         <f aca="false">J93*Datos!$B$15</f>
-        <v>1952.29466773478</v>
+        <v>1952.22302470115</v>
       </c>
       <c r="K94" s="9" t="n">
         <f aca="false">K93*Datos!$B$15</f>
-        <v>2206.396610719</v>
+        <v>2206.75139540985</v>
       </c>
       <c r="L94" s="9" t="n">
         <f aca="false">L93*Datos!$B$15</f>
-        <v>2550.13256530003</v>
+        <v>2550.45950902393</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19079,43 +19079,43 @@
       </c>
       <c r="C96" s="11" t="n">
         <f aca="false">C86+C88+C90+C94+C95</f>
-        <v>22352.8294338914</v>
+        <v>22356.5521452478</v>
       </c>
       <c r="D96" s="11" t="n">
         <f aca="false">D86+D88+D90+D94+D95</f>
-        <v>33875.0831753844</v>
+        <v>33915.485598783</v>
       </c>
       <c r="E96" s="11" t="n">
         <f aca="false">E86+E88+E90+E94+E95</f>
-        <v>56416.9763778624</v>
+        <v>56454.9580934245</v>
       </c>
       <c r="F96" s="11" t="n">
         <f aca="false">F86+F88+F90+F94+F95</f>
-        <v>103859.402423946</v>
+        <v>103943.280634868</v>
       </c>
       <c r="G96" s="11" t="n">
         <f aca="false">G86+G88+G90+G94+G95</f>
-        <v>172246.402468166</v>
+        <v>172418.089231794</v>
       </c>
       <c r="H96" s="11" t="n">
         <f aca="false">H86+H88+H90+H94+H95</f>
-        <v>237619.981575166</v>
+        <v>237652.378649934</v>
       </c>
       <c r="I96" s="11" t="n">
         <f aca="false">I86+I88+I90+I94+I95</f>
-        <v>319260.223702893</v>
+        <v>319454.768281726</v>
       </c>
       <c r="J96" s="11" t="n">
         <f aca="false">J86+J88+J90+J94+J95</f>
-        <v>402635.618804436</v>
+        <v>402653.650895829</v>
       </c>
       <c r="K96" s="11" t="n">
         <f aca="false">K86+K88+K90+K94+K95</f>
-        <v>454815.043611156</v>
+        <v>454914.870890853</v>
       </c>
       <c r="L96" s="11" t="n">
         <f aca="false">L86+L88+L90+L94+L95</f>
-        <v>523350.679103644</v>
+        <v>523443.217467392</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19132,43 +19132,43 @@
       </c>
       <c r="C99" s="30" t="n">
         <f aca="false">C54+C30</f>
-        <v>13.6958369641341</v>
+        <v>13.6988375313455</v>
       </c>
       <c r="D99" s="30" t="n">
         <f aca="false">D54+D30</f>
-        <v>22.847377266859</v>
+        <v>22.8777835074802</v>
       </c>
       <c r="E99" s="30" t="n">
         <f aca="false">E54+E30</f>
-        <v>41.2162748045226</v>
+        <v>41.2458604763384</v>
       </c>
       <c r="F99" s="30" t="n">
         <f aca="false">F54+F30</f>
-        <v>79.9710464542093</v>
+        <v>80.0360262490287</v>
       </c>
       <c r="G99" s="30" t="n">
         <f aca="false">G54+G30</f>
-        <v>136.296056096951</v>
+        <v>136.444378232654</v>
       </c>
       <c r="H99" s="30" t="n">
         <f aca="false">H54+H30</f>
-        <v>190.914260271651</v>
+        <v>190.932805444062</v>
       </c>
       <c r="I99" s="30" t="n">
         <f aca="false">I54+I30</f>
-        <v>259.111166829282</v>
+        <v>259.296769313403</v>
       </c>
       <c r="J99" s="30" t="n">
         <f aca="false">J54+J30</f>
-        <v>328.820116967212</v>
+        <v>328.804758260159</v>
       </c>
       <c r="K99" s="30" t="n">
         <f aca="false">K54+K30</f>
-        <v>373.230995568367</v>
+        <v>373.319289799812</v>
       </c>
       <c r="L99" s="30" t="n">
         <f aca="false">L54+L30</f>
-        <v>430.870850884214</v>
+        <v>430.933504596725</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19180,43 +19180,43 @@
       </c>
       <c r="C100" s="9" t="n">
         <f aca="false">C55+C31</f>
-        <v>17065.2489143294</v>
+        <v>17069.104592522</v>
       </c>
       <c r="D100" s="9" t="n">
         <f aca="false">D55+D31</f>
-        <v>28477.7195964164</v>
+        <v>28516.5639467713</v>
       </c>
       <c r="E100" s="9" t="n">
         <f aca="false">E55+E31</f>
-        <v>51706.5484103962</v>
+        <v>51744.6950339792</v>
       </c>
       <c r="F100" s="9" t="n">
         <f aca="false">F55+F31</f>
-        <v>100855.02506432</v>
+        <v>100938.289492101</v>
       </c>
       <c r="G100" s="9" t="n">
         <f aca="false">G55+G31</f>
-        <v>172086.078263786</v>
+        <v>172260.669787666</v>
       </c>
       <c r="H100" s="9" t="n">
         <f aca="false">H55+H31</f>
-        <v>241089.624429238</v>
+        <v>241122.782483449</v>
       </c>
       <c r="I100" s="9" t="n">
         <f aca="false">I55+I31</f>
-        <v>327433.096325883</v>
+        <v>327649.284916462</v>
       </c>
       <c r="J100" s="9" t="n">
         <f aca="false">J55+J31</f>
-        <v>415625.374030073</v>
+        <v>415618.151162764</v>
       </c>
       <c r="K100" s="9" t="n">
         <f aca="false">K55+K31</f>
-        <v>471617.136451018</v>
+        <v>471722.237692324</v>
       </c>
       <c r="L100" s="9" t="n">
         <f aca="false">L55+L31</f>
-        <v>544426.602978224</v>
+        <v>544505.124575307</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19228,43 +19228,43 @@
       </c>
       <c r="C101" s="30" t="n">
         <f aca="false">C99-C25</f>
-        <v>1.75085949193642</v>
+        <v>1.75122953023042</v>
       </c>
       <c r="D101" s="30" t="n">
         <f aca="false">D99-D25</f>
-        <v>2.90347492784298</v>
+        <v>2.90716314462068</v>
       </c>
       <c r="E101" s="30" t="n">
         <f aca="false">E99-E25</f>
-        <v>5.16791067428202</v>
+        <v>5.17161093574217</v>
       </c>
       <c r="F101" s="30" t="n">
         <f aca="false">F99-F25</f>
-        <v>9.91896626782135</v>
+        <v>9.92691779418024</v>
       </c>
       <c r="G101" s="30" t="n">
         <f aca="false">G99-G25</f>
-        <v>16.8741896868139</v>
+        <v>16.8931196010085</v>
       </c>
       <c r="H101" s="30" t="n">
         <f aca="false">H99-H25</f>
-        <v>23.6144537305448</v>
+        <v>23.614267179012</v>
       </c>
       <c r="I101" s="30" t="n">
         <f aca="false">I99-I25</f>
-        <v>32.0147374960949</v>
+        <v>32.0483540760584</v>
       </c>
       <c r="J101" s="30" t="n">
         <f aca="false">J99-J25</f>
-        <v>40.6055106875828</v>
+        <v>40.5944142042789</v>
       </c>
       <c r="K101" s="30" t="n">
         <f aca="false">K99-K25</f>
-        <v>46.1082088805801</v>
+        <v>46.1210157814019</v>
       </c>
       <c r="L101" s="30" t="n">
         <f aca="false">L99-L25</f>
-        <v>53.2313018235947</v>
+        <v>53.2400819599926</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19276,43 +19276,43 @@
       </c>
       <c r="C102" s="9" t="n">
         <f aca="false">-C101*Datos!$B$9</f>
-        <v>-437.714872984104</v>
+        <v>-437.807382557606</v>
       </c>
       <c r="D102" s="9" t="n">
         <f aca="false">-D101*Datos!$B$9</f>
-        <v>-725.868731960745</v>
+        <v>-726.79078615517</v>
       </c>
       <c r="E102" s="9" t="n">
         <f aca="false">-E101*Datos!$B$9</f>
-        <v>-1291.9776685705</v>
+        <v>-1292.90273393554</v>
       </c>
       <c r="F102" s="9" t="n">
         <f aca="false">-F101*Datos!$B$9</f>
-        <v>-2479.74156695534</v>
+        <v>-2481.72944854506</v>
       </c>
       <c r="G102" s="9" t="n">
         <f aca="false">-G101*Datos!$B$9</f>
-        <v>-4218.54742170347</v>
+        <v>-4223.27990025212</v>
       </c>
       <c r="H102" s="9" t="n">
         <f aca="false">-H101*Datos!$B$9</f>
-        <v>-5903.61343263619</v>
+        <v>-5903.56679475299</v>
       </c>
       <c r="I102" s="9" t="n">
         <f aca="false">-I101*Datos!$B$9</f>
-        <v>-8003.68437402372</v>
+        <v>-8012.08851901461</v>
       </c>
       <c r="J102" s="9" t="n">
         <f aca="false">-J101*Datos!$B$9</f>
-        <v>-10151.3776718957</v>
+        <v>-10148.6035510697</v>
       </c>
       <c r="K102" s="9" t="n">
         <f aca="false">-K101*Datos!$B$9</f>
-        <v>-11527.052220145</v>
+        <v>-11530.2539453505</v>
       </c>
       <c r="L102" s="9" t="n">
         <f aca="false">-L101*Datos!$B$9</f>
-        <v>-13307.8254558987</v>
+        <v>-13310.0204899982</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19324,43 +19324,43 @@
       </c>
       <c r="C103" s="30" t="n">
         <f aca="false">C54*(Datos!$B$51/2/12+Datos!$B$50/52)+C37</f>
-        <v>1.34541775755274</v>
+        <v>1.34573334599647</v>
       </c>
       <c r="D103" s="30" t="n">
         <f aca="false">D54*(Datos!$B$51/2/12+Datos!$B$50/52)+D37</f>
-        <v>2.25159203698153</v>
+        <v>2.25474980742021</v>
       </c>
       <c r="E103" s="30" t="n">
         <f aca="false">E54*(Datos!$B$51/2/12+Datos!$B$50/52)+E37</f>
-        <v>4.08503371284284</v>
+        <v>4.0881816842397</v>
       </c>
       <c r="F103" s="30" t="n">
         <f aca="false">F54*(Datos!$B$51/2/12+Datos!$B$50/52)+F37</f>
-        <v>7.95764630498611</v>
+        <v>7.96444033152732</v>
       </c>
       <c r="G103" s="30" t="n">
         <f aca="false">G54*(Datos!$B$51/2/12+Datos!$B$50/52)+G37</f>
-        <v>13.2518249900995</v>
+        <v>13.2640212872674</v>
       </c>
       <c r="H103" s="30" t="n">
         <f aca="false">H54*(Datos!$B$51/2/12+Datos!$B$50/52)+H37</f>
-        <v>17.3305867912496</v>
+        <v>17.3313785881811</v>
       </c>
       <c r="I103" s="30" t="n">
         <f aca="false">I54*(Datos!$B$51/2/12+Datos!$B$50/52)+I37</f>
-        <v>22.3340734789705</v>
+        <v>22.348354483692</v>
       </c>
       <c r="J103" s="30" t="n">
         <f aca="false">J54*(Datos!$B$51/2/12+Datos!$B$50/52)+J37</f>
-        <v>27.3719646463186</v>
+        <v>27.370149427687</v>
       </c>
       <c r="K103" s="30" t="n">
         <f aca="false">K54*(Datos!$B$51/2/12+Datos!$B$50/52)+K37</f>
-        <v>30.5120883725126</v>
+        <v>30.5185955389604</v>
       </c>
       <c r="L103" s="30" t="n">
         <f aca="false">L54*(Datos!$B$51/2/12+Datos!$B$50/52)+L37</f>
-        <v>34.5690370686019</v>
+        <v>34.5733750151538</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19372,43 +19372,43 @@
       </c>
       <c r="C104" s="9" t="n">
         <f aca="false">IF(C99=0,0,C103*C100/C99*Datos!$B$7)</f>
-        <v>201.169645811547</v>
+        <v>201.218211550266</v>
       </c>
       <c r="D104" s="9" t="n">
         <f aca="false">IF(D99=0,0,D103*D100/D99*Datos!$B$7)</f>
-        <v>336.77497032113</v>
+        <v>337.258460617458</v>
       </c>
       <c r="E104" s="9" t="n">
         <f aca="false">IF(E99=0,0,E103*E100/E99*Datos!$B$7)</f>
-        <v>614.969677195665</v>
+        <v>615.455840808572</v>
       </c>
       <c r="F104" s="9" t="n">
         <f aca="false">IF(F99=0,0,F103*F100/F99*Datos!$B$7)</f>
-        <v>1204.28878169338</v>
+        <v>1205.33268054801</v>
       </c>
       <c r="G104" s="9" t="n">
         <f aca="false">IF(G99=0,0,G103*G100/G99*Datos!$B$7)</f>
-        <v>2007.79508169667</v>
+        <v>2009.49505193382</v>
       </c>
       <c r="H104" s="9" t="n">
         <f aca="false">IF(H99=0,0,H103*H100/H99*Datos!$B$7)</f>
-        <v>2626.24153147838</v>
+        <v>2626.46760135557</v>
       </c>
       <c r="I104" s="9" t="n">
         <f aca="false">IF(I99=0,0,I103*I100/I99*Datos!$B$7)</f>
-        <v>3386.76943442146</v>
+        <v>3388.74520574884</v>
       </c>
       <c r="J104" s="9" t="n">
         <f aca="false">IF(J99=0,0,J103*J100/J99*Datos!$B$7)</f>
-        <v>4151.74709467006</v>
+        <v>4151.59353375898</v>
       </c>
       <c r="K104" s="9" t="n">
         <f aca="false">IF(K99=0,0,K103*K100/K99*Datos!$B$7)</f>
-        <v>4626.63302338154</v>
+        <v>4627.55627331828</v>
       </c>
       <c r="L104" s="9" t="n">
         <f aca="false">IF(L99=0,0,L103*L100/L99*Datos!$B$7)</f>
-        <v>5241.56230504757</v>
+        <v>5242.21384565553</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19420,43 +19420,43 @@
       </c>
       <c r="C105" s="9" t="n">
         <f aca="false">C56+C57+C40*Datos!$B$46/60</f>
-        <v>3.00309579676457</v>
+        <v>3.00368176316969</v>
       </c>
       <c r="D105" s="9" t="n">
         <f aca="false">D56+D57+D40*Datos!$B$46/60</f>
-        <v>4.94156887027411</v>
+        <v>4.94807987406418</v>
       </c>
       <c r="E105" s="9" t="n">
         <f aca="false">E56+E57+E40*Datos!$B$46/60</f>
-        <v>9.77687571910761</v>
+        <v>9.78272329163087</v>
       </c>
       <c r="F105" s="9" t="n">
         <f aca="false">F56+F57+F40*Datos!$B$46/60</f>
-        <v>20.5229612761976</v>
+        <v>20.5362717593644</v>
       </c>
       <c r="G105" s="9" t="n">
         <f aca="false">G56+G57+G40*Datos!$B$46/60</f>
-        <v>35.4492627482788</v>
+        <v>35.4659618841392</v>
       </c>
       <c r="H105" s="9" t="n">
         <f aca="false">H56+H57+H40*Datos!$B$46/60</f>
-        <v>49.7756443734183</v>
+        <v>49.7880586695141</v>
       </c>
       <c r="I105" s="9" t="n">
         <f aca="false">I56+I57+I40*Datos!$B$46/60</f>
-        <v>68.1828056112613</v>
+        <v>68.2010116041021</v>
       </c>
       <c r="J105" s="9" t="n">
         <f aca="false">J56+J57+J40*Datos!$B$46/60</f>
-        <v>86.8741947465183</v>
+        <v>86.882423754792</v>
       </c>
       <c r="K105" s="9" t="n">
         <f aca="false">K56+K57+K40*Datos!$B$46/60</f>
-        <v>98.3090072583123</v>
+        <v>98.3200804735262</v>
       </c>
       <c r="L105" s="9" t="n">
         <f aca="false">L56+L57+L40*Datos!$B$46/60</f>
-        <v>113.59536747308</v>
+        <v>113.606394245466</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19468,43 +19468,43 @@
       </c>
       <c r="C106" s="9" t="n">
         <f aca="false">C105*Datos!$B$15</f>
-        <v>18.8634175333279</v>
+        <v>18.8670981781386</v>
       </c>
       <c r="D106" s="9" t="n">
         <f aca="false">D105*Datos!$B$15</f>
-        <v>31.0395948641074</v>
+        <v>31.0804925881113</v>
       </c>
       <c r="E106" s="9" t="n">
         <f aca="false">E105*Datos!$B$15</f>
-        <v>61.411723548638</v>
+        <v>61.4484540459406</v>
       </c>
       <c r="F106" s="9" t="n">
         <f aca="false">F105*Datos!$B$15</f>
-        <v>128.911368059027</v>
+        <v>128.994975515645</v>
       </c>
       <c r="G106" s="9" t="n">
         <f aca="false">G105*Datos!$B$15</f>
-        <v>222.668302885928</v>
+        <v>222.773195567846</v>
       </c>
       <c r="H106" s="9" t="n">
         <f aca="false">H105*Datos!$B$15</f>
-        <v>312.656946813955</v>
+        <v>312.734925029266</v>
       </c>
       <c r="I106" s="9" t="n">
         <f aca="false">I105*Datos!$B$15</f>
-        <v>428.278289432065</v>
+        <v>428.392647170815</v>
       </c>
       <c r="J106" s="9" t="n">
         <f aca="false">J105*Datos!$B$15</f>
-        <v>545.684959547659</v>
+        <v>545.736648614361</v>
       </c>
       <c r="K106" s="9" t="n">
         <f aca="false">K105*Datos!$B$15</f>
-        <v>617.510721169276</v>
+        <v>617.580275621132</v>
       </c>
       <c r="L106" s="9" t="n">
         <f aca="false">L105*Datos!$B$15</f>
-        <v>713.529301597739</v>
+        <v>713.598564327144</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19564,43 +19564,43 @@
       </c>
       <c r="C108" s="11" t="n">
         <f aca="false">C100+C102+C104+C106+C107</f>
-        <v>19427.7548841238</v>
+        <v>19431.5702991265</v>
       </c>
       <c r="D108" s="11" t="n">
         <f aca="false">D100+D102+D104+D106+D107</f>
-        <v>30699.8532090746</v>
+        <v>30738.2998932554</v>
       </c>
       <c r="E108" s="11" t="n">
         <f aca="false">E100+E102+E104+E106+E107</f>
-        <v>53671.1399220037</v>
+        <v>53708.8843743318</v>
       </c>
       <c r="F108" s="11" t="n">
         <f aca="false">F100+F102+F104+F106+F107</f>
-        <v>102288.671426551</v>
+        <v>102371.075479053</v>
       </c>
       <c r="G108" s="11" t="n">
         <f aca="false">G100+G102+G104+G106+G107</f>
-        <v>172678.182006099</v>
+        <v>172849.845914349</v>
       </c>
       <c r="H108" s="11" t="n">
         <f aca="false">H100+H102+H104+H106+H107</f>
-        <v>240705.097254328</v>
+        <v>240738.605994515</v>
       </c>
       <c r="I108" s="11" t="n">
         <f aca="false">I100+I102+I104+I106+I107</f>
-        <v>325824.647455147</v>
+        <v>326034.522029801</v>
       </c>
       <c r="J108" s="11" t="n">
         <f aca="false">J100+J102+J104+J106+J107</f>
-        <v>412751.616191828</v>
+        <v>412747.065573501</v>
       </c>
       <c r="K108" s="11" t="n">
         <f aca="false">K100+K102+K104+K106+K107</f>
-        <v>467914.415754858</v>
+        <v>468017.308075347</v>
       </c>
       <c r="L108" s="11" t="n">
         <f aca="false">L100+L102+L104+L106+L107</f>
-        <v>539654.056908405</v>
+        <v>539731.104274726</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19617,43 +19617,43 @@
       </c>
       <c r="C111" s="30" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>9.74436245386314</v>
+        <v>9.74632335880314</v>
       </c>
       <c r="D111" s="30" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>16.2066883707767</v>
+        <v>16.2269770268257</v>
       </c>
       <c r="E111" s="30" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>29.1078692763175</v>
+        <v>29.126830107265</v>
       </c>
       <c r="F111" s="30" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>56.319897511078</v>
+        <v>56.3627812324881</v>
       </c>
       <c r="G111" s="30" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>95.9075832845086</v>
+        <v>96.0227901140449</v>
       </c>
       <c r="H111" s="30" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>134.332583077155</v>
+        <v>134.336164039562</v>
       </c>
       <c r="I111" s="30" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>182.257743808154</v>
+        <v>182.394275779078</v>
       </c>
       <c r="J111" s="30" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>231.280035549904</v>
+        <v>231.265127061054</v>
       </c>
       <c r="K111" s="30" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>262.560532780319</v>
+        <v>262.62590266107</v>
       </c>
       <c r="L111" s="30" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15,Piezas!$H$6:$H$13)/1000</f>
-        <v>303.127601765745</v>
+        <v>303.169314675562</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19665,43 +19665,43 @@
       </c>
       <c r="C112" s="9" t="n">
         <f aca="false">SUMPRODUCT(C$8:C$15,Corte!$I$32:$I$39)</f>
-        <v>13406.3605354273</v>
+        <v>13409.2097303051</v>
       </c>
       <c r="D112" s="9" t="n">
         <f aca="false">SUMPRODUCT(D$8:D$15,Corte!$I$32:$I$39)</f>
-        <v>22364.4626749836</v>
+        <v>22393.7822747132</v>
       </c>
       <c r="E112" s="9" t="n">
         <f aca="false">SUMPRODUCT(E$8:E$15,Corte!$I$32:$I$39)</f>
-        <v>40232.0208714075</v>
+        <v>40259.663210297</v>
       </c>
       <c r="F112" s="9" t="n">
         <f aca="false">SUMPRODUCT(F$8:F$15,Corte!$I$32:$I$39)</f>
-        <v>77878.3049898693</v>
+        <v>77940.4508371217</v>
       </c>
       <c r="G112" s="9" t="n">
         <f aca="false">SUMPRODUCT(G$8:G$15,Corte!$I$32:$I$39)</f>
-        <v>132658.745284838</v>
+        <v>132810.969924247</v>
       </c>
       <c r="H112" s="9" t="n">
         <f aca="false">SUMPRODUCT(H$8:H$15,Corte!$I$32:$I$39)</f>
-        <v>185829.776912118</v>
+        <v>185843.53402884</v>
       </c>
       <c r="I112" s="9" t="n">
         <f aca="false">SUMPRODUCT(I$8:I$15,Corte!$I$32:$I$39)</f>
-        <v>252126.496622955</v>
+        <v>252305.567734064</v>
       </c>
       <c r="J112" s="9" t="n">
         <f aca="false">SUMPRODUCT(J$8:J$15,Corte!$I$32:$I$39)</f>
-        <v>319925.209559701</v>
+        <v>319913.973106337</v>
       </c>
       <c r="K112" s="9" t="n">
         <f aca="false">SUMPRODUCT(K$8:K$15,Corte!$I$32:$I$39)</f>
-        <v>363183.583455873</v>
+        <v>363270.868477573</v>
       </c>
       <c r="L112" s="9" t="n">
         <f aca="false">SUMPRODUCT(L$8:L$15,Corte!$I$32:$I$39)</f>
-        <v>419269.833373514</v>
+        <v>419328.555459846</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19713,43 +19713,43 @@
       </c>
       <c r="C113" s="30" t="n">
         <f aca="false">C111+C30</f>
-        <v>12.7203015405208</v>
+        <v>12.7231643460055</v>
       </c>
       <c r="D113" s="30" t="n">
         <f aca="false">D111+D30</f>
-        <v>21.2571608271907</v>
+        <v>21.2861059586757</v>
       </c>
       <c r="E113" s="30" t="n">
         <f aca="false">E111+E30</f>
-        <v>38.4972403645445</v>
+        <v>38.5255290908929</v>
       </c>
       <c r="F113" s="30" t="n">
         <f aca="false">F111+F30</f>
-        <v>74.9164161957101</v>
+        <v>74.978347663673</v>
       </c>
       <c r="G113" s="30" t="n">
         <f aca="false">G111+G30</f>
-        <v>127.757002574009</v>
+        <v>127.891313507901</v>
       </c>
       <c r="H113" s="30" t="n">
         <f aca="false">H111+H30</f>
-        <v>178.986217454328</v>
+        <v>179.010202634716</v>
       </c>
       <c r="I113" s="30" t="n">
         <f aca="false">I111+I30</f>
-        <v>242.999970461348</v>
+        <v>243.15731252629</v>
       </c>
       <c r="J113" s="30" t="n">
         <f aca="false">J111+J30</f>
-        <v>308.413241565485</v>
+        <v>308.412672111893</v>
       </c>
       <c r="K113" s="30" t="n">
         <f aca="false">K111+K30</f>
-        <v>350.022326394569</v>
+        <v>350.101320879505</v>
       </c>
       <c r="L113" s="30" t="n">
         <f aca="false">L111+L30</f>
-        <v>404.06850228125</v>
+        <v>404.126592382497</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19761,43 +19761,43 @@
       </c>
       <c r="C114" s="9" t="n">
         <f aca="false">C112+C31</f>
-        <v>16955.7775450761</v>
+        <v>16959.6963939999</v>
       </c>
       <c r="D114" s="9" t="n">
         <f aca="false">D112+D31</f>
-        <v>28383.3112781369</v>
+        <v>28422.9052018137</v>
       </c>
       <c r="E114" s="9" t="n">
         <f aca="false">E112+E31</f>
-        <v>51437.3016783078</v>
+        <v>51475.9997765892</v>
       </c>
       <c r="F114" s="9" t="n">
         <f aca="false">F112+F31</f>
-        <v>100100.80779089</v>
+        <v>100185.552009634</v>
       </c>
       <c r="G114" s="9" t="n">
         <f aca="false">G112+G31</f>
-        <v>170727.133708532</v>
+        <v>170902.016435233</v>
       </c>
       <c r="H114" s="9" t="n">
         <f aca="false">H112+H31</f>
-        <v>239203.940442532</v>
+        <v>239241.897581307</v>
       </c>
       <c r="I114" s="9" t="n">
         <f aca="false">I112+I31</f>
-        <v>324744.45845183</v>
+        <v>324948.21869805</v>
       </c>
       <c r="J114" s="9" t="n">
         <f aca="false">J112+J31</f>
-        <v>412146.135512804</v>
+        <v>412151.906394309</v>
       </c>
       <c r="K114" s="9" t="n">
         <f aca="false">K112+K31</f>
-        <v>467745.922158803</v>
+        <v>467849.367200121</v>
       </c>
       <c r="L114" s="9" t="n">
         <f aca="false">L112+L31</f>
-        <v>539947.548396235</v>
+        <v>540025.695070655</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19809,43 +19809,43 @@
       </c>
       <c r="C115" s="30" t="n">
         <f aca="false">C113-C25</f>
-        <v>0.775324068323117</v>
+        <v>0.775556344890459</v>
       </c>
       <c r="D115" s="30" t="n">
         <f aca="false">D113-D25</f>
-        <v>1.31325848817471</v>
+        <v>1.31548559581618</v>
       </c>
       <c r="E115" s="30" t="n">
         <f aca="false">E113-E25</f>
-        <v>2.44887623430387</v>
+        <v>2.45127955029671</v>
       </c>
       <c r="F115" s="30" t="n">
         <f aca="false">F113-F25</f>
-        <v>4.86433600932222</v>
+        <v>4.8692392088245</v>
       </c>
       <c r="G115" s="30" t="n">
         <f aca="false">G113-G25</f>
-        <v>8.33513616387194</v>
+        <v>8.34005487625473</v>
       </c>
       <c r="H115" s="30" t="n">
         <f aca="false">H113-H25</f>
-        <v>11.6864109132216</v>
+        <v>11.6916643696663</v>
       </c>
       <c r="I115" s="30" t="n">
         <f aca="false">I113-I25</f>
-        <v>15.903541128161</v>
+        <v>15.9088972889454</v>
       </c>
       <c r="J115" s="30" t="n">
         <f aca="false">J113-J25</f>
-        <v>20.1986352858556</v>
+        <v>20.2023280560127</v>
       </c>
       <c r="K115" s="30" t="n">
         <f aca="false">K113-K25</f>
-        <v>22.8995397067815</v>
+        <v>22.9030468610949</v>
       </c>
       <c r="L115" s="30" t="n">
         <f aca="false">L113-L25</f>
-        <v>26.4289532206306</v>
+        <v>26.4331697457637</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19857,43 +19857,43 @@
       </c>
       <c r="C116" s="9" t="n">
         <f aca="false">-C115*Datos!$B$9</f>
-        <v>-193.831017080779</v>
+        <v>-193.889086222615</v>
       </c>
       <c r="D116" s="9" t="n">
         <f aca="false">-D115*Datos!$B$9</f>
-        <v>-328.314622043679</v>
+        <v>-328.871398954044</v>
       </c>
       <c r="E116" s="9" t="n">
         <f aca="false">-E115*Datos!$B$9</f>
-        <v>-612.219058575969</v>
+        <v>-612.819887574178</v>
       </c>
       <c r="F116" s="9" t="n">
         <f aca="false">-F115*Datos!$B$9</f>
-        <v>-1216.08400233055</v>
+        <v>-1217.30980220612</v>
       </c>
       <c r="G116" s="9" t="n">
         <f aca="false">-G115*Datos!$B$9</f>
-        <v>-2083.78404096798</v>
+        <v>-2085.01371906368</v>
       </c>
       <c r="H116" s="9" t="n">
         <f aca="false">-H115*Datos!$B$9</f>
-        <v>-2921.60272830539</v>
+        <v>-2922.91609241659</v>
       </c>
       <c r="I116" s="9" t="n">
         <f aca="false">-I115*Datos!$B$9</f>
-        <v>-3975.88528204025</v>
+        <v>-3977.22432223635</v>
       </c>
       <c r="J116" s="9" t="n">
         <f aca="false">-J115*Datos!$B$9</f>
-        <v>-5049.65882146391</v>
+        <v>-5050.58201400318</v>
       </c>
       <c r="K116" s="9" t="n">
         <f aca="false">-K115*Datos!$B$9</f>
-        <v>-5724.88492669537</v>
+        <v>-5725.76171527373</v>
       </c>
       <c r="L116" s="9" t="n">
         <f aca="false">-L115*Datos!$B$9</f>
-        <v>-6607.23830515765</v>
+        <v>-6608.29243644093</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19905,43 +19905,43 @@
       </c>
       <c r="C117" s="30" t="n">
         <f aca="false">C111*(Datos!$B$51/2/12+Datos!$B$50/52)+C37</f>
-        <v>1.26724985501962</v>
+        <v>1.26755440486346</v>
       </c>
       <c r="D117" s="30" t="n">
         <f aca="false">D111*(Datos!$B$51/2/12+Datos!$B$50/52)+D37</f>
-        <v>2.12417084790555</v>
+        <v>2.12721154229165</v>
       </c>
       <c r="E117" s="30" t="n">
         <f aca="false">E111*(Datos!$B$51/2/12+Datos!$B$50/52)+E37</f>
-        <v>3.86716236348562</v>
+        <v>3.87020641297003</v>
       </c>
       <c r="F117" s="30" t="n">
         <f aca="false">F111*(Datos!$B$51/2/12+Datos!$B$50/52)+F37</f>
-        <v>7.55262785478586</v>
+        <v>7.55917762436741</v>
       </c>
       <c r="G117" s="30" t="n">
         <f aca="false">G111*(Datos!$B$51/2/12+Datos!$B$50/52)+G37</f>
-        <v>12.5676059578125</v>
+        <v>12.5786795625275</v>
       </c>
       <c r="H117" s="30" t="n">
         <f aca="false">H111*(Datos!$B$51/2/12+Datos!$B$50/52)+H37</f>
-        <v>16.3748141296051</v>
+        <v>16.3760418246118</v>
       </c>
       <c r="I117" s="30" t="n">
         <f aca="false">I111*(Datos!$B$51/2/12+Datos!$B$50/52)+I37</f>
-        <v>21.0431122315399</v>
+        <v>21.0551287795964</v>
       </c>
       <c r="J117" s="30" t="n">
         <f aca="false">J111*(Datos!$B$51/2/12+Datos!$B$50/52)+J37</f>
-        <v>25.7367983481033</v>
+        <v>25.7361681658067</v>
       </c>
       <c r="K117" s="30" t="n">
         <f aca="false">K111*(Datos!$B$51/2/12+Datos!$B$50/52)+K37</f>
-        <v>28.6524193682018</v>
+        <v>28.6581813626538</v>
       </c>
       <c r="L117" s="30" t="n">
         <f aca="false">L111*(Datos!$B$51/2/12+Datos!$B$50/52)+L37</f>
-        <v>32.4214129818259</v>
+        <v>32.4253852543983</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19953,43 +19953,43 @@
       </c>
       <c r="C118" s="9" t="n">
         <f aca="false">IF(C113=0,0,C117*C114/C113*Datos!$B$7)</f>
-        <v>202.704691242998</v>
+        <v>202.754635102491</v>
       </c>
       <c r="D118" s="9" t="n">
         <f aca="false">IF(D113=0,0,D117*D114/D113*Datos!$B$7)</f>
-        <v>340.352145091326</v>
+        <v>340.850687080884</v>
       </c>
       <c r="E118" s="9" t="n">
         <f aca="false">IF(E113=0,0,E117*E114/E113*Datos!$B$7)</f>
-        <v>620.043603892628</v>
+        <v>620.542531097366</v>
       </c>
       <c r="F118" s="9" t="n">
         <f aca="false">IF(F113=0,0,F117*F114/F113*Datos!$B$7)</f>
-        <v>1210.9882254373</v>
+        <v>1212.06253266589</v>
       </c>
       <c r="G118" s="9" t="n">
         <f aca="false">IF(G113=0,0,G117*G114/G113*Datos!$B$7)</f>
-        <v>2015.35536951501</v>
+        <v>2017.07682158958</v>
       </c>
       <c r="H118" s="9" t="n">
         <f aca="false">IF(H113=0,0,H117*H114/H113*Datos!$B$7)</f>
-        <v>2626.07039996143</v>
+        <v>2626.33208386604</v>
       </c>
       <c r="I118" s="9" t="n">
         <f aca="false">IF(I113=0,0,I117*I114/I113*Datos!$B$7)</f>
-        <v>3374.63452664549</v>
+        <v>3376.49393487922</v>
       </c>
       <c r="J118" s="9" t="n">
         <f aca="false">IF(J113=0,0,J117*J114/J113*Datos!$B$7)</f>
-        <v>4127.18543178018</v>
+        <v>4127.1497828624</v>
       </c>
       <c r="K118" s="9" t="n">
         <f aca="false">IF(K113=0,0,K117*K114/K113*Datos!$B$7)</f>
-        <v>4594.69627238097</v>
+        <v>4595.5994619872</v>
       </c>
       <c r="L118" s="9" t="n">
         <f aca="false">IF(L113=0,0,L117*L114/L113*Datos!$B$7)</f>
-        <v>5198.87960271466</v>
+        <v>5199.5215974405</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20001,43 +20001,43 @@
       </c>
       <c r="C119" s="9" t="n">
         <f aca="false">C40*Datos!$B$46/60</f>
-        <v>0.523996023455547</v>
+        <v>0.524095878749553</v>
       </c>
       <c r="D119" s="9" t="n">
         <f aca="false">D40*Datos!$B$46/60</f>
-        <v>0.914368338106516</v>
+        <v>0.916210823378074</v>
       </c>
       <c r="E119" s="9" t="n">
         <f aca="false">E40*Datos!$B$46/60</f>
-        <v>1.77544748904557</v>
+        <v>1.77602469119846</v>
       </c>
       <c r="F119" s="9" t="n">
         <f aca="false">F40*Datos!$B$46/60</f>
-        <v>3.6467086152735</v>
+        <v>3.64973020955148</v>
       </c>
       <c r="G119" s="9" t="n">
         <f aca="false">G40*Datos!$B$46/60</f>
-        <v>6.27567265572325</v>
+        <v>6.27824493973174</v>
       </c>
       <c r="H119" s="9" t="n">
         <f aca="false">H40*Datos!$B$46/60</f>
-        <v>8.84766154455763</v>
+        <v>8.85040639620896</v>
       </c>
       <c r="I119" s="9" t="n">
         <f aca="false">I40*Datos!$B$46/60</f>
-        <v>12.0509571136469</v>
+        <v>12.0544806990803</v>
       </c>
       <c r="J119" s="9" t="n">
         <f aca="false">J40*Datos!$B$46/60</f>
-        <v>15.3258972990045</v>
+        <v>15.3275476035744</v>
       </c>
       <c r="K119" s="9" t="n">
         <f aca="false">K40*Datos!$B$46/60</f>
-        <v>17.4061978903632</v>
+        <v>17.4082914759475</v>
       </c>
       <c r="L119" s="9" t="n">
         <f aca="false">L40*Datos!$B$46/60</f>
-        <v>20.1444510435848</v>
+        <v>20.1466991122665</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20049,43 +20049,43 @@
       </c>
       <c r="C120" s="9" t="n">
         <f aca="false">C119*Datos!$B$15</f>
-        <v>3.29138876851499</v>
+        <v>3.29201599196413</v>
       </c>
       <c r="D120" s="9" t="n">
         <f aca="false">D119*Datos!$B$15</f>
-        <v>5.74344373547486</v>
+        <v>5.75501698232695</v>
       </c>
       <c r="E120" s="9" t="n">
         <f aca="false">E119*Datos!$B$15</f>
-        <v>11.1521608236565</v>
+        <v>11.1557864173597</v>
       </c>
       <c r="F120" s="9" t="n">
         <f aca="false">F119*Datos!$B$15</f>
-        <v>22.9061581406758</v>
+        <v>22.9251377531621</v>
       </c>
       <c r="G120" s="9" t="n">
         <f aca="false">G119*Datos!$B$15</f>
-        <v>39.4195329149792</v>
+        <v>39.4356902641116</v>
       </c>
       <c r="H120" s="9" t="n">
         <f aca="false">H119*Datos!$B$15</f>
-        <v>55.5750283052471</v>
+        <v>55.5922696076464</v>
       </c>
       <c r="I120" s="9" t="n">
         <f aca="false">I119*Datos!$B$15</f>
-        <v>75.6959654619939</v>
+        <v>75.7180982435445</v>
       </c>
       <c r="J120" s="9" t="n">
         <f aca="false">J119*Datos!$B$15</f>
-        <v>96.2669256623411</v>
+        <v>96.2772917599505</v>
       </c>
       <c r="K120" s="9" t="n">
         <f aca="false">K119*Datos!$B$15</f>
-        <v>109.333967576857</v>
+        <v>109.347118066116</v>
       </c>
       <c r="L120" s="9" t="n">
         <f aca="false">L119*Datos!$B$15</f>
-        <v>126.533822671995</v>
+        <v>126.547943519633</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20145,43 +20145,43 @@
       </c>
       <c r="C122" s="11" t="n">
         <f aca="false">C114+C116+C118+C120+C121</f>
-        <v>17417.9426080068</v>
+        <v>17421.8539588717</v>
       </c>
       <c r="D122" s="11" t="n">
         <f aca="false">D114+D116+D118+D120+D121</f>
-        <v>28851.09224492</v>
+        <v>28890.6395069228</v>
       </c>
       <c r="E122" s="11" t="n">
         <f aca="false">E114+E116+E118+E120+E121</f>
-        <v>51906.2783844481</v>
+        <v>51944.8782065297</v>
       </c>
       <c r="F122" s="11" t="n">
         <f aca="false">F114+F116+F118+F120+F121</f>
-        <v>100568.618172138</v>
+        <v>100653.229877847</v>
       </c>
       <c r="G122" s="11" t="n">
         <f aca="false">G114+G116+G118+G120+G121</f>
-        <v>171148.124569994</v>
+        <v>171323.515228023</v>
       </c>
       <c r="H122" s="11" t="n">
         <f aca="false">H114+H116+H118+H120+H121</f>
-        <v>239413.983142493</v>
+        <v>239450.905842364</v>
       </c>
       <c r="I122" s="11" t="n">
         <f aca="false">I114+I116+I118+I120+I121</f>
-        <v>324668.903661897</v>
+        <v>324873.206408936</v>
       </c>
       <c r="J122" s="11" t="n">
         <f aca="false">J114+J116+J118+J120+J121</f>
-        <v>411769.929048782</v>
+        <v>411774.751454928</v>
       </c>
       <c r="K122" s="11" t="n">
         <f aca="false">K114+K116+K118+K120+K121</f>
-        <v>467175.067472066</v>
+        <v>467278.5520649</v>
       </c>
       <c r="L122" s="11" t="n">
         <f aca="false">L114+L116+L118+L120+L121</f>
-        <v>539115.723516464</v>
+        <v>539193.472175174</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20250,39 +20250,39 @@
       </c>
       <c r="D126" s="9" t="n">
         <f aca="false">D9/Corte!$I$7</f>
-        <v>26.7454611222222</v>
+        <v>26.8195351962963</v>
       </c>
       <c r="E126" s="9" t="n">
         <f aca="false">E9/Corte!$I$7</f>
-        <v>48.5121502814815</v>
+        <v>48.5180762074074</v>
       </c>
       <c r="F126" s="9" t="n">
         <f aca="false">F9/Corte!$I$7</f>
-        <v>95.5391916296296</v>
+        <v>95.6191916296296</v>
       </c>
       <c r="G126" s="9" t="n">
         <f aca="false">G9/Corte!$I$7</f>
-        <v>158.603989851852</v>
+        <v>158.689915777778</v>
       </c>
       <c r="H126" s="9" t="n">
         <f aca="false">H9/Corte!$I$7</f>
-        <v>225.815921740741</v>
+        <v>225.907773592593</v>
       </c>
       <c r="I126" s="9" t="n">
         <f aca="false">I9/Corte!$I$7</f>
-        <v>300.078352740741</v>
+        <v>300.213167555556</v>
       </c>
       <c r="J126" s="9" t="n">
         <f aca="false">J9/Corte!$I$7</f>
-        <v>379.969873592593</v>
+        <v>379.965429148148</v>
       </c>
       <c r="K126" s="9" t="n">
         <f aca="false">K9/Corte!$I$7</f>
-        <v>443.14763862963</v>
+        <v>443.251342333333</v>
       </c>
       <c r="L126" s="9" t="n">
         <f aca="false">L9/Corte!$I$7</f>
-        <v>523.125127555556</v>
+        <v>523.197720148148</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20294,43 +20294,43 @@
       </c>
       <c r="C127" s="9" t="n">
         <f aca="false">C10/Corte!$I$8</f>
-        <v>190.06441875</v>
+        <v>190.147752083333</v>
       </c>
       <c r="D127" s="9" t="n">
         <f aca="false">D10/Corte!$I$8</f>
-        <v>326.748240083333</v>
+        <v>327.338240083333</v>
       </c>
       <c r="E127" s="9" t="n">
         <f aca="false">E10/Corte!$I$8</f>
-        <v>558.341465916667</v>
+        <v>559.311465916667</v>
       </c>
       <c r="F127" s="9" t="n">
         <f aca="false">F10/Corte!$I$8</f>
-        <v>1015.45627608333</v>
+        <v>1016.99960941667</v>
       </c>
       <c r="G127" s="9" t="n">
         <f aca="false">G10/Corte!$I$8</f>
-        <v>1714.40891166667</v>
+        <v>1716.06557833333</v>
       </c>
       <c r="H127" s="9" t="n">
         <f aca="false">H10/Corte!$I$8</f>
-        <v>2390.0303425</v>
+        <v>2391.8003425</v>
       </c>
       <c r="I127" s="9" t="n">
         <f aca="false">I10/Corte!$I$8</f>
-        <v>3220.41665333333</v>
+        <v>3222.04998666667</v>
       </c>
       <c r="J127" s="9" t="n">
         <f aca="false">J10/Corte!$I$8</f>
-        <v>4068.87553083333</v>
+        <v>4070.18553083333</v>
       </c>
       <c r="K127" s="9" t="n">
         <f aca="false">K10/Corte!$I$8</f>
-        <v>4622.32704583333</v>
+        <v>4623.44704583333</v>
       </c>
       <c r="L127" s="9" t="n">
         <f aca="false">L10/Corte!$I$8</f>
-        <v>5319.64489333333</v>
+        <v>5321.05489333333</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20346,39 +20346,39 @@
       </c>
       <c r="D128" s="9" t="n">
         <f aca="false">D11/Corte!$I$9</f>
-        <v>12.0991531133333</v>
+        <v>12.16581978</v>
       </c>
       <c r="E128" s="9" t="n">
         <f aca="false">E11/Corte!$I$9</f>
-        <v>23.5292519866667</v>
+        <v>23.4679186533333</v>
       </c>
       <c r="F128" s="9" t="n">
         <f aca="false">F11/Corte!$I$9</f>
-        <v>45.7533662733333</v>
+        <v>45.82003294</v>
       </c>
       <c r="G128" s="9" t="n">
         <f aca="false">G11/Corte!$I$9</f>
-        <v>80.0238767933333</v>
+        <v>80.0292101266667</v>
       </c>
       <c r="H128" s="9" t="n">
         <f aca="false">H11/Corte!$I$9</f>
-        <v>115.707002133333</v>
+        <v>115.712335466667</v>
       </c>
       <c r="I128" s="9" t="n">
         <f aca="false">I11/Corte!$I$9</f>
-        <v>155.658703</v>
+        <v>155.730703</v>
       </c>
       <c r="J128" s="9" t="n">
         <f aca="false">J11/Corte!$I$9</f>
-        <v>196.7603208</v>
+        <v>196.770987466667</v>
       </c>
       <c r="K128" s="9" t="n">
         <f aca="false">K11/Corte!$I$9</f>
-        <v>223.679336933333</v>
+        <v>223.6900036</v>
       </c>
       <c r="L128" s="9" t="n">
         <f aca="false">L11/Corte!$I$9</f>
-        <v>257.517871933333</v>
+        <v>257.5285386</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20454,27 +20454,27 @@
       </c>
       <c r="G130" s="9" t="n">
         <f aca="false">G51</f>
-        <v>71.061534325</v>
+        <v>71.311534325</v>
       </c>
       <c r="H130" s="9" t="n">
         <f aca="false">H51</f>
-        <v>99.2047701083333</v>
+        <v>99.0581034416667</v>
       </c>
       <c r="I130" s="9" t="n">
         <f aca="false">I51</f>
-        <v>131.915999383333</v>
+        <v>132.089332716667</v>
       </c>
       <c r="J130" s="9" t="n">
         <f aca="false">J51</f>
-        <v>166.270456708333</v>
+        <v>166.457123375</v>
       </c>
       <c r="K130" s="9" t="n">
         <f aca="false">K51</f>
-        <v>190.52776775</v>
+        <v>190.561101083333</v>
       </c>
       <c r="L130" s="9" t="n">
         <f aca="false">L51</f>
-        <v>220.26331775</v>
+        <v>219.96331775</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20550,27 +20550,27 @@
       </c>
       <c r="G132" s="9" t="n">
         <f aca="false">G49</f>
-        <v>13.4067201877778</v>
+        <v>13.2956090766667</v>
       </c>
       <c r="H132" s="9" t="n">
         <f aca="false">H49</f>
-        <v>18.2365057455556</v>
+        <v>18.3387279677778</v>
       </c>
       <c r="I132" s="9" t="n">
         <f aca="false">I49</f>
-        <v>24.8000835477778</v>
+        <v>25.02230577</v>
       </c>
       <c r="J132" s="9" t="n">
         <f aca="false">J49</f>
-        <v>31.0808179888889</v>
+        <v>30.8763735444444</v>
       </c>
       <c r="K132" s="9" t="n">
         <f aca="false">K49</f>
-        <v>35.4512399444444</v>
+        <v>35.3401288333333</v>
       </c>
       <c r="L132" s="9" t="n">
         <f aca="false">L49</f>
-        <v>41.0322062</v>
+        <v>40.9122062</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20598,27 +20598,27 @@
       </c>
       <c r="G133" s="9" t="n">
         <f aca="false">G50</f>
-        <v>41.8793339166667</v>
+        <v>42.0460005833333</v>
       </c>
       <c r="H133" s="9" t="n">
         <f aca="false">H50</f>
-        <v>58.24908045</v>
+        <v>58.2624137833333</v>
       </c>
       <c r="I133" s="9" t="n">
         <f aca="false">I50</f>
-        <v>77.5647055333333</v>
+        <v>77.5780388666667</v>
       </c>
       <c r="J133" s="9" t="n">
         <f aca="false">J50</f>
-        <v>97.77477845</v>
+        <v>97.7881117833333</v>
       </c>
       <c r="K133" s="9" t="n">
         <f aca="false">K50</f>
-        <v>112.084569266667</v>
+        <v>112.0979026</v>
       </c>
       <c r="L133" s="9" t="n">
         <f aca="false">L50</f>
-        <v>129.5384222</v>
+        <v>129.551755533333</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20646,27 +20646,27 @@
       </c>
       <c r="G134" s="9" t="n">
         <f aca="false">G47</f>
-        <v>40.4201605566667</v>
+        <v>40.75349389</v>
       </c>
       <c r="H134" s="9" t="n">
         <f aca="false">H47</f>
-        <v>56.1495172333333</v>
+        <v>55.8428505666667</v>
       </c>
       <c r="I134" s="9" t="n">
         <f aca="false">I47</f>
-        <v>74.4935839666667</v>
+        <v>74.8269173</v>
       </c>
       <c r="J134" s="9" t="n">
         <f aca="false">J47</f>
-        <v>94.1891206333334</v>
+        <v>93.8824539666667</v>
       </c>
       <c r="K134" s="9" t="n">
         <f aca="false">K47</f>
-        <v>107.607053166667</v>
+        <v>107.9403865</v>
       </c>
       <c r="L134" s="9" t="n">
         <f aca="false">L47</f>
-        <v>124.349952</v>
+        <v>124.709952</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20778,39 +20778,39 @@
       </c>
       <c r="D137" s="30" t="n">
         <f aca="false">D18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>0.366641930920256</v>
+        <v>0.367657380286619</v>
       </c>
       <c r="E137" s="30" t="n">
         <f aca="false">E18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>0.665032035567242</v>
+        <v>0.665113271516551</v>
       </c>
       <c r="F137" s="30" t="n">
         <f aca="false">F18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>1.30970535664248</v>
+        <v>1.31080204195816</v>
       </c>
       <c r="G137" s="30" t="n">
         <f aca="false">G18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>2.17423333346918</v>
+        <v>2.17541125473416</v>
       </c>
       <c r="H137" s="30" t="n">
         <f aca="false">H18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>3.09561256772541</v>
+        <v>3.0968717249397</v>
       </c>
       <c r="I137" s="30" t="n">
         <f aca="false">I18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>4.11364403752308</v>
+        <v>4.11549215536986</v>
       </c>
       <c r="J137" s="30" t="n">
         <f aca="false">J18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>5.2088422595848</v>
+        <v>5.20878133262282</v>
       </c>
       <c r="K137" s="30" t="n">
         <f aca="false">K18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>6.07491884949857</v>
+        <v>6.07634047861148</v>
       </c>
       <c r="L137" s="30" t="n">
         <f aca="false">L18*Corte!$I$46/1000/Corte!$K$46</f>
-        <v>7.17129557061597</v>
+        <v>7.17229071099501</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20826,39 +20826,39 @@
       </c>
       <c r="D138" s="30" t="n">
         <f aca="false">D19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>0.297073406143947</v>
+        <v>0.297896178927395</v>
       </c>
       <c r="E138" s="30" t="n">
         <f aca="false">E19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>0.538845438395242</v>
+        <v>0.538911260217918</v>
       </c>
       <c r="F138" s="30" t="n">
         <f aca="false">F19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>1.06119512944465</v>
+        <v>1.06208372405077</v>
       </c>
       <c r="G138" s="30" t="n">
         <f aca="false">G19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>1.761683123652</v>
+        <v>1.7626375400808</v>
       </c>
       <c r="H138" s="30" t="n">
         <f aca="false">H19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>2.50823512544782</v>
+        <v>2.5092553636993</v>
       </c>
       <c r="I138" s="30" t="n">
         <f aca="false">I19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>3.33310007075136</v>
+        <v>3.33459751721724</v>
       </c>
       <c r="J138" s="30" t="n">
         <f aca="false">J19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>4.22048975205171</v>
+        <v>4.22044038568471</v>
       </c>
       <c r="K138" s="30" t="n">
         <f aca="false">K19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>4.92223251753802</v>
+        <v>4.92338439943485</v>
       </c>
       <c r="L138" s="30" t="n">
         <f aca="false">L19*Corte!$I$47/1000/Corte!$K$47</f>
-        <v>5.81057708342489</v>
+        <v>5.81138340075266</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20870,43 +20870,43 @@
       </c>
       <c r="C139" s="30" t="n">
         <f aca="false">C20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>0.470104691351747</v>
+        <v>0.470310807736937</v>
       </c>
       <c r="D139" s="30" t="n">
         <f aca="false">D20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>0.808177993357854</v>
+        <v>0.809637297364999</v>
       </c>
       <c r="E139" s="30" t="n">
         <f aca="false">E20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>1.38099989587681</v>
+        <v>1.38339909060042</v>
       </c>
       <c r="F139" s="30" t="n">
         <f aca="false">F20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>2.51162612333693</v>
+        <v>2.51544339879065</v>
       </c>
       <c r="G139" s="30" t="n">
         <f aca="false">G20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>4.24041321132203</v>
+        <v>4.24451080505961</v>
       </c>
       <c r="H139" s="30" t="n">
         <f aca="false">H20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>5.91149297628477</v>
+        <v>5.91587088830621</v>
       </c>
       <c r="I139" s="30" t="n">
         <f aca="false">I20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>7.96536767268699</v>
+        <v>7.96940755383671</v>
       </c>
       <c r="J139" s="30" t="n">
         <f aca="false">J20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>10.0639429944385</v>
+        <v>10.0671831440136</v>
       </c>
       <c r="K139" s="30" t="n">
         <f aca="false">K20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>11.4328481022349</v>
+        <v>11.4356183064518</v>
       </c>
       <c r="L139" s="30" t="n">
         <f aca="false">L20*Corte!$I$48/1000/Corte!$K$48</f>
-        <v>13.1575917108965</v>
+        <v>13.1610792001339</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20918,43 +20918,43 @@
       </c>
       <c r="C140" s="30" t="n">
         <f aca="false">C21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>0.440884352537844</v>
+        <v>0.441077657328678</v>
       </c>
       <c r="D140" s="30" t="n">
         <f aca="false">D21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>0.757944002456906</v>
+        <v>0.759312600376012</v>
       </c>
       <c r="E140" s="30" t="n">
         <f aca="false">E21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>1.29516096339679</v>
+        <v>1.2974110311621</v>
       </c>
       <c r="F140" s="30" t="n">
         <f aca="false">F21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>2.35551075659442</v>
+        <v>2.35909076132067</v>
       </c>
       <c r="G140" s="30" t="n">
         <f aca="false">G21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>3.97684147288756</v>
+        <v>3.98068437212934</v>
       </c>
       <c r="H140" s="30" t="n">
         <f aca="false">H21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>5.54405178533141</v>
+        <v>5.54815757908873</v>
       </c>
       <c r="I140" s="30" t="n">
         <f aca="false">I21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>7.47026361085776</v>
+        <v>7.47405238475812</v>
       </c>
       <c r="J140" s="30" t="n">
         <f aca="false">J21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>9.43839760101616</v>
+        <v>9.44143635232807</v>
       </c>
       <c r="K140" s="30" t="n">
         <f aca="false">K21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>10.7222155531433</v>
+        <v>10.7248135695321</v>
       </c>
       <c r="L140" s="30" t="n">
         <f aca="false">L21*Corte!$I$49/1000/Corte!$K$49</f>
-        <v>12.3397541210144</v>
+        <v>12.3430248380753</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20970,39 +20970,39 @@
       </c>
       <c r="D141" s="30" t="n">
         <f aca="false">D22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>0.256466415842629</v>
+        <v>0.2578795528528</v>
       </c>
       <c r="E141" s="30" t="n">
         <f aca="false">E22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>0.498750852059921</v>
+        <v>0.497450766010564</v>
       </c>
       <c r="F141" s="30" t="n">
         <f aca="false">F22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>0.969836628311254</v>
+        <v>0.971249765321425</v>
       </c>
       <c r="G141" s="30" t="n">
         <f aca="false">G22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>1.69627052991018</v>
+        <v>1.69638358087099</v>
       </c>
       <c r="H141" s="30" t="n">
         <f aca="false">H22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>2.45264770575797</v>
+        <v>2.45276075671878</v>
       </c>
       <c r="I141" s="30" t="n">
         <f aca="false">I22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>3.2995061124674</v>
+        <v>3.30103230043838</v>
       </c>
       <c r="J141" s="30" t="n">
         <f aca="false">J22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>4.17073937183355</v>
+        <v>4.17096547375518</v>
       </c>
       <c r="K141" s="30" t="n">
         <f aca="false">K22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>4.74134324146455</v>
+        <v>4.74156934338617</v>
       </c>
       <c r="L141" s="30" t="n">
         <f aca="false">L22*Corte!$I$50/1000/Corte!$K$50</f>
-        <v>5.45862053414147</v>
+        <v>5.4588466360631</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21018,39 +21018,39 @@
       </c>
       <c r="D142" s="30" t="n">
         <f aca="false">D23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>0.234242024104756</v>
+        <v>0.235532704104756</v>
       </c>
       <c r="E142" s="30" t="n">
         <f aca="false">E23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>0.455531024312264</v>
+        <v>0.454343598712264</v>
       </c>
       <c r="F142" s="30" t="n">
         <f aca="false">F23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>0.885794321724988</v>
+        <v>0.887085001724988</v>
       </c>
       <c r="G142" s="30" t="n">
         <f aca="false">G23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>1.54927825949429</v>
+        <v>1.54938151389429</v>
       </c>
       <c r="H142" s="30" t="n">
         <f aca="false">H23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>2.24011070270176</v>
+        <v>2.24021395710176</v>
       </c>
       <c r="I142" s="30" t="n">
         <f aca="false">I23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>3.0135836218206</v>
+        <v>3.0149775562206</v>
       </c>
       <c r="J142" s="30" t="n">
         <f aca="false">J23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>3.80931916275216</v>
+        <v>3.80952567155216</v>
       </c>
       <c r="K142" s="30" t="n">
         <f aca="false">K23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>4.33047669889672</v>
+        <v>4.33068320769672</v>
       </c>
       <c r="L142" s="30" t="n">
         <f aca="false">L23*Corte!$I$51/1000/Corte!$K$51</f>
-        <v>4.98559750420372</v>
+        <v>4.98580401300372</v>
       </c>
     </row>
   </sheetData>

--- a/salida/Analisis_alternativas_corte_chapa.xlsx
+++ b/salida/Analisis_alternativas_corte_chapa.xlsx
@@ -2537,11 +2537,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="23936482"/>
-        <c:axId val="83372265"/>
+        <c:axId val="45722473"/>
+        <c:axId val="80739218"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="23936482"/>
+        <c:axId val="45722473"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2573,7 +2573,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83372265"/>
+        <c:crossAx val="80739218"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2581,7 +2581,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83372265"/>
+        <c:axId val="80739218"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2658,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23936482"/>
+        <c:crossAx val="45722473"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3069,42 +3069,15 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""Indexado Dim Técnico!B3:K10"")"),4178.736543)</f>
         <v>4178.736543</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5997.303977)</f>
-        <v>5997.303977</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6851.747758)</f>
-        <v>6851.747758</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8467.135549)</f>
-        <v>8467.135549</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12680.63271)</f>
-        <v>12680.63271</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15620.25307)</f>
-        <v>15620.25307</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20332.55326)</f>
-        <v>20332.55326</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25132.07848)</f>
-        <v>25132.07848</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28573.33614)</f>
-        <v>28573.33614</v>
-      </c>
-      <c r="L11" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32072.63913)</f>
-        <v>32072.63913</v>
-      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
@@ -3113,46 +3086,16 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0303572)</f>
-        <v>295.0303572</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),709.7274503)</f>
-        <v>709.7274503</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),986.8680576)</f>
-        <v>986.8680576</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.638174)</f>
-        <v>1500.638174</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2312.627726)</f>
-        <v>2312.627726</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3252.869887)</f>
-        <v>3252.869887</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4102.315524)</f>
-        <v>4102.315524</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5104.306587)</f>
-        <v>5104.306587</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6195.186243)</f>
-        <v>6195.186243</v>
-      </c>
-      <c r="L12" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7424.858444)</f>
-        <v>7424.858444</v>
-      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
@@ -3161,46 +3104,16 @@
       <c r="B13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2255.773025)</f>
-        <v>2255.773025</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3846.978881)</f>
-        <v>3846.978881</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5093.537591)</f>
-        <v>5093.537591</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6823.115313)</f>
-        <v>6823.115313</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10819.30694)</f>
-        <v>10819.30694</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14605.96411)</f>
-        <v>14605.96411</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18877.75984)</f>
-        <v>18877.75984</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23368.18637)</f>
-        <v>23368.18637</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26967.72455)</f>
-        <v>26967.72455</v>
-      </c>
-      <c r="L13" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30750.77872)</f>
-        <v>30750.77872</v>
-      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
@@ -3209,46 +3122,16 @@
       <c r="B14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.83318153)</f>
-        <v>91.83318153</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.2472967)</f>
-        <v>177.2472967</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),252.9787798)</f>
-        <v>252.9787798</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),358.0204941)</f>
-        <v>358.0204941</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),602.7181519)</f>
-        <v>602.7181519</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),872.605032)</f>
-        <v>872.605032</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1127.160545)</f>
-        <v>1127.160545</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1395.444812)</f>
-        <v>1395.444812</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1612.350054)</f>
-        <v>1612.350054</v>
-      </c>
-      <c r="L14" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1840.848079)</f>
-        <v>1840.848079</v>
-      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
@@ -3257,46 +3140,16 @@
       <c r="B15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.05179136)</f>
-        <v>34.05179136</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.46214745)</f>
-        <v>58.46214745</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),75.20853998)</f>
-        <v>75.20853998</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.5298529)</f>
-        <v>100.5298529</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),155.8760035)</f>
-        <v>155.8760035</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.9344827)</f>
-        <v>211.9344827</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),272.6682332)</f>
-        <v>272.6682332</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.8486707)</f>
-        <v>337.8486707</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),393.6274156)</f>
-        <v>393.6274156</v>
-      </c>
-      <c r="L15" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.2705332)</f>
-        <v>453.2705332</v>
-      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
@@ -3305,46 +3158,16 @@
       <c r="B16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.913941)</f>
-        <v>74.913941</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.6167244)</f>
-        <v>128.6167244</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),165.458788)</f>
-        <v>165.458788</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),221.1656765)</f>
-        <v>221.1656765</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),342.9272077)</f>
-        <v>342.9272077</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.255862)</f>
-        <v>466.255862</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),599.8701129)</f>
-        <v>599.8701129</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),743.2670756)</f>
-        <v>743.2670756</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),865.9803143)</f>
-        <v>865.9803143</v>
-      </c>
-      <c r="L16" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),997.1951731)</f>
-        <v>997.1951731</v>
-      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
@@ -3353,46 +3176,16 @@
       <c r="B17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.34485985)</f>
-        <v>16.34485985</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.06183078)</f>
-        <v>28.06183078</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.10009919)</f>
-        <v>36.10009919</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.25432941)</f>
-        <v>48.25432941</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.82048167)</f>
-        <v>74.82048167</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.7285517)</f>
-        <v>101.7285517</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),130.8807519)</f>
-        <v>130.8807519</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.1673619)</f>
-        <v>162.1673619</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),188.9411595)</f>
-        <v>188.9411595</v>
-      </c>
-      <c r="L17" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.569856)</f>
-        <v>217.569856</v>
-      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
@@ -3401,46 +3194,16 @@
       <c r="B18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.89657324)</f>
-        <v>10.89657324</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.70788719)</f>
-        <v>18.70788719</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.06673279)</f>
-        <v>24.06673279</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.16955294)</f>
-        <v>32.16955294</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.88032112)</f>
-        <v>49.88032112</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.81903447)</f>
-        <v>67.81903447</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),87.25383461)</f>
-        <v>87.25383461</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.1115746)</f>
-        <v>108.1115746</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),125.960773)</f>
-        <v>125.960773</v>
-      </c>
-      <c r="L18" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0465706)</f>
-        <v>145.0465706</v>
-      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
@@ -3496,42 +3259,15 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""Indexado Dim Técnico!B15:K22"")"),0)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7662.4)</f>
-        <v>7662.4</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26694.8)</f>
-        <v>26694.8</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49434.8)</f>
-        <v>49434.8</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71680.2)</f>
-        <v>71680.2</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101340.6)</f>
-        <v>101340.6</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),131001)</f>
-        <v>131001</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146819.8)</f>
-        <v>146819.8</v>
-      </c>
-      <c r="L22" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170548)</f>
-        <v>170548</v>
-      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
@@ -3540,46 +3276,16 @@
       <c r="B23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.6)</f>
-        <v>299.6</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1043.8)</f>
-        <v>1043.8</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1933)</f>
-        <v>1933</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2803)</f>
-        <v>2803</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3963)</f>
-        <v>3963</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5123)</f>
-        <v>5123</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5741.4)</f>
-        <v>5741.4</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6669)</f>
-        <v>6669</v>
-      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
@@ -3588,46 +3294,16 @@
       <c r="B24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1478.8)</f>
-        <v>1478.8</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5152)</f>
-        <v>5152</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9540.8)</f>
-        <v>9540.8</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13834.2)</f>
-        <v>13834.2</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19558.6)</f>
-        <v>19558.6</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25283)</f>
-        <v>25283</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28335.8)</f>
-        <v>28335.8</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32915)</f>
-        <v>32915</v>
-      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
@@ -3636,46 +3312,16 @@
       <c r="B25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.4)</f>
-        <v>90.4</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),315)</f>
-        <v>315</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),583.4)</f>
-        <v>583.4</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),845.8)</f>
-        <v>845.8</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1195.4)</f>
-        <v>1195.4</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1545)</f>
-        <v>1545</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1731.4)</f>
-        <v>1731.4</v>
-      </c>
-      <c r="L25" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2011)</f>
-        <v>2011</v>
-      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
@@ -3684,46 +3330,16 @@
       <c r="B26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.4)</f>
-        <v>14.4</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.2)</f>
-        <v>50.2</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93)</f>
-        <v>93</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),135)</f>
-        <v>135</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191)</f>
-        <v>191</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),247)</f>
-        <v>247</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277)</f>
-        <v>277</v>
-      </c>
-      <c r="L26" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),322)</f>
-        <v>322</v>
-      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
@@ -3732,46 +3348,16 @@
       <c r="B27" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.8)</f>
-        <v>31.8</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.8)</f>
-        <v>110.8</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.2)</f>
-        <v>205.2</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.6)</f>
-        <v>297.6</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.8)</f>
-        <v>420.8</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),544)</f>
-        <v>544</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),609.6)</f>
-        <v>609.6</v>
-      </c>
-      <c r="L27" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),708)</f>
-        <v>708</v>
-      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
@@ -3780,46 +3366,16 @@
       <c r="B28" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7)</f>
-        <v>7</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.4)</f>
-        <v>24.4</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.2)</f>
-        <v>45.2</v>
-      </c>
-      <c r="H28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.4)</f>
-        <v>65.4</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.2)</f>
-        <v>92.2</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119)</f>
-        <v>119</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.4)</f>
-        <v>133.4</v>
-      </c>
-      <c r="L28" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),155)</f>
-        <v>155</v>
-      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
@@ -3828,46 +3384,16 @@
       <c r="B29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16)</f>
-        <v>16</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.6)</f>
-        <v>29.6</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.8)</f>
-        <v>42.8</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.4)</f>
-        <v>60.4</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78)</f>
-        <v>78</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),87.6)</f>
-        <v>87.6</v>
-      </c>
-      <c r="L29" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102)</f>
-        <v>102</v>
-      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
@@ -3923,42 +3449,15 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$6,""sobrestock_sustitutos!B73:K76"")"),0)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
@@ -3967,46 +3466,16 @@
       <c r="B34" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
-        <v>2</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.16)</f>
-        <v>5.16</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.56)</f>
-        <v>7.56</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.12)</f>
-        <v>13.12</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.08)</f>
-        <v>13.08</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.96)</f>
-        <v>14.96</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.92)</f>
-        <v>13.92</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.72)</f>
-        <v>10.72</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.2)</f>
-        <v>10.2</v>
-      </c>
-      <c r="L34" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.6)</f>
-        <v>11.6</v>
-      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
@@ -4015,46 +3484,16 @@
       <c r="B35" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9)</f>
-        <v>9</v>
-      </c>
-      <c r="D35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.72)</f>
-        <v>27.72</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.88)</f>
-        <v>47.88</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.48)</f>
-        <v>78.48</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.24)</f>
-        <v>80.24</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.68)</f>
-        <v>89.68</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),77.44)</f>
-        <v>77.44</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.76)</f>
-        <v>65.76</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.8)</f>
-        <v>60.8</v>
-      </c>
-      <c r="L35" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.2)</f>
-        <v>64.2</v>
-      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
@@ -4063,46 +3502,16 @@
       <c r="B36" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.08)</f>
-        <v>2.08</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.24)</f>
-        <v>3.24</v>
-      </c>
-      <c r="F36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.48)</f>
-        <v>4.48</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.12)</f>
-        <v>6.12</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.52)</f>
-        <v>4.52</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.76)</f>
-        <v>3.76</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.92)</f>
-        <v>3.92</v>
-      </c>
-      <c r="L36" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.08)</f>
-        <v>4.08</v>
-      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
@@ -4115,42 +3524,15 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$6,""sobrestock_sustitutos!B86:K89"")"),1)</f>
         <v>1</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
-        <v>1.16</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
-        <v>1.24</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
-        <v>0.32</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
-        <v>0.32</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
-        <v>1.32</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
-        <v>0.4</v>
-      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
@@ -4159,46 +3541,16 @@
       <c r="B38" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.16)</f>
-        <v>2.16</v>
-      </c>
-      <c r="G38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.32)</f>
-        <v>2.32</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.48)</f>
-        <v>1.48</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.56)</f>
-        <v>1.56</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.64)</f>
-        <v>1.64</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.72)</f>
-        <v>1.72</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
-      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
@@ -4207,46 +3559,16 @@
       <c r="B39" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
-        <v>1.16</v>
-      </c>
-      <c r="L39" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
-        <v>0.24</v>
-      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
@@ -4255,46 +3577,16 @@
       <c r="B40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="H40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
-      </c>
-      <c r="K40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
-      </c>
-      <c r="L40" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
-      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
@@ -4350,42 +3642,15 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""sobrestock_sustitutos!B73:K76"")"),0)</f>
         <v>0</v>
       </c>
-      <c r="D44" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="L44" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
@@ -4394,46 +3659,16 @@
       <c r="B45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3)</f>
-        <v>3</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.24)</f>
-        <v>9.24</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.96)</f>
-        <v>15.96</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.16)</f>
-        <v>24.16</v>
-      </c>
-      <c r="G45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.92)</f>
-        <v>25.92</v>
-      </c>
-      <c r="H45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.68)</f>
-        <v>28.68</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.52)</f>
-        <v>26.52</v>
-      </c>
-      <c r="J45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.04)</f>
-        <v>21.04</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21)</f>
-        <v>21</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.88)</f>
-        <v>20.88</v>
-      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
@@ -4442,46 +3677,16 @@
       <c r="B46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17)</f>
-        <v>17</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.36)</f>
-        <v>53.36</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.52)</f>
-        <v>91.52</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.4)</f>
-        <v>150.4</v>
-      </c>
-      <c r="G46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),152.44)</f>
-        <v>152.44</v>
-      </c>
-      <c r="H46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),171.76)</f>
-        <v>171.76</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.8)</f>
-        <v>150.8</v>
-      </c>
-      <c r="J46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),125.28)</f>
-        <v>125.28</v>
-      </c>
-      <c r="K46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.04)</f>
-        <v>117.04</v>
-      </c>
-      <c r="L46" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),122.68)</f>
-        <v>122.68</v>
-      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
@@ -4490,46 +3695,16 @@
       <c r="B47" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
-        <v>2</v>
-      </c>
-      <c r="D47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.16)</f>
-        <v>3.16</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.4)</f>
-        <v>5.4</v>
-      </c>
-      <c r="F47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.8)</f>
-        <v>9.8</v>
-      </c>
-      <c r="G47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.52)</f>
-        <v>9.52</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.16)</f>
-        <v>11.16</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.88)</f>
-        <v>8.88</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.36)</f>
-        <v>7.36</v>
-      </c>
-      <c r="K47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.68)</f>
-        <v>7.68</v>
-      </c>
-      <c r="L47" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7)</f>
-        <v>7</v>
-      </c>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
@@ -4542,42 +3717,15 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""sobrestock_sustitutos!B86:K89"")"),1)</f>
         <v>1</v>
       </c>
-      <c r="D48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
-      </c>
-      <c r="F48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
-        <v>1.16</v>
-      </c>
-      <c r="G48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.24)</f>
-        <v>2.24</v>
-      </c>
-      <c r="H48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
-      </c>
-      <c r="I48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.48)</f>
-        <v>1.48</v>
-      </c>
-      <c r="J48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.56)</f>
-        <v>1.56</v>
-      </c>
-      <c r="K48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.64)</f>
-        <v>0.64</v>
-      </c>
-      <c r="L48" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.64)</f>
-        <v>1.64</v>
-      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
@@ -4586,46 +3734,16 @@
       <c r="B49" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="D49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
-      </c>
-      <c r="E49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.16)</f>
-        <v>2.16</v>
-      </c>
-      <c r="F49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.32)</f>
-        <v>3.32</v>
-      </c>
-      <c r="G49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.56)</f>
-        <v>3.56</v>
-      </c>
-      <c r="H49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
-      </c>
-      <c r="I49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.04)</f>
-        <v>3.04</v>
-      </c>
-      <c r="J49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
-      </c>
-      <c r="K49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.36)</f>
-        <v>2.36</v>
-      </c>
-      <c r="L49" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.44)</f>
-        <v>2.44</v>
-      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
@@ -4634,46 +3752,16 @@
       <c r="B50" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="D50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="F50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
-      </c>
-      <c r="G50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
-        <v>1.16</v>
-      </c>
-      <c r="H50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
-        <v>0.24</v>
-      </c>
-      <c r="I50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
-        <v>1.24</v>
-      </c>
-      <c r="J50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
-        <v>0.32</v>
-      </c>
-      <c r="K50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.32)</f>
-        <v>0.32</v>
-      </c>
-      <c r="L50" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
-        <v>1.32</v>
-      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
@@ -4682,46 +3770,16 @@
       <c r="B51" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="D51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="E51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="F51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
-      </c>
-      <c r="G51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
-      </c>
-      <c r="H51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.16)</f>
-        <v>0.16</v>
-      </c>
-      <c r="I51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
-        <v>1.16</v>
-      </c>
-      <c r="J51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
-        <v>0.24</v>
-      </c>
-      <c r="K51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
-        <v>0.24</v>
-      </c>
-      <c r="L51" s="9" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.24)</f>
-        <v>0.24</v>
-      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
